--- a/Översikt KUNGÄLV.xlsx
+++ b/Översikt KUNGÄLV.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE103"/>
+  <dimension ref="A1:AE102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45548</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>45868</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -851,7 +851,7 @@
         <v>45526</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -965,7 +965,7 @@
         <v>45919</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
         <v>45695</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         <v>45993</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1286,7 +1286,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 48345-2021</t>
+          <t>A 4263-2024</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>44451</v>
+        <v>45324</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1316,16 +1316,16 @@
         </is>
       </c>
       <c r="I8" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J8" t="n">
         <v>3</v>
-      </c>
-      <c r="J8" t="n">
-        <v>2</v>
       </c>
       <c r="K8" t="n">
         <v>1</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -1340,57 +1340,58 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T8" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="U8" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>Blåmossa
-Spillkråka
-Revlummer</t>
+          <t>Mindre hackspett
+Klippfrullania
+Gråsiska
+Spillkråka</t>
         </is>
       </c>
       <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 48345-2021 artfynd.xlsx", "A 48345-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 4263-2024 artfynd.xlsx", "A 4263-2024")</f>
         <v/>
       </c>
       <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 48345-2021 karta.png", "A 48345-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 4263-2024 karta.png", "A 4263-2024")</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 48345-2021 georefererad karta.tif", "A 48345-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 4263-2024 georefererad karta.tif", "A 4263-2024")</f>
         <v/>
       </c>
       <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 48345-2021 FSC-klagomål.docx", "A 48345-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 4263-2024 FSC-klagomål.docx", "A 4263-2024")</f>
         <v/>
       </c>
       <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 48345-2021 FSC-klagomål mail.docx", "A 48345-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 4263-2024 FSC-klagomål mail.docx", "A 4263-2024")</f>
         <v/>
       </c>
       <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 48345-2021 tillsynsbegäran.docx", "A 48345-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 4263-2024 tillsynsbegäran.docx", "A 4263-2024")</f>
         <v/>
       </c>
       <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 48345-2021 tillsynsbegäran mail.docx", "A 48345-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 4263-2024 tillsynsbegäran mail.docx", "A 4263-2024")</f>
         <v/>
       </c>
       <c r="AE8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 48345-2021 prioriterade fågelarter.docx", "A 48345-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 4263-2024 prioriterade fågelarter.docx", "A 4263-2024")</f>
         <v/>
       </c>
     </row>
@@ -1414,7 +1415,7 @@
         <v>45985</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1525,7 +1526,7 @@
         <v>46199</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1636,7 +1637,7 @@
         <v>45355</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1747,7 +1748,7 @@
         <v>46212</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1858,7 +1859,7 @@
         <v>45957</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1952,7 +1953,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 56394-2025</t>
+          <t>A 57116-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1962,14 +1963,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45974</v>
+        <v>45979</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1982,7 +1983,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.3</v>
+        <v>3.5</v>
       </c>
       <c r="J14" t="n">
         <v>1</v>
@@ -2015,343 +2016,343 @@
         <v>2</v>
       </c>
       <c r="T14" t="n">
+        <v>3</v>
+      </c>
+      <c r="U14" t="n">
+        <v>3</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Västlig hakmossa
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 57116-2025 artfynd.xlsx", "A 57116-2025")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 57116-2025 karta.png", "A 57116-2025")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 57116-2025 georefererad karta.tif", "A 57116-2025")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 57116-2025 FSC-klagomål.docx", "A 57116-2025")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 57116-2025 FSC-klagomål mail.docx", "A 57116-2025")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 57116-2025 tillsynsbegäran.docx", "A 57116-2025")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 57116-2025 tillsynsbegäran mail.docx", "A 57116-2025")</f>
+        <v/>
+      </c>
+      <c r="AE14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 57116-2025 prioriterade fågelarter.docx", "A 57116-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 56394-2025</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>45974</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>KUNGÄLV</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
         <v>2</v>
       </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
         <is>
           <t>Kambräken
 Revlummer</t>
         </is>
       </c>
-      <c r="W14">
+      <c r="W15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 56394-2025 artfynd.xlsx", "A 56394-2025")</f>
         <v/>
       </c>
-      <c r="X14">
+      <c r="X15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 56394-2025 karta.png", "A 56394-2025")</f>
         <v/>
       </c>
-      <c r="Y14">
+      <c r="Y15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 56394-2025 georefererad karta.tif", "A 56394-2025")</f>
         <v/>
       </c>
-      <c r="AA14">
+      <c r="AA15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 56394-2025 FSC-klagomål.docx", "A 56394-2025")</f>
         <v/>
       </c>
-      <c r="AB14">
+      <c r="AB15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 56394-2025 FSC-klagomål mail.docx", "A 56394-2025")</f>
         <v/>
       </c>
-      <c r="AC14">
+      <c r="AC15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 56394-2025 tillsynsbegäran.docx", "A 56394-2025")</f>
         <v/>
       </c>
-      <c r="AD14">
+      <c r="AD15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 56394-2025 tillsynsbegäran mail.docx", "A 56394-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 57116-2025</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>45979</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>KUNGÄLV</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="J15" t="n">
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 30860-2026</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>46212</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>KUNGÄLV</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J16" t="n">
         <v>1</v>
       </c>
-      <c r="K15" t="n">
+      <c r="K16" t="n">
         <v>1</v>
       </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
+      <c r="L16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
         <v>2</v>
       </c>
-      <c r="T15" t="n">
-        <v>3</v>
-      </c>
-      <c r="U15" t="n">
-        <v>3</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Grönsångare
+Västlig hakmossa</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 30860-2026 artfynd.xlsx", "A 30860-2026")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 30860-2026 karta.png", "A 30860-2026")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 30860-2026 georefererad karta.tif", "A 30860-2026")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 30860-2026 FSC-klagomål.docx", "A 30860-2026")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 30860-2026 FSC-klagomål mail.docx", "A 30860-2026")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 30860-2026 tillsynsbegäran.docx", "A 30860-2026")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 30860-2026 tillsynsbegäran mail.docx", "A 30860-2026")</f>
+        <v/>
+      </c>
+      <c r="AE16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 30860-2026 prioriterade fågelarter.docx", "A 30860-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 53007-2025</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>45957</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>KUNGÄLV</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2</v>
+      </c>
+      <c r="T17" t="n">
+        <v>5</v>
+      </c>
+      <c r="U17" t="n">
+        <v>5</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>Västlig hakmossa
 Spillkråka</t>
         </is>
       </c>
-      <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 57116-2025 artfynd.xlsx", "A 57116-2025")</f>
-        <v/>
-      </c>
-      <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 57116-2025 karta.png", "A 57116-2025")</f>
-        <v/>
-      </c>
-      <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 57116-2025 georefererad karta.tif", "A 57116-2025")</f>
-        <v/>
-      </c>
-      <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 57116-2025 FSC-klagomål.docx", "A 57116-2025")</f>
-        <v/>
-      </c>
-      <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 57116-2025 FSC-klagomål mail.docx", "A 57116-2025")</f>
-        <v/>
-      </c>
-      <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 57116-2025 tillsynsbegäran.docx", "A 57116-2025")</f>
-        <v/>
-      </c>
-      <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 57116-2025 tillsynsbegäran mail.docx", "A 57116-2025")</f>
-        <v/>
-      </c>
-      <c r="AE15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 57116-2025 prioriterade fågelarter.docx", "A 57116-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 30860-2026</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>46212</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>KUNGÄLV</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="J16" t="n">
-        <v>1</v>
-      </c>
-      <c r="K16" t="n">
-        <v>1</v>
-      </c>
-      <c r="L16" t="n">
-        <v>1</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>Grönsångare
-Västlig hakmossa</t>
-        </is>
-      </c>
-      <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 30860-2026 artfynd.xlsx", "A 30860-2026")</f>
-        <v/>
-      </c>
-      <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 30860-2026 karta.png", "A 30860-2026")</f>
-        <v/>
-      </c>
-      <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 30860-2026 georefererad karta.tif", "A 30860-2026")</f>
-        <v/>
-      </c>
-      <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 30860-2026 FSC-klagomål.docx", "A 30860-2026")</f>
-        <v/>
-      </c>
-      <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 30860-2026 FSC-klagomål mail.docx", "A 30860-2026")</f>
-        <v/>
-      </c>
-      <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 30860-2026 tillsynsbegäran.docx", "A 30860-2026")</f>
-        <v/>
-      </c>
-      <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 30860-2026 tillsynsbegäran mail.docx", "A 30860-2026")</f>
-        <v/>
-      </c>
-      <c r="AE16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 30860-2026 prioriterade fågelarter.docx", "A 30860-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 53007-2025</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>45957</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>KUNGÄLV</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="J17" t="n">
-        <v>1</v>
-      </c>
-      <c r="K17" t="n">
-        <v>1</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2</v>
-      </c>
-      <c r="T17" t="n">
-        <v>5</v>
-      </c>
-      <c r="U17" t="n">
-        <v>5</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Västlig hakmossa
-Spillkråka</t>
-        </is>
-      </c>
       <c r="W17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 53007-2025 artfynd.xlsx", "A 53007-2025")</f>
         <v/>
@@ -2405,7 +2406,7 @@
         <v>45334</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2511,7 +2512,7 @@
         <v>45334</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2600,7 +2601,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 49988-2023</t>
+          <t>A 43847-2022</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2614,10 +2615,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45215</v>
+        <v>44838</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2630,7 +2631,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>2.3</v>
+        <v>0.6</v>
       </c>
       <c r="J20" t="n">
         <v>1</v>
@@ -2666,46 +2667,46 @@
         <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Gråsiska</t>
         </is>
       </c>
       <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 49988-2023 artfynd.xlsx", "A 49988-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 43847-2022 artfynd.xlsx", "A 43847-2022")</f>
         <v/>
       </c>
       <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 49988-2023 karta.png", "A 49988-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 43847-2022 karta.png", "A 43847-2022")</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 49988-2023 georefererad karta.tif", "A 49988-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 43847-2022 georefererad karta.tif", "A 43847-2022")</f>
         <v/>
       </c>
       <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 49988-2023 FSC-klagomål.docx", "A 49988-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 43847-2022 FSC-klagomål.docx", "A 43847-2022")</f>
         <v/>
       </c>
       <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 49988-2023 FSC-klagomål mail.docx", "A 49988-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 43847-2022 FSC-klagomål mail.docx", "A 43847-2022")</f>
         <v/>
       </c>
       <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 49988-2023 tillsynsbegäran.docx", "A 49988-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 43847-2022 tillsynsbegäran.docx", "A 43847-2022")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 49988-2023 tillsynsbegäran mail.docx", "A 49988-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 43847-2022 tillsynsbegäran mail.docx", "A 43847-2022")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 30862-2026</t>
+          <t>A 6082-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2719,10 +2720,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46212</v>
+        <v>45697</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2735,7 +2736,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.7</v>
+        <v>2.8</v>
       </c>
       <c r="J21" t="n">
         <v>1</v>
@@ -2768,49 +2769,53 @@
         <v>1</v>
       </c>
       <c r="T21" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 30862-2026 artfynd.xlsx", "A 30862-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 6082-2025 artfynd.xlsx", "A 6082-2025")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 30862-2026 karta.png", "A 30862-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 6082-2025 karta.png", "A 6082-2025")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 30862-2026 georefererad karta.tif", "A 30862-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 6082-2025 georefererad karta.tif", "A 6082-2025")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 30862-2026 FSC-klagomål.docx", "A 30862-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 6082-2025 FSC-klagomål.docx", "A 6082-2025")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 30862-2026 FSC-klagomål mail.docx", "A 30862-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 6082-2025 FSC-klagomål mail.docx", "A 6082-2025")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 30862-2026 tillsynsbegäran.docx", "A 30862-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 6082-2025 tillsynsbegäran.docx", "A 6082-2025")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 30862-2026 tillsynsbegäran mail.docx", "A 30862-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 6082-2025 tillsynsbegäran mail.docx", "A 6082-2025")</f>
+        <v/>
+      </c>
+      <c r="AE21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 6082-2025 prioriterade fågelarter.docx", "A 6082-2025")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 23704-2024</t>
+          <t>A 30862-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2824,10 +2829,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45454</v>
+        <v>46212</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2840,7 +2845,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>4.9</v>
+        <v>1.7</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
@@ -2852,7 +2857,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
@@ -2864,58 +2869,58 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
       </c>
       <c r="T22" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="U22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Hedjohannesört</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 23704-2024 artfynd.xlsx", "A 23704-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 30862-2026 artfynd.xlsx", "A 30862-2026")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 23704-2024 karta.png", "A 23704-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 30862-2026 karta.png", "A 30862-2026")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 23704-2024 georefererad karta.tif", "A 23704-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 30862-2026 georefererad karta.tif", "A 30862-2026")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 23704-2024 FSC-klagomål.docx", "A 23704-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 30862-2026 FSC-klagomål.docx", "A 30862-2026")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 23704-2024 FSC-klagomål mail.docx", "A 23704-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 30862-2026 FSC-klagomål mail.docx", "A 30862-2026")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 23704-2024 tillsynsbegäran.docx", "A 23704-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 30862-2026 tillsynsbegäran.docx", "A 30862-2026")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 23704-2024 tillsynsbegäran mail.docx", "A 23704-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 30862-2026 tillsynsbegäran mail.docx", "A 30862-2026")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 6082-2025</t>
+          <t>A 23704-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2929,10 +2934,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45697</v>
+        <v>45454</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2945,7 +2950,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>2.8</v>
+        <v>4.9</v>
       </c>
       <c r="J23" t="n">
         <v>1</v>
@@ -2957,7 +2962,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
@@ -2969,62 +2974,58 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
       </c>
       <c r="T23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U23" t="n">
         <v>1</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Hedjohannesört</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 6082-2025 artfynd.xlsx", "A 6082-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 23704-2024 artfynd.xlsx", "A 23704-2024")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 6082-2025 karta.png", "A 6082-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 23704-2024 karta.png", "A 23704-2024")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 6082-2025 georefererad karta.tif", "A 6082-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 23704-2024 georefererad karta.tif", "A 23704-2024")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 6082-2025 FSC-klagomål.docx", "A 6082-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 23704-2024 FSC-klagomål.docx", "A 23704-2024")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 6082-2025 FSC-klagomål mail.docx", "A 6082-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 23704-2024 FSC-klagomål mail.docx", "A 23704-2024")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 6082-2025 tillsynsbegäran.docx", "A 6082-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 23704-2024 tillsynsbegäran.docx", "A 23704-2024")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 6082-2025 tillsynsbegäran mail.docx", "A 6082-2025")</f>
-        <v/>
-      </c>
-      <c r="AE23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 6082-2025 prioriterade fågelarter.docx", "A 6082-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 23704-2024 tillsynsbegäran mail.docx", "A 23704-2024")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 19132-2022</t>
+          <t>A 49988-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3038,10 +3039,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44691</v>
+        <v>45215</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3054,10 +3055,10 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.3</v>
+        <v>2.3</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -3084,20 +3085,52 @@
         <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U24" t="n">
         <v>0</v>
       </c>
-      <c r="V24" s="2" t="inlineStr"/>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="W24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 49988-2023 artfynd.xlsx", "A 49988-2023")</f>
+        <v/>
+      </c>
+      <c r="X24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 49988-2023 karta.png", "A 49988-2023")</f>
+        <v/>
+      </c>
+      <c r="Y24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 49988-2023 georefererad karta.tif", "A 49988-2023")</f>
+        <v/>
+      </c>
+      <c r="AA24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 49988-2023 FSC-klagomål.docx", "A 49988-2023")</f>
+        <v/>
+      </c>
+      <c r="AB24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 49988-2023 FSC-klagomål mail.docx", "A 49988-2023")</f>
+        <v/>
+      </c>
+      <c r="AC24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 49988-2023 tillsynsbegäran.docx", "A 49988-2023")</f>
+        <v/>
+      </c>
+      <c r="AD24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 49988-2023 tillsynsbegäran mail.docx", "A 49988-2023")</f>
+        <v/>
+      </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 19133-2022</t>
+          <t>A 19132-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3114,7 +3147,7 @@
         <v>44691</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3170,7 +3203,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 43847-2022</t>
+          <t>A 19133-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3184,10 +3217,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44838</v>
+        <v>44691</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3200,7 +3233,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3260,7 +3293,7 @@
         <v>44836</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3333,7 +3366,7 @@
         <v>44459</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3406,7 +3439,7 @@
         <v>44459</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3479,7 +3512,7 @@
         <v>44760</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3552,7 +3585,7 @@
         <v>44760</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3625,7 +3658,7 @@
         <v>44760</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3681,7 +3714,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 62221-2023</t>
+          <t>A 17455-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3695,10 +3728,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45267</v>
+        <v>45757</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3711,7 +3744,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.3</v>
+        <v>2.1</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3754,7 +3787,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 4204-2024</t>
+          <t>A 62221-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3768,10 +3801,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45324</v>
+        <v>45267</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3784,7 +3817,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>4.4</v>
+        <v>1.3</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3827,7 +3860,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 30170-2022</t>
+          <t>A 21240-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3841,10 +3874,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44757</v>
+        <v>45058</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3857,7 +3890,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>3.1</v>
+        <v>2.3</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3900,7 +3933,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 13880-2024</t>
+          <t>A 29223-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3914,10 +3947,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45391</v>
+        <v>45482</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3930,7 +3963,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2.4</v>
+        <v>5.6</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3973,7 +4006,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 1995-2024</t>
+          <t>A 10655-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3987,10 +4020,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45308</v>
+        <v>44624</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4003,7 +4036,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.5</v>
+        <v>13.3</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4046,7 +4079,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 45990-2022</t>
+          <t>A 39714-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4060,10 +4093,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44846</v>
+        <v>45552</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4076,7 +4109,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>3.3</v>
+        <v>1.2</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4119,7 +4152,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 43520-2022</t>
+          <t>A 74285-2021</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4133,10 +4166,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44837</v>
+        <v>44558</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4149,7 +4182,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4192,7 +4225,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 29223-2024</t>
+          <t>A 61417-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4206,10 +4239,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45482</v>
+        <v>44916</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4222,7 +4255,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>5.6</v>
+        <v>3.6</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4265,7 +4298,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 17922-2025</t>
+          <t>A 32272-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4279,10 +4312,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45758</v>
+        <v>45120</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4295,7 +4328,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.8</v>
+        <v>4.9</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4338,7 +4371,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 8334-2023</t>
+          <t>A 32847-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4352,10 +4385,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44975</v>
+        <v>45124</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4368,7 +4401,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.8</v>
+        <v>4.7</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4428,7 +4461,7 @@
         <v>45897</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4484,7 +4517,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 34244-2025</t>
+          <t>A 34366-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4498,10 +4531,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45844</v>
+        <v>44792</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4514,7 +4547,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2.9</v>
+        <v>0.5</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4557,7 +4590,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 25624-2025</t>
+          <t>A 4673-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4571,10 +4604,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45803</v>
+        <v>46048</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4587,7 +4620,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4630,7 +4663,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 41442-2025</t>
+          <t>A 19531-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4644,10 +4677,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45869</v>
+        <v>45050</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4660,7 +4693,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4703,7 +4736,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 45124-2025</t>
+          <t>A 5705-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4713,14 +4746,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45919</v>
+        <v>45694</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4733,7 +4766,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>3.7</v>
+        <v>1.2</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4776,7 +4809,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 4262-2024</t>
+          <t>A 45124-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4790,10 +4823,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45324</v>
+        <v>45919</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4806,7 +4839,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>14</v>
+        <v>3.7</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4849,7 +4882,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 47564-2025</t>
+          <t>A 6946-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4859,14 +4892,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45931</v>
+        <v>46057</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4879,7 +4912,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4922,7 +4955,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 37443-2025</t>
+          <t>A 7505-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4936,10 +4969,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45877</v>
+        <v>45347</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4951,13 +4984,8 @@
           <t>KUNGÄLV</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I50" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5000,7 +5028,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 661-2025</t>
+          <t>A 47564-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5014,10 +5042,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45664</v>
+        <v>45931</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5030,7 +5058,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>3.1</v>
+        <v>2</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5073,7 +5101,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 13990-2026</t>
+          <t>A 34244-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5087,10 +5115,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46098</v>
+        <v>45844</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5103,7 +5131,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5146,7 +5174,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 52932-2025</t>
+          <t>A 25624-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5160,10 +5188,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45957</v>
+        <v>45803</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5176,7 +5204,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>3.4</v>
+        <v>5</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5219,7 +5247,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 24461-2023</t>
+          <t>A 41442-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5233,10 +5261,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45082</v>
+        <v>45869</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5249,7 +5277,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5292,7 +5320,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 143-2023</t>
+          <t>A 8334-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5306,10 +5334,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44928</v>
+        <v>44975</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5322,7 +5350,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5365,7 +5393,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 49985-2023</t>
+          <t>A 17922-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5379,10 +5407,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45215</v>
+        <v>45758</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5395,7 +5423,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>8.199999999999999</v>
+        <v>0.8</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5438,7 +5466,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 63319-2021</t>
+          <t>A 37443-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5452,10 +5480,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44508</v>
+        <v>45877</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5467,8 +5495,13 @@
           <t>KUNGÄLV</t>
         </is>
       </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I57" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5511,7 +5544,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 50071-2023</t>
+          <t>A 13990-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5525,10 +5558,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45215</v>
+        <v>46098</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5541,7 +5574,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>4</v>
+        <v>2.6</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5584,7 +5617,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 34366-2022</t>
+          <t>A 52932-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5598,10 +5631,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44792</v>
+        <v>45957</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5614,7 +5647,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.5</v>
+        <v>3.4</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5657,7 +5690,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 4673-2026</t>
+          <t>A 49985-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5671,10 +5704,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46048</v>
+        <v>45215</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5730,7 +5763,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 7505-2024</t>
+          <t>A 50071-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5744,10 +5777,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45347</v>
+        <v>45215</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5760,7 +5793,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.8</v>
+        <v>4</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5803,7 +5836,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 6946-2026</t>
+          <t>A 49981-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5813,14 +5846,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46057</v>
+        <v>45215</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5833,7 +5866,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5876,7 +5909,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 10655-2022</t>
+          <t>A 56782-2022</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5890,10 +5923,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44624</v>
+        <v>44894</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5906,7 +5939,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>13.3</v>
+        <v>0.5</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5949,7 +5982,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 17455-2025</t>
+          <t>A 1995-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5963,10 +5996,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45757</v>
+        <v>45308</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5979,7 +6012,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2.1</v>
+        <v>0.5</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6022,7 +6055,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 22731-2026</t>
+          <t>A 30170-2022</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6036,10 +6069,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46157</v>
+        <v>44757</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6052,7 +6085,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.8</v>
+        <v>3.1</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6095,7 +6128,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 32391-2025</t>
+          <t>A 10810-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6109,10 +6142,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45837</v>
+        <v>44989</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6125,7 +6158,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>2.1</v>
+        <v>0.4</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6168,7 +6201,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 19531-2023</t>
+          <t>A 4204-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6182,10 +6215,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45050</v>
+        <v>45324</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6198,7 +6231,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.9</v>
+        <v>4.4</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6241,7 +6274,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 4263-2024</t>
+          <t>A 22731-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6255,10 +6288,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45324</v>
+        <v>46157</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6271,7 +6304,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2.6</v>
+        <v>1.8</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6314,7 +6347,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 23607-2026</t>
+          <t>A 32391-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6328,10 +6361,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46163</v>
+        <v>45837</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6344,7 +6377,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>5.3</v>
+        <v>2.1</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6387,7 +6420,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 25135-2025</t>
+          <t>A 23607-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6401,10 +6434,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45798</v>
+        <v>46163</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6417,7 +6450,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.1</v>
+        <v>5.3</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6460,7 +6493,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 5705-2025</t>
+          <t>A 25135-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6470,14 +6503,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45694</v>
+        <v>45798</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6490,7 +6523,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6533,7 +6566,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 62979-2023</t>
+          <t>A 62128-2021</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6543,14 +6576,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45271</v>
+        <v>44502</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6563,7 +6596,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.8</v>
+        <v>1.8</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6606,7 +6639,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 16538-2025</t>
+          <t>A 62979-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6616,14 +6649,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45751</v>
+        <v>45271</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6679,7 +6712,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 29801-2022</t>
+          <t>A 29952-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6693,10 +6726,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44755</v>
+        <v>46205</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6709,7 +6742,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>4.8</v>
+        <v>2</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6752,7 +6785,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 49981-2023</t>
+          <t>A 34392-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6766,10 +6799,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45215</v>
+        <v>46254</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6782,7 +6815,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>2.5</v>
+        <v>0.4</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6825,7 +6858,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 71835-2021</t>
+          <t>A 34387-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6839,10 +6872,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44543</v>
+        <v>46254</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6855,7 +6888,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>7.5</v>
+        <v>0.3</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6898,7 +6931,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 56782-2022</t>
+          <t>A 34386-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6912,10 +6945,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44894</v>
+        <v>46254</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6928,7 +6961,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6971,7 +7004,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 29952-2026</t>
+          <t>A 34396-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6985,10 +7018,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46205</v>
+        <v>46254</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7001,7 +7034,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7044,7 +7077,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 26812-2024</t>
+          <t>A 30738-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7058,10 +7091,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45470</v>
+        <v>46211</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7074,7 +7107,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.7</v>
+        <v>3.5</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7117,7 +7150,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 34386-2026</t>
+          <t>A 30859-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7131,10 +7164,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46254</v>
+        <v>46212</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7147,7 +7180,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7190,7 +7223,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 30738-2026</t>
+          <t>A 44176-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7204,10 +7237,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46211</v>
+        <v>45188</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7220,7 +7253,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>3.5</v>
+        <v>7.1</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7263,7 +7296,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 30859-2026</t>
+          <t>A 26812-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7277,10 +7310,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46212</v>
+        <v>45470</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7293,7 +7326,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7336,7 +7369,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 34387-2026</t>
+          <t>A 29801-2022</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7350,10 +7383,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46254</v>
+        <v>44755</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7366,7 +7399,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>0.3</v>
+        <v>4.8</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7409,7 +7442,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 34396-2026</t>
+          <t>A 18852-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7423,10 +7456,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46254</v>
+        <v>45426</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7439,7 +7472,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>0.8</v>
+        <v>2.7</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7482,7 +7515,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 34392-2026</t>
+          <t>A 43520-2022</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7496,10 +7529,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46254</v>
+        <v>44837</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7512,7 +7545,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>0.4</v>
+        <v>1.5</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7555,7 +7588,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 10810-2023</t>
+          <t>A 16538-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7569,10 +7602,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44989</v>
+        <v>45751</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7585,7 +7618,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7628,7 +7661,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 62128-2021</t>
+          <t>A 45990-2022</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7642,10 +7675,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>44502</v>
+        <v>44846</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7658,7 +7691,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.8</v>
+        <v>3.3</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7701,7 +7734,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 21240-2023</t>
+          <t>A 143-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7715,10 +7748,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45058</v>
+        <v>44928</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7731,7 +7764,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>2.3</v>
+        <v>0.5</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7791,7 +7824,7 @@
         <v>45426</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7847,7 +7880,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 21389-2023</t>
+          <t>A 71835-2021</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7861,10 +7894,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45063</v>
+        <v>44543</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7877,7 +7910,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>3.4</v>
+        <v>7.5</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7920,7 +7953,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 44176-2023</t>
+          <t>A 51724-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7934,10 +7967,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45188</v>
+        <v>45222</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7950,7 +7983,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>7.1</v>
+        <v>3.1</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7993,7 +8026,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 23457-2024</t>
+          <t>A 661-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8007,10 +8040,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45453</v>
+        <v>45664</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8023,7 +8056,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>5.1</v>
+        <v>3.1</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8066,7 +8099,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 39714-2024</t>
+          <t>A 24461-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8080,10 +8113,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45552</v>
+        <v>45082</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8096,7 +8129,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8139,7 +8172,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 18852-2024</t>
+          <t>A 13880-2024</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8153,10 +8186,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45426</v>
+        <v>45391</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8169,7 +8202,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8212,7 +8245,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 51724-2023</t>
+          <t>A 23457-2024</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8226,10 +8259,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45222</v>
+        <v>45453</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8242,7 +8275,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>3.1</v>
+        <v>5.1</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8285,7 +8318,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 10679-2025</t>
+          <t>A 21389-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8299,10 +8332,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45721</v>
+        <v>45063</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8315,7 +8348,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>4.4</v>
+        <v>3.4</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8358,7 +8391,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 11237-2025</t>
+          <t>A 4262-2024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8372,10 +8405,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45726</v>
+        <v>45324</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8388,7 +8421,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>4.2</v>
+        <v>14</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8431,7 +8464,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 10677-2025</t>
+          <t>A 63319-2021</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8445,10 +8478,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45721</v>
+        <v>44508</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8461,7 +8494,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>7.4</v>
+        <v>1.6</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8504,7 +8537,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 74285-2021</t>
+          <t>A 10677-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8518,10 +8551,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>44558</v>
+        <v>45721</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8534,7 +8567,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1.1</v>
+        <v>7.4</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8577,7 +8610,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 61417-2022</t>
+          <t>A 10679-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8591,10 +8624,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>44916</v>
+        <v>45721</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8607,7 +8640,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>3.6</v>
+        <v>4.4</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8650,7 +8683,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 32272-2023</t>
+          <t>A 11237-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8664,10 +8697,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45120</v>
+        <v>45726</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8680,7 +8713,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>4.9</v>
+        <v>4.2</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8720,27 +8753,27 @@
       </c>
       <c r="V101" s="2" t="inlineStr"/>
     </row>
-    <row r="102" ht="15" customHeight="1">
+    <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 32847-2023</t>
+          <t>S 817-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45124</v>
+        <v>45371</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8752,8 +8785,13 @@
           <t>KUNGÄLV</t>
         </is>
       </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I102" t="n">
-        <v>4.7</v>
+        <v>2.4</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8792,84 +8830,6 @@
         <v>0</v>
       </c>
       <c r="V102" s="2" t="inlineStr"/>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>S 817-2024</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D103" s="1" t="n">
-        <v>45371</v>
-      </c>
-      <c r="E103" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>KUNGÄLV</t>
-        </is>
-      </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
-      <c r="I103" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="J103" t="n">
-        <v>0</v>
-      </c>
-      <c r="K103" t="n">
-        <v>0</v>
-      </c>
-      <c r="L103" t="n">
-        <v>0</v>
-      </c>
-      <c r="M103" t="n">
-        <v>0</v>
-      </c>
-      <c r="N103" t="n">
-        <v>0</v>
-      </c>
-      <c r="O103" t="n">
-        <v>0</v>
-      </c>
-      <c r="P103" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q103" t="n">
-        <v>0</v>
-      </c>
-      <c r="R103" t="n">
-        <v>0</v>
-      </c>
-      <c r="S103" t="n">
-        <v>0</v>
-      </c>
-      <c r="T103" t="n">
-        <v>0</v>
-      </c>
-      <c r="U103" t="n">
-        <v>0</v>
-      </c>
-      <c r="V103" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt KUNGÄLV.xlsx
+++ b/Översikt KUNGÄLV.xlsx
@@ -601,7 +601,7 @@
         <v>45548</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>45868</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -851,7 +851,7 @@
         <v>45526</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -965,7 +965,7 @@
         <v>45919</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
         <v>45695</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         <v>45993</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         <v>45324</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>45985</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>46199</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>45355</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>46212</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         <v>45957</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 57116-2025</t>
+          <t>A 56394-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1963,14 +1963,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45979</v>
+        <v>45974</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1983,7 +1983,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>3.5</v>
+        <v>1.3</v>
       </c>
       <c r="J14" t="n">
         <v>1</v>
@@ -2016,153 +2016,153 @@
         <v>2</v>
       </c>
       <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Kambräken
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 56394-2025 artfynd.xlsx", "A 56394-2025")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 56394-2025 karta.png", "A 56394-2025")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 56394-2025 georefererad karta.tif", "A 56394-2025")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 56394-2025 FSC-klagomål.docx", "A 56394-2025")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 56394-2025 FSC-klagomål mail.docx", "A 56394-2025")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 56394-2025 tillsynsbegäran.docx", "A 56394-2025")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 56394-2025 tillsynsbegäran mail.docx", "A 56394-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 57116-2025</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>45979</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>KUNGÄLV</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2</v>
+      </c>
+      <c r="T15" t="n">
         <v>3</v>
       </c>
-      <c r="U14" t="n">
+      <c r="U15" t="n">
         <v>3</v>
       </c>
-      <c r="V14" s="2" t="inlineStr">
+      <c r="V15" s="2" t="inlineStr">
         <is>
           <t>Västlig hakmossa
 Spillkråka</t>
         </is>
       </c>
-      <c r="W14">
+      <c r="W15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 57116-2025 artfynd.xlsx", "A 57116-2025")</f>
         <v/>
       </c>
-      <c r="X14">
+      <c r="X15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 57116-2025 karta.png", "A 57116-2025")</f>
         <v/>
       </c>
-      <c r="Y14">
+      <c r="Y15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 57116-2025 georefererad karta.tif", "A 57116-2025")</f>
         <v/>
       </c>
-      <c r="AA14">
+      <c r="AA15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 57116-2025 FSC-klagomål.docx", "A 57116-2025")</f>
         <v/>
       </c>
-      <c r="AB14">
+      <c r="AB15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 57116-2025 FSC-klagomål mail.docx", "A 57116-2025")</f>
         <v/>
       </c>
-      <c r="AC14">
+      <c r="AC15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 57116-2025 tillsynsbegäran.docx", "A 57116-2025")</f>
         <v/>
       </c>
-      <c r="AD14">
+      <c r="AD15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 57116-2025 tillsynsbegäran mail.docx", "A 57116-2025")</f>
         <v/>
       </c>
-      <c r="AE14">
+      <c r="AE15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 57116-2025 prioriterade fågelarter.docx", "A 57116-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 56394-2025</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>45974</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>KUNGÄLV</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="J15" t="n">
-        <v>1</v>
-      </c>
-      <c r="K15" t="n">
-        <v>1</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>Kambräken
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 56394-2025 artfynd.xlsx", "A 56394-2025")</f>
-        <v/>
-      </c>
-      <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 56394-2025 karta.png", "A 56394-2025")</f>
-        <v/>
-      </c>
-      <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 56394-2025 georefererad karta.tif", "A 56394-2025")</f>
-        <v/>
-      </c>
-      <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 56394-2025 FSC-klagomål.docx", "A 56394-2025")</f>
-        <v/>
-      </c>
-      <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 56394-2025 FSC-klagomål mail.docx", "A 56394-2025")</f>
-        <v/>
-      </c>
-      <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 56394-2025 tillsynsbegäran.docx", "A 56394-2025")</f>
-        <v/>
-      </c>
-      <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 56394-2025 tillsynsbegäran mail.docx", "A 56394-2025")</f>
         <v/>
       </c>
     </row>
@@ -2186,7 +2186,7 @@
         <v>46212</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 53007-2025</t>
+          <t>A 5631-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2293,10 +2293,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45957</v>
+        <v>45334</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2309,13 +2309,13 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>2.9</v>
+        <v>1.3</v>
       </c>
       <c r="J17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -2342,259 +2342,259 @@
         <v>2</v>
       </c>
       <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>Vanlig groda
+Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="W17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 5631-2024 artfynd.xlsx", "A 5631-2024")</f>
+        <v/>
+      </c>
+      <c r="X17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 5631-2024 karta.png", "A 5631-2024")</f>
+        <v/>
+      </c>
+      <c r="Y17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 5631-2024 georefererad karta.tif", "A 5631-2024")</f>
+        <v/>
+      </c>
+      <c r="AA17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 5631-2024 FSC-klagomål.docx", "A 5631-2024")</f>
+        <v/>
+      </c>
+      <c r="AB17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 5631-2024 FSC-klagomål mail.docx", "A 5631-2024")</f>
+        <v/>
+      </c>
+      <c r="AC17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 5631-2024 tillsynsbegäran.docx", "A 5631-2024")</f>
+        <v/>
+      </c>
+      <c r="AD17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 5631-2024 tillsynsbegäran mail.docx", "A 5631-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>A 5637-2024</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>45334</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>KUNGÄLV</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>2</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>Klofibbla
+Åkerrödtoppa</t>
+        </is>
+      </c>
+      <c r="W18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 5637-2024 artfynd.xlsx", "A 5637-2024")</f>
+        <v/>
+      </c>
+      <c r="X18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 5637-2024 karta.png", "A 5637-2024")</f>
+        <v/>
+      </c>
+      <c r="Y18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 5637-2024 georefererad karta.tif", "A 5637-2024")</f>
+        <v/>
+      </c>
+      <c r="AA18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 5637-2024 FSC-klagomål.docx", "A 5637-2024")</f>
+        <v/>
+      </c>
+      <c r="AB18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 5637-2024 FSC-klagomål mail.docx", "A 5637-2024")</f>
+        <v/>
+      </c>
+      <c r="AC18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 5637-2024 tillsynsbegäran.docx", "A 5637-2024")</f>
+        <v/>
+      </c>
+      <c r="AD18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 5637-2024 tillsynsbegäran mail.docx", "A 5637-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>A 53007-2025</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>45957</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>KUNGÄLV</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2</v>
+      </c>
+      <c r="T19" t="n">
         <v>5</v>
       </c>
-      <c r="U17" t="n">
+      <c r="U19" t="n">
         <v>5</v>
       </c>
-      <c r="V17" s="2" t="inlineStr">
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>Västlig hakmossa
 Spillkråka</t>
         </is>
       </c>
-      <c r="W17">
+      <c r="W19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 53007-2025 artfynd.xlsx", "A 53007-2025")</f>
         <v/>
       </c>
-      <c r="X17">
+      <c r="X19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 53007-2025 karta.png", "A 53007-2025")</f>
         <v/>
       </c>
-      <c r="Y17">
+      <c r="Y19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 53007-2025 georefererad karta.tif", "A 53007-2025")</f>
         <v/>
       </c>
-      <c r="AA17">
+      <c r="AA19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 53007-2025 FSC-klagomål.docx", "A 53007-2025")</f>
         <v/>
       </c>
-      <c r="AB17">
+      <c r="AB19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 53007-2025 FSC-klagomål mail.docx", "A 53007-2025")</f>
         <v/>
       </c>
-      <c r="AC17">
+      <c r="AC19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 53007-2025 tillsynsbegäran.docx", "A 53007-2025")</f>
         <v/>
       </c>
-      <c r="AD17">
+      <c r="AD19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 53007-2025 tillsynsbegäran mail.docx", "A 53007-2025")</f>
         <v/>
       </c>
-      <c r="AE17">
+      <c r="AE19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 53007-2025 prioriterade fågelarter.docx", "A 53007-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 5631-2024</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>45334</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>KUNGÄLV</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="J18" t="n">
-        <v>2</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>Vanlig groda
-Fläcknycklar</t>
-        </is>
-      </c>
-      <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 5631-2024 artfynd.xlsx", "A 5631-2024")</f>
-        <v/>
-      </c>
-      <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 5631-2024 karta.png", "A 5631-2024")</f>
-        <v/>
-      </c>
-      <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 5631-2024 georefererad karta.tif", "A 5631-2024")</f>
-        <v/>
-      </c>
-      <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 5631-2024 FSC-klagomål.docx", "A 5631-2024")</f>
-        <v/>
-      </c>
-      <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 5631-2024 FSC-klagomål mail.docx", "A 5631-2024")</f>
-        <v/>
-      </c>
-      <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 5631-2024 tillsynsbegäran.docx", "A 5631-2024")</f>
-        <v/>
-      </c>
-      <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 5631-2024 tillsynsbegäran mail.docx", "A 5631-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>A 5637-2024</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>45334</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>KUNGÄLV</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>2</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>2</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>Klofibbla
-Åkerrödtoppa</t>
-        </is>
-      </c>
-      <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 5637-2024 artfynd.xlsx", "A 5637-2024")</f>
-        <v/>
-      </c>
-      <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 5637-2024 karta.png", "A 5637-2024")</f>
-        <v/>
-      </c>
-      <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 5637-2024 georefererad karta.tif", "A 5637-2024")</f>
-        <v/>
-      </c>
-      <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 5637-2024 FSC-klagomål.docx", "A 5637-2024")</f>
-        <v/>
-      </c>
-      <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 5637-2024 FSC-klagomål mail.docx", "A 5637-2024")</f>
-        <v/>
-      </c>
-      <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 5637-2024 tillsynsbegäran.docx", "A 5637-2024")</f>
-        <v/>
-      </c>
-      <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 5637-2024 tillsynsbegäran mail.docx", "A 5637-2024")</f>
         <v/>
       </c>
     </row>
@@ -2618,7 +2618,7 @@
         <v>44838</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2706,7 +2706,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 6082-2025</t>
+          <t>A 49988-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2720,10 +2720,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45697</v>
+        <v>45215</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="J21" t="n">
         <v>1</v>
@@ -2772,43 +2772,39 @@
         <v>1</v>
       </c>
       <c r="U21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 6082-2025 artfynd.xlsx", "A 6082-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 49988-2023 artfynd.xlsx", "A 49988-2023")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 6082-2025 karta.png", "A 6082-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 49988-2023 karta.png", "A 49988-2023")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 6082-2025 georefererad karta.tif", "A 6082-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 49988-2023 georefererad karta.tif", "A 49988-2023")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 6082-2025 FSC-klagomål.docx", "A 6082-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 49988-2023 FSC-klagomål.docx", "A 49988-2023")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 6082-2025 FSC-klagomål mail.docx", "A 6082-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 49988-2023 FSC-klagomål mail.docx", "A 49988-2023")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 6082-2025 tillsynsbegäran.docx", "A 6082-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 49988-2023 tillsynsbegäran.docx", "A 49988-2023")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 6082-2025 tillsynsbegäran mail.docx", "A 6082-2025")</f>
-        <v/>
-      </c>
-      <c r="AE21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 6082-2025 prioriterade fågelarter.docx", "A 6082-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 49988-2023 tillsynsbegäran mail.docx", "A 49988-2023")</f>
         <v/>
       </c>
     </row>
@@ -2832,7 +2828,7 @@
         <v>46212</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2937,7 +2933,7 @@
         <v>45454</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3025,7 +3021,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 49988-2023</t>
+          <t>A 6082-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3039,10 +3035,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45215</v>
+        <v>45697</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3055,7 +3051,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="J24" t="n">
         <v>1</v>
@@ -3091,39 +3087,43 @@
         <v>1</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 49988-2023 artfynd.xlsx", "A 49988-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 6082-2025 artfynd.xlsx", "A 6082-2025")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 49988-2023 karta.png", "A 49988-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 6082-2025 karta.png", "A 6082-2025")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 49988-2023 georefererad karta.tif", "A 49988-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 6082-2025 georefererad karta.tif", "A 6082-2025")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 49988-2023 FSC-klagomål.docx", "A 49988-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 6082-2025 FSC-klagomål.docx", "A 6082-2025")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 49988-2023 FSC-klagomål mail.docx", "A 49988-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 6082-2025 FSC-klagomål mail.docx", "A 6082-2025")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 49988-2023 tillsynsbegäran.docx", "A 49988-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 6082-2025 tillsynsbegäran.docx", "A 6082-2025")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 49988-2023 tillsynsbegäran mail.docx", "A 49988-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 6082-2025 tillsynsbegäran mail.docx", "A 6082-2025")</f>
+        <v/>
+      </c>
+      <c r="AE24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 6082-2025 prioriterade fågelarter.docx", "A 6082-2025")</f>
         <v/>
       </c>
     </row>
@@ -3147,7 +3147,7 @@
         <v>44691</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
         <v>44691</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         <v>44836</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3366,7 +3366,7 @@
         <v>44459</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         <v>44459</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
         <v>44760</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3585,7 +3585,7 @@
         <v>44760</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3658,7 +3658,7 @@
         <v>44760</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3714,7 +3714,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 17455-2025</t>
+          <t>A 30170-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3728,10 +3728,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45757</v>
+        <v>44757</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3744,7 +3744,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>2.1</v>
+        <v>3.1</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3787,7 +3787,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 62221-2023</t>
+          <t>A 13880-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3801,10 +3801,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45267</v>
+        <v>45391</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3817,7 +3817,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.3</v>
+        <v>2.4</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3860,7 +3860,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 21240-2023</t>
+          <t>A 1995-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3874,10 +3874,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45058</v>
+        <v>45308</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3890,7 +3890,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>2.3</v>
+        <v>0.5</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3933,7 +3933,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 29223-2024</t>
+          <t>A 62221-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3947,10 +3947,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45482</v>
+        <v>45267</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3963,7 +3963,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>5.6</v>
+        <v>1.3</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4006,7 +4006,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 10655-2022</t>
+          <t>A 4204-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4020,10 +4020,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44624</v>
+        <v>45324</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>13.3</v>
+        <v>4.4</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4079,7 +4079,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 39714-2024</t>
+          <t>A 16538-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4093,10 +4093,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45552</v>
+        <v>45751</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4109,7 +4109,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4152,7 +4152,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 74285-2021</t>
+          <t>A 29801-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4166,10 +4166,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44558</v>
+        <v>44755</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4182,7 +4182,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.1</v>
+        <v>4.8</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4225,7 +4225,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 61417-2022</t>
+          <t>A 49981-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4239,10 +4239,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44916</v>
+        <v>45215</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4255,7 +4255,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>3.6</v>
+        <v>2.5</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4298,7 +4298,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 32272-2023</t>
+          <t>A 45990-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4312,10 +4312,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45120</v>
+        <v>44846</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4328,7 +4328,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>4.9</v>
+        <v>3.3</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4371,7 +4371,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 32847-2023</t>
+          <t>A 17922-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4385,10 +4385,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45124</v>
+        <v>45758</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4401,7 +4401,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>4.7</v>
+        <v>0.8</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4444,7 +4444,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 40951-2025</t>
+          <t>A 71835-2021</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4458,10 +4458,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45897</v>
+        <v>44543</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4474,7 +4474,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.8</v>
+        <v>7.5</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4517,7 +4517,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 34366-2022</t>
+          <t>A 37443-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4531,10 +4531,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44792</v>
+        <v>45877</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4546,8 +4546,13 @@
           <t>KUNGÄLV</t>
         </is>
       </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I44" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4590,7 +4595,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 4673-2026</t>
+          <t>A 43520-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4604,10 +4609,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46048</v>
+        <v>44837</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4620,7 +4625,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>8.199999999999999</v>
+        <v>1.5</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4663,7 +4668,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 19531-2023</t>
+          <t>A 40951-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4677,10 +4682,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45050</v>
+        <v>45897</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4693,7 +4698,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.9</v>
+        <v>0.8</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4736,7 +4741,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 5705-2025</t>
+          <t>A 13990-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4746,14 +4751,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45694</v>
+        <v>46098</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4766,7 +4771,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.2</v>
+        <v>2.6</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4809,7 +4814,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 45124-2025</t>
+          <t>A 29223-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4823,10 +4828,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45919</v>
+        <v>45482</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4839,7 +4844,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>3.7</v>
+        <v>5.6</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4882,7 +4887,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 6946-2026</t>
+          <t>A 45124-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4892,14 +4897,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46057</v>
+        <v>45919</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4912,7 +4917,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2.2</v>
+        <v>3.7</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4955,7 +4960,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 7505-2024</t>
+          <t>A 8334-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4969,10 +4974,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45347</v>
+        <v>44975</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5045,7 +5050,7 @@
         <v>45931</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5101,7 +5106,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 34244-2025</t>
+          <t>A 49985-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5115,10 +5120,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45844</v>
+        <v>45215</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5131,7 +5136,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5174,7 +5179,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 25624-2025</t>
+          <t>A 50071-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5188,10 +5193,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45803</v>
+        <v>45215</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5204,7 +5209,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5247,7 +5252,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 41442-2025</t>
+          <t>A 52932-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5261,10 +5266,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45869</v>
+        <v>45957</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5277,7 +5282,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.8</v>
+        <v>3.4</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5320,7 +5325,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 8334-2023</t>
+          <t>A 4262-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5334,10 +5339,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44975</v>
+        <v>45324</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5350,7 +5355,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.8</v>
+        <v>14</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5393,7 +5398,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 17922-2025</t>
+          <t>A 661-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5407,10 +5412,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45758</v>
+        <v>45664</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5423,7 +5428,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.8</v>
+        <v>3.1</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5466,7 +5471,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 37443-2025</t>
+          <t>A 56782-2022</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5480,10 +5485,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45877</v>
+        <v>44894</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5495,13 +5500,8 @@
           <t>KUNGÄLV</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I57" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5544,7 +5544,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 13990-2026</t>
+          <t>A 22731-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5558,10 +5558,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46098</v>
+        <v>46157</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5574,7 +5574,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>2.6</v>
+        <v>1.8</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5617,7 +5617,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 52932-2025</t>
+          <t>A 32391-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5631,10 +5631,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45957</v>
+        <v>45837</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5647,7 +5647,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>3.4</v>
+        <v>2.1</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5690,7 +5690,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 49985-2023</t>
+          <t>A 23607-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5704,10 +5704,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45215</v>
+        <v>46163</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5720,7 +5720,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>8.199999999999999</v>
+        <v>5.3</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5763,7 +5763,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 50071-2023</t>
+          <t>A 25135-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5777,10 +5777,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45215</v>
+        <v>45798</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5793,7 +5793,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>4</v>
+        <v>1.1</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5836,7 +5836,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 49981-2023</t>
+          <t>A 34366-2022</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5850,10 +5850,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45215</v>
+        <v>44792</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5866,7 +5866,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5909,7 +5909,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 56782-2022</t>
+          <t>A 4673-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5923,10 +5923,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44894</v>
+        <v>46048</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5939,7 +5939,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5982,7 +5982,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 1995-2024</t>
+          <t>A 24461-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5996,10 +5996,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45308</v>
+        <v>45082</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6012,7 +6012,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6055,7 +6055,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 30170-2022</t>
+          <t>A 26812-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6069,10 +6069,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44757</v>
+        <v>45470</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6085,7 +6085,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>3.1</v>
+        <v>1.7</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6128,7 +6128,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 10810-2023</t>
+          <t>A 143-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6142,10 +6142,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44989</v>
+        <v>44928</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6158,7 +6158,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6201,7 +6201,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 4204-2024</t>
+          <t>A 6946-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6211,14 +6211,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45324</v>
+        <v>46057</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6231,7 +6231,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>4.4</v>
+        <v>2.2</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6274,7 +6274,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 22731-2026</t>
+          <t>A 63319-2021</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6288,10 +6288,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46157</v>
+        <v>44508</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6304,7 +6304,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6347,7 +6347,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 32391-2025</t>
+          <t>A 7505-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6361,10 +6361,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45837</v>
+        <v>45347</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6377,7 +6377,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6420,7 +6420,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 23607-2026</t>
+          <t>A 29952-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6434,10 +6434,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46163</v>
+        <v>46205</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6450,7 +6450,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>5.3</v>
+        <v>2</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6493,7 +6493,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 25135-2025</t>
+          <t>A 10655-2022</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6507,10 +6507,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45798</v>
+        <v>44624</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6523,7 +6523,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.1</v>
+        <v>13.3</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6566,7 +6566,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 62128-2021</t>
+          <t>A 17455-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6580,10 +6580,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44502</v>
+        <v>45757</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6596,7 +6596,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6639,7 +6639,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 62979-2023</t>
+          <t>A 34386-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6649,14 +6649,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45271</v>
+        <v>46254</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6669,7 +6669,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6712,7 +6712,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 29952-2026</t>
+          <t>A 30738-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6726,10 +6726,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46205</v>
+        <v>46211</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6742,7 +6742,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6785,7 +6785,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 34392-2026</t>
+          <t>A 30859-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6799,10 +6799,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46254</v>
+        <v>46212</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6815,7 +6815,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6858,7 +6858,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 34387-2026</t>
+          <t>A 10810-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6872,10 +6872,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46254</v>
+        <v>44989</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6888,7 +6888,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6931,7 +6931,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 34386-2026</t>
+          <t>A 34387-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6948,7 +6948,7 @@
         <v>46254</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6961,7 +6961,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7021,7 +7021,7 @@
         <v>46254</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7077,7 +7077,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 30738-2026</t>
+          <t>A 34392-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7091,10 +7091,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46211</v>
+        <v>46254</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7107,7 +7107,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>3.5</v>
+        <v>0.4</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7150,7 +7150,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 30859-2026</t>
+          <t>A 19531-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7164,10 +7164,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46212</v>
+        <v>45050</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7180,7 +7180,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7223,7 +7223,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 44176-2023</t>
+          <t>A 62128-2021</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7237,10 +7237,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45188</v>
+        <v>44502</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7253,7 +7253,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>7.1</v>
+        <v>1.8</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7296,7 +7296,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 26812-2024</t>
+          <t>A 5705-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7306,14 +7306,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45470</v>
+        <v>45694</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7326,7 +7326,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7369,7 +7369,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 29801-2022</t>
+          <t>A 62979-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7379,14 +7379,14 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>44755</v>
+        <v>45271</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>4.8</v>
+        <v>0.8</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7442,7 +7442,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 18852-2024</t>
+          <t>A 21240-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7456,10 +7456,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45426</v>
+        <v>45058</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7472,7 +7472,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7515,7 +7515,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 43520-2022</t>
+          <t>A 18851-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7529,10 +7529,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>44837</v>
+        <v>45426</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7545,7 +7545,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.5</v>
+        <v>2.7</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7588,7 +7588,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 16538-2025</t>
+          <t>A 21389-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7602,10 +7602,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45751</v>
+        <v>45063</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7618,7 +7618,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>0.8</v>
+        <v>3.4</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7661,7 +7661,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 45990-2022</t>
+          <t>A 44176-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7675,10 +7675,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>44846</v>
+        <v>45188</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7691,7 +7691,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>3.3</v>
+        <v>7.1</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7734,7 +7734,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 143-2023</t>
+          <t>A 23457-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7748,10 +7748,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>44928</v>
+        <v>45453</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7764,7 +7764,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0.5</v>
+        <v>5.1</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7807,7 +7807,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 18851-2024</t>
+          <t>A 39714-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7821,10 +7821,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45426</v>
+        <v>45552</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7837,7 +7837,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>2.7</v>
+        <v>1.2</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7880,7 +7880,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 71835-2021</t>
+          <t>A 18852-2024</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7894,10 +7894,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>44543</v>
+        <v>45426</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7910,7 +7910,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>7.5</v>
+        <v>2.7</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7970,7 +7970,7 @@
         <v>45222</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8026,7 +8026,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 661-2025</t>
+          <t>A 10679-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45664</v>
+        <v>45721</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8056,7 +8056,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>3.1</v>
+        <v>4.4</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 24461-2023</t>
+          <t>A 11237-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8113,10 +8113,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45082</v>
+        <v>45726</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8129,7 +8129,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1.5</v>
+        <v>4.2</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8172,7 +8172,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 13880-2024</t>
+          <t>A 10677-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8186,10 +8186,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45391</v>
+        <v>45721</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8202,7 +8202,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>2.4</v>
+        <v>7.4</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8245,7 +8245,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 23457-2024</t>
+          <t>A 74285-2021</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8259,10 +8259,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45453</v>
+        <v>44558</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8275,7 +8275,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>5.1</v>
+        <v>1.1</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8318,7 +8318,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 21389-2023</t>
+          <t>A 61417-2022</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8332,10 +8332,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45063</v>
+        <v>44916</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8348,7 +8348,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8391,7 +8391,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 4262-2024</t>
+          <t>A 32272-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8405,10 +8405,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45324</v>
+        <v>45120</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8421,7 +8421,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>14</v>
+        <v>4.9</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8464,7 +8464,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 63319-2021</t>
+          <t>A 32847-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8478,10 +8478,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>44508</v>
+        <v>45124</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8494,7 +8494,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1.6</v>
+        <v>4.7</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8537,7 +8537,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 10677-2025</t>
+          <t>A 34244-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8551,10 +8551,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45721</v>
+        <v>45844</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8567,7 +8567,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>7.4</v>
+        <v>2.9</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8610,7 +8610,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 10679-2025</t>
+          <t>A 25624-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8624,10 +8624,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45721</v>
+        <v>45803</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8640,7 +8640,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8683,7 +8683,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 11237-2025</t>
+          <t>A 41442-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8697,10 +8697,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45726</v>
+        <v>45869</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8713,7 +8713,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>4.2</v>
+        <v>1.8</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8773,7 +8773,7 @@
         <v>45371</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>

--- a/Översikt KUNGÄLV.xlsx
+++ b/Översikt KUNGÄLV.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE102"/>
+  <dimension ref="A1:AE103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45548</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>45868</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -851,7 +851,7 @@
         <v>45526</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -965,7 +965,7 @@
         <v>45919</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
         <v>45695</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         <v>45993</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         <v>45324</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>45985</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>46199</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>45355</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>46212</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         <v>45957</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1970,7 +1970,7 @@
         <v>45974</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2076,7 +2076,7 @@
         <v>45979</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
         <v>46212</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 5631-2024</t>
+          <t>A 53007-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2293,10 +2293,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45334</v>
+        <v>45957</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2309,13 +2309,13 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.3</v>
+        <v>2.9</v>
       </c>
       <c r="J17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -2342,259 +2342,259 @@
         <v>2</v>
       </c>
       <c r="T17" t="n">
+        <v>5</v>
+      </c>
+      <c r="U17" t="n">
+        <v>5</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>Västlig hakmossa
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 53007-2025 artfynd.xlsx", "A 53007-2025")</f>
+        <v/>
+      </c>
+      <c r="X17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 53007-2025 karta.png", "A 53007-2025")</f>
+        <v/>
+      </c>
+      <c r="Y17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 53007-2025 georefererad karta.tif", "A 53007-2025")</f>
+        <v/>
+      </c>
+      <c r="AA17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 53007-2025 FSC-klagomål.docx", "A 53007-2025")</f>
+        <v/>
+      </c>
+      <c r="AB17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 53007-2025 FSC-klagomål mail.docx", "A 53007-2025")</f>
+        <v/>
+      </c>
+      <c r="AC17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 53007-2025 tillsynsbegäran.docx", "A 53007-2025")</f>
+        <v/>
+      </c>
+      <c r="AD17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 53007-2025 tillsynsbegäran mail.docx", "A 53007-2025")</f>
+        <v/>
+      </c>
+      <c r="AE17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 53007-2025 prioriterade fågelarter.docx", "A 53007-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>A 5631-2024</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>45334</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>KUNGÄLV</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J18" t="n">
         <v>2</v>
       </c>
-      <c r="U17" t="n">
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
         <v>1</v>
       </c>
-      <c r="V17" s="2" t="inlineStr">
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>Vanlig groda
 Fläcknycklar</t>
         </is>
       </c>
-      <c r="W17">
+      <c r="W18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 5631-2024 artfynd.xlsx", "A 5631-2024")</f>
         <v/>
       </c>
-      <c r="X17">
+      <c r="X18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 5631-2024 karta.png", "A 5631-2024")</f>
         <v/>
       </c>
-      <c r="Y17">
+      <c r="Y18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 5631-2024 georefererad karta.tif", "A 5631-2024")</f>
         <v/>
       </c>
-      <c r="AA17">
+      <c r="AA18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 5631-2024 FSC-klagomål.docx", "A 5631-2024")</f>
         <v/>
       </c>
-      <c r="AB17">
+      <c r="AB18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 5631-2024 FSC-klagomål mail.docx", "A 5631-2024")</f>
         <v/>
       </c>
-      <c r="AC17">
+      <c r="AC18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 5631-2024 tillsynsbegäran.docx", "A 5631-2024")</f>
         <v/>
       </c>
-      <c r="AD17">
+      <c r="AD18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 5631-2024 tillsynsbegäran mail.docx", "A 5631-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
         <is>
           <t>A 5637-2024</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
         <v>45334</v>
       </c>
-      <c r="E18" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>KUNGÄLV</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
+      <c r="E19" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>KUNGÄLV</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
         <v>1.8</v>
       </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
         <v>2</v>
       </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
         <v>2</v>
       </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
         <v>2</v>
       </c>
-      <c r="T18" t="n">
+      <c r="T19" t="n">
         <v>2</v>
       </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>Klofibbla
 Åkerrödtoppa</t>
         </is>
       </c>
-      <c r="W18">
+      <c r="W19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 5637-2024 artfynd.xlsx", "A 5637-2024")</f>
         <v/>
       </c>
-      <c r="X18">
+      <c r="X19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 5637-2024 karta.png", "A 5637-2024")</f>
         <v/>
       </c>
-      <c r="Y18">
+      <c r="Y19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 5637-2024 georefererad karta.tif", "A 5637-2024")</f>
         <v/>
       </c>
-      <c r="AA18">
+      <c r="AA19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 5637-2024 FSC-klagomål.docx", "A 5637-2024")</f>
         <v/>
       </c>
-      <c r="AB18">
+      <c r="AB19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 5637-2024 FSC-klagomål mail.docx", "A 5637-2024")</f>
         <v/>
       </c>
-      <c r="AC18">
+      <c r="AC19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 5637-2024 tillsynsbegäran.docx", "A 5637-2024")</f>
         <v/>
       </c>
-      <c r="AD18">
+      <c r="AD19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 5637-2024 tillsynsbegäran mail.docx", "A 5637-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>A 53007-2025</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>45957</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>KUNGÄLV</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="J19" t="n">
-        <v>1</v>
-      </c>
-      <c r="K19" t="n">
-        <v>1</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2</v>
-      </c>
-      <c r="T19" t="n">
-        <v>5</v>
-      </c>
-      <c r="U19" t="n">
-        <v>5</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>Västlig hakmossa
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 53007-2025 artfynd.xlsx", "A 53007-2025")</f>
-        <v/>
-      </c>
-      <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 53007-2025 karta.png", "A 53007-2025")</f>
-        <v/>
-      </c>
-      <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 53007-2025 georefererad karta.tif", "A 53007-2025")</f>
-        <v/>
-      </c>
-      <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 53007-2025 FSC-klagomål.docx", "A 53007-2025")</f>
-        <v/>
-      </c>
-      <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 53007-2025 FSC-klagomål mail.docx", "A 53007-2025")</f>
-        <v/>
-      </c>
-      <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 53007-2025 tillsynsbegäran.docx", "A 53007-2025")</f>
-        <v/>
-      </c>
-      <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 53007-2025 tillsynsbegäran mail.docx", "A 53007-2025")</f>
-        <v/>
-      </c>
-      <c r="AE19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 53007-2025 prioriterade fågelarter.docx", "A 53007-2025")</f>
         <v/>
       </c>
     </row>
@@ -2618,7 +2618,7 @@
         <v>44838</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2706,7 +2706,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 49988-2023</t>
+          <t>A 6082-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2720,10 +2720,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45215</v>
+        <v>45697</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="J21" t="n">
         <v>1</v>
@@ -2772,46 +2772,50 @@
         <v>1</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 49988-2023 artfynd.xlsx", "A 49988-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 6082-2025 artfynd.xlsx", "A 6082-2025")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 49988-2023 karta.png", "A 49988-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 6082-2025 karta.png", "A 6082-2025")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 49988-2023 georefererad karta.tif", "A 49988-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 6082-2025 georefererad karta.tif", "A 6082-2025")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 49988-2023 FSC-klagomål.docx", "A 49988-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 6082-2025 FSC-klagomål.docx", "A 6082-2025")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 49988-2023 FSC-klagomål mail.docx", "A 49988-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 6082-2025 FSC-klagomål mail.docx", "A 6082-2025")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 49988-2023 tillsynsbegäran.docx", "A 49988-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 6082-2025 tillsynsbegäran.docx", "A 6082-2025")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 49988-2023 tillsynsbegäran mail.docx", "A 49988-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 6082-2025 tillsynsbegäran mail.docx", "A 6082-2025")</f>
+        <v/>
+      </c>
+      <c r="AE21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 6082-2025 prioriterade fågelarter.docx", "A 6082-2025")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 30862-2026</t>
+          <t>A 23704-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2825,10 +2829,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46212</v>
+        <v>45454</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2841,7 +2845,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.7</v>
+        <v>4.9</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
@@ -2853,7 +2857,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
@@ -2865,58 +2869,58 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
       </c>
       <c r="T22" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Hedjohannesört</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 30862-2026 artfynd.xlsx", "A 30862-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 23704-2024 artfynd.xlsx", "A 23704-2024")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 30862-2026 karta.png", "A 30862-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 23704-2024 karta.png", "A 23704-2024")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 30862-2026 georefererad karta.tif", "A 30862-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 23704-2024 georefererad karta.tif", "A 23704-2024")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 30862-2026 FSC-klagomål.docx", "A 30862-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 23704-2024 FSC-klagomål.docx", "A 23704-2024")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 30862-2026 FSC-klagomål mail.docx", "A 30862-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 23704-2024 FSC-klagomål mail.docx", "A 23704-2024")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 30862-2026 tillsynsbegäran.docx", "A 30862-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 23704-2024 tillsynsbegäran.docx", "A 23704-2024")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 30862-2026 tillsynsbegäran mail.docx", "A 30862-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 23704-2024 tillsynsbegäran mail.docx", "A 23704-2024")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 23704-2024</t>
+          <t>A 49988-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2930,10 +2934,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45454</v>
+        <v>45215</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2946,7 +2950,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>4.9</v>
+        <v>2.3</v>
       </c>
       <c r="J23" t="n">
         <v>1</v>
@@ -2958,7 +2962,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
@@ -2970,58 +2974,58 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
       </c>
       <c r="T23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Hedjohannesört</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 23704-2024 artfynd.xlsx", "A 23704-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 49988-2023 artfynd.xlsx", "A 49988-2023")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 23704-2024 karta.png", "A 23704-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 49988-2023 karta.png", "A 49988-2023")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 23704-2024 georefererad karta.tif", "A 23704-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 49988-2023 georefererad karta.tif", "A 49988-2023")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 23704-2024 FSC-klagomål.docx", "A 23704-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 49988-2023 FSC-klagomål.docx", "A 49988-2023")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 23704-2024 FSC-klagomål mail.docx", "A 23704-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 49988-2023 FSC-klagomål mail.docx", "A 49988-2023")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 23704-2024 tillsynsbegäran.docx", "A 23704-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 49988-2023 tillsynsbegäran.docx", "A 49988-2023")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 23704-2024 tillsynsbegäran mail.docx", "A 23704-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 49988-2023 tillsynsbegäran mail.docx", "A 49988-2023")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 6082-2025</t>
+          <t>A 30862-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3035,10 +3039,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45697</v>
+        <v>46212</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3051,7 +3055,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.8</v>
+        <v>1.7</v>
       </c>
       <c r="J24" t="n">
         <v>1</v>
@@ -3084,46 +3088,42 @@
         <v>1</v>
       </c>
       <c r="T24" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 6082-2025 artfynd.xlsx", "A 6082-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 30862-2026 artfynd.xlsx", "A 30862-2026")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 6082-2025 karta.png", "A 6082-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 30862-2026 karta.png", "A 30862-2026")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 6082-2025 georefererad karta.tif", "A 6082-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 30862-2026 georefererad karta.tif", "A 30862-2026")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 6082-2025 FSC-klagomål.docx", "A 6082-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 30862-2026 FSC-klagomål.docx", "A 30862-2026")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 6082-2025 FSC-klagomål mail.docx", "A 6082-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 30862-2026 FSC-klagomål mail.docx", "A 30862-2026")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 6082-2025 tillsynsbegäran.docx", "A 6082-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 30862-2026 tillsynsbegäran.docx", "A 30862-2026")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 6082-2025 tillsynsbegäran mail.docx", "A 6082-2025")</f>
-        <v/>
-      </c>
-      <c r="AE24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 6082-2025 prioriterade fågelarter.docx", "A 6082-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 30862-2026 tillsynsbegäran mail.docx", "A 30862-2026")</f>
         <v/>
       </c>
     </row>
@@ -3147,7 +3147,7 @@
         <v>44691</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
         <v>44691</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         <v>44836</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3366,7 +3366,7 @@
         <v>44459</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         <v>44459</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
         <v>44760</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3585,7 +3585,7 @@
         <v>44760</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3658,7 +3658,7 @@
         <v>44760</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3714,7 +3714,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 30170-2022</t>
+          <t>A 21240-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3728,10 +3728,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44757</v>
+        <v>45058</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3744,7 +3744,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>3.1</v>
+        <v>2.3</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3787,7 +3787,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 13880-2024</t>
+          <t>A 29223-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3801,10 +3801,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45391</v>
+        <v>45482</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3817,7 +3817,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2.4</v>
+        <v>5.6</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3860,7 +3860,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 1995-2024</t>
+          <t>A 10655-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3874,10 +3874,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45308</v>
+        <v>44624</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3890,7 +3890,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.5</v>
+        <v>13.3</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3933,7 +3933,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 62221-2023</t>
+          <t>A 17455-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3947,10 +3947,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45267</v>
+        <v>45757</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3963,7 +3963,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.3</v>
+        <v>2.1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4006,7 +4006,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 4204-2024</t>
+          <t>A 62221-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4020,10 +4020,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45324</v>
+        <v>45267</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>4.4</v>
+        <v>1.3</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4079,7 +4079,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 16538-2025</t>
+          <t>A 39714-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4093,10 +4093,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45751</v>
+        <v>45552</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4109,7 +4109,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4152,7 +4152,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 29801-2022</t>
+          <t>A 61417-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4166,10 +4166,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44755</v>
+        <v>44916</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4182,7 +4182,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>4.8</v>
+        <v>3.6</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4225,7 +4225,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 49981-2023</t>
+          <t>A 32272-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4239,10 +4239,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45215</v>
+        <v>45120</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4255,7 +4255,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2.5</v>
+        <v>4.9</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4298,7 +4298,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 45990-2022</t>
+          <t>A 32847-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4312,10 +4312,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44846</v>
+        <v>45124</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4328,7 +4328,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>3.3</v>
+        <v>4.7</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4371,7 +4371,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 17922-2025</t>
+          <t>A 19531-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4385,10 +4385,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45758</v>
+        <v>45050</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4401,7 +4401,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.8</v>
+        <v>1.9</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4444,7 +4444,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 71835-2021</t>
+          <t>A 5705-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4454,14 +4454,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44543</v>
+        <v>45694</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4474,7 +4474,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>7.5</v>
+        <v>1.2</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4517,7 +4517,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 37443-2025</t>
+          <t>A 40951-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4531,10 +4531,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45877</v>
+        <v>45897</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4546,13 +4546,8 @@
           <t>KUNGÄLV</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I44" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4595,7 +4590,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 43520-2022</t>
+          <t>A 7505-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4609,10 +4604,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44837</v>
+        <v>45347</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4625,7 +4620,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4668,7 +4663,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 40951-2025</t>
+          <t>A 45124-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4682,10 +4677,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45897</v>
+        <v>45919</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4698,7 +4693,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.8</v>
+        <v>3.7</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4741,7 +4736,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 13990-2026</t>
+          <t>A 8334-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4755,10 +4750,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46098</v>
+        <v>44975</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4771,7 +4766,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2.6</v>
+        <v>1.8</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4814,7 +4809,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 29223-2024</t>
+          <t>A 34244-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4828,10 +4823,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45482</v>
+        <v>45844</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4844,7 +4839,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>5.6</v>
+        <v>2.9</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4887,7 +4882,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 45124-2025</t>
+          <t>A 47564-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4901,10 +4896,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45919</v>
+        <v>45931</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4917,7 +4912,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>3.7</v>
+        <v>2</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4960,7 +4955,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 8334-2023</t>
+          <t>A 25624-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4974,10 +4969,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44975</v>
+        <v>45803</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4990,7 +4985,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.8</v>
+        <v>5</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5033,7 +5028,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 47564-2025</t>
+          <t>A 41442-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5047,10 +5042,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45931</v>
+        <v>45869</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5063,7 +5058,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5106,7 +5101,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 49985-2023</t>
+          <t>A 34366-2022</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5120,10 +5115,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45215</v>
+        <v>44792</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5136,7 +5131,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>8.199999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5179,7 +5174,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 50071-2023</t>
+          <t>A 4673-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5193,10 +5188,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45215</v>
+        <v>46048</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5209,7 +5204,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5252,7 +5247,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 52932-2025</t>
+          <t>A 17922-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5266,10 +5261,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45957</v>
+        <v>45758</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5282,7 +5277,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>3.4</v>
+        <v>0.8</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5325,7 +5320,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 4262-2024</t>
+          <t>A 52932-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5339,10 +5334,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45324</v>
+        <v>45957</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5355,7 +5350,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>14</v>
+        <v>3.4</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5398,7 +5393,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 661-2025</t>
+          <t>A 6946-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5408,14 +5403,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45664</v>
+        <v>46057</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5428,7 +5423,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>3.1</v>
+        <v>2.2</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5471,7 +5466,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 56782-2022</t>
+          <t>A 49981-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5485,10 +5480,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44894</v>
+        <v>45215</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5501,7 +5496,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5544,7 +5539,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 22731-2026</t>
+          <t>A 56782-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5558,10 +5553,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46157</v>
+        <v>44894</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5574,7 +5569,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5617,7 +5612,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 32391-2025</t>
+          <t>A 37443-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5631,10 +5626,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45837</v>
+        <v>45877</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5646,8 +5641,13 @@
           <t>KUNGÄLV</t>
         </is>
       </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I59" t="n">
-        <v>2.1</v>
+        <v>0.7</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5690,7 +5690,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 23607-2026</t>
+          <t>A 1995-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5704,10 +5704,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46163</v>
+        <v>45308</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5720,7 +5720,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>5.3</v>
+        <v>0.5</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5763,7 +5763,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 25135-2025</t>
+          <t>A 30170-2022</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5777,10 +5777,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45798</v>
+        <v>44757</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5793,7 +5793,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.1</v>
+        <v>3.1</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5836,7 +5836,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 34366-2022</t>
+          <t>A 10810-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5850,10 +5850,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44792</v>
+        <v>44989</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5866,7 +5866,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5909,7 +5909,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 4673-2026</t>
+          <t>A 13990-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5923,10 +5923,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46048</v>
+        <v>46098</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5939,7 +5939,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>8.199999999999999</v>
+        <v>2.6</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5982,7 +5982,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 24461-2023</t>
+          <t>A 4204-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5996,10 +5996,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45082</v>
+        <v>45324</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6012,7 +6012,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.5</v>
+        <v>4.4</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6055,7 +6055,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 26812-2024</t>
+          <t>A 62128-2021</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6069,10 +6069,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45470</v>
+        <v>44502</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6085,7 +6085,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6128,7 +6128,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 143-2023</t>
+          <t>A 62979-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6138,14 +6138,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44928</v>
+        <v>45271</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6158,7 +6158,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6201,7 +6201,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 6946-2026</t>
+          <t>A 49985-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6211,14 +6211,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46057</v>
+        <v>45215</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6231,7 +6231,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>2.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6274,7 +6274,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 63319-2021</t>
+          <t>A 50071-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6288,10 +6288,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44508</v>
+        <v>45215</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6304,7 +6304,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.6</v>
+        <v>4</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6347,7 +6347,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 7505-2024</t>
+          <t>A 44176-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6361,10 +6361,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45347</v>
+        <v>45188</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6377,7 +6377,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.8</v>
+        <v>7.1</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6420,7 +6420,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 29952-2026</t>
+          <t>A 26812-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6434,10 +6434,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46205</v>
+        <v>45470</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6450,7 +6450,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6493,7 +6493,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 10655-2022</t>
+          <t>A 29801-2022</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6507,10 +6507,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44624</v>
+        <v>44755</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6523,7 +6523,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>13.3</v>
+        <v>4.8</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6566,7 +6566,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 17455-2025</t>
+          <t>A 18852-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6580,10 +6580,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45757</v>
+        <v>45426</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6596,7 +6596,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>2.1</v>
+        <v>2.7</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6639,7 +6639,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 34386-2026</t>
+          <t>A 43520-2022</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6653,10 +6653,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46254</v>
+        <v>44837</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6669,7 +6669,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6712,7 +6712,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 30738-2026</t>
+          <t>A 16538-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6726,10 +6726,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46211</v>
+        <v>45751</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6742,7 +6742,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>3.5</v>
+        <v>0.8</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6785,7 +6785,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 30859-2026</t>
+          <t>A 45990-2022</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6799,10 +6799,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46212</v>
+        <v>44846</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6815,7 +6815,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.5</v>
+        <v>3.3</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6858,7 +6858,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 10810-2023</t>
+          <t>A 22731-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6872,10 +6872,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44989</v>
+        <v>46157</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6888,7 +6888,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.4</v>
+        <v>1.8</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6931,7 +6931,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 34387-2026</t>
+          <t>A 32391-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6945,10 +6945,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46254</v>
+        <v>45837</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6961,7 +6961,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.3</v>
+        <v>2.1</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7004,7 +7004,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 34396-2026</t>
+          <t>A 23607-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7018,10 +7018,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46254</v>
+        <v>46163</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7034,7 +7034,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.8</v>
+        <v>5.3</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7077,7 +7077,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 34392-2026</t>
+          <t>A 143-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7091,10 +7091,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46254</v>
+        <v>44928</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7107,7 +7107,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7150,7 +7150,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 19531-2023</t>
+          <t>A 25135-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7164,10 +7164,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45050</v>
+        <v>45798</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7180,7 +7180,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7223,7 +7223,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 62128-2021</t>
+          <t>A 18851-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7237,10 +7237,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44502</v>
+        <v>45426</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7253,7 +7253,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.8</v>
+        <v>2.7</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7296,7 +7296,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 5705-2025</t>
+          <t>A 71835-2021</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7306,14 +7306,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45694</v>
+        <v>44543</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7326,7 +7326,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.2</v>
+        <v>7.5</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7369,7 +7369,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 62979-2023</t>
+          <t>A 51724-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7379,14 +7379,14 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45271</v>
+        <v>45222</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>0.8</v>
+        <v>3.1</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7442,7 +7442,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 21240-2023</t>
+          <t>A 661-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7456,10 +7456,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45058</v>
+        <v>45664</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7472,7 +7472,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7515,7 +7515,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 18851-2024</t>
+          <t>A 24461-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7529,10 +7529,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45426</v>
+        <v>45082</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7545,7 +7545,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>2.7</v>
+        <v>1.5</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7588,7 +7588,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 21389-2023</t>
+          <t>A 13880-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7602,10 +7602,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45063</v>
+        <v>45391</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7618,7 +7618,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>3.4</v>
+        <v>2.4</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7661,7 +7661,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 44176-2023</t>
+          <t>A 29952-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7675,10 +7675,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45188</v>
+        <v>46205</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7691,7 +7691,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>7.1</v>
+        <v>2</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7734,7 +7734,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 23457-2024</t>
+          <t>A 34392-2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7748,10 +7748,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45453</v>
+        <v>46254</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7764,7 +7764,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>5.1</v>
+        <v>0.4</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7807,7 +7807,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 39714-2024</t>
+          <t>A 34387-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7821,10 +7821,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45552</v>
+        <v>46254</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7837,7 +7837,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1.2</v>
+        <v>0.3</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7880,7 +7880,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 18852-2024</t>
+          <t>A 34386-2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7894,10 +7894,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45426</v>
+        <v>46254</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7910,7 +7910,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>2.7</v>
+        <v>0.7</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7953,7 +7953,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 51724-2023</t>
+          <t>A 34396-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7967,10 +7967,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45222</v>
+        <v>46254</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7983,7 +7983,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>3.1</v>
+        <v>0.8</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8026,7 +8026,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 10679-2025</t>
+          <t>A 30738-2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45721</v>
+        <v>46211</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8056,7 +8056,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>4.4</v>
+        <v>3.5</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 11237-2025</t>
+          <t>A 30859-2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8113,10 +8113,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45726</v>
+        <v>46212</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8129,7 +8129,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>4.2</v>
+        <v>0.5</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8172,7 +8172,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 10677-2025</t>
+          <t>A 23457-2024</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8186,10 +8186,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45721</v>
+        <v>45453</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8202,7 +8202,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>7.4</v>
+        <v>5.1</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8245,7 +8245,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 74285-2021</t>
+          <t>A 21389-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8259,10 +8259,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>44558</v>
+        <v>45063</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8275,7 +8275,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>1.1</v>
+        <v>3.4</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8318,7 +8318,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 61417-2022</t>
+          <t>A 4262-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8332,10 +8332,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>44916</v>
+        <v>45324</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8348,7 +8348,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>3.6</v>
+        <v>14</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8391,7 +8391,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 32272-2023</t>
+          <t>A 63319-2021</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8405,10 +8405,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45120</v>
+        <v>44508</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8421,7 +8421,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>4.9</v>
+        <v>1.6</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8464,7 +8464,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 32847-2023</t>
+          <t>A 38262-2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8478,10 +8478,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45124</v>
+        <v>46281</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8494,7 +8494,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>4.7</v>
+        <v>2.8</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8537,7 +8537,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 34244-2025</t>
+          <t>A 10677-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8551,10 +8551,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45844</v>
+        <v>45721</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8567,7 +8567,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>2.9</v>
+        <v>7.4</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8610,7 +8610,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 25624-2025</t>
+          <t>A 10679-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8624,10 +8624,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45803</v>
+        <v>45721</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8640,7 +8640,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8683,7 +8683,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 41442-2025</t>
+          <t>A 11237-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8697,10 +8697,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45869</v>
+        <v>45726</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8713,7 +8713,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1.8</v>
+        <v>4.2</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8753,83 +8753,156 @@
       </c>
       <c r="V101" s="2" t="inlineStr"/>
     </row>
-    <row r="102">
+    <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
+          <t>A 74285-2021</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D102" s="1" t="n">
+        <v>44558</v>
+      </c>
+      <c r="E102" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>KUNGÄLV</t>
+        </is>
+      </c>
+      <c r="I102" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J102" t="n">
+        <v>0</v>
+      </c>
+      <c r="K102" t="n">
+        <v>0</v>
+      </c>
+      <c r="L102" t="n">
+        <v>0</v>
+      </c>
+      <c r="M102" t="n">
+        <v>0</v>
+      </c>
+      <c r="N102" t="n">
+        <v>0</v>
+      </c>
+      <c r="O102" t="n">
+        <v>0</v>
+      </c>
+      <c r="P102" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q102" t="n">
+        <v>0</v>
+      </c>
+      <c r="R102" t="n">
+        <v>0</v>
+      </c>
+      <c r="S102" t="n">
+        <v>0</v>
+      </c>
+      <c r="T102" t="n">
+        <v>0</v>
+      </c>
+      <c r="U102" t="n">
+        <v>0</v>
+      </c>
+      <c r="V102" s="2" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
           <t>S 817-2024</t>
         </is>
       </c>
-      <c r="B102" t="inlineStr">
+      <c r="B103" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C102" t="inlineStr">
+      <c r="C103" t="inlineStr">
         <is>
           <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
-      <c r="D102" s="1" t="n">
+      <c r="D103" s="1" t="n">
         <v>45371</v>
       </c>
-      <c r="E102" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>KUNGÄLV</t>
-        </is>
-      </c>
-      <c r="H102" t="inlineStr">
+      <c r="E103" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>KUNGÄLV</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
         <is>
           <t>Övriga statliga verk och myndigheter</t>
         </is>
       </c>
-      <c r="I102" t="n">
+      <c r="I103" t="n">
         <v>2.4</v>
       </c>
-      <c r="J102" t="n">
-        <v>0</v>
-      </c>
-      <c r="K102" t="n">
-        <v>0</v>
-      </c>
-      <c r="L102" t="n">
-        <v>0</v>
-      </c>
-      <c r="M102" t="n">
-        <v>0</v>
-      </c>
-      <c r="N102" t="n">
-        <v>0</v>
-      </c>
-      <c r="O102" t="n">
-        <v>0</v>
-      </c>
-      <c r="P102" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q102" t="n">
-        <v>0</v>
-      </c>
-      <c r="R102" t="n">
-        <v>0</v>
-      </c>
-      <c r="S102" t="n">
-        <v>0</v>
-      </c>
-      <c r="T102" t="n">
-        <v>0</v>
-      </c>
-      <c r="U102" t="n">
-        <v>0</v>
-      </c>
-      <c r="V102" s="2" t="inlineStr"/>
+      <c r="J103" t="n">
+        <v>0</v>
+      </c>
+      <c r="K103" t="n">
+        <v>0</v>
+      </c>
+      <c r="L103" t="n">
+        <v>0</v>
+      </c>
+      <c r="M103" t="n">
+        <v>0</v>
+      </c>
+      <c r="N103" t="n">
+        <v>0</v>
+      </c>
+      <c r="O103" t="n">
+        <v>0</v>
+      </c>
+      <c r="P103" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q103" t="n">
+        <v>0</v>
+      </c>
+      <c r="R103" t="n">
+        <v>0</v>
+      </c>
+      <c r="S103" t="n">
+        <v>0</v>
+      </c>
+      <c r="T103" t="n">
+        <v>0</v>
+      </c>
+      <c r="U103" t="n">
+        <v>0</v>
+      </c>
+      <c r="V103" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt KUNGÄLV.xlsx
+++ b/Översikt KUNGÄLV.xlsx
@@ -601,7 +601,7 @@
         <v>45548</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>45868</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -851,7 +851,7 @@
         <v>45526</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -965,7 +965,7 @@
         <v>45919</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
         <v>45695</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 59985-2025</t>
+          <t>A 4263-2024</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1188,10 +1188,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45993</v>
+        <v>45324</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1204,16 +1204,16 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>5.3</v>
+        <v>2.6</v>
       </c>
       <c r="J7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -1228,7 +1228,7 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1237,12 +1237,124 @@
         <v>4</v>
       </c>
       <c r="T7" t="n">
+        <v>6</v>
+      </c>
+      <c r="U7" t="n">
+        <v>6</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Mindre hackspett
+Klippfrullania
+Gråsiska
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 4263-2024 artfynd.xlsx", "A 4263-2024")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 4263-2024 karta.png", "A 4263-2024")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 4263-2024 georefererad karta.tif", "A 4263-2024")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 4263-2024 FSC-klagomål.docx", "A 4263-2024")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 4263-2024 FSC-klagomål mail.docx", "A 4263-2024")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 4263-2024 tillsynsbegäran.docx", "A 4263-2024")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 4263-2024 tillsynsbegäran mail.docx", "A 4263-2024")</f>
+        <v/>
+      </c>
+      <c r="AE7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 4263-2024 prioriterade fågelarter.docx", "A 4263-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 59985-2025</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>45993</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>KUNGÄLV</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2</v>
+      </c>
+      <c r="K8" t="n">
+        <v>2</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>4</v>
+      </c>
+      <c r="T8" t="n">
         <v>19</v>
       </c>
-      <c r="U7" t="n">
+      <c r="U8" t="n">
         <v>19</v>
       </c>
-      <c r="V7" s="2" t="inlineStr">
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>Blåmossa
 Västlig hakmossa
@@ -1250,155 +1362,43 @@
 Äkta lopplummer</t>
         </is>
       </c>
-      <c r="W7">
+      <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 59985-2025 artfynd.xlsx", "A 59985-2025")</f>
         <v/>
       </c>
-      <c r="X7">
+      <c r="X8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 59985-2025 karta.png", "A 59985-2025")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 59985-2025 georefererad karta.tif", "A 59985-2025")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 59985-2025 FSC-klagomål.docx", "A 59985-2025")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 59985-2025 FSC-klagomål mail.docx", "A 59985-2025")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 59985-2025 tillsynsbegäran.docx", "A 59985-2025")</f>
         <v/>
       </c>
-      <c r="AD7">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 59985-2025 tillsynsbegäran mail.docx", "A 59985-2025")</f>
         <v/>
       </c>
-      <c r="AE7">
+      <c r="AE8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 59985-2025 prioriterade fågelarter.docx", "A 59985-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A 4263-2024</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>45324</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>KUNGÄLV</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="J8" t="n">
-        <v>3</v>
-      </c>
-      <c r="K8" t="n">
-        <v>1</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>4</v>
-      </c>
-      <c r="T8" t="n">
-        <v>6</v>
-      </c>
-      <c r="U8" t="n">
-        <v>6</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>Mindre hackspett
-Klippfrullania
-Gråsiska
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 4263-2024 artfynd.xlsx", "A 4263-2024")</f>
-        <v/>
-      </c>
-      <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 4263-2024 karta.png", "A 4263-2024")</f>
-        <v/>
-      </c>
-      <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 4263-2024 georefererad karta.tif", "A 4263-2024")</f>
-        <v/>
-      </c>
-      <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 4263-2024 FSC-klagomål.docx", "A 4263-2024")</f>
-        <v/>
-      </c>
-      <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 4263-2024 FSC-klagomål mail.docx", "A 4263-2024")</f>
-        <v/>
-      </c>
-      <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 4263-2024 tillsynsbegäran.docx", "A 4263-2024")</f>
-        <v/>
-      </c>
-      <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 4263-2024 tillsynsbegäran mail.docx", "A 4263-2024")</f>
-        <v/>
-      </c>
-      <c r="AE8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 4263-2024 prioriterade fågelarter.docx", "A 4263-2024")</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 58408-2025</t>
+          <t>A 29061-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1408,14 +1408,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45985</v>
+        <v>46199</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1428,16 +1428,16 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>8.1</v>
+        <v>7.5</v>
       </c>
       <c r="J9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -1452,7 +1452,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -1461,270 +1461,270 @@
         <v>3</v>
       </c>
       <c r="T9" t="n">
+        <v>4</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Blåsippa
+Spillkråka
+Skogsödla</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 29061-2026 artfynd.xlsx", "A 29061-2026")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 29061-2026 karta.png", "A 29061-2026")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 29061-2026 georefererad karta.tif", "A 29061-2026")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 29061-2026 FSC-klagomål.docx", "A 29061-2026")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 29061-2026 FSC-klagomål mail.docx", "A 29061-2026")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 29061-2026 tillsynsbegäran.docx", "A 29061-2026")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 29061-2026 tillsynsbegäran mail.docx", "A 29061-2026")</f>
+        <v/>
+      </c>
+      <c r="AE9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 29061-2026 prioriterade fågelarter.docx", "A 29061-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 8558-2024</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>45355</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>KUNGÄLV</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="J10" t="n">
         <v>3</v>
       </c>
-      <c r="U9" t="n">
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
         <v>3</v>
       </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>3</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Gulsparv
+Spillkråka
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 8558-2024 artfynd.xlsx", "A 8558-2024")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 8558-2024 karta.png", "A 8558-2024")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 8558-2024 georefererad karta.tif", "A 8558-2024")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 8558-2024 FSC-klagomål.docx", "A 8558-2024")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 8558-2024 FSC-klagomål mail.docx", "A 8558-2024")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 8558-2024 tillsynsbegäran.docx", "A 8558-2024")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 8558-2024 tillsynsbegäran mail.docx", "A 8558-2024")</f>
+        <v/>
+      </c>
+      <c r="AE10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 8558-2024 prioriterade fågelarter.docx", "A 8558-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 58408-2025</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>45985</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>KUNGÄLV</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>3</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Älg
 Spillkråka
 Revlummer</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 58408-2025 artfynd.xlsx", "A 58408-2025")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 58408-2025 karta.png", "A 58408-2025")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 58408-2025 georefererad karta.tif", "A 58408-2025")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 58408-2025 FSC-klagomål.docx", "A 58408-2025")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 58408-2025 FSC-klagomål mail.docx", "A 58408-2025")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 58408-2025 tillsynsbegäran.docx", "A 58408-2025")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 58408-2025 tillsynsbegäran mail.docx", "A 58408-2025")</f>
         <v/>
       </c>
-      <c r="AE9">
+      <c r="AE11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 58408-2025 prioriterade fågelarter.docx", "A 58408-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 29061-2026</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>46199</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>KUNGÄLV</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="J10" t="n">
-        <v>3</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3</v>
-      </c>
-      <c r="T10" t="n">
-        <v>4</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Blåsippa
-Spillkråka
-Skogsödla</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 29061-2026 artfynd.xlsx", "A 29061-2026")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 29061-2026 karta.png", "A 29061-2026")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 29061-2026 georefererad karta.tif", "A 29061-2026")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 29061-2026 FSC-klagomål.docx", "A 29061-2026")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 29061-2026 FSC-klagomål mail.docx", "A 29061-2026")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 29061-2026 tillsynsbegäran.docx", "A 29061-2026")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 29061-2026 tillsynsbegäran mail.docx", "A 29061-2026")</f>
-        <v/>
-      </c>
-      <c r="AE10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 29061-2026 prioriterade fågelarter.docx", "A 29061-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 8558-2024</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>45355</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>KUNGÄLV</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="J11" t="n">
-        <v>3</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3</v>
-      </c>
-      <c r="T11" t="n">
-        <v>3</v>
-      </c>
-      <c r="U11" t="n">
-        <v>3</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Gulsparv
-Spillkråka
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 8558-2024 artfynd.xlsx", "A 8558-2024")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 8558-2024 karta.png", "A 8558-2024")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 8558-2024 georefererad karta.tif", "A 8558-2024")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 8558-2024 FSC-klagomål.docx", "A 8558-2024")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 8558-2024 FSC-klagomål mail.docx", "A 8558-2024")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 8558-2024 tillsynsbegäran.docx", "A 8558-2024")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 8558-2024 tillsynsbegäran mail.docx", "A 8558-2024")</f>
-        <v/>
-      </c>
-      <c r="AE11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 8558-2024 prioriterade fågelarter.docx", "A 8558-2024")</f>
         <v/>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
         <v>46212</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         <v>45957</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1970,7 +1970,7 @@
         <v>45974</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2059,7 +2059,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 57116-2025</t>
+          <t>A 30860-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2073,10 +2073,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45979</v>
+        <v>46212</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2089,7 +2089,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>3.5</v>
+        <v>1.7</v>
       </c>
       <c r="J15" t="n">
         <v>1</v>
@@ -2098,7 +2098,7 @@
         <v>1</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -2122,157 +2122,157 @@
         <v>2</v>
       </c>
       <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Grönsångare
+Västlig hakmossa</t>
+        </is>
+      </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 30860-2026 artfynd.xlsx", "A 30860-2026")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 30860-2026 karta.png", "A 30860-2026")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 30860-2026 georefererad karta.tif", "A 30860-2026")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 30860-2026 FSC-klagomål.docx", "A 30860-2026")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 30860-2026 FSC-klagomål mail.docx", "A 30860-2026")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 30860-2026 tillsynsbegäran.docx", "A 30860-2026")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 30860-2026 tillsynsbegäran mail.docx", "A 30860-2026")</f>
+        <v/>
+      </c>
+      <c r="AE15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 30860-2026 prioriterade fågelarter.docx", "A 30860-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 57116-2025</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>45979</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>KUNGÄLV</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2</v>
+      </c>
+      <c r="T16" t="n">
         <v>3</v>
       </c>
-      <c r="U15" t="n">
+      <c r="U16" t="n">
         <v>3</v>
       </c>
-      <c r="V15" s="2" t="inlineStr">
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>Västlig hakmossa
 Spillkråka</t>
         </is>
       </c>
-      <c r="W15">
+      <c r="W16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 57116-2025 artfynd.xlsx", "A 57116-2025")</f>
         <v/>
       </c>
-      <c r="X15">
+      <c r="X16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 57116-2025 karta.png", "A 57116-2025")</f>
         <v/>
       </c>
-      <c r="Y15">
+      <c r="Y16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 57116-2025 georefererad karta.tif", "A 57116-2025")</f>
         <v/>
       </c>
-      <c r="AA15">
+      <c r="AA16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 57116-2025 FSC-klagomål.docx", "A 57116-2025")</f>
         <v/>
       </c>
-      <c r="AB15">
+      <c r="AB16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 57116-2025 FSC-klagomål mail.docx", "A 57116-2025")</f>
         <v/>
       </c>
-      <c r="AC15">
+      <c r="AC16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 57116-2025 tillsynsbegäran.docx", "A 57116-2025")</f>
         <v/>
       </c>
-      <c r="AD15">
+      <c r="AD16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 57116-2025 tillsynsbegäran mail.docx", "A 57116-2025")</f>
         <v/>
       </c>
-      <c r="AE15">
+      <c r="AE16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 57116-2025 prioriterade fågelarter.docx", "A 57116-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 30860-2026</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>46212</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>KUNGÄLV</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="J16" t="n">
-        <v>1</v>
-      </c>
-      <c r="K16" t="n">
-        <v>1</v>
-      </c>
-      <c r="L16" t="n">
-        <v>1</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>Grönsångare
-Västlig hakmossa</t>
-        </is>
-      </c>
-      <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 30860-2026 artfynd.xlsx", "A 30860-2026")</f>
-        <v/>
-      </c>
-      <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 30860-2026 karta.png", "A 30860-2026")</f>
-        <v/>
-      </c>
-      <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 30860-2026 georefererad karta.tif", "A 30860-2026")</f>
-        <v/>
-      </c>
-      <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 30860-2026 FSC-klagomål.docx", "A 30860-2026")</f>
-        <v/>
-      </c>
-      <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 30860-2026 FSC-klagomål mail.docx", "A 30860-2026")</f>
-        <v/>
-      </c>
-      <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 30860-2026 tillsynsbegäran.docx", "A 30860-2026")</f>
-        <v/>
-      </c>
-      <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 30860-2026 tillsynsbegäran mail.docx", "A 30860-2026")</f>
-        <v/>
-      </c>
-      <c r="AE16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 30860-2026 prioriterade fågelarter.docx", "A 30860-2026")</f>
         <v/>
       </c>
     </row>
@@ -2296,7 +2296,7 @@
         <v>45957</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2406,7 +2406,7 @@
         <v>45334</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2512,7 +2512,7 @@
         <v>45334</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
         <v>44838</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2706,7 +2706,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 6082-2025</t>
+          <t>A 49988-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2720,10 +2720,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45697</v>
+        <v>45215</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="J21" t="n">
         <v>1</v>
@@ -2772,50 +2772,46 @@
         <v>1</v>
       </c>
       <c r="U21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 6082-2025 artfynd.xlsx", "A 6082-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 49988-2023 artfynd.xlsx", "A 49988-2023")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 6082-2025 karta.png", "A 6082-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 49988-2023 karta.png", "A 49988-2023")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 6082-2025 georefererad karta.tif", "A 6082-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 49988-2023 georefererad karta.tif", "A 49988-2023")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 6082-2025 FSC-klagomål.docx", "A 6082-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 49988-2023 FSC-klagomål.docx", "A 49988-2023")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 6082-2025 FSC-klagomål mail.docx", "A 6082-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 49988-2023 FSC-klagomål mail.docx", "A 49988-2023")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 6082-2025 tillsynsbegäran.docx", "A 6082-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 49988-2023 tillsynsbegäran.docx", "A 49988-2023")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 6082-2025 tillsynsbegäran mail.docx", "A 6082-2025")</f>
-        <v/>
-      </c>
-      <c r="AE21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 6082-2025 prioriterade fågelarter.docx", "A 6082-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 49988-2023 tillsynsbegäran mail.docx", "A 49988-2023")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 23704-2024</t>
+          <t>A 30862-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2829,10 +2825,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45454</v>
+        <v>46212</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2845,7 +2841,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>4.9</v>
+        <v>1.7</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
@@ -2857,7 +2853,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
@@ -2869,58 +2865,58 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
       </c>
       <c r="T22" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="U22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Hedjohannesört</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 23704-2024 artfynd.xlsx", "A 23704-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 30862-2026 artfynd.xlsx", "A 30862-2026")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 23704-2024 karta.png", "A 23704-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 30862-2026 karta.png", "A 30862-2026")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 23704-2024 georefererad karta.tif", "A 23704-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 30862-2026 georefererad karta.tif", "A 30862-2026")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 23704-2024 FSC-klagomål.docx", "A 23704-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 30862-2026 FSC-klagomål.docx", "A 30862-2026")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 23704-2024 FSC-klagomål mail.docx", "A 23704-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 30862-2026 FSC-klagomål mail.docx", "A 30862-2026")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 23704-2024 tillsynsbegäran.docx", "A 23704-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 30862-2026 tillsynsbegäran.docx", "A 30862-2026")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 23704-2024 tillsynsbegäran mail.docx", "A 23704-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 30862-2026 tillsynsbegäran mail.docx", "A 30862-2026")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 49988-2023</t>
+          <t>A 23704-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2934,10 +2930,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45215</v>
+        <v>45454</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2950,7 +2946,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>2.3</v>
+        <v>4.9</v>
       </c>
       <c r="J23" t="n">
         <v>1</v>
@@ -2962,7 +2958,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
@@ -2974,58 +2970,58 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
       </c>
       <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
         <v>1</v>
       </c>
-      <c r="U23" t="n">
-        <v>0</v>
-      </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Hedjohannesört</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 49988-2023 artfynd.xlsx", "A 49988-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 23704-2024 artfynd.xlsx", "A 23704-2024")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 49988-2023 karta.png", "A 49988-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 23704-2024 karta.png", "A 23704-2024")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 49988-2023 georefererad karta.tif", "A 49988-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 23704-2024 georefererad karta.tif", "A 23704-2024")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 49988-2023 FSC-klagomål.docx", "A 49988-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 23704-2024 FSC-klagomål.docx", "A 23704-2024")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 49988-2023 FSC-klagomål mail.docx", "A 49988-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 23704-2024 FSC-klagomål mail.docx", "A 23704-2024")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 49988-2023 tillsynsbegäran.docx", "A 49988-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 23704-2024 tillsynsbegäran.docx", "A 23704-2024")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 49988-2023 tillsynsbegäran mail.docx", "A 49988-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 23704-2024 tillsynsbegäran mail.docx", "A 23704-2024")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 30862-2026</t>
+          <t>A 6082-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3039,10 +3035,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46212</v>
+        <v>45697</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3055,7 +3051,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.7</v>
+        <v>2.8</v>
       </c>
       <c r="J24" t="n">
         <v>1</v>
@@ -3088,42 +3084,46 @@
         <v>1</v>
       </c>
       <c r="T24" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 30862-2026 artfynd.xlsx", "A 30862-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 6082-2025 artfynd.xlsx", "A 6082-2025")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 30862-2026 karta.png", "A 30862-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 6082-2025 karta.png", "A 6082-2025")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 30862-2026 georefererad karta.tif", "A 30862-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 6082-2025 georefererad karta.tif", "A 6082-2025")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 30862-2026 FSC-klagomål.docx", "A 30862-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 6082-2025 FSC-klagomål.docx", "A 6082-2025")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 30862-2026 FSC-klagomål mail.docx", "A 30862-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 6082-2025 FSC-klagomål mail.docx", "A 6082-2025")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 30862-2026 tillsynsbegäran.docx", "A 30862-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 6082-2025 tillsynsbegäran.docx", "A 6082-2025")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 30862-2026 tillsynsbegäran mail.docx", "A 30862-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 6082-2025 tillsynsbegäran mail.docx", "A 6082-2025")</f>
+        <v/>
+      </c>
+      <c r="AE24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 6082-2025 prioriterade fågelarter.docx", "A 6082-2025")</f>
         <v/>
       </c>
     </row>
@@ -3147,7 +3147,7 @@
         <v>44691</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
         <v>44691</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         <v>44836</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3366,7 +3366,7 @@
         <v>44459</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         <v>44459</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
         <v>44760</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3585,7 +3585,7 @@
         <v>44760</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3658,7 +3658,7 @@
         <v>44760</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3714,7 +3714,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 21240-2023</t>
+          <t>A 62221-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3728,10 +3728,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45058</v>
+        <v>45267</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3744,7 +3744,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>2.3</v>
+        <v>1.3</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3787,7 +3787,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 29223-2024</t>
+          <t>A 4204-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3801,10 +3801,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45482</v>
+        <v>45324</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3817,7 +3817,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>5.6</v>
+        <v>4.4</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3860,7 +3860,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 10655-2022</t>
+          <t>A 30170-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3874,10 +3874,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44624</v>
+        <v>44757</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3890,7 +3890,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>13.3</v>
+        <v>3.1</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3933,7 +3933,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 17455-2025</t>
+          <t>A 13880-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3947,10 +3947,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45757</v>
+        <v>45391</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3963,7 +3963,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4006,7 +4006,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 62221-2023</t>
+          <t>A 1995-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4020,10 +4020,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45267</v>
+        <v>45308</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4079,7 +4079,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 39714-2024</t>
+          <t>A 45990-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4093,10 +4093,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45552</v>
+        <v>44846</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4109,7 +4109,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.2</v>
+        <v>3.3</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4152,7 +4152,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 61417-2022</t>
+          <t>A 43520-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4166,10 +4166,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44916</v>
+        <v>44837</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4182,7 +4182,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>3.6</v>
+        <v>1.5</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4225,7 +4225,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 32272-2023</t>
+          <t>A 29223-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4239,10 +4239,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45120</v>
+        <v>45482</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4255,7 +4255,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>4.9</v>
+        <v>5.6</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4298,7 +4298,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 32847-2023</t>
+          <t>A 17922-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4312,10 +4312,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45124</v>
+        <v>45758</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4328,7 +4328,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>4.7</v>
+        <v>0.8</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4371,7 +4371,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 19531-2023</t>
+          <t>A 8334-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4385,10 +4385,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45050</v>
+        <v>44975</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4401,7 +4401,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4444,7 +4444,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 5705-2025</t>
+          <t>A 37443-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4454,14 +4454,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45694</v>
+        <v>45877</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4473,8 +4473,13 @@
           <t>KUNGÄLV</t>
         </is>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I43" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4517,7 +4522,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 40951-2025</t>
+          <t>A 13990-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4531,10 +4536,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45897</v>
+        <v>46098</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4547,7 +4552,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.8</v>
+        <v>2.6</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4590,7 +4595,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 7505-2024</t>
+          <t>A 34244-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4604,10 +4609,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45347</v>
+        <v>45844</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4620,7 +4625,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.8</v>
+        <v>2.9</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4663,7 +4668,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 45124-2025</t>
+          <t>A 25624-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4677,10 +4682,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45919</v>
+        <v>45803</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4693,7 +4698,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>3.7</v>
+        <v>5</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4736,7 +4741,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 8334-2023</t>
+          <t>A 41442-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4750,10 +4755,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44975</v>
+        <v>45869</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4809,7 +4814,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 34244-2025</t>
+          <t>A 4262-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4823,10 +4828,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45844</v>
+        <v>45324</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4839,7 +4844,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2.9</v>
+        <v>14</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4882,7 +4887,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 47564-2025</t>
+          <t>A 40951-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4896,10 +4901,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45931</v>
+        <v>45897</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4912,7 +4917,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4955,7 +4960,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 25624-2025</t>
+          <t>A 661-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4969,10 +4974,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45803</v>
+        <v>45664</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4985,7 +4990,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>5</v>
+        <v>3.1</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5028,7 +5033,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 41442-2025</t>
+          <t>A 49985-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5042,10 +5047,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45869</v>
+        <v>45215</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5058,7 +5063,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5101,7 +5106,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 34366-2022</t>
+          <t>A 45124-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5115,10 +5120,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44792</v>
+        <v>45919</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5131,7 +5136,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.5</v>
+        <v>3.7</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5174,7 +5179,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 4673-2026</t>
+          <t>A 50071-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5188,10 +5193,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46048</v>
+        <v>45215</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5204,7 +5209,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>8.199999999999999</v>
+        <v>4</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5247,7 +5252,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 17922-2025</t>
+          <t>A 24461-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5261,10 +5266,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45758</v>
+        <v>45082</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5277,7 +5282,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5320,7 +5325,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 52932-2025</t>
+          <t>A 143-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5334,10 +5339,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45957</v>
+        <v>44928</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5350,7 +5355,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>3.4</v>
+        <v>0.5</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5393,7 +5398,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 6946-2026</t>
+          <t>A 47564-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5403,14 +5408,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46057</v>
+        <v>45931</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5423,7 +5428,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5466,7 +5471,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 49981-2023</t>
+          <t>A 63319-2021</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5480,10 +5485,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45215</v>
+        <v>44508</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5496,7 +5501,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2.5</v>
+        <v>1.6</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5539,7 +5544,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 56782-2022</t>
+          <t>A 22731-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5553,10 +5558,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44894</v>
+        <v>46157</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5569,7 +5574,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5612,7 +5617,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 37443-2025</t>
+          <t>A 32391-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5626,10 +5631,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45877</v>
+        <v>45837</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5641,13 +5646,8 @@
           <t>KUNGÄLV</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I59" t="n">
-        <v>0.7</v>
+        <v>2.1</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5690,7 +5690,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 1995-2024</t>
+          <t>A 23607-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5704,10 +5704,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45308</v>
+        <v>46163</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5720,7 +5720,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.5</v>
+        <v>5.3</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5763,7 +5763,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 30170-2022</t>
+          <t>A 7505-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5777,10 +5777,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44757</v>
+        <v>45347</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5793,7 +5793,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>3.1</v>
+        <v>1.8</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5836,7 +5836,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 10810-2023</t>
+          <t>A 25135-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5850,10 +5850,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44989</v>
+        <v>45798</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5866,7 +5866,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5909,7 +5909,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 13990-2026</t>
+          <t>A 52932-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5923,10 +5923,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46098</v>
+        <v>45957</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5939,7 +5939,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>2.6</v>
+        <v>3.4</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5982,7 +5982,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 4204-2024</t>
+          <t>A 10655-2022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5996,10 +5996,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45324</v>
+        <v>44624</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6012,7 +6012,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>4.4</v>
+        <v>13.3</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6055,7 +6055,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 62128-2021</t>
+          <t>A 17455-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6069,10 +6069,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44502</v>
+        <v>45757</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6085,7 +6085,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6128,7 +6128,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 62979-2023</t>
+          <t>A 19531-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6138,14 +6138,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45271</v>
+        <v>45050</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6158,7 +6158,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.8</v>
+        <v>1.9</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6201,7 +6201,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 49985-2023</t>
+          <t>A 29952-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6215,10 +6215,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45215</v>
+        <v>46205</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6231,7 +6231,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>8.199999999999999</v>
+        <v>2</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6274,7 +6274,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 50071-2023</t>
+          <t>A 5705-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6284,14 +6284,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45215</v>
+        <v>45694</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6304,7 +6304,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>4</v>
+        <v>1.2</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6347,7 +6347,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 44176-2023</t>
+          <t>A 62979-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6357,14 +6357,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45188</v>
+        <v>45271</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6377,7 +6377,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>7.1</v>
+        <v>0.8</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6420,7 +6420,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 26812-2024</t>
+          <t>A 34386-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6434,10 +6434,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45470</v>
+        <v>46254</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6450,7 +6450,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.7</v>
+        <v>0.7</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6493,7 +6493,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 29801-2022</t>
+          <t>A 30738-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6507,10 +6507,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44755</v>
+        <v>46211</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6523,7 +6523,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>4.8</v>
+        <v>3.5</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6566,7 +6566,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 18852-2024</t>
+          <t>A 30859-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6580,10 +6580,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45426</v>
+        <v>46212</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6596,7 +6596,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>2.7</v>
+        <v>0.5</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6639,7 +6639,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 43520-2022</t>
+          <t>A 34387-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6653,10 +6653,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44837</v>
+        <v>46254</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6669,7 +6669,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6712,7 +6712,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 16538-2025</t>
+          <t>A 34396-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6726,10 +6726,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45751</v>
+        <v>46254</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6785,7 +6785,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 45990-2022</t>
+          <t>A 16538-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6799,10 +6799,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44846</v>
+        <v>45751</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6815,7 +6815,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>3.3</v>
+        <v>0.8</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6858,7 +6858,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 22731-2026</t>
+          <t>A 34392-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6872,10 +6872,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46157</v>
+        <v>46254</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6888,7 +6888,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.8</v>
+        <v>0.4</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6931,7 +6931,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 32391-2025</t>
+          <t>A 29801-2022</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6945,10 +6945,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45837</v>
+        <v>44755</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6961,7 +6961,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>2.1</v>
+        <v>4.8</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7004,7 +7004,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 23607-2026</t>
+          <t>A 49981-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7018,10 +7018,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46163</v>
+        <v>45215</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7034,7 +7034,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>5.3</v>
+        <v>2.5</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7077,7 +7077,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 143-2023</t>
+          <t>A 71835-2021</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7091,10 +7091,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44928</v>
+        <v>44543</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7107,7 +7107,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.5</v>
+        <v>7.5</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7150,7 +7150,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 25135-2025</t>
+          <t>A 38262-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7164,10 +7164,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45798</v>
+        <v>46281</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7180,7 +7180,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.1</v>
+        <v>2.8</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7223,7 +7223,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 18851-2024</t>
+          <t>A 56782-2022</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7237,10 +7237,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45426</v>
+        <v>44894</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7253,7 +7253,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>2.7</v>
+        <v>0.5</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7296,7 +7296,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 71835-2021</t>
+          <t>A 34366-2022</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7310,10 +7310,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44543</v>
+        <v>44792</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7326,7 +7326,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>7.5</v>
+        <v>0.5</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7369,7 +7369,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 51724-2023</t>
+          <t>A 26812-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7383,10 +7383,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45222</v>
+        <v>45470</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>3.1</v>
+        <v>1.7</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7442,7 +7442,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 661-2025</t>
+          <t>A 4673-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7456,10 +7456,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45664</v>
+        <v>46048</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7472,7 +7472,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>3.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7515,7 +7515,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 24461-2023</t>
+          <t>A 6946-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7525,14 +7525,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45082</v>
+        <v>46057</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7545,7 +7545,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7588,7 +7588,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 13880-2024</t>
+          <t>A 10810-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7602,10 +7602,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45391</v>
+        <v>44989</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7618,7 +7618,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>2.4</v>
+        <v>0.4</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7661,7 +7661,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 29952-2026</t>
+          <t>A 62128-2021</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7675,10 +7675,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46205</v>
+        <v>44502</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7691,7 +7691,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7734,7 +7734,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 34392-2026</t>
+          <t>A 21240-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7748,10 +7748,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>46254</v>
+        <v>45058</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7764,7 +7764,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0.4</v>
+        <v>2.3</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7807,7 +7807,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 34387-2026</t>
+          <t>A 18851-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7821,10 +7821,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46254</v>
+        <v>45426</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7837,7 +7837,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>0.3</v>
+        <v>2.7</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7880,7 +7880,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 34386-2026</t>
+          <t>A 21389-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7894,10 +7894,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46254</v>
+        <v>45063</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7910,7 +7910,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0.7</v>
+        <v>3.4</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7953,7 +7953,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 34396-2026</t>
+          <t>A 44176-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7967,10 +7967,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46254</v>
+        <v>45188</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7983,7 +7983,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.8</v>
+        <v>7.1</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8026,7 +8026,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 30738-2026</t>
+          <t>A 23457-2024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>46211</v>
+        <v>45453</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8056,7 +8056,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>3.5</v>
+        <v>5.1</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 30859-2026</t>
+          <t>A 39714-2024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8113,10 +8113,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>46212</v>
+        <v>45552</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8129,7 +8129,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8172,7 +8172,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 23457-2024</t>
+          <t>A 18852-2024</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8186,10 +8186,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45453</v>
+        <v>45426</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8202,7 +8202,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>5.1</v>
+        <v>2.7</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8245,7 +8245,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 21389-2023</t>
+          <t>A 51724-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8259,10 +8259,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45063</v>
+        <v>45222</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8275,7 +8275,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8318,7 +8318,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 4262-2024</t>
+          <t>A 10679-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8332,10 +8332,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45324</v>
+        <v>45721</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8348,7 +8348,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>14</v>
+        <v>4.4</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8391,7 +8391,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 63319-2021</t>
+          <t>A 11237-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8405,10 +8405,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>44508</v>
+        <v>45726</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8421,7 +8421,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1.6</v>
+        <v>4.2</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8464,7 +8464,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 38262-2026</t>
+          <t>A 10677-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8478,10 +8478,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>46281</v>
+        <v>45721</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8494,7 +8494,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>2.8</v>
+        <v>7.4</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8537,7 +8537,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 10677-2025</t>
+          <t>A 74285-2021</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8551,10 +8551,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45721</v>
+        <v>44558</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8567,7 +8567,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>7.4</v>
+        <v>1.1</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8610,7 +8610,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 10679-2025</t>
+          <t>A 61417-2022</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8624,10 +8624,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45721</v>
+        <v>44916</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8640,7 +8640,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>4.4</v>
+        <v>3.6</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8683,7 +8683,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 11237-2025</t>
+          <t>A 32272-2023</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8697,10 +8697,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45726</v>
+        <v>45120</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8713,7 +8713,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8756,7 +8756,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 74285-2021</t>
+          <t>A 32847-2023</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8770,10 +8770,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>44558</v>
+        <v>45124</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8786,7 +8786,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>1.1</v>
+        <v>4.7</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8846,7 +8846,7 @@
         <v>45371</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>

--- a/Översikt KUNGÄLV.xlsx
+++ b/Översikt KUNGÄLV.xlsx
@@ -601,7 +601,7 @@
         <v>45548</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>45868</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -851,7 +851,7 @@
         <v>45526</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -965,7 +965,7 @@
         <v>45919</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
         <v>45695</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 4263-2024</t>
+          <t>A 59985-2025</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1188,10 +1188,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45324</v>
+        <v>45993</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1204,16 +1204,16 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>2.6</v>
+        <v>5.3</v>
       </c>
       <c r="J7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -1228,7 +1228,7 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1237,12 +1237,124 @@
         <v>4</v>
       </c>
       <c r="T7" t="n">
+        <v>19</v>
+      </c>
+      <c r="U7" t="n">
+        <v>19</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Blåmossa
+Västlig hakmossa
+Spillkråka
+Äkta lopplummer</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 59985-2025 artfynd.xlsx", "A 59985-2025")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 59985-2025 karta.png", "A 59985-2025")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 59985-2025 georefererad karta.tif", "A 59985-2025")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 59985-2025 FSC-klagomål.docx", "A 59985-2025")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 59985-2025 FSC-klagomål mail.docx", "A 59985-2025")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 59985-2025 tillsynsbegäran.docx", "A 59985-2025")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 59985-2025 tillsynsbegäran mail.docx", "A 59985-2025")</f>
+        <v/>
+      </c>
+      <c r="AE7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 59985-2025 prioriterade fågelarter.docx", "A 59985-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 4263-2024</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>45324</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>KUNGÄLV</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J8" t="n">
+        <v>3</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>4</v>
+      </c>
+      <c r="T8" t="n">
         <v>6</v>
       </c>
-      <c r="U7" t="n">
+      <c r="U8" t="n">
         <v>6</v>
       </c>
-      <c r="V7" s="2" t="inlineStr">
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>Mindre hackspett
 Klippfrullania
@@ -1250,155 +1362,43 @@
 Spillkråka</t>
         </is>
       </c>
-      <c r="W7">
+      <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 4263-2024 artfynd.xlsx", "A 4263-2024")</f>
         <v/>
       </c>
-      <c r="X7">
+      <c r="X8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 4263-2024 karta.png", "A 4263-2024")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 4263-2024 georefererad karta.tif", "A 4263-2024")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 4263-2024 FSC-klagomål.docx", "A 4263-2024")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 4263-2024 FSC-klagomål mail.docx", "A 4263-2024")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 4263-2024 tillsynsbegäran.docx", "A 4263-2024")</f>
         <v/>
       </c>
-      <c r="AD7">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 4263-2024 tillsynsbegäran mail.docx", "A 4263-2024")</f>
         <v/>
       </c>
-      <c r="AE7">
+      <c r="AE8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 4263-2024 prioriterade fågelarter.docx", "A 4263-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A 59985-2025</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>45993</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>KUNGÄLV</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="J8" t="n">
-        <v>2</v>
-      </c>
-      <c r="K8" t="n">
-        <v>2</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>4</v>
-      </c>
-      <c r="T8" t="n">
-        <v>19</v>
-      </c>
-      <c r="U8" t="n">
-        <v>19</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>Blåmossa
-Västlig hakmossa
-Spillkråka
-Äkta lopplummer</t>
-        </is>
-      </c>
-      <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 59985-2025 artfynd.xlsx", "A 59985-2025")</f>
-        <v/>
-      </c>
-      <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 59985-2025 karta.png", "A 59985-2025")</f>
-        <v/>
-      </c>
-      <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 59985-2025 georefererad karta.tif", "A 59985-2025")</f>
-        <v/>
-      </c>
-      <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 59985-2025 FSC-klagomål.docx", "A 59985-2025")</f>
-        <v/>
-      </c>
-      <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 59985-2025 FSC-klagomål mail.docx", "A 59985-2025")</f>
-        <v/>
-      </c>
-      <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 59985-2025 tillsynsbegäran.docx", "A 59985-2025")</f>
-        <v/>
-      </c>
-      <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 59985-2025 tillsynsbegäran mail.docx", "A 59985-2025")</f>
-        <v/>
-      </c>
-      <c r="AE8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 59985-2025 prioriterade fågelarter.docx", "A 59985-2025")</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 29061-2026</t>
+          <t>A 58408-2025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1408,14 +1408,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46199</v>
+        <v>45985</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1428,16 +1428,16 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>7.5</v>
+        <v>8.1</v>
       </c>
       <c r="J9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -1452,7 +1452,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -1461,270 +1461,270 @@
         <v>3</v>
       </c>
       <c r="T9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>3</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Älg
+Spillkråka
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 58408-2025 artfynd.xlsx", "A 58408-2025")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 58408-2025 karta.png", "A 58408-2025")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 58408-2025 georefererad karta.tif", "A 58408-2025")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 58408-2025 FSC-klagomål.docx", "A 58408-2025")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 58408-2025 FSC-klagomål mail.docx", "A 58408-2025")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 58408-2025 tillsynsbegäran.docx", "A 58408-2025")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 58408-2025 tillsynsbegäran mail.docx", "A 58408-2025")</f>
+        <v/>
+      </c>
+      <c r="AE9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 58408-2025 prioriterade fågelarter.docx", "A 58408-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 29061-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>46199</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>KUNGÄLV</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3</v>
+      </c>
+      <c r="T10" t="n">
         <v>4</v>
       </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Blåsippa
 Spillkråka
 Skogsödla</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 29061-2026 artfynd.xlsx", "A 29061-2026")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 29061-2026 karta.png", "A 29061-2026")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 29061-2026 georefererad karta.tif", "A 29061-2026")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 29061-2026 FSC-klagomål.docx", "A 29061-2026")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 29061-2026 FSC-klagomål mail.docx", "A 29061-2026")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 29061-2026 tillsynsbegäran.docx", "A 29061-2026")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 29061-2026 tillsynsbegäran mail.docx", "A 29061-2026")</f>
         <v/>
       </c>
-      <c r="AE9">
+      <c r="AE10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 29061-2026 prioriterade fågelarter.docx", "A 29061-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
         <is>
           <t>A 8558-2024</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
         <v>45355</v>
       </c>
-      <c r="E10" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>KUNGÄLV</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
+      <c r="E11" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>KUNGÄLV</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
         <v>12.5</v>
       </c>
-      <c r="J10" t="n">
+      <c r="J11" t="n">
         <v>3</v>
       </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
         <v>1</v>
       </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
         <v>1</v>
       </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
         <v>3</v>
       </c>
-      <c r="T10" t="n">
+      <c r="T11" t="n">
         <v>3</v>
       </c>
-      <c r="U10" t="n">
+      <c r="U11" t="n">
         <v>3</v>
       </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Gulsparv
 Spillkråka
 Revlummer</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 8558-2024 artfynd.xlsx", "A 8558-2024")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 8558-2024 karta.png", "A 8558-2024")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 8558-2024 georefererad karta.tif", "A 8558-2024")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 8558-2024 FSC-klagomål.docx", "A 8558-2024")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 8558-2024 FSC-klagomål mail.docx", "A 8558-2024")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 8558-2024 tillsynsbegäran.docx", "A 8558-2024")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 8558-2024 tillsynsbegäran mail.docx", "A 8558-2024")</f>
         <v/>
       </c>
-      <c r="AE10">
+      <c r="AE11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 8558-2024 prioriterade fågelarter.docx", "A 8558-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 58408-2025</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>45985</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>KUNGÄLV</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="J11" t="n">
-        <v>2</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3</v>
-      </c>
-      <c r="T11" t="n">
-        <v>3</v>
-      </c>
-      <c r="U11" t="n">
-        <v>3</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Älg
-Spillkråka
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 58408-2025 artfynd.xlsx", "A 58408-2025")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 58408-2025 karta.png", "A 58408-2025")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 58408-2025 georefererad karta.tif", "A 58408-2025")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 58408-2025 FSC-klagomål.docx", "A 58408-2025")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 58408-2025 FSC-klagomål mail.docx", "A 58408-2025")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 58408-2025 tillsynsbegäran.docx", "A 58408-2025")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 58408-2025 tillsynsbegäran mail.docx", "A 58408-2025")</f>
-        <v/>
-      </c>
-      <c r="AE11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 58408-2025 prioriterade fågelarter.docx", "A 58408-2025")</f>
         <v/>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
         <v>46212</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         <v>45957</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1970,7 +1970,7 @@
         <v>45974</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2059,7 +2059,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 30860-2026</t>
+          <t>A 57116-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2073,10 +2073,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46212</v>
+        <v>45979</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2089,7 +2089,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.7</v>
+        <v>3.5</v>
       </c>
       <c r="J15" t="n">
         <v>1</v>
@@ -2098,7 +2098,7 @@
         <v>1</v>
       </c>
       <c r="L15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -2122,479 +2122,479 @@
         <v>2</v>
       </c>
       <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>3</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Västlig hakmossa
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 57116-2025 artfynd.xlsx", "A 57116-2025")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 57116-2025 karta.png", "A 57116-2025")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 57116-2025 georefererad karta.tif", "A 57116-2025")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 57116-2025 FSC-klagomål.docx", "A 57116-2025")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 57116-2025 FSC-klagomål mail.docx", "A 57116-2025")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 57116-2025 tillsynsbegäran.docx", "A 57116-2025")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 57116-2025 tillsynsbegäran mail.docx", "A 57116-2025")</f>
+        <v/>
+      </c>
+      <c r="AE15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 57116-2025 prioriterade fågelarter.docx", "A 57116-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 30860-2026</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>46212</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>KUNGÄLV</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
         <v>2</v>
       </c>
-      <c r="U15" t="n">
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
         <v>1</v>
       </c>
-      <c r="V15" s="2" t="inlineStr">
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>Grönsångare
 Västlig hakmossa</t>
         </is>
       </c>
-      <c r="W15">
+      <c r="W16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 30860-2026 artfynd.xlsx", "A 30860-2026")</f>
         <v/>
       </c>
-      <c r="X15">
+      <c r="X16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 30860-2026 karta.png", "A 30860-2026")</f>
         <v/>
       </c>
-      <c r="Y15">
+      <c r="Y16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 30860-2026 georefererad karta.tif", "A 30860-2026")</f>
         <v/>
       </c>
-      <c r="AA15">
+      <c r="AA16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 30860-2026 FSC-klagomål.docx", "A 30860-2026")</f>
         <v/>
       </c>
-      <c r="AB15">
+      <c r="AB16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 30860-2026 FSC-klagomål mail.docx", "A 30860-2026")</f>
         <v/>
       </c>
-      <c r="AC15">
+      <c r="AC16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 30860-2026 tillsynsbegäran.docx", "A 30860-2026")</f>
         <v/>
       </c>
-      <c r="AD15">
+      <c r="AD16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 30860-2026 tillsynsbegäran mail.docx", "A 30860-2026")</f>
         <v/>
       </c>
-      <c r="AE15">
+      <c r="AE16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 30860-2026 prioriterade fågelarter.docx", "A 30860-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 57116-2025</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>45979</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>KUNGÄLV</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="J16" t="n">
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 5631-2024</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>45334</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>KUNGÄLV</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
         <v>1</v>
       </c>
-      <c r="K16" t="n">
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>Vanlig groda
+Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="W17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 5631-2024 artfynd.xlsx", "A 5631-2024")</f>
+        <v/>
+      </c>
+      <c r="X17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 5631-2024 karta.png", "A 5631-2024")</f>
+        <v/>
+      </c>
+      <c r="Y17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 5631-2024 georefererad karta.tif", "A 5631-2024")</f>
+        <v/>
+      </c>
+      <c r="AA17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 5631-2024 FSC-klagomål.docx", "A 5631-2024")</f>
+        <v/>
+      </c>
+      <c r="AB17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 5631-2024 FSC-klagomål mail.docx", "A 5631-2024")</f>
+        <v/>
+      </c>
+      <c r="AC17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 5631-2024 tillsynsbegäran.docx", "A 5631-2024")</f>
+        <v/>
+      </c>
+      <c r="AD17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 5631-2024 tillsynsbegäran mail.docx", "A 5631-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>A 5637-2024</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>45334</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>KUNGÄLV</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>2</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>Klofibbla
+Åkerrödtoppa</t>
+        </is>
+      </c>
+      <c r="W18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 5637-2024 artfynd.xlsx", "A 5637-2024")</f>
+        <v/>
+      </c>
+      <c r="X18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 5637-2024 karta.png", "A 5637-2024")</f>
+        <v/>
+      </c>
+      <c r="Y18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 5637-2024 georefererad karta.tif", "A 5637-2024")</f>
+        <v/>
+      </c>
+      <c r="AA18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 5637-2024 FSC-klagomål.docx", "A 5637-2024")</f>
+        <v/>
+      </c>
+      <c r="AB18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 5637-2024 FSC-klagomål mail.docx", "A 5637-2024")</f>
+        <v/>
+      </c>
+      <c r="AC18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 5637-2024 tillsynsbegäran.docx", "A 5637-2024")</f>
+        <v/>
+      </c>
+      <c r="AD18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 5637-2024 tillsynsbegäran mail.docx", "A 5637-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>A 53007-2025</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>45957</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>KUNGÄLV</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J19" t="n">
         <v>1</v>
       </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
+      <c r="K19" t="n">
+        <v>1</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
         <v>2</v>
       </c>
-      <c r="T16" t="n">
-        <v>3</v>
-      </c>
-      <c r="U16" t="n">
-        <v>3</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
+      <c r="T19" t="n">
+        <v>5</v>
+      </c>
+      <c r="U19" t="n">
+        <v>5</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>Västlig hakmossa
 Spillkråka</t>
         </is>
       </c>
-      <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 57116-2025 artfynd.xlsx", "A 57116-2025")</f>
-        <v/>
-      </c>
-      <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 57116-2025 karta.png", "A 57116-2025")</f>
-        <v/>
-      </c>
-      <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 57116-2025 georefererad karta.tif", "A 57116-2025")</f>
-        <v/>
-      </c>
-      <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 57116-2025 FSC-klagomål.docx", "A 57116-2025")</f>
-        <v/>
-      </c>
-      <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 57116-2025 FSC-klagomål mail.docx", "A 57116-2025")</f>
-        <v/>
-      </c>
-      <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 57116-2025 tillsynsbegäran.docx", "A 57116-2025")</f>
-        <v/>
-      </c>
-      <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 57116-2025 tillsynsbegäran mail.docx", "A 57116-2025")</f>
-        <v/>
-      </c>
-      <c r="AE16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 57116-2025 prioriterade fågelarter.docx", "A 57116-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 53007-2025</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>45957</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>KUNGÄLV</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="J17" t="n">
-        <v>1</v>
-      </c>
-      <c r="K17" t="n">
-        <v>1</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2</v>
-      </c>
-      <c r="T17" t="n">
-        <v>5</v>
-      </c>
-      <c r="U17" t="n">
-        <v>5</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Västlig hakmossa
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W17">
+      <c r="W19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 53007-2025 artfynd.xlsx", "A 53007-2025")</f>
         <v/>
       </c>
-      <c r="X17">
+      <c r="X19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 53007-2025 karta.png", "A 53007-2025")</f>
         <v/>
       </c>
-      <c r="Y17">
+      <c r="Y19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 53007-2025 georefererad karta.tif", "A 53007-2025")</f>
         <v/>
       </c>
-      <c r="AA17">
+      <c r="AA19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 53007-2025 FSC-klagomål.docx", "A 53007-2025")</f>
         <v/>
       </c>
-      <c r="AB17">
+      <c r="AB19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 53007-2025 FSC-klagomål mail.docx", "A 53007-2025")</f>
         <v/>
       </c>
-      <c r="AC17">
+      <c r="AC19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 53007-2025 tillsynsbegäran.docx", "A 53007-2025")</f>
         <v/>
       </c>
-      <c r="AD17">
+      <c r="AD19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 53007-2025 tillsynsbegäran mail.docx", "A 53007-2025")</f>
         <v/>
       </c>
-      <c r="AE17">
+      <c r="AE19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 53007-2025 prioriterade fågelarter.docx", "A 53007-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 5631-2024</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>45334</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>KUNGÄLV</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="J18" t="n">
-        <v>2</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>Vanlig groda
-Fläcknycklar</t>
-        </is>
-      </c>
-      <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 5631-2024 artfynd.xlsx", "A 5631-2024")</f>
-        <v/>
-      </c>
-      <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 5631-2024 karta.png", "A 5631-2024")</f>
-        <v/>
-      </c>
-      <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 5631-2024 georefererad karta.tif", "A 5631-2024")</f>
-        <v/>
-      </c>
-      <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 5631-2024 FSC-klagomål.docx", "A 5631-2024")</f>
-        <v/>
-      </c>
-      <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 5631-2024 FSC-klagomål mail.docx", "A 5631-2024")</f>
-        <v/>
-      </c>
-      <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 5631-2024 tillsynsbegäran.docx", "A 5631-2024")</f>
-        <v/>
-      </c>
-      <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 5631-2024 tillsynsbegäran mail.docx", "A 5631-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>A 5637-2024</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>45334</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>KUNGÄLV</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>2</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>2</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>Klofibbla
-Åkerrödtoppa</t>
-        </is>
-      </c>
-      <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 5637-2024 artfynd.xlsx", "A 5637-2024")</f>
-        <v/>
-      </c>
-      <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 5637-2024 karta.png", "A 5637-2024")</f>
-        <v/>
-      </c>
-      <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 5637-2024 georefererad karta.tif", "A 5637-2024")</f>
-        <v/>
-      </c>
-      <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 5637-2024 FSC-klagomål.docx", "A 5637-2024")</f>
-        <v/>
-      </c>
-      <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 5637-2024 FSC-klagomål mail.docx", "A 5637-2024")</f>
-        <v/>
-      </c>
-      <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 5637-2024 tillsynsbegäran.docx", "A 5637-2024")</f>
-        <v/>
-      </c>
-      <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 5637-2024 tillsynsbegäran mail.docx", "A 5637-2024")</f>
         <v/>
       </c>
     </row>
@@ -2618,7 +2618,7 @@
         <v>44838</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2706,7 +2706,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 49988-2023</t>
+          <t>A 23704-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2720,10 +2720,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45215</v>
+        <v>45454</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>2.3</v>
+        <v>4.9</v>
       </c>
       <c r="J21" t="n">
         <v>1</v>
@@ -2748,7 +2748,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -2760,58 +2760,58 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
       </c>
       <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
         <v>1</v>
       </c>
-      <c r="U21" t="n">
-        <v>0</v>
-      </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Hedjohannesört</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 49988-2023 artfynd.xlsx", "A 49988-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 23704-2024 artfynd.xlsx", "A 23704-2024")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 49988-2023 karta.png", "A 49988-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 23704-2024 karta.png", "A 23704-2024")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 49988-2023 georefererad karta.tif", "A 49988-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 23704-2024 georefererad karta.tif", "A 23704-2024")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 49988-2023 FSC-klagomål.docx", "A 49988-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 23704-2024 FSC-klagomål.docx", "A 23704-2024")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 49988-2023 FSC-klagomål mail.docx", "A 49988-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 23704-2024 FSC-klagomål mail.docx", "A 23704-2024")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 49988-2023 tillsynsbegäran.docx", "A 49988-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 23704-2024 tillsynsbegäran.docx", "A 23704-2024")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 49988-2023 tillsynsbegäran mail.docx", "A 49988-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 23704-2024 tillsynsbegäran mail.docx", "A 23704-2024")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 30862-2026</t>
+          <t>A 49988-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2825,10 +2825,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46212</v>
+        <v>45215</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2841,7 +2841,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
@@ -2874,49 +2874,49 @@
         <v>1</v>
       </c>
       <c r="T22" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U22" t="n">
         <v>0</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 30862-2026 artfynd.xlsx", "A 30862-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 49988-2023 artfynd.xlsx", "A 49988-2023")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 30862-2026 karta.png", "A 30862-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 49988-2023 karta.png", "A 49988-2023")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 30862-2026 georefererad karta.tif", "A 30862-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 49988-2023 georefererad karta.tif", "A 49988-2023")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 30862-2026 FSC-klagomål.docx", "A 30862-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 49988-2023 FSC-klagomål.docx", "A 49988-2023")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 30862-2026 FSC-klagomål mail.docx", "A 30862-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 49988-2023 FSC-klagomål mail.docx", "A 49988-2023")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 30862-2026 tillsynsbegäran.docx", "A 30862-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 49988-2023 tillsynsbegäran.docx", "A 49988-2023")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 30862-2026 tillsynsbegäran mail.docx", "A 30862-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 49988-2023 tillsynsbegäran mail.docx", "A 49988-2023")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 23704-2024</t>
+          <t>A 30862-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2930,10 +2930,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45454</v>
+        <v>46212</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2946,7 +2946,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>4.9</v>
+        <v>1.7</v>
       </c>
       <c r="J23" t="n">
         <v>1</v>
@@ -2958,7 +2958,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
@@ -2970,51 +2970,51 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
       </c>
       <c r="T23" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="U23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Hedjohannesört</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 23704-2024 artfynd.xlsx", "A 23704-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 30862-2026 artfynd.xlsx", "A 30862-2026")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 23704-2024 karta.png", "A 23704-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 30862-2026 karta.png", "A 30862-2026")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 23704-2024 georefererad karta.tif", "A 23704-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 30862-2026 georefererad karta.tif", "A 30862-2026")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 23704-2024 FSC-klagomål.docx", "A 23704-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 30862-2026 FSC-klagomål.docx", "A 30862-2026")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 23704-2024 FSC-klagomål mail.docx", "A 23704-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 30862-2026 FSC-klagomål mail.docx", "A 30862-2026")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 23704-2024 tillsynsbegäran.docx", "A 23704-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 30862-2026 tillsynsbegäran.docx", "A 30862-2026")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 23704-2024 tillsynsbegäran mail.docx", "A 23704-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 30862-2026 tillsynsbegäran mail.docx", "A 30862-2026")</f>
         <v/>
       </c>
     </row>
@@ -3038,7 +3038,7 @@
         <v>45697</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>44691</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
         <v>44691</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         <v>44836</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3366,7 +3366,7 @@
         <v>44459</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         <v>44459</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
         <v>44760</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3585,7 +3585,7 @@
         <v>44760</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3658,7 +3658,7 @@
         <v>44760</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3714,7 +3714,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 62221-2023</t>
+          <t>A 17455-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3728,10 +3728,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45267</v>
+        <v>45757</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3744,7 +3744,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.3</v>
+        <v>2.1</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3787,7 +3787,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 4204-2024</t>
+          <t>A 62221-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3801,10 +3801,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45324</v>
+        <v>45267</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3817,7 +3817,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>4.4</v>
+        <v>1.3</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3860,7 +3860,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 30170-2022</t>
+          <t>A 21240-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3874,10 +3874,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44757</v>
+        <v>45058</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3890,7 +3890,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>3.1</v>
+        <v>2.3</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3933,7 +3933,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 13880-2024</t>
+          <t>A 29223-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3947,10 +3947,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45391</v>
+        <v>45482</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3963,7 +3963,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2.4</v>
+        <v>5.6</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4006,7 +4006,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 1995-2024</t>
+          <t>A 10655-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4020,10 +4020,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45308</v>
+        <v>44624</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.5</v>
+        <v>13.3</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4079,7 +4079,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 45990-2022</t>
+          <t>A 39714-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4093,10 +4093,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44846</v>
+        <v>45552</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4109,7 +4109,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>3.3</v>
+        <v>1.2</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4152,7 +4152,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 43520-2022</t>
+          <t>A 19531-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4166,10 +4166,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44837</v>
+        <v>45050</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4182,7 +4182,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4225,7 +4225,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 29223-2024</t>
+          <t>A 5705-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4235,14 +4235,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45482</v>
+        <v>45694</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4255,7 +4255,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>5.6</v>
+        <v>1.2</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4298,7 +4298,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 17922-2025</t>
+          <t>A 7505-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4312,10 +4312,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45758</v>
+        <v>45347</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4328,7 +4328,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.8</v>
+        <v>1.8</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4388,7 +4388,7 @@
         <v>44975</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4444,7 +4444,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 37443-2025</t>
+          <t>A 50071-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4458,10 +4458,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45877</v>
+        <v>45215</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4473,13 +4473,8 @@
           <t>KUNGÄLV</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I43" t="n">
-        <v>0.7</v>
+        <v>4</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4522,7 +4517,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 13990-2026</t>
+          <t>A 40951-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4536,10 +4531,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46098</v>
+        <v>45897</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4552,7 +4547,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2.6</v>
+        <v>0.8</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4595,7 +4590,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 34244-2025</t>
+          <t>A 49981-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4609,10 +4604,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45844</v>
+        <v>45215</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4625,7 +4620,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4668,7 +4663,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 25624-2025</t>
+          <t>A 56782-2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4682,10 +4677,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45803</v>
+        <v>44894</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4698,7 +4693,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4741,7 +4736,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 41442-2025</t>
+          <t>A 1995-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4755,10 +4750,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45869</v>
+        <v>45308</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4771,7 +4766,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4814,7 +4809,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 4262-2024</t>
+          <t>A 30170-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4828,10 +4823,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45324</v>
+        <v>44757</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4844,7 +4839,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>14</v>
+        <v>3.1</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4887,7 +4882,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 40951-2025</t>
+          <t>A 10810-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4901,10 +4896,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45897</v>
+        <v>44989</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4917,7 +4912,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4960,7 +4955,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 661-2025</t>
+          <t>A 45124-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4974,10 +4969,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45664</v>
+        <v>45919</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4990,7 +4985,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5033,7 +5028,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 49985-2023</t>
+          <t>A 4204-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5047,10 +5042,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45215</v>
+        <v>45324</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5063,7 +5058,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>8.199999999999999</v>
+        <v>4.4</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5106,7 +5101,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 45124-2025</t>
+          <t>A 47564-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5120,10 +5115,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45919</v>
+        <v>45931</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5136,7 +5131,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>3.7</v>
+        <v>2</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5179,7 +5174,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 50071-2023</t>
+          <t>A 62128-2021</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5193,10 +5188,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45215</v>
+        <v>44502</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5209,7 +5204,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>4</v>
+        <v>1.8</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5252,7 +5247,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 24461-2023</t>
+          <t>A 62979-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5262,14 +5257,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45082</v>
+        <v>45271</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5282,7 +5277,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5325,7 +5320,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 143-2023</t>
+          <t>A 52932-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5339,10 +5334,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44928</v>
+        <v>45957</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5355,7 +5350,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.5</v>
+        <v>3.4</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5398,7 +5393,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 47564-2025</t>
+          <t>A 44176-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5412,10 +5407,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45931</v>
+        <v>45188</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5428,7 +5423,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>2</v>
+        <v>7.1</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5471,7 +5466,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 63319-2021</t>
+          <t>A 26812-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5485,10 +5480,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44508</v>
+        <v>45470</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5501,7 +5496,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5561,7 +5556,7 @@
         <v>46157</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5634,7 +5629,7 @@
         <v>45837</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5690,7 +5685,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 23607-2026</t>
+          <t>A 29801-2022</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5704,10 +5699,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46163</v>
+        <v>44755</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5720,7 +5715,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>5.3</v>
+        <v>4.8</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5763,7 +5758,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 7505-2024</t>
+          <t>A 18852-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5777,10 +5772,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45347</v>
+        <v>45426</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5793,7 +5788,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.8</v>
+        <v>2.7</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5836,7 +5831,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 25135-2025</t>
+          <t>A 23607-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5850,10 +5845,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45798</v>
+        <v>46163</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5866,7 +5861,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.1</v>
+        <v>5.3</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5909,7 +5904,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 52932-2025</t>
+          <t>A 43520-2022</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5923,10 +5918,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45957</v>
+        <v>44837</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5939,7 +5934,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>3.4</v>
+        <v>1.5</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5982,7 +5977,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 10655-2022</t>
+          <t>A 25135-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5996,10 +5991,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44624</v>
+        <v>45798</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6012,7 +6007,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>13.3</v>
+        <v>1.1</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6055,7 +6050,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 17455-2025</t>
+          <t>A 16538-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6069,10 +6064,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45757</v>
+        <v>45751</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6085,7 +6080,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>2.1</v>
+        <v>0.8</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6128,7 +6123,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 19531-2023</t>
+          <t>A 45990-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6142,10 +6137,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45050</v>
+        <v>44846</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6158,7 +6153,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.9</v>
+        <v>3.3</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6201,7 +6196,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 29952-2026</t>
+          <t>A 143-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6215,10 +6210,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46205</v>
+        <v>44928</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6231,7 +6226,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6274,7 +6269,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 5705-2025</t>
+          <t>A 34366-2022</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6284,14 +6279,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45694</v>
+        <v>44792</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6304,7 +6299,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6347,7 +6342,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 62979-2023</t>
+          <t>A 18851-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6357,14 +6352,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45271</v>
+        <v>45426</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6377,7 +6372,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.8</v>
+        <v>2.7</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6420,7 +6415,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 34386-2026</t>
+          <t>A 71835-2021</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6434,10 +6429,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46254</v>
+        <v>44543</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6450,7 +6445,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.7</v>
+        <v>7.5</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6493,7 +6488,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 30738-2026</t>
+          <t>A 4673-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6507,10 +6502,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46211</v>
+        <v>46048</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6523,7 +6518,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>3.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6566,7 +6561,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 30859-2026</t>
+          <t>A 6946-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6576,14 +6571,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46212</v>
+        <v>46057</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6596,7 +6591,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.5</v>
+        <v>2.2</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6639,7 +6634,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 34387-2026</t>
+          <t>A 51724-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6653,10 +6648,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46254</v>
+        <v>45222</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6669,7 +6664,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.3</v>
+        <v>3.1</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6712,7 +6707,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 34396-2026</t>
+          <t>A 37443-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6726,10 +6721,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46254</v>
+        <v>45877</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6741,8 +6736,13 @@
           <t>KUNGÄLV</t>
         </is>
       </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I74" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6785,7 +6785,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 16538-2025</t>
+          <t>A 13990-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6799,10 +6799,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45751</v>
+        <v>46098</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6815,7 +6815,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.8</v>
+        <v>2.6</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6858,7 +6858,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 34392-2026</t>
+          <t>A 661-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6872,10 +6872,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46254</v>
+        <v>45664</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6888,7 +6888,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.4</v>
+        <v>3.1</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6931,7 +6931,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 29801-2022</t>
+          <t>A 24461-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6945,10 +6945,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44755</v>
+        <v>45082</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6961,7 +6961,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>4.8</v>
+        <v>1.5</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7004,7 +7004,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 49981-2023</t>
+          <t>A 13880-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7018,10 +7018,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45215</v>
+        <v>45391</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7034,7 +7034,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7077,7 +7077,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 71835-2021</t>
+          <t>A 49985-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7091,10 +7091,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44543</v>
+        <v>45215</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7107,7 +7107,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>7.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7150,7 +7150,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 38262-2026</t>
+          <t>A 23457-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7164,10 +7164,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46281</v>
+        <v>45453</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7180,7 +7180,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>2.8</v>
+        <v>5.1</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7223,7 +7223,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 56782-2022</t>
+          <t>A 29952-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7237,10 +7237,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44894</v>
+        <v>46205</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7253,7 +7253,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7296,7 +7296,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 34366-2022</t>
+          <t>A 21389-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7310,10 +7310,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44792</v>
+        <v>45063</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7326,7 +7326,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.5</v>
+        <v>3.4</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7369,7 +7369,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 26812-2024</t>
+          <t>A 4262-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7383,10 +7383,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45470</v>
+        <v>45324</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.7</v>
+        <v>14</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7442,7 +7442,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 4673-2026</t>
+          <t>A 34392-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7456,10 +7456,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46048</v>
+        <v>46254</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7472,7 +7472,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>8.199999999999999</v>
+        <v>0.4</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7515,7 +7515,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 6946-2026</t>
+          <t>A 34387-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7525,14 +7525,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46057</v>
+        <v>46254</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7545,7 +7545,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>2.2</v>
+        <v>0.3</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7588,7 +7588,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 10810-2023</t>
+          <t>A 34386-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7602,10 +7602,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44989</v>
+        <v>46254</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7618,7 +7618,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7661,7 +7661,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 62128-2021</t>
+          <t>A 34396-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7675,10 +7675,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>44502</v>
+        <v>46254</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7691,7 +7691,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7734,7 +7734,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 21240-2023</t>
+          <t>A 30738-2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7748,10 +7748,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45058</v>
+        <v>46211</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7764,7 +7764,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>2.3</v>
+        <v>3.5</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7807,7 +7807,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 18851-2024</t>
+          <t>A 30859-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7821,10 +7821,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45426</v>
+        <v>46212</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7837,7 +7837,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>2.7</v>
+        <v>0.5</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7880,7 +7880,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 21389-2023</t>
+          <t>A 63319-2021</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7894,10 +7894,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45063</v>
+        <v>44508</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7910,7 +7910,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>3.4</v>
+        <v>1.6</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7953,7 +7953,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 44176-2023</t>
+          <t>A 38262-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7967,10 +7967,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45188</v>
+        <v>46281</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7983,7 +7983,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>7.1</v>
+        <v>2.8</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8026,7 +8026,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 23457-2024</t>
+          <t>A 10677-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45453</v>
+        <v>45721</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8056,7 +8056,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>5.1</v>
+        <v>7.4</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 39714-2024</t>
+          <t>A 10679-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8113,10 +8113,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45552</v>
+        <v>45721</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8129,7 +8129,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1.2</v>
+        <v>4.4</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8172,7 +8172,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 18852-2024</t>
+          <t>A 11237-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8186,10 +8186,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45426</v>
+        <v>45726</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8202,7 +8202,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>2.7</v>
+        <v>4.2</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8245,7 +8245,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 51724-2023</t>
+          <t>A 74285-2021</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8259,10 +8259,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45222</v>
+        <v>44558</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8275,7 +8275,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>3.1</v>
+        <v>1.1</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8318,7 +8318,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 10679-2025</t>
+          <t>A 61417-2022</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8332,10 +8332,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45721</v>
+        <v>44916</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8348,7 +8348,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>4.4</v>
+        <v>3.6</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8391,7 +8391,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 11237-2025</t>
+          <t>A 32272-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8405,10 +8405,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45726</v>
+        <v>45120</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8421,7 +8421,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8464,7 +8464,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 10677-2025</t>
+          <t>A 32847-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8478,10 +8478,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45721</v>
+        <v>45124</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8494,7 +8494,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>7.4</v>
+        <v>4.7</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8537,7 +8537,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 74285-2021</t>
+          <t>A 34244-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8551,10 +8551,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>44558</v>
+        <v>45844</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8567,7 +8567,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1.1</v>
+        <v>2.9</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8610,7 +8610,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 61417-2022</t>
+          <t>A 25624-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8624,10 +8624,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>44916</v>
+        <v>45803</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8640,7 +8640,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>3.6</v>
+        <v>5</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8683,7 +8683,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 32272-2023</t>
+          <t>A 41442-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8697,10 +8697,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45120</v>
+        <v>45869</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8713,7 +8713,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>4.9</v>
+        <v>1.8</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8756,7 +8756,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 32847-2023</t>
+          <t>A 17922-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8770,10 +8770,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45124</v>
+        <v>45758</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8786,7 +8786,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>4.7</v>
+        <v>0.8</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8846,7 +8846,7 @@
         <v>45371</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>

--- a/Översikt KUNGÄLV.xlsx
+++ b/Översikt KUNGÄLV.xlsx
@@ -601,7 +601,7 @@
         <v>45548</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>45868</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -851,7 +851,7 @@
         <v>45526</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -965,7 +965,7 @@
         <v>45919</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
         <v>45695</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         <v>45993</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         <v>45324</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>45985</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>46199</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>45355</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>46212</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         <v>45957</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1970,7 +1970,7 @@
         <v>45974</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2076,7 +2076,7 @@
         <v>45979</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
         <v>46212</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
         <v>45334</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2402,7 +2402,7 @@
         <v>45334</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2508,7 +2508,7 @@
         <v>45957</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
         <v>44838</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2723,7 +2723,7 @@
         <v>45454</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2828,7 +2828,7 @@
         <v>45215</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2933,7 +2933,7 @@
         <v>46212</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3038,7 +3038,7 @@
         <v>45697</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>44691</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
         <v>44691</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         <v>44836</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3366,7 +3366,7 @@
         <v>44459</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         <v>44459</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
         <v>44760</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3585,7 +3585,7 @@
         <v>44760</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3658,7 +3658,7 @@
         <v>44760</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3731,7 +3731,7 @@
         <v>45757</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3804,7 +3804,7 @@
         <v>45267</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3877,7 +3877,7 @@
         <v>45058</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3950,7 +3950,7 @@
         <v>45482</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4023,7 +4023,7 @@
         <v>44624</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4096,7 +4096,7 @@
         <v>45552</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
         <v>45050</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4242,7 +4242,7 @@
         <v>45694</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4315,7 +4315,7 @@
         <v>45347</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4388,7 +4388,7 @@
         <v>44975</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4461,7 +4461,7 @@
         <v>45215</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4534,7 +4534,7 @@
         <v>45897</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4607,7 +4607,7 @@
         <v>45215</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4680,7 +4680,7 @@
         <v>44894</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4753,7 +4753,7 @@
         <v>45308</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4826,7 +4826,7 @@
         <v>44757</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4899,7 +4899,7 @@
         <v>44989</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4972,7 +4972,7 @@
         <v>45919</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5045,7 +5045,7 @@
         <v>45324</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5118,7 +5118,7 @@
         <v>45931</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5191,7 +5191,7 @@
         <v>44502</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5264,7 +5264,7 @@
         <v>45271</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5337,7 +5337,7 @@
         <v>45957</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5410,7 +5410,7 @@
         <v>45188</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5483,7 +5483,7 @@
         <v>45470</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5556,7 +5556,7 @@
         <v>46157</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5629,7 +5629,7 @@
         <v>45837</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5702,7 +5702,7 @@
         <v>44755</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5775,7 +5775,7 @@
         <v>45426</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5848,7 +5848,7 @@
         <v>46163</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5921,7 +5921,7 @@
         <v>44837</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5994,7 +5994,7 @@
         <v>45798</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6067,7 +6067,7 @@
         <v>45751</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6140,7 +6140,7 @@
         <v>44846</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6213,7 +6213,7 @@
         <v>44928</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6286,7 +6286,7 @@
         <v>44792</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6359,7 +6359,7 @@
         <v>45426</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6432,7 +6432,7 @@
         <v>44543</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6505,7 +6505,7 @@
         <v>46048</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6578,7 +6578,7 @@
         <v>46057</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6651,7 +6651,7 @@
         <v>45222</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6724,7 +6724,7 @@
         <v>45877</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6802,7 +6802,7 @@
         <v>46098</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6875,7 +6875,7 @@
         <v>45664</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6948,7 +6948,7 @@
         <v>45082</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7021,7 +7021,7 @@
         <v>45391</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7094,7 +7094,7 @@
         <v>45215</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7167,7 +7167,7 @@
         <v>45453</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7240,7 +7240,7 @@
         <v>46205</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7313,7 +7313,7 @@
         <v>45063</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7386,7 +7386,7 @@
         <v>45324</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7459,7 +7459,7 @@
         <v>46254</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7532,7 +7532,7 @@
         <v>46254</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7605,7 +7605,7 @@
         <v>46254</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7678,7 +7678,7 @@
         <v>46254</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7751,7 +7751,7 @@
         <v>46211</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7824,7 +7824,7 @@
         <v>46212</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7897,7 +7897,7 @@
         <v>44508</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7970,7 +7970,7 @@
         <v>46281</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         <v>45721</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8116,7 +8116,7 @@
         <v>45721</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8189,7 +8189,7 @@
         <v>45726</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8262,7 +8262,7 @@
         <v>44558</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8335,7 +8335,7 @@
         <v>44916</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8408,7 +8408,7 @@
         <v>45120</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8481,7 +8481,7 @@
         <v>45124</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8554,7 +8554,7 @@
         <v>45844</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8627,7 +8627,7 @@
         <v>45803</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8700,7 +8700,7 @@
         <v>45869</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8773,7 +8773,7 @@
         <v>45758</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8846,7 +8846,7 @@
         <v>45371</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>

--- a/Översikt KUNGÄLV.xlsx
+++ b/Översikt KUNGÄLV.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE103"/>
+  <dimension ref="A1:AE101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45548</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>45868</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -851,7 +851,7 @@
         <v>45526</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -965,7 +965,7 @@
         <v>45919</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
         <v>45695</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         <v>45993</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         <v>45324</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>45985</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>46199</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>45355</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>46212</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         <v>45957</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1970,7 +1970,7 @@
         <v>45974</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2076,7 +2076,7 @@
         <v>45979</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
         <v>46212</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 5631-2024</t>
+          <t>A 53007-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2293,10 +2293,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45334</v>
+        <v>45957</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2309,13 +2309,13 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.3</v>
+        <v>2.9</v>
       </c>
       <c r="J17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -2342,259 +2342,259 @@
         <v>2</v>
       </c>
       <c r="T17" t="n">
+        <v>5</v>
+      </c>
+      <c r="U17" t="n">
+        <v>5</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>Västlig hakmossa
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 53007-2025 artfynd.xlsx", "A 53007-2025")</f>
+        <v/>
+      </c>
+      <c r="X17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 53007-2025 karta.png", "A 53007-2025")</f>
+        <v/>
+      </c>
+      <c r="Y17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 53007-2025 georefererad karta.tif", "A 53007-2025")</f>
+        <v/>
+      </c>
+      <c r="AA17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 53007-2025 FSC-klagomål.docx", "A 53007-2025")</f>
+        <v/>
+      </c>
+      <c r="AB17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 53007-2025 FSC-klagomål mail.docx", "A 53007-2025")</f>
+        <v/>
+      </c>
+      <c r="AC17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 53007-2025 tillsynsbegäran.docx", "A 53007-2025")</f>
+        <v/>
+      </c>
+      <c r="AD17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 53007-2025 tillsynsbegäran mail.docx", "A 53007-2025")</f>
+        <v/>
+      </c>
+      <c r="AE17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 53007-2025 prioriterade fågelarter.docx", "A 53007-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>A 5631-2024</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>45334</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>KUNGÄLV</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J18" t="n">
         <v>2</v>
       </c>
-      <c r="U17" t="n">
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
         <v>1</v>
       </c>
-      <c r="V17" s="2" t="inlineStr">
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>Vanlig groda
 Fläcknycklar</t>
         </is>
       </c>
-      <c r="W17">
+      <c r="W18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 5631-2024 artfynd.xlsx", "A 5631-2024")</f>
         <v/>
       </c>
-      <c r="X17">
+      <c r="X18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 5631-2024 karta.png", "A 5631-2024")</f>
         <v/>
       </c>
-      <c r="Y17">
+      <c r="Y18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 5631-2024 georefererad karta.tif", "A 5631-2024")</f>
         <v/>
       </c>
-      <c r="AA17">
+      <c r="AA18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 5631-2024 FSC-klagomål.docx", "A 5631-2024")</f>
         <v/>
       </c>
-      <c r="AB17">
+      <c r="AB18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 5631-2024 FSC-klagomål mail.docx", "A 5631-2024")</f>
         <v/>
       </c>
-      <c r="AC17">
+      <c r="AC18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 5631-2024 tillsynsbegäran.docx", "A 5631-2024")</f>
         <v/>
       </c>
-      <c r="AD17">
+      <c r="AD18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 5631-2024 tillsynsbegäran mail.docx", "A 5631-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
         <is>
           <t>A 5637-2024</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
         <v>45334</v>
       </c>
-      <c r="E18" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>KUNGÄLV</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
+      <c r="E19" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>KUNGÄLV</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
         <v>1.8</v>
       </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
         <v>2</v>
       </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
         <v>2</v>
       </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
         <v>2</v>
       </c>
-      <c r="T18" t="n">
+      <c r="T19" t="n">
         <v>2</v>
       </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>Klofibbla
 Åkerrödtoppa</t>
         </is>
       </c>
-      <c r="W18">
+      <c r="W19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 5637-2024 artfynd.xlsx", "A 5637-2024")</f>
         <v/>
       </c>
-      <c r="X18">
+      <c r="X19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 5637-2024 karta.png", "A 5637-2024")</f>
         <v/>
       </c>
-      <c r="Y18">
+      <c r="Y19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 5637-2024 georefererad karta.tif", "A 5637-2024")</f>
         <v/>
       </c>
-      <c r="AA18">
+      <c r="AA19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 5637-2024 FSC-klagomål.docx", "A 5637-2024")</f>
         <v/>
       </c>
-      <c r="AB18">
+      <c r="AB19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 5637-2024 FSC-klagomål mail.docx", "A 5637-2024")</f>
         <v/>
       </c>
-      <c r="AC18">
+      <c r="AC19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 5637-2024 tillsynsbegäran.docx", "A 5637-2024")</f>
         <v/>
       </c>
-      <c r="AD18">
+      <c r="AD19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 5637-2024 tillsynsbegäran mail.docx", "A 5637-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>A 53007-2025</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>45957</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>KUNGÄLV</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="J19" t="n">
-        <v>1</v>
-      </c>
-      <c r="K19" t="n">
-        <v>1</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2</v>
-      </c>
-      <c r="T19" t="n">
-        <v>5</v>
-      </c>
-      <c r="U19" t="n">
-        <v>5</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>Västlig hakmossa
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 53007-2025 artfynd.xlsx", "A 53007-2025")</f>
-        <v/>
-      </c>
-      <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 53007-2025 karta.png", "A 53007-2025")</f>
-        <v/>
-      </c>
-      <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 53007-2025 georefererad karta.tif", "A 53007-2025")</f>
-        <v/>
-      </c>
-      <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 53007-2025 FSC-klagomål.docx", "A 53007-2025")</f>
-        <v/>
-      </c>
-      <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 53007-2025 FSC-klagomål mail.docx", "A 53007-2025")</f>
-        <v/>
-      </c>
-      <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 53007-2025 tillsynsbegäran.docx", "A 53007-2025")</f>
-        <v/>
-      </c>
-      <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 53007-2025 tillsynsbegäran mail.docx", "A 53007-2025")</f>
-        <v/>
-      </c>
-      <c r="AE19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 53007-2025 prioriterade fågelarter.docx", "A 53007-2025")</f>
         <v/>
       </c>
     </row>
@@ -2618,7 +2618,7 @@
         <v>44838</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2723,7 +2723,7 @@
         <v>45454</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2828,7 +2828,7 @@
         <v>45215</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2933,7 +2933,7 @@
         <v>46212</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3038,7 +3038,7 @@
         <v>45697</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>44691</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
         <v>44691</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         <v>44836</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3349,7 +3349,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 50648-2021</t>
+          <t>A 30322-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3363,10 +3363,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44459</v>
+        <v>44760</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3379,7 +3379,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3422,7 +3422,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 50413-2021</t>
+          <t>A 30373-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3436,10 +3436,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44459</v>
+        <v>44760</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3452,7 +3452,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>3.9</v>
+        <v>0.8</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3495,7 +3495,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 30322-2022</t>
+          <t>A 30377-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3512,7 +3512,7 @@
         <v>44760</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3525,7 +3525,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.9</v>
+        <v>0.6</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3568,7 +3568,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 30373-2022</t>
+          <t>A 21240-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3582,10 +3582,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44760</v>
+        <v>45058</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3598,7 +3598,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.8</v>
+        <v>2.3</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3641,7 +3641,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 30377-2022</t>
+          <t>A 29223-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3655,10 +3655,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44760</v>
+        <v>45482</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3671,7 +3671,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.6</v>
+        <v>5.6</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3714,7 +3714,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 17455-2025</t>
+          <t>A 10655-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3728,10 +3728,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45757</v>
+        <v>44624</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3744,7 +3744,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>2.1</v>
+        <v>13.3</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3787,7 +3787,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 62221-2023</t>
+          <t>A 17455-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3801,10 +3801,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45267</v>
+        <v>45757</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3817,7 +3817,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.3</v>
+        <v>2.1</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3860,7 +3860,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 21240-2023</t>
+          <t>A 39714-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3874,10 +3874,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45058</v>
+        <v>45552</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3890,7 +3890,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>2.3</v>
+        <v>1.2</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3933,7 +3933,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 29223-2024</t>
+          <t>A 62221-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3947,10 +3947,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45482</v>
+        <v>45267</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3963,7 +3963,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>5.6</v>
+        <v>1.3</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4006,7 +4006,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 10655-2022</t>
+          <t>A 19531-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4020,10 +4020,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44624</v>
+        <v>45050</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>13.3</v>
+        <v>1.9</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4079,7 +4079,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 39714-2024</t>
+          <t>A 5705-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4089,14 +4089,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45552</v>
+        <v>45694</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4152,7 +4152,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 19531-2023</t>
+          <t>A 7505-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4166,10 +4166,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45050</v>
+        <v>45347</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4182,7 +4182,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4225,7 +4225,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 5705-2025</t>
+          <t>A 8334-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4235,14 +4235,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45694</v>
+        <v>44975</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4255,7 +4255,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4298,7 +4298,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 7505-2024</t>
+          <t>A 17922-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4312,10 +4312,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45347</v>
+        <v>45758</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4328,7 +4328,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4371,7 +4371,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 8334-2023</t>
+          <t>A 49985-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4385,10 +4385,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44975</v>
+        <v>45215</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4401,7 +4401,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4461,7 +4461,7 @@
         <v>45215</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4534,7 +4534,7 @@
         <v>45897</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4590,7 +4590,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 49981-2023</t>
+          <t>A 45124-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4604,10 +4604,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45215</v>
+        <v>45919</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4620,7 +4620,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2.5</v>
+        <v>3.7</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4663,7 +4663,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 56782-2022</t>
+          <t>A 47564-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4677,10 +4677,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44894</v>
+        <v>45931</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4736,7 +4736,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 1995-2024</t>
+          <t>A 49981-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4750,10 +4750,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45308</v>
+        <v>45215</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4766,7 +4766,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4809,7 +4809,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 30170-2022</t>
+          <t>A 56782-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4823,10 +4823,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44757</v>
+        <v>44894</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>3.1</v>
+        <v>0.5</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4882,7 +4882,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 10810-2023</t>
+          <t>A 1995-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4896,10 +4896,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44989</v>
+        <v>45308</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4912,7 +4912,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4955,7 +4955,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 45124-2025</t>
+          <t>A 30170-2022</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4969,10 +4969,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45919</v>
+        <v>44757</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4985,7 +4985,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5028,7 +5028,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 4204-2024</t>
+          <t>A 10810-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5042,10 +5042,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45324</v>
+        <v>44989</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5058,7 +5058,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>4.4</v>
+        <v>0.4</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5101,7 +5101,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 47564-2025</t>
+          <t>A 22731-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5115,10 +5115,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45931</v>
+        <v>46157</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5131,7 +5131,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5174,7 +5174,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 62128-2021</t>
+          <t>A 32391-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5188,10 +5188,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44502</v>
+        <v>45837</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5204,7 +5204,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5247,7 +5247,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 62979-2023</t>
+          <t>A 52932-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5257,14 +5257,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45271</v>
+        <v>45957</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5277,7 +5277,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.8</v>
+        <v>3.4</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5320,7 +5320,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 52932-2025</t>
+          <t>A 4204-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5334,10 +5334,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45957</v>
+        <v>45324</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5350,7 +5350,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>3.4</v>
+        <v>4.4</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5393,7 +5393,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 44176-2023</t>
+          <t>A 23607-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5407,10 +5407,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45188</v>
+        <v>46163</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5423,7 +5423,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>7.1</v>
+        <v>5.3</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5466,7 +5466,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 26812-2024</t>
+          <t>A 25135-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5480,10 +5480,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45470</v>
+        <v>45798</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5496,7 +5496,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5539,7 +5539,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 22731-2026</t>
+          <t>A 62128-2021</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5553,10 +5553,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46157</v>
+        <v>44502</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5612,7 +5612,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 32391-2025</t>
+          <t>A 62979-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5622,14 +5622,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45837</v>
+        <v>45271</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5642,7 +5642,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>2.1</v>
+        <v>0.8</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5685,7 +5685,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 29801-2022</t>
+          <t>A 44176-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5699,10 +5699,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44755</v>
+        <v>45188</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5715,7 +5715,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>4.8</v>
+        <v>7.1</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5758,7 +5758,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 18852-2024</t>
+          <t>A 26812-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5772,10 +5772,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45426</v>
+        <v>45470</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5788,7 +5788,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>2.7</v>
+        <v>1.7</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5831,7 +5831,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 23607-2026</t>
+          <t>A 29801-2022</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5845,10 +5845,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46163</v>
+        <v>44755</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5861,7 +5861,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>5.3</v>
+        <v>4.8</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5904,7 +5904,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 43520-2022</t>
+          <t>A 18852-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5918,10 +5918,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44837</v>
+        <v>45426</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5934,7 +5934,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.5</v>
+        <v>2.7</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5977,7 +5977,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 25135-2025</t>
+          <t>A 34366-2022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5991,10 +5991,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45798</v>
+        <v>44792</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6007,7 +6007,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6050,7 +6050,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 16538-2025</t>
+          <t>A 4673-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6064,10 +6064,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45751</v>
+        <v>46048</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6080,7 +6080,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6123,7 +6123,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 45990-2022</t>
+          <t>A 43520-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6137,10 +6137,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44846</v>
+        <v>44837</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6153,7 +6153,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>3.3</v>
+        <v>1.5</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6196,7 +6196,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 143-2023</t>
+          <t>A 6946-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6206,14 +6206,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44928</v>
+        <v>46057</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6226,7 +6226,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.5</v>
+        <v>2.2</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 34366-2022</t>
+          <t>A 16538-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6283,10 +6283,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44792</v>
+        <v>45751</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6299,7 +6299,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6342,7 +6342,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 18851-2024</t>
+          <t>A 45990-2022</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6356,10 +6356,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45426</v>
+        <v>44846</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6372,7 +6372,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6415,7 +6415,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 71835-2021</t>
+          <t>A 37443-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6429,10 +6429,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44543</v>
+        <v>45877</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6444,8 +6444,13 @@
           <t>KUNGÄLV</t>
         </is>
       </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I70" t="n">
-        <v>7.5</v>
+        <v>0.7</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6488,7 +6493,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 4673-2026</t>
+          <t>A 13990-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6502,10 +6507,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46048</v>
+        <v>46098</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6518,7 +6523,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>8.199999999999999</v>
+        <v>2.6</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6561,7 +6566,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 6946-2026</t>
+          <t>A 143-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6571,14 +6576,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46057</v>
+        <v>44928</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6591,7 +6596,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>2.2</v>
+        <v>0.5</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6634,7 +6639,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 51724-2023</t>
+          <t>A 18851-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6648,10 +6653,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45222</v>
+        <v>45426</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6664,7 +6669,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6707,7 +6712,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 37443-2025</t>
+          <t>A 71835-2021</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6721,10 +6726,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45877</v>
+        <v>44543</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6736,13 +6741,8 @@
           <t>KUNGÄLV</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I74" t="n">
-        <v>0.7</v>
+        <v>7.5</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6785,7 +6785,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 13990-2026</t>
+          <t>A 29952-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6799,10 +6799,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46098</v>
+        <v>46205</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6815,7 +6815,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6858,7 +6858,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 661-2025</t>
+          <t>A 51724-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6872,10 +6872,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45664</v>
+        <v>45222</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6931,7 +6931,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 24461-2023</t>
+          <t>A 34392-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6945,10 +6945,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45082</v>
+        <v>46254</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6961,7 +6961,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.5</v>
+        <v>0.4</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7004,7 +7004,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 13880-2024</t>
+          <t>A 34387-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7018,10 +7018,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45391</v>
+        <v>46254</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7034,7 +7034,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>2.4</v>
+        <v>0.3</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7077,7 +7077,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 49985-2023</t>
+          <t>A 34386-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7091,10 +7091,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45215</v>
+        <v>46254</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7107,7 +7107,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>8.199999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7150,7 +7150,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 23457-2024</t>
+          <t>A 34396-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7164,10 +7164,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45453</v>
+        <v>46254</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7180,7 +7180,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>5.1</v>
+        <v>0.8</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7223,7 +7223,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 29952-2026</t>
+          <t>A 30738-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7237,10 +7237,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46205</v>
+        <v>46211</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7253,7 +7253,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7296,7 +7296,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 21389-2023</t>
+          <t>A 661-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7310,10 +7310,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45063</v>
+        <v>45664</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7326,7 +7326,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7369,7 +7369,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 4262-2024</t>
+          <t>A 30859-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7383,10 +7383,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45324</v>
+        <v>46212</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>14</v>
+        <v>0.5</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7442,7 +7442,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 34392-2026</t>
+          <t>A 24461-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7456,10 +7456,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46254</v>
+        <v>45082</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7472,7 +7472,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>0.4</v>
+        <v>1.5</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7515,7 +7515,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 34387-2026</t>
+          <t>A 13880-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7529,10 +7529,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46254</v>
+        <v>45391</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7545,7 +7545,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>0.3</v>
+        <v>2.4</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7588,7 +7588,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 34386-2026</t>
+          <t>A 23457-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7602,10 +7602,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46254</v>
+        <v>45453</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7618,7 +7618,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>0.7</v>
+        <v>5.1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7661,7 +7661,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 34396-2026</t>
+          <t>A 21389-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7675,10 +7675,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46254</v>
+        <v>45063</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7691,7 +7691,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.8</v>
+        <v>3.4</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7734,7 +7734,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 30738-2026</t>
+          <t>A 4262-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7748,10 +7748,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>46211</v>
+        <v>45324</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7764,7 +7764,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>3.5</v>
+        <v>14</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7807,7 +7807,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 30859-2026</t>
+          <t>A 38262-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7821,10 +7821,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46212</v>
+        <v>46281</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7837,7 +7837,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>0.5</v>
+        <v>2.8</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7897,7 +7897,7 @@
         <v>44508</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7953,7 +7953,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 38262-2026</t>
+          <t>A 10677-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7967,10 +7967,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46281</v>
+        <v>45721</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7983,7 +7983,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>2.8</v>
+        <v>7.4</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8026,7 +8026,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 10677-2025</t>
+          <t>A 10679-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8043,7 +8043,7 @@
         <v>45721</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8056,7 +8056,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>7.4</v>
+        <v>4.4</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 10679-2025</t>
+          <t>A 11237-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8113,10 +8113,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45721</v>
+        <v>45726</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8129,7 +8129,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8172,7 +8172,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 11237-2025</t>
+          <t>A 74285-2021</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8186,10 +8186,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45726</v>
+        <v>44558</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8202,7 +8202,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>4.2</v>
+        <v>1.1</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8245,7 +8245,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 74285-2021</t>
+          <t>A 61417-2022</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8259,10 +8259,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>44558</v>
+        <v>44916</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8275,7 +8275,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>1.1</v>
+        <v>3.6</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8318,7 +8318,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 61417-2022</t>
+          <t>A 32272-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8332,10 +8332,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>44916</v>
+        <v>45120</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8348,7 +8348,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>3.6</v>
+        <v>4.9</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8391,7 +8391,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 32272-2023</t>
+          <t>A 32847-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8405,10 +8405,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45120</v>
+        <v>45124</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8421,7 +8421,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8464,7 +8464,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 32847-2023</t>
+          <t>A 34244-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8478,10 +8478,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45124</v>
+        <v>45844</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8494,7 +8494,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>4.7</v>
+        <v>2.9</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8537,7 +8537,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 34244-2025</t>
+          <t>A 25624-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8551,10 +8551,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45844</v>
+        <v>45803</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8567,7 +8567,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>2.9</v>
+        <v>5</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8610,7 +8610,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 25624-2025</t>
+          <t>A 41442-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8624,10 +8624,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45803</v>
+        <v>45869</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8640,7 +8640,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>5</v>
+        <v>1.8</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8680,27 +8680,27 @@
       </c>
       <c r="V100" s="2" t="inlineStr"/>
     </row>
-    <row r="101" ht="15" customHeight="1">
+    <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 41442-2025</t>
+          <t>S 817-2024</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45869</v>
+        <v>45371</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8712,8 +8712,13 @@
           <t>KUNGÄLV</t>
         </is>
       </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I101" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8752,157 +8757,6 @@
         <v>0</v>
       </c>
       <c r="V101" s="2" t="inlineStr"/>
-    </row>
-    <row r="102" ht="15" customHeight="1">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>A 17922-2025</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D102" s="1" t="n">
-        <v>45758</v>
-      </c>
-      <c r="E102" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>KUNGÄLV</t>
-        </is>
-      </c>
-      <c r="I102" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J102" t="n">
-        <v>0</v>
-      </c>
-      <c r="K102" t="n">
-        <v>0</v>
-      </c>
-      <c r="L102" t="n">
-        <v>0</v>
-      </c>
-      <c r="M102" t="n">
-        <v>0</v>
-      </c>
-      <c r="N102" t="n">
-        <v>0</v>
-      </c>
-      <c r="O102" t="n">
-        <v>0</v>
-      </c>
-      <c r="P102" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q102" t="n">
-        <v>0</v>
-      </c>
-      <c r="R102" t="n">
-        <v>0</v>
-      </c>
-      <c r="S102" t="n">
-        <v>0</v>
-      </c>
-      <c r="T102" t="n">
-        <v>0</v>
-      </c>
-      <c r="U102" t="n">
-        <v>0</v>
-      </c>
-      <c r="V102" s="2" t="inlineStr"/>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>S 817-2024</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D103" s="1" t="n">
-        <v>45371</v>
-      </c>
-      <c r="E103" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>KUNGÄLV</t>
-        </is>
-      </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
-      <c r="I103" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="J103" t="n">
-        <v>0</v>
-      </c>
-      <c r="K103" t="n">
-        <v>0</v>
-      </c>
-      <c r="L103" t="n">
-        <v>0</v>
-      </c>
-      <c r="M103" t="n">
-        <v>0</v>
-      </c>
-      <c r="N103" t="n">
-        <v>0</v>
-      </c>
-      <c r="O103" t="n">
-        <v>0</v>
-      </c>
-      <c r="P103" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q103" t="n">
-        <v>0</v>
-      </c>
-      <c r="R103" t="n">
-        <v>0</v>
-      </c>
-      <c r="S103" t="n">
-        <v>0</v>
-      </c>
-      <c r="T103" t="n">
-        <v>0</v>
-      </c>
-      <c r="U103" t="n">
-        <v>0</v>
-      </c>
-      <c r="V103" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt KUNGÄLV.xlsx
+++ b/Översikt KUNGÄLV.xlsx
@@ -601,7 +601,7 @@
         <v>45548</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>45868</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -851,7 +851,7 @@
         <v>45526</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -965,7 +965,7 @@
         <v>45919</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
         <v>45695</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 59985-2025</t>
+          <t>A 4263-2024</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1188,10 +1188,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45993</v>
+        <v>45324</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1204,16 +1204,16 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>5.3</v>
+        <v>2.6</v>
       </c>
       <c r="J7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -1228,7 +1228,7 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1237,12 +1237,124 @@
         <v>4</v>
       </c>
       <c r="T7" t="n">
+        <v>6</v>
+      </c>
+      <c r="U7" t="n">
+        <v>6</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Mindre hackspett
+Klippfrullania
+Gråsiska
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 4263-2024 artfynd.xlsx", "A 4263-2024")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 4263-2024 karta.png", "A 4263-2024")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 4263-2024 georefererad karta.tif", "A 4263-2024")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 4263-2024 FSC-klagomål.docx", "A 4263-2024")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 4263-2024 FSC-klagomål mail.docx", "A 4263-2024")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 4263-2024 tillsynsbegäran.docx", "A 4263-2024")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 4263-2024 tillsynsbegäran mail.docx", "A 4263-2024")</f>
+        <v/>
+      </c>
+      <c r="AE7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 4263-2024 prioriterade fågelarter.docx", "A 4263-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 59985-2025</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>45993</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>KUNGÄLV</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2</v>
+      </c>
+      <c r="K8" t="n">
+        <v>2</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>4</v>
+      </c>
+      <c r="T8" t="n">
         <v>19</v>
       </c>
-      <c r="U7" t="n">
+      <c r="U8" t="n">
         <v>19</v>
       </c>
-      <c r="V7" s="2" t="inlineStr">
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>Blåmossa
 Västlig hakmossa
@@ -1250,148 +1362,36 @@
 Äkta lopplummer</t>
         </is>
       </c>
-      <c r="W7">
+      <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 59985-2025 artfynd.xlsx", "A 59985-2025")</f>
         <v/>
       </c>
-      <c r="X7">
+      <c r="X8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 59985-2025 karta.png", "A 59985-2025")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 59985-2025 georefererad karta.tif", "A 59985-2025")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 59985-2025 FSC-klagomål.docx", "A 59985-2025")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 59985-2025 FSC-klagomål mail.docx", "A 59985-2025")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 59985-2025 tillsynsbegäran.docx", "A 59985-2025")</f>
         <v/>
       </c>
-      <c r="AD7">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 59985-2025 tillsynsbegäran mail.docx", "A 59985-2025")</f>
         <v/>
       </c>
-      <c r="AE7">
+      <c r="AE8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 59985-2025 prioriterade fågelarter.docx", "A 59985-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A 4263-2024</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>45324</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>KUNGÄLV</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="J8" t="n">
-        <v>3</v>
-      </c>
-      <c r="K8" t="n">
-        <v>1</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>4</v>
-      </c>
-      <c r="T8" t="n">
-        <v>6</v>
-      </c>
-      <c r="U8" t="n">
-        <v>6</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>Mindre hackspett
-Klippfrullania
-Gråsiska
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 4263-2024 artfynd.xlsx", "A 4263-2024")</f>
-        <v/>
-      </c>
-      <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 4263-2024 karta.png", "A 4263-2024")</f>
-        <v/>
-      </c>
-      <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 4263-2024 georefererad karta.tif", "A 4263-2024")</f>
-        <v/>
-      </c>
-      <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 4263-2024 FSC-klagomål.docx", "A 4263-2024")</f>
-        <v/>
-      </c>
-      <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 4263-2024 FSC-klagomål mail.docx", "A 4263-2024")</f>
-        <v/>
-      </c>
-      <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 4263-2024 tillsynsbegäran.docx", "A 4263-2024")</f>
-        <v/>
-      </c>
-      <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 4263-2024 tillsynsbegäran mail.docx", "A 4263-2024")</f>
-        <v/>
-      </c>
-      <c r="AE8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 4263-2024 prioriterade fågelarter.docx", "A 4263-2024")</f>
         <v/>
       </c>
     </row>
@@ -1415,7 +1415,7 @@
         <v>45985</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>46199</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>45355</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>46212</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         <v>45957</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1970,7 +1970,7 @@
         <v>45974</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2076,7 +2076,7 @@
         <v>45979</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2169,7 +2169,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 30860-2026</t>
+          <t>A 5631-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2183,10 +2183,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46212</v>
+        <v>45334</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2199,16 +2199,16 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2223,7 +2223,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2239,362 +2239,362 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
+          <t>Vanlig groda
+Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 5631-2024 artfynd.xlsx", "A 5631-2024")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 5631-2024 karta.png", "A 5631-2024")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 5631-2024 georefererad karta.tif", "A 5631-2024")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 5631-2024 FSC-klagomål.docx", "A 5631-2024")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 5631-2024 FSC-klagomål mail.docx", "A 5631-2024")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 5631-2024 tillsynsbegäran.docx", "A 5631-2024")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 5631-2024 tillsynsbegäran mail.docx", "A 5631-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 5637-2024</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>45334</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>KUNGÄLV</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>2</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>Klofibbla
+Åkerrödtoppa</t>
+        </is>
+      </c>
+      <c r="W17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 5637-2024 artfynd.xlsx", "A 5637-2024")</f>
+        <v/>
+      </c>
+      <c r="X17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 5637-2024 karta.png", "A 5637-2024")</f>
+        <v/>
+      </c>
+      <c r="Y17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 5637-2024 georefererad karta.tif", "A 5637-2024")</f>
+        <v/>
+      </c>
+      <c r="AA17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 5637-2024 FSC-klagomål.docx", "A 5637-2024")</f>
+        <v/>
+      </c>
+      <c r="AB17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 5637-2024 FSC-klagomål mail.docx", "A 5637-2024")</f>
+        <v/>
+      </c>
+      <c r="AC17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 5637-2024 tillsynsbegäran.docx", "A 5637-2024")</f>
+        <v/>
+      </c>
+      <c r="AD17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 5637-2024 tillsynsbegäran mail.docx", "A 5637-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>A 30860-2026</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>46212</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>KUNGÄLV</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
           <t>Grönsångare
 Västlig hakmossa</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 30860-2026 artfynd.xlsx", "A 30860-2026")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 30860-2026 karta.png", "A 30860-2026")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 30860-2026 georefererad karta.tif", "A 30860-2026")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 30860-2026 FSC-klagomål.docx", "A 30860-2026")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 30860-2026 FSC-klagomål mail.docx", "A 30860-2026")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 30860-2026 tillsynsbegäran.docx", "A 30860-2026")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 30860-2026 tillsynsbegäran mail.docx", "A 30860-2026")</f>
         <v/>
       </c>
-      <c r="AE16">
+      <c r="AE18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 30860-2026 prioriterade fågelarter.docx", "A 30860-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
         <is>
           <t>A 53007-2025</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
         <v>45957</v>
       </c>
-      <c r="E17" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>KUNGÄLV</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
+      <c r="E19" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>KUNGÄLV</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
         <v>2.9</v>
       </c>
-      <c r="J17" t="n">
+      <c r="J19" t="n">
         <v>1</v>
       </c>
-      <c r="K17" t="n">
+      <c r="K19" t="n">
         <v>1</v>
       </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
         <v>2</v>
       </c>
-      <c r="T17" t="n">
+      <c r="T19" t="n">
         <v>5</v>
       </c>
-      <c r="U17" t="n">
+      <c r="U19" t="n">
         <v>5</v>
       </c>
-      <c r="V17" s="2" t="inlineStr">
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>Västlig hakmossa
 Spillkråka</t>
         </is>
       </c>
-      <c r="W17">
+      <c r="W19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 53007-2025 artfynd.xlsx", "A 53007-2025")</f>
         <v/>
       </c>
-      <c r="X17">
+      <c r="X19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 53007-2025 karta.png", "A 53007-2025")</f>
         <v/>
       </c>
-      <c r="Y17">
+      <c r="Y19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 53007-2025 georefererad karta.tif", "A 53007-2025")</f>
         <v/>
       </c>
-      <c r="AA17">
+      <c r="AA19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 53007-2025 FSC-klagomål.docx", "A 53007-2025")</f>
         <v/>
       </c>
-      <c r="AB17">
+      <c r="AB19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 53007-2025 FSC-klagomål mail.docx", "A 53007-2025")</f>
         <v/>
       </c>
-      <c r="AC17">
+      <c r="AC19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 53007-2025 tillsynsbegäran.docx", "A 53007-2025")</f>
         <v/>
       </c>
-      <c r="AD17">
+      <c r="AD19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 53007-2025 tillsynsbegäran mail.docx", "A 53007-2025")</f>
         <v/>
       </c>
-      <c r="AE17">
+      <c r="AE19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 53007-2025 prioriterade fågelarter.docx", "A 53007-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 5631-2024</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>45334</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>KUNGÄLV</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="J18" t="n">
-        <v>2</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>Vanlig groda
-Fläcknycklar</t>
-        </is>
-      </c>
-      <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 5631-2024 artfynd.xlsx", "A 5631-2024")</f>
-        <v/>
-      </c>
-      <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 5631-2024 karta.png", "A 5631-2024")</f>
-        <v/>
-      </c>
-      <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 5631-2024 georefererad karta.tif", "A 5631-2024")</f>
-        <v/>
-      </c>
-      <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 5631-2024 FSC-klagomål.docx", "A 5631-2024")</f>
-        <v/>
-      </c>
-      <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 5631-2024 FSC-klagomål mail.docx", "A 5631-2024")</f>
-        <v/>
-      </c>
-      <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 5631-2024 tillsynsbegäran.docx", "A 5631-2024")</f>
-        <v/>
-      </c>
-      <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 5631-2024 tillsynsbegäran mail.docx", "A 5631-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>A 5637-2024</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>45334</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>KUNGÄLV</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>2</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>2</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>Klofibbla
-Åkerrödtoppa</t>
-        </is>
-      </c>
-      <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 5637-2024 artfynd.xlsx", "A 5637-2024")</f>
-        <v/>
-      </c>
-      <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 5637-2024 karta.png", "A 5637-2024")</f>
-        <v/>
-      </c>
-      <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 5637-2024 georefererad karta.tif", "A 5637-2024")</f>
-        <v/>
-      </c>
-      <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 5637-2024 FSC-klagomål.docx", "A 5637-2024")</f>
-        <v/>
-      </c>
-      <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 5637-2024 FSC-klagomål mail.docx", "A 5637-2024")</f>
-        <v/>
-      </c>
-      <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 5637-2024 tillsynsbegäran.docx", "A 5637-2024")</f>
-        <v/>
-      </c>
-      <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 5637-2024 tillsynsbegäran mail.docx", "A 5637-2024")</f>
         <v/>
       </c>
     </row>
@@ -2618,7 +2618,7 @@
         <v>44838</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2706,7 +2706,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 23704-2024</t>
+          <t>A 49988-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2720,10 +2720,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45454</v>
+        <v>45215</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>4.9</v>
+        <v>2.3</v>
       </c>
       <c r="J21" t="n">
         <v>1</v>
@@ -2748,7 +2748,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -2760,58 +2760,58 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
       </c>
       <c r="T21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Hedjohannesört</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 23704-2024 artfynd.xlsx", "A 23704-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 49988-2023 artfynd.xlsx", "A 49988-2023")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 23704-2024 karta.png", "A 23704-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 49988-2023 karta.png", "A 49988-2023")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 23704-2024 georefererad karta.tif", "A 23704-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 49988-2023 georefererad karta.tif", "A 49988-2023")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 23704-2024 FSC-klagomål.docx", "A 23704-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 49988-2023 FSC-klagomål.docx", "A 49988-2023")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 23704-2024 FSC-klagomål mail.docx", "A 23704-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 49988-2023 FSC-klagomål mail.docx", "A 49988-2023")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 23704-2024 tillsynsbegäran.docx", "A 23704-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 49988-2023 tillsynsbegäran.docx", "A 49988-2023")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 23704-2024 tillsynsbegäran mail.docx", "A 23704-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 49988-2023 tillsynsbegäran mail.docx", "A 49988-2023")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 49988-2023</t>
+          <t>A 6082-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2825,10 +2825,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45215</v>
+        <v>45697</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2841,7 +2841,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
@@ -2877,46 +2877,50 @@
         <v>1</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 49988-2023 artfynd.xlsx", "A 49988-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 6082-2025 artfynd.xlsx", "A 6082-2025")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 49988-2023 karta.png", "A 49988-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 6082-2025 karta.png", "A 6082-2025")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 49988-2023 georefererad karta.tif", "A 49988-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 6082-2025 georefererad karta.tif", "A 6082-2025")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 49988-2023 FSC-klagomål.docx", "A 49988-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 6082-2025 FSC-klagomål.docx", "A 6082-2025")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 49988-2023 FSC-klagomål mail.docx", "A 49988-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 6082-2025 FSC-klagomål mail.docx", "A 6082-2025")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 49988-2023 tillsynsbegäran.docx", "A 49988-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 6082-2025 tillsynsbegäran.docx", "A 6082-2025")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 49988-2023 tillsynsbegäran mail.docx", "A 49988-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 6082-2025 tillsynsbegäran mail.docx", "A 6082-2025")</f>
+        <v/>
+      </c>
+      <c r="AE22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 6082-2025 prioriterade fågelarter.docx", "A 6082-2025")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 30862-2026</t>
+          <t>A 23704-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2930,10 +2934,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46212</v>
+        <v>45454</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2946,7 +2950,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.7</v>
+        <v>4.9</v>
       </c>
       <c r="J23" t="n">
         <v>1</v>
@@ -2958,7 +2962,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
@@ -2970,58 +2974,58 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
       </c>
       <c r="T23" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Hedjohannesört</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 30862-2026 artfynd.xlsx", "A 30862-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 23704-2024 artfynd.xlsx", "A 23704-2024")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 30862-2026 karta.png", "A 30862-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 23704-2024 karta.png", "A 23704-2024")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 30862-2026 georefererad karta.tif", "A 30862-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 23704-2024 georefererad karta.tif", "A 23704-2024")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 30862-2026 FSC-klagomål.docx", "A 30862-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 23704-2024 FSC-klagomål.docx", "A 23704-2024")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 30862-2026 FSC-klagomål mail.docx", "A 30862-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 23704-2024 FSC-klagomål mail.docx", "A 23704-2024")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 30862-2026 tillsynsbegäran.docx", "A 30862-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 23704-2024 tillsynsbegäran.docx", "A 23704-2024")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 30862-2026 tillsynsbegäran mail.docx", "A 30862-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 23704-2024 tillsynsbegäran mail.docx", "A 23704-2024")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 6082-2025</t>
+          <t>A 30862-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3035,10 +3039,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45697</v>
+        <v>46212</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3051,7 +3055,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.8</v>
+        <v>1.7</v>
       </c>
       <c r="J24" t="n">
         <v>1</v>
@@ -3084,46 +3088,42 @@
         <v>1</v>
       </c>
       <c r="T24" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 6082-2025 artfynd.xlsx", "A 6082-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 30862-2026 artfynd.xlsx", "A 30862-2026")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 6082-2025 karta.png", "A 6082-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 30862-2026 karta.png", "A 30862-2026")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 6082-2025 georefererad karta.tif", "A 6082-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 30862-2026 georefererad karta.tif", "A 30862-2026")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 6082-2025 FSC-klagomål.docx", "A 6082-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 30862-2026 FSC-klagomål.docx", "A 30862-2026")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 6082-2025 FSC-klagomål mail.docx", "A 6082-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 30862-2026 FSC-klagomål mail.docx", "A 30862-2026")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 6082-2025 tillsynsbegäran.docx", "A 6082-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 30862-2026 tillsynsbegäran.docx", "A 30862-2026")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 6082-2025 tillsynsbegäran mail.docx", "A 6082-2025")</f>
-        <v/>
-      </c>
-      <c r="AE24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 6082-2025 prioriterade fågelarter.docx", "A 6082-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 30862-2026 tillsynsbegäran mail.docx", "A 30862-2026")</f>
         <v/>
       </c>
     </row>
@@ -3147,7 +3147,7 @@
         <v>44691</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
         <v>44691</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         <v>44836</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3366,7 +3366,7 @@
         <v>44760</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         <v>44760</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
         <v>44760</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3568,7 +3568,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 21240-2023</t>
+          <t>A 661-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3582,10 +3582,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45058</v>
+        <v>45664</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3598,7 +3598,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3641,7 +3641,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 29223-2024</t>
+          <t>A 62221-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3655,10 +3655,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45482</v>
+        <v>45267</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3671,7 +3671,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>5.6</v>
+        <v>1.3</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3714,7 +3714,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 10655-2022</t>
+          <t>A 4204-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3728,10 +3728,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44624</v>
+        <v>45324</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3744,7 +3744,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>13.3</v>
+        <v>4.4</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3787,7 +3787,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 17455-2025</t>
+          <t>A 10679-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3801,10 +3801,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45757</v>
+        <v>45721</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3817,7 +3817,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2.1</v>
+        <v>4.4</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3860,7 +3860,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 39714-2024</t>
+          <t>A 30170-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3874,10 +3874,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45552</v>
+        <v>44757</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3890,7 +3890,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.2</v>
+        <v>3.1</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3933,7 +3933,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 62221-2023</t>
+          <t>A 11237-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3947,10 +3947,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45267</v>
+        <v>45726</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3963,7 +3963,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.3</v>
+        <v>4.2</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4006,7 +4006,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 19531-2023</t>
+          <t>A 10677-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4020,10 +4020,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45050</v>
+        <v>45721</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.9</v>
+        <v>7.4</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4079,7 +4079,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 5705-2025</t>
+          <t>A 17922-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4089,14 +4089,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45694</v>
+        <v>45758</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4109,7 +4109,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4152,7 +4152,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 7505-2024</t>
+          <t>A 74285-2021</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4166,10 +4166,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45347</v>
+        <v>44558</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4182,7 +4182,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4225,7 +4225,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 8334-2023</t>
+          <t>A 13880-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4239,10 +4239,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44975</v>
+        <v>45391</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4255,7 +4255,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4298,7 +4298,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 17922-2025</t>
+          <t>A 1995-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4312,10 +4312,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45758</v>
+        <v>45308</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4328,7 +4328,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4371,7 +4371,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 49985-2023</t>
+          <t>A 24461-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4385,10 +4385,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45215</v>
+        <v>45082</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4401,7 +4401,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>8.199999999999999</v>
+        <v>1.5</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4444,7 +4444,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 50071-2023</t>
+          <t>A 45990-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4458,10 +4458,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45215</v>
+        <v>44846</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4474,7 +4474,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4517,7 +4517,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 40951-2025</t>
+          <t>A 143-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4531,10 +4531,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45897</v>
+        <v>44928</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4547,7 +4547,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4590,7 +4590,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 45124-2025</t>
+          <t>A 63319-2021</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4604,10 +4604,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45919</v>
+        <v>44508</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4620,7 +4620,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>3.7</v>
+        <v>1.6</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4663,7 +4663,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 47564-2025</t>
+          <t>A 40951-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4677,10 +4677,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45931</v>
+        <v>45897</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4736,7 +4736,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 49981-2023</t>
+          <t>A 7505-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4750,10 +4750,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45215</v>
+        <v>45347</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4766,7 +4766,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4809,7 +4809,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 56782-2022</t>
+          <t>A 43520-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4823,10 +4823,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44894</v>
+        <v>44837</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4882,7 +4882,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 1995-2024</t>
+          <t>A 45124-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4896,10 +4896,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45308</v>
+        <v>45919</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4912,7 +4912,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.5</v>
+        <v>3.7</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4955,7 +4955,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 30170-2022</t>
+          <t>A 29223-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4969,10 +4969,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44757</v>
+        <v>45482</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4985,7 +4985,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>3.1</v>
+        <v>5.6</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5028,7 +5028,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 10810-2023</t>
+          <t>A 61417-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5042,10 +5042,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44989</v>
+        <v>44916</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5058,7 +5058,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.4</v>
+        <v>3.6</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5101,7 +5101,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 22731-2026</t>
+          <t>A 32272-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5115,10 +5115,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46157</v>
+        <v>45120</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5131,7 +5131,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.8</v>
+        <v>4.9</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5174,7 +5174,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 32391-2025</t>
+          <t>A 47564-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5188,10 +5188,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45837</v>
+        <v>45931</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5204,7 +5204,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5247,7 +5247,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 52932-2025</t>
+          <t>A 32847-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5261,10 +5261,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45957</v>
+        <v>45124</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5277,7 +5277,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>3.4</v>
+        <v>4.7</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5320,7 +5320,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 4204-2024</t>
+          <t>A 10655-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5334,10 +5334,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45324</v>
+        <v>44624</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5350,7 +5350,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>4.4</v>
+        <v>13.3</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5393,7 +5393,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 23607-2026</t>
+          <t>A 17455-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5407,10 +5407,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46163</v>
+        <v>45757</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5423,7 +5423,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>5.3</v>
+        <v>2.1</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5466,7 +5466,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 25135-2025</t>
+          <t>A 8334-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5480,10 +5480,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45798</v>
+        <v>44975</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5496,7 +5496,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5539,7 +5539,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 62128-2021</t>
+          <t>A 52932-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5553,10 +5553,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44502</v>
+        <v>45957</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5569,7 +5569,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.8</v>
+        <v>3.4</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5612,7 +5612,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 62979-2023</t>
+          <t>A 19531-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5622,14 +5622,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45271</v>
+        <v>45050</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5642,7 +5642,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.8</v>
+        <v>1.9</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5685,7 +5685,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 44176-2023</t>
+          <t>A 5705-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5695,14 +5695,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45188</v>
+        <v>45694</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5715,7 +5715,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>7.1</v>
+        <v>1.2</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5758,7 +5758,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 26812-2024</t>
+          <t>A 62979-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5768,14 +5768,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45470</v>
+        <v>45271</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5788,7 +5788,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5831,7 +5831,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 29801-2022</t>
+          <t>A 4262-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5845,10 +5845,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44755</v>
+        <v>45324</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5861,7 +5861,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>4.8</v>
+        <v>14</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5904,7 +5904,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 18852-2024</t>
+          <t>A 16538-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5918,10 +5918,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45426</v>
+        <v>45751</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5934,7 +5934,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>2.7</v>
+        <v>0.8</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5977,7 +5977,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 34366-2022</t>
+          <t>A 29801-2022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5991,10 +5991,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44792</v>
+        <v>44755</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6007,7 +6007,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.5</v>
+        <v>4.8</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6050,7 +6050,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 4673-2026</t>
+          <t>A 49981-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6064,10 +6064,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46048</v>
+        <v>45215</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6080,7 +6080,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>8.199999999999999</v>
+        <v>2.5</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6123,7 +6123,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 43520-2022</t>
+          <t>A 34366-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6137,10 +6137,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44837</v>
+        <v>44792</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6153,7 +6153,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6196,7 +6196,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 6946-2026</t>
+          <t>A 4673-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6206,14 +6206,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46057</v>
+        <v>46048</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6226,7 +6226,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>2.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 16538-2025</t>
+          <t>A 71835-2021</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6283,10 +6283,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45751</v>
+        <v>44543</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6299,7 +6299,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.8</v>
+        <v>7.5</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6342,7 +6342,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 45990-2022</t>
+          <t>A 6946-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6352,14 +6352,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44846</v>
+        <v>46057</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6372,7 +6372,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>3.3</v>
+        <v>2.2</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6432,7 +6432,7 @@
         <v>45877</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6493,7 +6493,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 13990-2026</t>
+          <t>A 56782-2022</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6507,10 +6507,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46098</v>
+        <v>44894</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6523,7 +6523,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>2.6</v>
+        <v>0.5</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6566,7 +6566,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 143-2023</t>
+          <t>A 34244-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6580,10 +6580,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44928</v>
+        <v>45844</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6596,7 +6596,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.5</v>
+        <v>2.9</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6639,7 +6639,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 18851-2024</t>
+          <t>A 13990-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6653,10 +6653,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45426</v>
+        <v>46098</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6669,7 +6669,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6712,7 +6712,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 71835-2021</t>
+          <t>A 25624-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6726,10 +6726,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44543</v>
+        <v>45803</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6742,7 +6742,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>7.5</v>
+        <v>5</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6785,7 +6785,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 29952-2026</t>
+          <t>A 26812-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6799,10 +6799,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46205</v>
+        <v>45470</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6815,7 +6815,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6858,7 +6858,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 51724-2023</t>
+          <t>A 41442-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6872,10 +6872,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45222</v>
+        <v>45869</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6888,7 +6888,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>3.1</v>
+        <v>1.8</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6931,7 +6931,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 34392-2026</t>
+          <t>A 49985-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6945,10 +6945,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46254</v>
+        <v>45215</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6961,7 +6961,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7004,7 +7004,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 34387-2026</t>
+          <t>A 10810-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7018,10 +7018,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46254</v>
+        <v>44989</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7034,7 +7034,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7077,7 +7077,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 34386-2026</t>
+          <t>A 50071-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7091,10 +7091,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46254</v>
+        <v>45215</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7107,7 +7107,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.7</v>
+        <v>4</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7150,7 +7150,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 34396-2026</t>
+          <t>A 62128-2021</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7164,10 +7164,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46254</v>
+        <v>44502</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7180,7 +7180,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.8</v>
+        <v>1.8</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7223,7 +7223,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 30738-2026</t>
+          <t>A 21240-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7237,10 +7237,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46211</v>
+        <v>45058</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7253,7 +7253,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>3.5</v>
+        <v>2.3</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7296,7 +7296,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 661-2025</t>
+          <t>A 18851-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7310,10 +7310,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45664</v>
+        <v>45426</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7326,7 +7326,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7369,7 +7369,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 30859-2026</t>
+          <t>A 21389-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7383,10 +7383,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46212</v>
+        <v>45063</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>0.5</v>
+        <v>3.4</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7442,7 +7442,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 24461-2023</t>
+          <t>A 44176-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7456,10 +7456,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45082</v>
+        <v>45188</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7472,7 +7472,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.5</v>
+        <v>7.1</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7515,7 +7515,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 13880-2024</t>
+          <t>A 23457-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7529,10 +7529,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45391</v>
+        <v>45453</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7545,7 +7545,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>2.4</v>
+        <v>5.1</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7588,7 +7588,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 23457-2024</t>
+          <t>A 39714-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7602,10 +7602,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45453</v>
+        <v>45552</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7618,7 +7618,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>5.1</v>
+        <v>1.2</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7661,7 +7661,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 21389-2023</t>
+          <t>A 18852-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7675,10 +7675,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45063</v>
+        <v>45426</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7691,7 +7691,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>3.4</v>
+        <v>2.7</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7734,7 +7734,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 4262-2024</t>
+          <t>A 51724-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7748,10 +7748,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45324</v>
+        <v>45222</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7764,7 +7764,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>14</v>
+        <v>3.1</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7807,7 +7807,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 38262-2026</t>
+          <t>A 22731-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7821,10 +7821,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46281</v>
+        <v>46157</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7837,7 +7837,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>2.8</v>
+        <v>1.8</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7880,7 +7880,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 63319-2021</t>
+          <t>A 32391-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7894,10 +7894,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>44508</v>
+        <v>45837</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7910,7 +7910,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7953,7 +7953,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 10677-2025</t>
+          <t>A 23607-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7967,10 +7967,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45721</v>
+        <v>46163</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7983,7 +7983,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>7.4</v>
+        <v>5.3</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8026,7 +8026,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 10679-2025</t>
+          <t>A 25135-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45721</v>
+        <v>45798</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8056,7 +8056,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>4.4</v>
+        <v>1.1</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 11237-2025</t>
+          <t>A 29952-2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8113,10 +8113,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45726</v>
+        <v>46205</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8129,7 +8129,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>4.2</v>
+        <v>2</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8172,7 +8172,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 74285-2021</t>
+          <t>A 34386-2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8186,10 +8186,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>44558</v>
+        <v>46254</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8202,7 +8202,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8245,7 +8245,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 61417-2022</t>
+          <t>A 30738-2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8259,10 +8259,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>44916</v>
+        <v>46211</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8275,7 +8275,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8318,7 +8318,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 32272-2023</t>
+          <t>A 30859-2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8332,10 +8332,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45120</v>
+        <v>46212</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8348,7 +8348,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>4.9</v>
+        <v>0.5</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8391,7 +8391,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 32847-2023</t>
+          <t>A 34387-2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8405,10 +8405,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45124</v>
+        <v>46254</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8421,7 +8421,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>4.7</v>
+        <v>0.3</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8464,7 +8464,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 34244-2025</t>
+          <t>A 34396-2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8478,10 +8478,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45844</v>
+        <v>46254</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8494,7 +8494,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>2.9</v>
+        <v>0.8</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8537,7 +8537,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 25624-2025</t>
+          <t>A 34392-2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8551,10 +8551,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45803</v>
+        <v>46254</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8567,7 +8567,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>5</v>
+        <v>0.4</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8610,7 +8610,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 41442-2025</t>
+          <t>A 38262-2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8624,10 +8624,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45869</v>
+        <v>46281</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8640,7 +8640,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1.8</v>
+        <v>2.8</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8700,7 +8700,7 @@
         <v>45371</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>

--- a/Översikt KUNGÄLV.xlsx
+++ b/Översikt KUNGÄLV.xlsx
@@ -601,7 +601,7 @@
         <v>45548</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>45868</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -851,7 +851,7 @@
         <v>45526</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -965,7 +965,7 @@
         <v>45919</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
         <v>45695</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 4263-2024</t>
+          <t>A 59985-2025</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1188,10 +1188,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45324</v>
+        <v>45993</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1204,16 +1204,16 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>2.6</v>
+        <v>5.3</v>
       </c>
       <c r="J7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -1228,7 +1228,7 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1237,12 +1237,124 @@
         <v>4</v>
       </c>
       <c r="T7" t="n">
+        <v>19</v>
+      </c>
+      <c r="U7" t="n">
+        <v>19</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Blåmossa
+Västlig hakmossa
+Spillkråka
+Äkta lopplummer</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 59985-2025 artfynd.xlsx", "A 59985-2025")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 59985-2025 karta.png", "A 59985-2025")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 59985-2025 georefererad karta.tif", "A 59985-2025")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 59985-2025 FSC-klagomål.docx", "A 59985-2025")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 59985-2025 FSC-klagomål mail.docx", "A 59985-2025")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 59985-2025 tillsynsbegäran.docx", "A 59985-2025")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 59985-2025 tillsynsbegäran mail.docx", "A 59985-2025")</f>
+        <v/>
+      </c>
+      <c r="AE7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 59985-2025 prioriterade fågelarter.docx", "A 59985-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 4263-2024</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>45324</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>KUNGÄLV</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J8" t="n">
+        <v>3</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>4</v>
+      </c>
+      <c r="T8" t="n">
         <v>6</v>
       </c>
-      <c r="U7" t="n">
+      <c r="U8" t="n">
         <v>6</v>
       </c>
-      <c r="V7" s="2" t="inlineStr">
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>Mindre hackspett
 Klippfrullania
@@ -1250,148 +1362,36 @@
 Spillkråka</t>
         </is>
       </c>
-      <c r="W7">
+      <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 4263-2024 artfynd.xlsx", "A 4263-2024")</f>
         <v/>
       </c>
-      <c r="X7">
+      <c r="X8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 4263-2024 karta.png", "A 4263-2024")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 4263-2024 georefererad karta.tif", "A 4263-2024")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 4263-2024 FSC-klagomål.docx", "A 4263-2024")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 4263-2024 FSC-klagomål mail.docx", "A 4263-2024")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 4263-2024 tillsynsbegäran.docx", "A 4263-2024")</f>
         <v/>
       </c>
-      <c r="AD7">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 4263-2024 tillsynsbegäran mail.docx", "A 4263-2024")</f>
         <v/>
       </c>
-      <c r="AE7">
+      <c r="AE8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 4263-2024 prioriterade fågelarter.docx", "A 4263-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A 59985-2025</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>45993</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>KUNGÄLV</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="J8" t="n">
-        <v>2</v>
-      </c>
-      <c r="K8" t="n">
-        <v>2</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>4</v>
-      </c>
-      <c r="T8" t="n">
-        <v>19</v>
-      </c>
-      <c r="U8" t="n">
-        <v>19</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>Blåmossa
-Västlig hakmossa
-Spillkråka
-Äkta lopplummer</t>
-        </is>
-      </c>
-      <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 59985-2025 artfynd.xlsx", "A 59985-2025")</f>
-        <v/>
-      </c>
-      <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 59985-2025 karta.png", "A 59985-2025")</f>
-        <v/>
-      </c>
-      <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 59985-2025 georefererad karta.tif", "A 59985-2025")</f>
-        <v/>
-      </c>
-      <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 59985-2025 FSC-klagomål.docx", "A 59985-2025")</f>
-        <v/>
-      </c>
-      <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 59985-2025 FSC-klagomål mail.docx", "A 59985-2025")</f>
-        <v/>
-      </c>
-      <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 59985-2025 tillsynsbegäran.docx", "A 59985-2025")</f>
-        <v/>
-      </c>
-      <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 59985-2025 tillsynsbegäran mail.docx", "A 59985-2025")</f>
-        <v/>
-      </c>
-      <c r="AE8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 59985-2025 prioriterade fågelarter.docx", "A 59985-2025")</f>
         <v/>
       </c>
     </row>
@@ -1415,7 +1415,7 @@
         <v>45985</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>46199</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>45355</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>46212</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         <v>45957</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1970,7 +1970,7 @@
         <v>45974</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2076,7 +2076,7 @@
         <v>45979</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2169,7 +2169,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 5631-2024</t>
+          <t>A 30860-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2183,10 +2183,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45334</v>
+        <v>46212</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2199,16 +2199,16 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="J16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2223,7 +2223,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2239,362 +2239,362 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
+          <t>Grönsångare
+Västlig hakmossa</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 30860-2026 artfynd.xlsx", "A 30860-2026")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 30860-2026 karta.png", "A 30860-2026")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 30860-2026 georefererad karta.tif", "A 30860-2026")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 30860-2026 FSC-klagomål.docx", "A 30860-2026")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 30860-2026 FSC-klagomål mail.docx", "A 30860-2026")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 30860-2026 tillsynsbegäran.docx", "A 30860-2026")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 30860-2026 tillsynsbegäran mail.docx", "A 30860-2026")</f>
+        <v/>
+      </c>
+      <c r="AE16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 30860-2026 prioriterade fågelarter.docx", "A 30860-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 53007-2025</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>45957</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>KUNGÄLV</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2</v>
+      </c>
+      <c r="T17" t="n">
+        <v>5</v>
+      </c>
+      <c r="U17" t="n">
+        <v>5</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>Västlig hakmossa
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 53007-2025 artfynd.xlsx", "A 53007-2025")</f>
+        <v/>
+      </c>
+      <c r="X17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 53007-2025 karta.png", "A 53007-2025")</f>
+        <v/>
+      </c>
+      <c r="Y17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 53007-2025 georefererad karta.tif", "A 53007-2025")</f>
+        <v/>
+      </c>
+      <c r="AA17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 53007-2025 FSC-klagomål.docx", "A 53007-2025")</f>
+        <v/>
+      </c>
+      <c r="AB17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 53007-2025 FSC-klagomål mail.docx", "A 53007-2025")</f>
+        <v/>
+      </c>
+      <c r="AC17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 53007-2025 tillsynsbegäran.docx", "A 53007-2025")</f>
+        <v/>
+      </c>
+      <c r="AD17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 53007-2025 tillsynsbegäran mail.docx", "A 53007-2025")</f>
+        <v/>
+      </c>
+      <c r="AE17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 53007-2025 prioriterade fågelarter.docx", "A 53007-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>A 5631-2024</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>45334</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>KUNGÄLV</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
           <t>Vanlig groda
 Fläcknycklar</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 5631-2024 artfynd.xlsx", "A 5631-2024")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 5631-2024 karta.png", "A 5631-2024")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 5631-2024 georefererad karta.tif", "A 5631-2024")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 5631-2024 FSC-klagomål.docx", "A 5631-2024")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 5631-2024 FSC-klagomål mail.docx", "A 5631-2024")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 5631-2024 tillsynsbegäran.docx", "A 5631-2024")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 5631-2024 tillsynsbegäran mail.docx", "A 5631-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
         <is>
           <t>A 5637-2024</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
         <v>45334</v>
       </c>
-      <c r="E17" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>KUNGÄLV</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
+      <c r="E19" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>KUNGÄLV</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
         <v>1.8</v>
       </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
         <v>2</v>
       </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
         <v>2</v>
       </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
         <v>2</v>
       </c>
-      <c r="T17" t="n">
+      <c r="T19" t="n">
         <v>2</v>
       </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>Klofibbla
 Åkerrödtoppa</t>
         </is>
       </c>
-      <c r="W17">
+      <c r="W19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 5637-2024 artfynd.xlsx", "A 5637-2024")</f>
         <v/>
       </c>
-      <c r="X17">
+      <c r="X19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 5637-2024 karta.png", "A 5637-2024")</f>
         <v/>
       </c>
-      <c r="Y17">
+      <c r="Y19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 5637-2024 georefererad karta.tif", "A 5637-2024")</f>
         <v/>
       </c>
-      <c r="AA17">
+      <c r="AA19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 5637-2024 FSC-klagomål.docx", "A 5637-2024")</f>
         <v/>
       </c>
-      <c r="AB17">
+      <c r="AB19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 5637-2024 FSC-klagomål mail.docx", "A 5637-2024")</f>
         <v/>
       </c>
-      <c r="AC17">
+      <c r="AC19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 5637-2024 tillsynsbegäran.docx", "A 5637-2024")</f>
         <v/>
       </c>
-      <c r="AD17">
+      <c r="AD19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 5637-2024 tillsynsbegäran mail.docx", "A 5637-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 30860-2026</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>46212</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>KUNGÄLV</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="J18" t="n">
-        <v>1</v>
-      </c>
-      <c r="K18" t="n">
-        <v>1</v>
-      </c>
-      <c r="L18" t="n">
-        <v>1</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>1</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>Grönsångare
-Västlig hakmossa</t>
-        </is>
-      </c>
-      <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 30860-2026 artfynd.xlsx", "A 30860-2026")</f>
-        <v/>
-      </c>
-      <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 30860-2026 karta.png", "A 30860-2026")</f>
-        <v/>
-      </c>
-      <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 30860-2026 georefererad karta.tif", "A 30860-2026")</f>
-        <v/>
-      </c>
-      <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 30860-2026 FSC-klagomål.docx", "A 30860-2026")</f>
-        <v/>
-      </c>
-      <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 30860-2026 FSC-klagomål mail.docx", "A 30860-2026")</f>
-        <v/>
-      </c>
-      <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 30860-2026 tillsynsbegäran.docx", "A 30860-2026")</f>
-        <v/>
-      </c>
-      <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 30860-2026 tillsynsbegäran mail.docx", "A 30860-2026")</f>
-        <v/>
-      </c>
-      <c r="AE18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 30860-2026 prioriterade fågelarter.docx", "A 30860-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>A 53007-2025</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>45957</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>KUNGÄLV</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="J19" t="n">
-        <v>1</v>
-      </c>
-      <c r="K19" t="n">
-        <v>1</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2</v>
-      </c>
-      <c r="T19" t="n">
-        <v>5</v>
-      </c>
-      <c r="U19" t="n">
-        <v>5</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>Västlig hakmossa
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 53007-2025 artfynd.xlsx", "A 53007-2025")</f>
-        <v/>
-      </c>
-      <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 53007-2025 karta.png", "A 53007-2025")</f>
-        <v/>
-      </c>
-      <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 53007-2025 georefererad karta.tif", "A 53007-2025")</f>
-        <v/>
-      </c>
-      <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 53007-2025 FSC-klagomål.docx", "A 53007-2025")</f>
-        <v/>
-      </c>
-      <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 53007-2025 FSC-klagomål mail.docx", "A 53007-2025")</f>
-        <v/>
-      </c>
-      <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 53007-2025 tillsynsbegäran.docx", "A 53007-2025")</f>
-        <v/>
-      </c>
-      <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 53007-2025 tillsynsbegäran mail.docx", "A 53007-2025")</f>
-        <v/>
-      </c>
-      <c r="AE19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 53007-2025 prioriterade fågelarter.docx", "A 53007-2025")</f>
         <v/>
       </c>
     </row>
@@ -2618,7 +2618,7 @@
         <v>44838</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2706,7 +2706,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 49988-2023</t>
+          <t>A 23704-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2720,10 +2720,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45215</v>
+        <v>45454</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>2.3</v>
+        <v>4.9</v>
       </c>
       <c r="J21" t="n">
         <v>1</v>
@@ -2748,7 +2748,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -2760,58 +2760,58 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
       </c>
       <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
         <v>1</v>
       </c>
-      <c r="U21" t="n">
-        <v>0</v>
-      </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Hedjohannesört</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 49988-2023 artfynd.xlsx", "A 49988-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 23704-2024 artfynd.xlsx", "A 23704-2024")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 49988-2023 karta.png", "A 49988-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 23704-2024 karta.png", "A 23704-2024")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 49988-2023 georefererad karta.tif", "A 49988-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 23704-2024 georefererad karta.tif", "A 23704-2024")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 49988-2023 FSC-klagomål.docx", "A 49988-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 23704-2024 FSC-klagomål.docx", "A 23704-2024")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 49988-2023 FSC-klagomål mail.docx", "A 49988-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 23704-2024 FSC-klagomål mail.docx", "A 23704-2024")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 49988-2023 tillsynsbegäran.docx", "A 49988-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 23704-2024 tillsynsbegäran.docx", "A 23704-2024")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 49988-2023 tillsynsbegäran mail.docx", "A 49988-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 23704-2024 tillsynsbegäran mail.docx", "A 23704-2024")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 6082-2025</t>
+          <t>A 49988-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2825,10 +2825,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45697</v>
+        <v>45215</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2841,7 +2841,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
@@ -2877,50 +2877,46 @@
         <v>1</v>
       </c>
       <c r="U22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 6082-2025 artfynd.xlsx", "A 6082-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 49988-2023 artfynd.xlsx", "A 49988-2023")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 6082-2025 karta.png", "A 6082-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 49988-2023 karta.png", "A 49988-2023")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 6082-2025 georefererad karta.tif", "A 6082-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 49988-2023 georefererad karta.tif", "A 49988-2023")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 6082-2025 FSC-klagomål.docx", "A 6082-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 49988-2023 FSC-klagomål.docx", "A 49988-2023")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 6082-2025 FSC-klagomål mail.docx", "A 6082-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 49988-2023 FSC-klagomål mail.docx", "A 49988-2023")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 6082-2025 tillsynsbegäran.docx", "A 6082-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 49988-2023 tillsynsbegäran.docx", "A 49988-2023")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 6082-2025 tillsynsbegäran mail.docx", "A 6082-2025")</f>
-        <v/>
-      </c>
-      <c r="AE22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 6082-2025 prioriterade fågelarter.docx", "A 6082-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 49988-2023 tillsynsbegäran mail.docx", "A 49988-2023")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 23704-2024</t>
+          <t>A 30862-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2934,10 +2930,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45454</v>
+        <v>46212</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2950,7 +2946,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>4.9</v>
+        <v>1.7</v>
       </c>
       <c r="J23" t="n">
         <v>1</v>
@@ -2962,7 +2958,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
@@ -2974,58 +2970,58 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
       </c>
       <c r="T23" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="U23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Hedjohannesört</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 23704-2024 artfynd.xlsx", "A 23704-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 30862-2026 artfynd.xlsx", "A 30862-2026")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 23704-2024 karta.png", "A 23704-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 30862-2026 karta.png", "A 30862-2026")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 23704-2024 georefererad karta.tif", "A 23704-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 30862-2026 georefererad karta.tif", "A 30862-2026")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 23704-2024 FSC-klagomål.docx", "A 23704-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 30862-2026 FSC-klagomål.docx", "A 30862-2026")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 23704-2024 FSC-klagomål mail.docx", "A 23704-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 30862-2026 FSC-klagomål mail.docx", "A 30862-2026")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 23704-2024 tillsynsbegäran.docx", "A 23704-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 30862-2026 tillsynsbegäran.docx", "A 30862-2026")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 23704-2024 tillsynsbegäran mail.docx", "A 23704-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 30862-2026 tillsynsbegäran mail.docx", "A 30862-2026")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 30862-2026</t>
+          <t>A 6082-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3039,10 +3035,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46212</v>
+        <v>45697</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3055,7 +3051,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.7</v>
+        <v>2.8</v>
       </c>
       <c r="J24" t="n">
         <v>1</v>
@@ -3088,42 +3084,46 @@
         <v>1</v>
       </c>
       <c r="T24" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 30862-2026 artfynd.xlsx", "A 30862-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 6082-2025 artfynd.xlsx", "A 6082-2025")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 30862-2026 karta.png", "A 30862-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 6082-2025 karta.png", "A 6082-2025")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 30862-2026 georefererad karta.tif", "A 30862-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 6082-2025 georefererad karta.tif", "A 6082-2025")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 30862-2026 FSC-klagomål.docx", "A 30862-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 6082-2025 FSC-klagomål.docx", "A 6082-2025")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 30862-2026 FSC-klagomål mail.docx", "A 30862-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 6082-2025 FSC-klagomål mail.docx", "A 6082-2025")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 30862-2026 tillsynsbegäran.docx", "A 30862-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 6082-2025 tillsynsbegäran.docx", "A 6082-2025")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 30862-2026 tillsynsbegäran mail.docx", "A 30862-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 6082-2025 tillsynsbegäran mail.docx", "A 6082-2025")</f>
+        <v/>
+      </c>
+      <c r="AE24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 6082-2025 prioriterade fågelarter.docx", "A 6082-2025")</f>
         <v/>
       </c>
     </row>
@@ -3147,7 +3147,7 @@
         <v>44691</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
         <v>44691</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         <v>44836</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3366,7 +3366,7 @@
         <v>44760</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         <v>44760</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
         <v>44760</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3568,7 +3568,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 661-2025</t>
+          <t>A 17455-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3582,10 +3582,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45664</v>
+        <v>45757</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3598,7 +3598,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>3.1</v>
+        <v>2.1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3658,7 +3658,7 @@
         <v>45267</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3714,7 +3714,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 4204-2024</t>
+          <t>A 21240-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3728,10 +3728,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45324</v>
+        <v>45058</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3744,7 +3744,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>4.4</v>
+        <v>2.3</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3787,7 +3787,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 10679-2025</t>
+          <t>A 29223-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3801,10 +3801,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45721</v>
+        <v>45482</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3817,7 +3817,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>4.4</v>
+        <v>5.6</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3860,7 +3860,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 30170-2022</t>
+          <t>A 10655-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3874,10 +3874,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44757</v>
+        <v>44624</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3890,7 +3890,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>3.1</v>
+        <v>13.3</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3933,7 +3933,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 11237-2025</t>
+          <t>A 39714-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3947,10 +3947,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45726</v>
+        <v>45552</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3963,7 +3963,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>4.2</v>
+        <v>1.2</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4006,7 +4006,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 10677-2025</t>
+          <t>A 19531-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4020,10 +4020,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45721</v>
+        <v>45050</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>7.4</v>
+        <v>1.9</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4079,7 +4079,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 17922-2025</t>
+          <t>A 5705-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4089,14 +4089,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45758</v>
+        <v>45694</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4109,7 +4109,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4152,7 +4152,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 74285-2021</t>
+          <t>A 7505-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4166,10 +4166,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44558</v>
+        <v>45347</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4182,7 +4182,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4225,7 +4225,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 13880-2024</t>
+          <t>A 8334-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4239,10 +4239,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45391</v>
+        <v>44975</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4255,7 +4255,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4298,7 +4298,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 1995-2024</t>
+          <t>A 41442-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4312,10 +4312,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45308</v>
+        <v>45869</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4328,7 +4328,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4371,7 +4371,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 24461-2023</t>
+          <t>A 49985-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4385,10 +4385,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45082</v>
+        <v>45215</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4401,7 +4401,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4444,7 +4444,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 45990-2022</t>
+          <t>A 17922-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4458,10 +4458,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44846</v>
+        <v>45758</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4474,7 +4474,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>3.3</v>
+        <v>0.8</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4517,7 +4517,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 143-2023</t>
+          <t>A 40951-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4531,10 +4531,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44928</v>
+        <v>45897</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4547,7 +4547,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4590,7 +4590,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 63319-2021</t>
+          <t>A 50071-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4604,10 +4604,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44508</v>
+        <v>45215</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4620,7 +4620,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.6</v>
+        <v>4</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4663,7 +4663,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 40951-2025</t>
+          <t>A 45124-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4677,10 +4677,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45897</v>
+        <v>45919</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.8</v>
+        <v>3.7</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4736,7 +4736,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 7505-2024</t>
+          <t>A 47564-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4750,10 +4750,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45347</v>
+        <v>45931</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4766,7 +4766,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4809,7 +4809,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 43520-2022</t>
+          <t>A 49981-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4823,10 +4823,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44837</v>
+        <v>45215</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4882,7 +4882,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 45124-2025</t>
+          <t>A 56782-2022</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4896,10 +4896,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45919</v>
+        <v>44894</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4912,7 +4912,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>3.7</v>
+        <v>0.5</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4955,7 +4955,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 29223-2024</t>
+          <t>A 1995-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4969,10 +4969,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45482</v>
+        <v>45308</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4985,7 +4985,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>5.6</v>
+        <v>0.5</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5028,7 +5028,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 61417-2022</t>
+          <t>A 30170-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5042,10 +5042,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44916</v>
+        <v>44757</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5058,7 +5058,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5101,7 +5101,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 32272-2023</t>
+          <t>A 10810-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5115,10 +5115,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45120</v>
+        <v>44989</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5131,7 +5131,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>4.9</v>
+        <v>0.4</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5174,7 +5174,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 47564-2025</t>
+          <t>A 52932-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5188,10 +5188,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45931</v>
+        <v>45957</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5204,7 +5204,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2</v>
+        <v>3.4</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5247,7 +5247,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 32847-2023</t>
+          <t>A 4204-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5261,10 +5261,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45124</v>
+        <v>45324</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5277,7 +5277,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5320,7 +5320,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 10655-2022</t>
+          <t>A 62128-2021</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5334,10 +5334,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44624</v>
+        <v>44502</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5350,7 +5350,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>13.3</v>
+        <v>1.8</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5393,7 +5393,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 17455-2025</t>
+          <t>A 62979-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5403,14 +5403,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45757</v>
+        <v>45271</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5423,7 +5423,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>2.1</v>
+        <v>0.8</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5466,7 +5466,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 8334-2023</t>
+          <t>A 22731-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5480,10 +5480,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44975</v>
+        <v>46157</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5539,7 +5539,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 52932-2025</t>
+          <t>A 32391-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5553,10 +5553,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45957</v>
+        <v>45837</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5569,7 +5569,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>3.4</v>
+        <v>2.1</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5612,7 +5612,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 19531-2023</t>
+          <t>A 44176-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5626,10 +5626,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45050</v>
+        <v>45188</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5642,7 +5642,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.9</v>
+        <v>7.1</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5685,7 +5685,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 5705-2025</t>
+          <t>A 26812-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5695,14 +5695,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45694</v>
+        <v>45470</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5715,7 +5715,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5758,7 +5758,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 62979-2023</t>
+          <t>A 23607-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5768,14 +5768,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45271</v>
+        <v>46163</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5788,7 +5788,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.8</v>
+        <v>5.3</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5831,7 +5831,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 4262-2024</t>
+          <t>A 29801-2022</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5845,10 +5845,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45324</v>
+        <v>44755</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5861,7 +5861,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>14</v>
+        <v>4.8</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5904,7 +5904,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 16538-2025</t>
+          <t>A 18852-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5918,10 +5918,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45751</v>
+        <v>45426</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5934,7 +5934,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.8</v>
+        <v>2.7</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5977,7 +5977,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 29801-2022</t>
+          <t>A 43520-2022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5991,10 +5991,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44755</v>
+        <v>44837</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6007,7 +6007,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>4.8</v>
+        <v>1.5</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6050,7 +6050,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 49981-2023</t>
+          <t>A 25135-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6064,10 +6064,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45215</v>
+        <v>45798</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6080,7 +6080,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>2.5</v>
+        <v>1.1</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6140,7 +6140,7 @@
         <v>44792</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6213,7 +6213,7 @@
         <v>46048</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6269,7 +6269,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 71835-2021</t>
+          <t>A 6946-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6279,14 +6279,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44543</v>
+        <v>46057</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6299,7 +6299,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>7.5</v>
+        <v>2.2</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6342,7 +6342,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 6946-2026</t>
+          <t>A 16538-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6352,14 +6352,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46057</v>
+        <v>45751</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6372,7 +6372,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>2.2</v>
+        <v>0.8</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6415,7 +6415,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 37443-2025</t>
+          <t>A 45990-2022</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6429,10 +6429,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45877</v>
+        <v>44846</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6444,13 +6444,8 @@
           <t>KUNGÄLV</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I70" t="n">
-        <v>0.7</v>
+        <v>3.3</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6493,7 +6488,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 56782-2022</t>
+          <t>A 143-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6507,10 +6502,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44894</v>
+        <v>44928</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6566,7 +6561,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 34244-2025</t>
+          <t>A 37443-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6580,10 +6575,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45844</v>
+        <v>45877</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6595,8 +6590,13 @@
           <t>KUNGÄLV</t>
         </is>
       </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I72" t="n">
-        <v>2.9</v>
+        <v>0.7</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6639,7 +6639,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 13990-2026</t>
+          <t>A 18851-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6653,10 +6653,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46098</v>
+        <v>45426</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6669,7 +6669,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6712,7 +6712,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 25624-2025</t>
+          <t>A 13990-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6726,10 +6726,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45803</v>
+        <v>46098</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6742,7 +6742,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>5</v>
+        <v>2.6</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6785,7 +6785,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 26812-2024</t>
+          <t>A 71835-2021</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6799,10 +6799,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45470</v>
+        <v>44543</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6815,7 +6815,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.7</v>
+        <v>7.5</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6858,7 +6858,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 41442-2025</t>
+          <t>A 51724-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6872,10 +6872,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45869</v>
+        <v>45222</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6888,7 +6888,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.8</v>
+        <v>3.1</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6931,7 +6931,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 49985-2023</t>
+          <t>A 661-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6945,10 +6945,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45215</v>
+        <v>45664</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6961,7 +6961,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>8.199999999999999</v>
+        <v>3.1</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7004,7 +7004,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 10810-2023</t>
+          <t>A 24461-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7018,10 +7018,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44989</v>
+        <v>45082</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7034,7 +7034,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.4</v>
+        <v>1.5</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7077,7 +7077,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 50071-2023</t>
+          <t>A 13880-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7091,10 +7091,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45215</v>
+        <v>45391</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7107,7 +7107,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>4</v>
+        <v>2.4</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7150,7 +7150,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 62128-2021</t>
+          <t>A 29952-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7164,10 +7164,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44502</v>
+        <v>46205</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7180,7 +7180,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7223,7 +7223,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 21240-2023</t>
+          <t>A 34392-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7237,10 +7237,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45058</v>
+        <v>46254</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7253,7 +7253,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>2.3</v>
+        <v>0.4</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7296,7 +7296,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 18851-2024</t>
+          <t>A 34387-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7310,10 +7310,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45426</v>
+        <v>46254</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7326,7 +7326,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>2.7</v>
+        <v>0.3</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7369,7 +7369,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 21389-2023</t>
+          <t>A 34386-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7383,10 +7383,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45063</v>
+        <v>46254</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>3.4</v>
+        <v>0.7</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7442,7 +7442,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 44176-2023</t>
+          <t>A 34396-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7456,10 +7456,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45188</v>
+        <v>46254</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7472,7 +7472,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>7.1</v>
+        <v>0.8</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7515,7 +7515,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 23457-2024</t>
+          <t>A 30738-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7529,10 +7529,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45453</v>
+        <v>46211</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7545,7 +7545,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>5.1</v>
+        <v>3.5</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7588,7 +7588,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 39714-2024</t>
+          <t>A 30859-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7602,10 +7602,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45552</v>
+        <v>46212</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7618,7 +7618,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7661,7 +7661,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 18852-2024</t>
+          <t>A 23457-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7675,10 +7675,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45426</v>
+        <v>45453</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7691,7 +7691,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>2.7</v>
+        <v>5.1</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7734,7 +7734,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 51724-2023</t>
+          <t>A 21389-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7748,10 +7748,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45222</v>
+        <v>45063</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7764,7 +7764,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7807,7 +7807,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 22731-2026</t>
+          <t>A 4262-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7821,10 +7821,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46157</v>
+        <v>45324</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7837,7 +7837,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1.8</v>
+        <v>14</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7880,7 +7880,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 32391-2025</t>
+          <t>A 63319-2021</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7894,10 +7894,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45837</v>
+        <v>44508</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7910,7 +7910,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7953,7 +7953,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 23607-2026</t>
+          <t>A 38262-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7967,10 +7967,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46163</v>
+        <v>46281</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7983,7 +7983,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>5.3</v>
+        <v>2.8</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8026,7 +8026,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 25135-2025</t>
+          <t>A 10677-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45798</v>
+        <v>45721</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8056,7 +8056,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1.1</v>
+        <v>7.4</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 29952-2026</t>
+          <t>A 10679-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8113,10 +8113,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>46205</v>
+        <v>45721</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8129,7 +8129,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>2</v>
+        <v>4.4</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8172,7 +8172,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 34386-2026</t>
+          <t>A 11237-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8186,10 +8186,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>46254</v>
+        <v>45726</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8202,7 +8202,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>0.7</v>
+        <v>4.2</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8245,7 +8245,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 30738-2026</t>
+          <t>A 74285-2021</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8259,10 +8259,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>46211</v>
+        <v>44558</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8275,7 +8275,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>3.5</v>
+        <v>1.1</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8318,7 +8318,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 30859-2026</t>
+          <t>A 61417-2022</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8332,10 +8332,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>46212</v>
+        <v>44916</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8348,7 +8348,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>0.5</v>
+        <v>3.6</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8391,7 +8391,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 34387-2026</t>
+          <t>A 32272-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8405,10 +8405,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>46254</v>
+        <v>45120</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8421,7 +8421,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>0.3</v>
+        <v>4.9</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8464,7 +8464,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 34396-2026</t>
+          <t>A 32847-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8478,10 +8478,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>46254</v>
+        <v>45124</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8494,7 +8494,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>0.8</v>
+        <v>4.7</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8537,7 +8537,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 34392-2026</t>
+          <t>A 34244-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8551,10 +8551,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>46254</v>
+        <v>45844</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8567,7 +8567,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>0.4</v>
+        <v>2.9</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8610,7 +8610,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 38262-2026</t>
+          <t>A 25624-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8624,10 +8624,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>46281</v>
+        <v>45803</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8640,7 +8640,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>2.8</v>
+        <v>5</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8700,7 +8700,7 @@
         <v>45371</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>

--- a/Översikt KUNGÄLV.xlsx
+++ b/Översikt KUNGÄLV.xlsx
@@ -601,7 +601,7 @@
         <v>45548</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>45868</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -851,7 +851,7 @@
         <v>45526</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -965,7 +965,7 @@
         <v>45919</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
         <v>45695</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         <v>45993</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         <v>45324</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>45985</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>46199</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>45355</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>46212</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         <v>45957</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1970,7 +1970,7 @@
         <v>45974</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2076,7 +2076,7 @@
         <v>45979</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
         <v>46212</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
         <v>45957</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2406,7 +2406,7 @@
         <v>45334</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2512,7 +2512,7 @@
         <v>45334</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
         <v>44838</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2706,7 +2706,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 23704-2024</t>
+          <t>A 49988-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2720,10 +2720,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45454</v>
+        <v>45215</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>4.9</v>
+        <v>2.3</v>
       </c>
       <c r="J21" t="n">
         <v>1</v>
@@ -2748,7 +2748,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -2760,58 +2760,58 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
       </c>
       <c r="T21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Hedjohannesört</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 23704-2024 artfynd.xlsx", "A 23704-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 49988-2023 artfynd.xlsx", "A 49988-2023")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 23704-2024 karta.png", "A 23704-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 49988-2023 karta.png", "A 49988-2023")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 23704-2024 georefererad karta.tif", "A 23704-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 49988-2023 georefererad karta.tif", "A 49988-2023")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 23704-2024 FSC-klagomål.docx", "A 23704-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 49988-2023 FSC-klagomål.docx", "A 49988-2023")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 23704-2024 FSC-klagomål mail.docx", "A 23704-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 49988-2023 FSC-klagomål mail.docx", "A 49988-2023")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 23704-2024 tillsynsbegäran.docx", "A 23704-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 49988-2023 tillsynsbegäran.docx", "A 49988-2023")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 23704-2024 tillsynsbegäran mail.docx", "A 23704-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 49988-2023 tillsynsbegäran mail.docx", "A 49988-2023")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 49988-2023</t>
+          <t>A 6082-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2825,10 +2825,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45215</v>
+        <v>45697</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2841,7 +2841,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
@@ -2877,39 +2877,43 @@
         <v>1</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 49988-2023 artfynd.xlsx", "A 49988-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 6082-2025 artfynd.xlsx", "A 6082-2025")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 49988-2023 karta.png", "A 49988-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 6082-2025 karta.png", "A 6082-2025")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 49988-2023 georefererad karta.tif", "A 49988-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 6082-2025 georefererad karta.tif", "A 6082-2025")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 49988-2023 FSC-klagomål.docx", "A 49988-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 6082-2025 FSC-klagomål.docx", "A 6082-2025")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 49988-2023 FSC-klagomål mail.docx", "A 49988-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 6082-2025 FSC-klagomål mail.docx", "A 6082-2025")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 49988-2023 tillsynsbegäran.docx", "A 49988-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 6082-2025 tillsynsbegäran.docx", "A 6082-2025")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 49988-2023 tillsynsbegäran mail.docx", "A 49988-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 6082-2025 tillsynsbegäran mail.docx", "A 6082-2025")</f>
+        <v/>
+      </c>
+      <c r="AE22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 6082-2025 prioriterade fågelarter.docx", "A 6082-2025")</f>
         <v/>
       </c>
     </row>
@@ -2933,7 +2937,7 @@
         <v>46212</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3021,7 +3025,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 6082-2025</t>
+          <t>A 23704-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3035,10 +3039,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45697</v>
+        <v>45454</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3051,7 +3055,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.8</v>
+        <v>4.9</v>
       </c>
       <c r="J24" t="n">
         <v>1</v>
@@ -3063,7 +3067,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
@@ -3075,55 +3079,51 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
       </c>
       <c r="T24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U24" t="n">
         <v>1</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Hedjohannesört</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 6082-2025 artfynd.xlsx", "A 6082-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 23704-2024 artfynd.xlsx", "A 23704-2024")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 6082-2025 karta.png", "A 6082-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 23704-2024 karta.png", "A 23704-2024")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 6082-2025 georefererad karta.tif", "A 6082-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 23704-2024 georefererad karta.tif", "A 23704-2024")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 6082-2025 FSC-klagomål.docx", "A 6082-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 23704-2024 FSC-klagomål.docx", "A 23704-2024")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 6082-2025 FSC-klagomål mail.docx", "A 6082-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 23704-2024 FSC-klagomål mail.docx", "A 23704-2024")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 6082-2025 tillsynsbegäran.docx", "A 6082-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 23704-2024 tillsynsbegäran.docx", "A 23704-2024")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 6082-2025 tillsynsbegäran mail.docx", "A 6082-2025")</f>
-        <v/>
-      </c>
-      <c r="AE24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 6082-2025 prioriterade fågelarter.docx", "A 6082-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 23704-2024 tillsynsbegäran mail.docx", "A 23704-2024")</f>
         <v/>
       </c>
     </row>
@@ -3147,7 +3147,7 @@
         <v>44691</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
         <v>44691</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         <v>44836</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3366,7 +3366,7 @@
         <v>44760</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         <v>44760</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
         <v>44760</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3568,7 +3568,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 17455-2025</t>
+          <t>A 62221-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3582,10 +3582,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45757</v>
+        <v>45267</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3598,7 +3598,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2.1</v>
+        <v>1.3</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3641,7 +3641,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 62221-2023</t>
+          <t>A 4204-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3655,10 +3655,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45267</v>
+        <v>45324</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3671,7 +3671,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.3</v>
+        <v>4.4</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3714,7 +3714,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 21240-2023</t>
+          <t>A 30170-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3728,10 +3728,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45058</v>
+        <v>44757</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3744,7 +3744,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3787,7 +3787,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 29223-2024</t>
+          <t>A 13880-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3801,10 +3801,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45482</v>
+        <v>45391</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3817,7 +3817,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>5.6</v>
+        <v>2.4</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3860,7 +3860,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 10655-2022</t>
+          <t>A 1995-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3874,10 +3874,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44624</v>
+        <v>45308</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3890,7 +3890,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>13.3</v>
+        <v>0.5</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3933,7 +3933,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 39714-2024</t>
+          <t>A 45990-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3947,10 +3947,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45552</v>
+        <v>44846</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3963,7 +3963,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.2</v>
+        <v>3.3</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4006,7 +4006,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 19531-2023</t>
+          <t>A 74285-2021</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4020,10 +4020,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45050</v>
+        <v>44558</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4079,7 +4079,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 5705-2025</t>
+          <t>A 17922-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4089,14 +4089,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45694</v>
+        <v>45758</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4109,7 +4109,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4152,7 +4152,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 7505-2024</t>
+          <t>A 43520-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4166,10 +4166,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45347</v>
+        <v>44837</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4182,7 +4182,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4225,7 +4225,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 8334-2023</t>
+          <t>A 34366-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4239,10 +4239,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44975</v>
+        <v>44792</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4255,7 +4255,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4298,7 +4298,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 41442-2025</t>
+          <t>A 4673-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4312,10 +4312,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45869</v>
+        <v>46048</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4328,7 +4328,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4371,7 +4371,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 49985-2023</t>
+          <t>A 40951-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4385,10 +4385,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45215</v>
+        <v>45897</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4401,7 +4401,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>8.199999999999999</v>
+        <v>0.8</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4444,7 +4444,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 17922-2025</t>
+          <t>A 29223-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4458,10 +4458,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45758</v>
+        <v>45482</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4474,7 +4474,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.8</v>
+        <v>5.6</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4517,7 +4517,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 40951-2025</t>
+          <t>A 6946-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4527,14 +4527,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45897</v>
+        <v>46057</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4547,7 +4547,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.8</v>
+        <v>2.2</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4590,7 +4590,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 50071-2023</t>
+          <t>A 45124-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4604,10 +4604,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45215</v>
+        <v>45919</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4620,7 +4620,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4663,7 +4663,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 45124-2025</t>
+          <t>A 8334-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4677,10 +4677,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45919</v>
+        <v>44975</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>3.7</v>
+        <v>1.8</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4753,7 +4753,7 @@
         <v>45931</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4809,7 +4809,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 49981-2023</t>
+          <t>A 61417-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4823,10 +4823,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45215</v>
+        <v>44916</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2.5</v>
+        <v>3.6</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4882,7 +4882,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 56782-2022</t>
+          <t>A 37443-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4896,10 +4896,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44894</v>
+        <v>45877</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4911,8 +4911,13 @@
           <t>KUNGÄLV</t>
         </is>
       </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I49" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4955,7 +4960,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 1995-2024</t>
+          <t>A 13990-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4969,10 +4974,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45308</v>
+        <v>46098</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4985,7 +4990,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.5</v>
+        <v>2.6</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5028,7 +5033,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 30170-2022</t>
+          <t>A 32272-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5042,10 +5047,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44757</v>
+        <v>45120</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5058,7 +5063,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>3.1</v>
+        <v>4.9</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5101,7 +5106,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 10810-2023</t>
+          <t>A 32847-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5115,10 +5120,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44989</v>
+        <v>45124</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5131,7 +5136,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.4</v>
+        <v>4.7</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5191,7 +5196,7 @@
         <v>45957</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5247,7 +5252,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 4204-2024</t>
+          <t>A 4262-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5264,7 +5269,7 @@
         <v>45324</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5277,7 +5282,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>4.4</v>
+        <v>14</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5320,7 +5325,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 62128-2021</t>
+          <t>A 49985-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5334,10 +5339,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44502</v>
+        <v>45215</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5350,7 +5355,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5393,7 +5398,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 62979-2023</t>
+          <t>A 661-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5403,14 +5408,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45271</v>
+        <v>45664</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5423,7 +5428,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.8</v>
+        <v>3.1</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5466,7 +5471,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 22731-2026</t>
+          <t>A 50071-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5480,10 +5485,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46157</v>
+        <v>45215</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5496,7 +5501,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.8</v>
+        <v>4</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5539,7 +5544,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 32391-2025</t>
+          <t>A 24461-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5553,10 +5558,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45837</v>
+        <v>45082</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5569,7 +5574,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5612,7 +5617,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 44176-2023</t>
+          <t>A 143-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5626,10 +5631,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45188</v>
+        <v>44928</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5642,7 +5647,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>7.1</v>
+        <v>0.5</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5685,7 +5690,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 26812-2024</t>
+          <t>A 22731-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5699,10 +5704,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45470</v>
+        <v>46157</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5715,7 +5720,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5758,7 +5763,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 23607-2026</t>
+          <t>A 32391-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5772,10 +5777,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46163</v>
+        <v>45837</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5788,7 +5793,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>5.3</v>
+        <v>2.1</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5831,7 +5836,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 29801-2022</t>
+          <t>A 63319-2021</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5845,10 +5850,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44755</v>
+        <v>44508</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5861,7 +5866,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>4.8</v>
+        <v>1.6</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5904,7 +5909,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 18852-2024</t>
+          <t>A 23607-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5918,10 +5923,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45426</v>
+        <v>46163</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5934,7 +5939,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>2.7</v>
+        <v>5.3</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5977,7 +5982,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 43520-2022</t>
+          <t>A 34244-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5991,10 +5996,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44837</v>
+        <v>45844</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6007,7 +6012,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.5</v>
+        <v>2.9</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6067,7 +6072,7 @@
         <v>45798</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6123,7 +6128,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 34366-2022</t>
+          <t>A 25624-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6137,10 +6142,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44792</v>
+        <v>45803</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6153,7 +6158,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.5</v>
+        <v>5</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6196,7 +6201,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 4673-2026</t>
+          <t>A 7505-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6210,10 +6215,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46048</v>
+        <v>45347</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6226,7 +6231,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>8.199999999999999</v>
+        <v>1.8</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6269,7 +6274,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 6946-2026</t>
+          <t>A 41442-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6279,14 +6284,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46057</v>
+        <v>45869</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6299,7 +6304,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6342,7 +6347,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 16538-2025</t>
+          <t>A 10655-2022</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6356,10 +6361,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45751</v>
+        <v>44624</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6372,7 +6377,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.8</v>
+        <v>13.3</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6415,7 +6420,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 45990-2022</t>
+          <t>A 17455-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6429,10 +6434,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44846</v>
+        <v>45757</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6445,7 +6450,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>3.3</v>
+        <v>2.1</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6488,7 +6493,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 143-2023</t>
+          <t>A 29952-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6502,10 +6507,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44928</v>
+        <v>46205</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6518,7 +6523,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6561,7 +6566,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 37443-2025</t>
+          <t>A 19531-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6575,10 +6580,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45877</v>
+        <v>45050</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6590,13 +6595,8 @@
           <t>KUNGÄLV</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I72" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6639,7 +6639,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 18851-2024</t>
+          <t>A 34386-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6653,10 +6653,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45426</v>
+        <v>46254</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6669,7 +6669,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>2.7</v>
+        <v>0.7</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6712,7 +6712,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 13990-2026</t>
+          <t>A 30738-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6726,10 +6726,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46098</v>
+        <v>46211</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6742,7 +6742,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>2.6</v>
+        <v>3.5</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6785,7 +6785,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 71835-2021</t>
+          <t>A 30859-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6799,10 +6799,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44543</v>
+        <v>46212</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6815,7 +6815,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>7.5</v>
+        <v>0.5</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6858,7 +6858,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 51724-2023</t>
+          <t>A 34387-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6872,10 +6872,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45222</v>
+        <v>46254</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6888,7 +6888,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>3.1</v>
+        <v>0.3</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6931,7 +6931,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 661-2025</t>
+          <t>A 34396-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6945,10 +6945,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45664</v>
+        <v>46254</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6961,7 +6961,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>3.1</v>
+        <v>0.8</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7004,7 +7004,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 24461-2023</t>
+          <t>A 34392-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7018,10 +7018,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45082</v>
+        <v>46254</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7034,7 +7034,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.5</v>
+        <v>0.4</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7077,7 +7077,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 13880-2024</t>
+          <t>A 5705-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7087,14 +7087,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45391</v>
+        <v>45694</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7107,7 +7107,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>2.4</v>
+        <v>1.2</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7150,7 +7150,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 29952-2026</t>
+          <t>A 62979-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7160,14 +7160,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46205</v>
+        <v>45271</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7180,7 +7180,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7223,7 +7223,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 34392-2026</t>
+          <t>A 16538-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7237,10 +7237,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46254</v>
+        <v>45751</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7253,7 +7253,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7296,7 +7296,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 34387-2026</t>
+          <t>A 29801-2022</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7310,10 +7310,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46254</v>
+        <v>44755</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7326,7 +7326,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.3</v>
+        <v>4.8</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7369,7 +7369,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 34386-2026</t>
+          <t>A 49981-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7383,10 +7383,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46254</v>
+        <v>45215</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>0.7</v>
+        <v>2.5</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7442,7 +7442,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 34396-2026</t>
+          <t>A 71835-2021</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7456,10 +7456,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46254</v>
+        <v>44543</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7472,7 +7472,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>0.8</v>
+        <v>7.5</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7515,7 +7515,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 30738-2026</t>
+          <t>A 38262-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7529,10 +7529,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46211</v>
+        <v>46281</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7545,7 +7545,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7588,7 +7588,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 30859-2026</t>
+          <t>A 56782-2022</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7602,10 +7602,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46212</v>
+        <v>44894</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7661,7 +7661,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 23457-2024</t>
+          <t>A 26812-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7675,10 +7675,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45453</v>
+        <v>45470</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7691,7 +7691,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>5.1</v>
+        <v>1.7</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7734,7 +7734,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 21389-2023</t>
+          <t>A 10810-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7748,10 +7748,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45063</v>
+        <v>44989</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7764,7 +7764,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>3.4</v>
+        <v>0.4</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7807,7 +7807,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 4262-2024</t>
+          <t>A 62128-2021</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7821,10 +7821,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45324</v>
+        <v>44502</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7837,7 +7837,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>14</v>
+        <v>1.8</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7880,7 +7880,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 63319-2021</t>
+          <t>A 21240-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7894,10 +7894,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>44508</v>
+        <v>45058</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7910,7 +7910,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7953,7 +7953,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 38262-2026</t>
+          <t>A 18851-2024</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7967,10 +7967,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46281</v>
+        <v>45426</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7983,7 +7983,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8026,7 +8026,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 10677-2025</t>
+          <t>A 21389-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45721</v>
+        <v>45063</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8056,7 +8056,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>7.4</v>
+        <v>3.4</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 10679-2025</t>
+          <t>A 44176-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8113,10 +8113,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45721</v>
+        <v>45188</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8129,7 +8129,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>4.4</v>
+        <v>7.1</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8172,7 +8172,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 11237-2025</t>
+          <t>A 23457-2024</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8186,10 +8186,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45726</v>
+        <v>45453</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8202,7 +8202,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>4.2</v>
+        <v>5.1</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8245,7 +8245,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 74285-2021</t>
+          <t>A 39714-2024</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8259,10 +8259,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>44558</v>
+        <v>45552</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8275,7 +8275,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8318,7 +8318,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 61417-2022</t>
+          <t>A 18852-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8332,10 +8332,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>44916</v>
+        <v>45426</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8348,7 +8348,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>3.6</v>
+        <v>2.7</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8391,7 +8391,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 32272-2023</t>
+          <t>A 51724-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8405,10 +8405,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45120</v>
+        <v>45222</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8421,7 +8421,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>4.9</v>
+        <v>3.1</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8464,7 +8464,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 32847-2023</t>
+          <t>A 10679-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8478,10 +8478,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45124</v>
+        <v>45721</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8494,7 +8494,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8537,7 +8537,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 34244-2025</t>
+          <t>A 11237-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8551,10 +8551,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45844</v>
+        <v>45726</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8567,7 +8567,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>2.9</v>
+        <v>4.2</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8610,7 +8610,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 25624-2025</t>
+          <t>A 10677-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8624,10 +8624,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45803</v>
+        <v>45721</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8640,7 +8640,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>5</v>
+        <v>7.4</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8700,7 +8700,7 @@
         <v>45371</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>

--- a/Översikt KUNGÄLV.xlsx
+++ b/Översikt KUNGÄLV.xlsx
@@ -601,7 +601,7 @@
         <v>45548</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>45868</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -851,7 +851,7 @@
         <v>45526</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -965,7 +965,7 @@
         <v>45919</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
         <v>45695</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         <v>45993</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         <v>45324</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>45985</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>46199</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>45355</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>46212</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         <v>45957</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1970,7 +1970,7 @@
         <v>45974</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2076,7 +2076,7 @@
         <v>45979</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
         <v>46212</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
         <v>45957</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2406,7 +2406,7 @@
         <v>45334</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2512,7 +2512,7 @@
         <v>45334</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
         <v>44838</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2723,7 +2723,7 @@
         <v>45215</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2828,7 +2828,7 @@
         <v>45697</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2937,7 +2937,7 @@
         <v>46212</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3042,7 +3042,7 @@
         <v>45454</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>44691</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
         <v>44691</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         <v>44836</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3366,7 +3366,7 @@
         <v>44760</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         <v>44760</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
         <v>44760</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3585,7 +3585,7 @@
         <v>45267</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3658,7 +3658,7 @@
         <v>45324</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3731,7 +3731,7 @@
         <v>44757</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3804,7 +3804,7 @@
         <v>45391</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3877,7 +3877,7 @@
         <v>45308</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3950,7 +3950,7 @@
         <v>44846</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4023,7 +4023,7 @@
         <v>44558</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4096,7 +4096,7 @@
         <v>45758</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
         <v>44837</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4242,7 +4242,7 @@
         <v>44792</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4315,7 +4315,7 @@
         <v>46048</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4388,7 +4388,7 @@
         <v>45897</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4461,7 +4461,7 @@
         <v>45482</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4534,7 +4534,7 @@
         <v>46057</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4607,7 +4607,7 @@
         <v>45919</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4680,7 +4680,7 @@
         <v>44975</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4753,7 +4753,7 @@
         <v>45931</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4826,7 +4826,7 @@
         <v>44916</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4899,7 +4899,7 @@
         <v>45877</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4977,7 +4977,7 @@
         <v>46098</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5050,7 +5050,7 @@
         <v>45120</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5123,7 +5123,7 @@
         <v>45124</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5196,7 +5196,7 @@
         <v>45957</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5269,7 +5269,7 @@
         <v>45324</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5342,7 +5342,7 @@
         <v>45215</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5415,7 +5415,7 @@
         <v>45664</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5488,7 +5488,7 @@
         <v>45215</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5561,7 +5561,7 @@
         <v>45082</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5634,7 +5634,7 @@
         <v>44928</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5707,7 +5707,7 @@
         <v>46157</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5780,7 +5780,7 @@
         <v>45837</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5853,7 +5853,7 @@
         <v>44508</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5926,7 +5926,7 @@
         <v>46163</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         <v>45844</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6072,7 +6072,7 @@
         <v>45798</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6145,7 +6145,7 @@
         <v>45803</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6218,7 +6218,7 @@
         <v>45347</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6291,7 +6291,7 @@
         <v>45869</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6364,7 +6364,7 @@
         <v>44624</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6437,7 +6437,7 @@
         <v>45757</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6510,7 +6510,7 @@
         <v>46205</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6583,7 +6583,7 @@
         <v>45050</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6656,7 +6656,7 @@
         <v>46254</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6729,7 +6729,7 @@
         <v>46211</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6802,7 +6802,7 @@
         <v>46212</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6875,7 +6875,7 @@
         <v>46254</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6948,7 +6948,7 @@
         <v>46254</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7021,7 +7021,7 @@
         <v>46254</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7094,7 +7094,7 @@
         <v>45694</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7167,7 +7167,7 @@
         <v>45271</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7240,7 +7240,7 @@
         <v>45751</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7313,7 +7313,7 @@
         <v>44755</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7386,7 +7386,7 @@
         <v>45215</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7459,7 +7459,7 @@
         <v>44543</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7532,7 +7532,7 @@
         <v>46281</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7605,7 +7605,7 @@
         <v>44894</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7678,7 +7678,7 @@
         <v>45470</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7751,7 +7751,7 @@
         <v>44989</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7824,7 +7824,7 @@
         <v>44502</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7897,7 +7897,7 @@
         <v>45058</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7970,7 +7970,7 @@
         <v>45426</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         <v>45063</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8116,7 +8116,7 @@
         <v>45188</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8189,7 +8189,7 @@
         <v>45453</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8262,7 +8262,7 @@
         <v>45552</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8335,7 +8335,7 @@
         <v>45426</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8408,7 +8408,7 @@
         <v>45222</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8481,7 +8481,7 @@
         <v>45721</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8554,7 +8554,7 @@
         <v>45726</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8627,7 +8627,7 @@
         <v>45721</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8700,7 +8700,7 @@
         <v>45371</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>

--- a/Översikt KUNGÄLV.xlsx
+++ b/Översikt KUNGÄLV.xlsx
@@ -601,7 +601,7 @@
         <v>45548</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>45868</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -851,7 +851,7 @@
         <v>45526</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -965,7 +965,7 @@
         <v>45919</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
         <v>45695</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         <v>45993</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         <v>45324</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>45985</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>46199</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>45355</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>46212</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         <v>45957</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1970,7 +1970,7 @@
         <v>45974</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2076,7 +2076,7 @@
         <v>45979</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
         <v>46212</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
         <v>45957</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2406,7 +2406,7 @@
         <v>45334</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2512,7 +2512,7 @@
         <v>45334</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
         <v>44838</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2723,7 +2723,7 @@
         <v>45215</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2828,7 +2828,7 @@
         <v>45697</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2937,7 +2937,7 @@
         <v>46212</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3042,7 +3042,7 @@
         <v>45454</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>44691</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
         <v>44691</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         <v>44836</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3366,7 +3366,7 @@
         <v>44760</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         <v>44760</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
         <v>44760</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3585,7 +3585,7 @@
         <v>45267</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3658,7 +3658,7 @@
         <v>45324</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3731,7 +3731,7 @@
         <v>44757</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3804,7 +3804,7 @@
         <v>45391</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3877,7 +3877,7 @@
         <v>45308</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3950,7 +3950,7 @@
         <v>44846</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4023,7 +4023,7 @@
         <v>44558</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4096,7 +4096,7 @@
         <v>45758</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
         <v>44837</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4242,7 +4242,7 @@
         <v>44792</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4315,7 +4315,7 @@
         <v>46048</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4388,7 +4388,7 @@
         <v>45897</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4461,7 +4461,7 @@
         <v>45482</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4534,7 +4534,7 @@
         <v>46057</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4607,7 +4607,7 @@
         <v>45919</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4680,7 +4680,7 @@
         <v>44975</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4753,7 +4753,7 @@
         <v>45931</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4826,7 +4826,7 @@
         <v>44916</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4899,7 +4899,7 @@
         <v>45877</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4977,7 +4977,7 @@
         <v>46098</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5050,7 +5050,7 @@
         <v>45120</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5123,7 +5123,7 @@
         <v>45124</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5196,7 +5196,7 @@
         <v>45957</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5269,7 +5269,7 @@
         <v>45324</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5342,7 +5342,7 @@
         <v>45215</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5415,7 +5415,7 @@
         <v>45664</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5488,7 +5488,7 @@
         <v>45215</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5561,7 +5561,7 @@
         <v>45082</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5634,7 +5634,7 @@
         <v>44928</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5707,7 +5707,7 @@
         <v>46157</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5780,7 +5780,7 @@
         <v>45837</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5853,7 +5853,7 @@
         <v>44508</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5926,7 +5926,7 @@
         <v>46163</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         <v>45844</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6072,7 +6072,7 @@
         <v>45798</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6145,7 +6145,7 @@
         <v>45803</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6218,7 +6218,7 @@
         <v>45347</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6291,7 +6291,7 @@
         <v>45869</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6364,7 +6364,7 @@
         <v>44624</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6437,7 +6437,7 @@
         <v>45757</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6510,7 +6510,7 @@
         <v>46205</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6583,7 +6583,7 @@
         <v>45050</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6656,7 +6656,7 @@
         <v>46254</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6729,7 +6729,7 @@
         <v>46211</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6802,7 +6802,7 @@
         <v>46212</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6875,7 +6875,7 @@
         <v>46254</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6948,7 +6948,7 @@
         <v>46254</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7021,7 +7021,7 @@
         <v>46254</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7094,7 +7094,7 @@
         <v>45694</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7167,7 +7167,7 @@
         <v>45271</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7240,7 +7240,7 @@
         <v>45751</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7313,7 +7313,7 @@
         <v>44755</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7386,7 +7386,7 @@
         <v>45215</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7459,7 +7459,7 @@
         <v>44543</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7532,7 +7532,7 @@
         <v>46281</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7605,7 +7605,7 @@
         <v>44894</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7678,7 +7678,7 @@
         <v>45470</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7751,7 +7751,7 @@
         <v>44989</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7824,7 +7824,7 @@
         <v>44502</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7897,7 +7897,7 @@
         <v>45058</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7970,7 +7970,7 @@
         <v>45426</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         <v>45063</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8116,7 +8116,7 @@
         <v>45188</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8189,7 +8189,7 @@
         <v>45453</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8262,7 +8262,7 @@
         <v>45552</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8335,7 +8335,7 @@
         <v>45426</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8408,7 +8408,7 @@
         <v>45222</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8481,7 +8481,7 @@
         <v>45721</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8554,7 +8554,7 @@
         <v>45726</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8627,7 +8627,7 @@
         <v>45721</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8700,7 +8700,7 @@
         <v>45371</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>

--- a/Översikt KUNGÄLV.xlsx
+++ b/Översikt KUNGÄLV.xlsx
@@ -601,7 +601,7 @@
         <v>45548</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>45868</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -851,7 +851,7 @@
         <v>45526</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -965,7 +965,7 @@
         <v>45919</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
         <v>45695</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         <v>45993</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         <v>45324</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>45985</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>46199</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>45355</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>46212</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         <v>45957</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 56394-2025</t>
+          <t>A 57116-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1963,14 +1963,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45974</v>
+        <v>45979</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1983,7 +1983,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.3</v>
+        <v>3.5</v>
       </c>
       <c r="J14" t="n">
         <v>1</v>
@@ -2016,585 +2016,585 @@
         <v>2</v>
       </c>
       <c r="T14" t="n">
+        <v>3</v>
+      </c>
+      <c r="U14" t="n">
+        <v>3</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Västlig hakmossa
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 57116-2025 artfynd.xlsx", "A 57116-2025")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 57116-2025 karta.png", "A 57116-2025")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 57116-2025 georefererad karta.tif", "A 57116-2025")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 57116-2025 FSC-klagomål.docx", "A 57116-2025")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 57116-2025 FSC-klagomål mail.docx", "A 57116-2025")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 57116-2025 tillsynsbegäran.docx", "A 57116-2025")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 57116-2025 tillsynsbegäran mail.docx", "A 57116-2025")</f>
+        <v/>
+      </c>
+      <c r="AE14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 57116-2025 prioriterade fågelarter.docx", "A 57116-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 56394-2025</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>45974</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>KUNGÄLV</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
         <v>2</v>
       </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
         <is>
           <t>Kambräken
 Revlummer</t>
         </is>
       </c>
-      <c r="W14">
+      <c r="W15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 56394-2025 artfynd.xlsx", "A 56394-2025")</f>
         <v/>
       </c>
-      <c r="X14">
+      <c r="X15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 56394-2025 karta.png", "A 56394-2025")</f>
         <v/>
       </c>
-      <c r="Y14">
+      <c r="Y15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 56394-2025 georefererad karta.tif", "A 56394-2025")</f>
         <v/>
       </c>
-      <c r="AA14">
+      <c r="AA15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 56394-2025 FSC-klagomål.docx", "A 56394-2025")</f>
         <v/>
       </c>
-      <c r="AB14">
+      <c r="AB15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 56394-2025 FSC-klagomål mail.docx", "A 56394-2025")</f>
         <v/>
       </c>
-      <c r="AC14">
+      <c r="AC15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 56394-2025 tillsynsbegäran.docx", "A 56394-2025")</f>
         <v/>
       </c>
-      <c r="AD14">
+      <c r="AD15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 56394-2025 tillsynsbegäran mail.docx", "A 56394-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 57116-2025</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>45979</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>KUNGÄLV</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="J15" t="n">
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 30860-2026</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>46212</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>KUNGÄLV</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J16" t="n">
         <v>1</v>
       </c>
-      <c r="K15" t="n">
+      <c r="K16" t="n">
         <v>1</v>
       </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
+      <c r="L16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
         <v>2</v>
       </c>
-      <c r="T15" t="n">
-        <v>3</v>
-      </c>
-      <c r="U15" t="n">
-        <v>3</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Grönsångare
+Västlig hakmossa</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 30860-2026 artfynd.xlsx", "A 30860-2026")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 30860-2026 karta.png", "A 30860-2026")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 30860-2026 georefererad karta.tif", "A 30860-2026")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 30860-2026 FSC-klagomål.docx", "A 30860-2026")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 30860-2026 FSC-klagomål mail.docx", "A 30860-2026")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 30860-2026 tillsynsbegäran.docx", "A 30860-2026")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 30860-2026 tillsynsbegäran mail.docx", "A 30860-2026")</f>
+        <v/>
+      </c>
+      <c r="AE16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 30860-2026 prioriterade fågelarter.docx", "A 30860-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 5631-2024</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>45334</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>KUNGÄLV</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>Vanlig groda
+Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="W17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 5631-2024 artfynd.xlsx", "A 5631-2024")</f>
+        <v/>
+      </c>
+      <c r="X17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 5631-2024 karta.png", "A 5631-2024")</f>
+        <v/>
+      </c>
+      <c r="Y17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 5631-2024 georefererad karta.tif", "A 5631-2024")</f>
+        <v/>
+      </c>
+      <c r="AA17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 5631-2024 FSC-klagomål.docx", "A 5631-2024")</f>
+        <v/>
+      </c>
+      <c r="AB17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 5631-2024 FSC-klagomål mail.docx", "A 5631-2024")</f>
+        <v/>
+      </c>
+      <c r="AC17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 5631-2024 tillsynsbegäran.docx", "A 5631-2024")</f>
+        <v/>
+      </c>
+      <c r="AD17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 5631-2024 tillsynsbegäran mail.docx", "A 5631-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>A 5637-2024</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>45334</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>KUNGÄLV</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>2</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>Klofibbla
+Åkerrödtoppa</t>
+        </is>
+      </c>
+      <c r="W18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 5637-2024 artfynd.xlsx", "A 5637-2024")</f>
+        <v/>
+      </c>
+      <c r="X18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 5637-2024 karta.png", "A 5637-2024")</f>
+        <v/>
+      </c>
+      <c r="Y18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 5637-2024 georefererad karta.tif", "A 5637-2024")</f>
+        <v/>
+      </c>
+      <c r="AA18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 5637-2024 FSC-klagomål.docx", "A 5637-2024")</f>
+        <v/>
+      </c>
+      <c r="AB18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 5637-2024 FSC-klagomål mail.docx", "A 5637-2024")</f>
+        <v/>
+      </c>
+      <c r="AC18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 5637-2024 tillsynsbegäran.docx", "A 5637-2024")</f>
+        <v/>
+      </c>
+      <c r="AD18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 5637-2024 tillsynsbegäran mail.docx", "A 5637-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>A 53007-2025</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>45957</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>KUNGÄLV</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2</v>
+      </c>
+      <c r="T19" t="n">
+        <v>5</v>
+      </c>
+      <c r="U19" t="n">
+        <v>5</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>Västlig hakmossa
 Spillkråka</t>
         </is>
       </c>
-      <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 57116-2025 artfynd.xlsx", "A 57116-2025")</f>
-        <v/>
-      </c>
-      <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 57116-2025 karta.png", "A 57116-2025")</f>
-        <v/>
-      </c>
-      <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 57116-2025 georefererad karta.tif", "A 57116-2025")</f>
-        <v/>
-      </c>
-      <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 57116-2025 FSC-klagomål.docx", "A 57116-2025")</f>
-        <v/>
-      </c>
-      <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 57116-2025 FSC-klagomål mail.docx", "A 57116-2025")</f>
-        <v/>
-      </c>
-      <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 57116-2025 tillsynsbegäran.docx", "A 57116-2025")</f>
-        <v/>
-      </c>
-      <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 57116-2025 tillsynsbegäran mail.docx", "A 57116-2025")</f>
-        <v/>
-      </c>
-      <c r="AE15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 57116-2025 prioriterade fågelarter.docx", "A 57116-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 30860-2026</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>46212</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>KUNGÄLV</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="J16" t="n">
-        <v>1</v>
-      </c>
-      <c r="K16" t="n">
-        <v>1</v>
-      </c>
-      <c r="L16" t="n">
-        <v>1</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>Grönsångare
-Västlig hakmossa</t>
-        </is>
-      </c>
-      <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 30860-2026 artfynd.xlsx", "A 30860-2026")</f>
-        <v/>
-      </c>
-      <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 30860-2026 karta.png", "A 30860-2026")</f>
-        <v/>
-      </c>
-      <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 30860-2026 georefererad karta.tif", "A 30860-2026")</f>
-        <v/>
-      </c>
-      <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 30860-2026 FSC-klagomål.docx", "A 30860-2026")</f>
-        <v/>
-      </c>
-      <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 30860-2026 FSC-klagomål mail.docx", "A 30860-2026")</f>
-        <v/>
-      </c>
-      <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 30860-2026 tillsynsbegäran.docx", "A 30860-2026")</f>
-        <v/>
-      </c>
-      <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 30860-2026 tillsynsbegäran mail.docx", "A 30860-2026")</f>
-        <v/>
-      </c>
-      <c r="AE16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 30860-2026 prioriterade fågelarter.docx", "A 30860-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 53007-2025</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>45957</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>KUNGÄLV</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="J17" t="n">
-        <v>1</v>
-      </c>
-      <c r="K17" t="n">
-        <v>1</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2</v>
-      </c>
-      <c r="T17" t="n">
-        <v>5</v>
-      </c>
-      <c r="U17" t="n">
-        <v>5</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Västlig hakmossa
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W17">
+      <c r="W19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 53007-2025 artfynd.xlsx", "A 53007-2025")</f>
         <v/>
       </c>
-      <c r="X17">
+      <c r="X19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 53007-2025 karta.png", "A 53007-2025")</f>
         <v/>
       </c>
-      <c r="Y17">
+      <c r="Y19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 53007-2025 georefererad karta.tif", "A 53007-2025")</f>
         <v/>
       </c>
-      <c r="AA17">
+      <c r="AA19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 53007-2025 FSC-klagomål.docx", "A 53007-2025")</f>
         <v/>
       </c>
-      <c r="AB17">
+      <c r="AB19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 53007-2025 FSC-klagomål mail.docx", "A 53007-2025")</f>
         <v/>
       </c>
-      <c r="AC17">
+      <c r="AC19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 53007-2025 tillsynsbegäran.docx", "A 53007-2025")</f>
         <v/>
       </c>
-      <c r="AD17">
+      <c r="AD19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 53007-2025 tillsynsbegäran mail.docx", "A 53007-2025")</f>
         <v/>
       </c>
-      <c r="AE17">
+      <c r="AE19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 53007-2025 prioriterade fågelarter.docx", "A 53007-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 5631-2024</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>45334</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>KUNGÄLV</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="J18" t="n">
-        <v>2</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>Vanlig groda
-Fläcknycklar</t>
-        </is>
-      </c>
-      <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 5631-2024 artfynd.xlsx", "A 5631-2024")</f>
-        <v/>
-      </c>
-      <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 5631-2024 karta.png", "A 5631-2024")</f>
-        <v/>
-      </c>
-      <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 5631-2024 georefererad karta.tif", "A 5631-2024")</f>
-        <v/>
-      </c>
-      <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 5631-2024 FSC-klagomål.docx", "A 5631-2024")</f>
-        <v/>
-      </c>
-      <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 5631-2024 FSC-klagomål mail.docx", "A 5631-2024")</f>
-        <v/>
-      </c>
-      <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 5631-2024 tillsynsbegäran.docx", "A 5631-2024")</f>
-        <v/>
-      </c>
-      <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 5631-2024 tillsynsbegäran mail.docx", "A 5631-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>A 5637-2024</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>45334</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>KUNGÄLV</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>2</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>2</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>Klofibbla
-Åkerrödtoppa</t>
-        </is>
-      </c>
-      <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 5637-2024 artfynd.xlsx", "A 5637-2024")</f>
-        <v/>
-      </c>
-      <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 5637-2024 karta.png", "A 5637-2024")</f>
-        <v/>
-      </c>
-      <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 5637-2024 georefererad karta.tif", "A 5637-2024")</f>
-        <v/>
-      </c>
-      <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 5637-2024 FSC-klagomål.docx", "A 5637-2024")</f>
-        <v/>
-      </c>
-      <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 5637-2024 FSC-klagomål mail.docx", "A 5637-2024")</f>
-        <v/>
-      </c>
-      <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 5637-2024 tillsynsbegäran.docx", "A 5637-2024")</f>
-        <v/>
-      </c>
-      <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 5637-2024 tillsynsbegäran mail.docx", "A 5637-2024")</f>
         <v/>
       </c>
     </row>
@@ -2618,7 +2618,7 @@
         <v>44838</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2706,7 +2706,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 49988-2023</t>
+          <t>A 6082-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2720,10 +2720,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45215</v>
+        <v>45697</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="J21" t="n">
         <v>1</v>
@@ -2772,46 +2772,50 @@
         <v>1</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 49988-2023 artfynd.xlsx", "A 49988-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 6082-2025 artfynd.xlsx", "A 6082-2025")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 49988-2023 karta.png", "A 49988-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 6082-2025 karta.png", "A 6082-2025")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 49988-2023 georefererad karta.tif", "A 49988-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 6082-2025 georefererad karta.tif", "A 6082-2025")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 49988-2023 FSC-klagomål.docx", "A 49988-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 6082-2025 FSC-klagomål.docx", "A 6082-2025")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 49988-2023 FSC-klagomål mail.docx", "A 49988-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 6082-2025 FSC-klagomål mail.docx", "A 6082-2025")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 49988-2023 tillsynsbegäran.docx", "A 49988-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 6082-2025 tillsynsbegäran.docx", "A 6082-2025")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 49988-2023 tillsynsbegäran mail.docx", "A 49988-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 6082-2025 tillsynsbegäran mail.docx", "A 6082-2025")</f>
+        <v/>
+      </c>
+      <c r="AE21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 6082-2025 prioriterade fågelarter.docx", "A 6082-2025")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 6082-2025</t>
+          <t>A 23704-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2825,10 +2829,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45697</v>
+        <v>45454</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2841,7 +2845,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>2.8</v>
+        <v>4.9</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
@@ -2853,7 +2857,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
@@ -2865,62 +2869,58 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
       </c>
       <c r="T22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U22" t="n">
         <v>1</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Hedjohannesört</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 6082-2025 artfynd.xlsx", "A 6082-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 23704-2024 artfynd.xlsx", "A 23704-2024")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 6082-2025 karta.png", "A 6082-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 23704-2024 karta.png", "A 23704-2024")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 6082-2025 georefererad karta.tif", "A 6082-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 23704-2024 georefererad karta.tif", "A 23704-2024")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 6082-2025 FSC-klagomål.docx", "A 6082-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 23704-2024 FSC-klagomål.docx", "A 23704-2024")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 6082-2025 FSC-klagomål mail.docx", "A 6082-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 23704-2024 FSC-klagomål mail.docx", "A 23704-2024")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 6082-2025 tillsynsbegäran.docx", "A 6082-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 23704-2024 tillsynsbegäran.docx", "A 23704-2024")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 6082-2025 tillsynsbegäran mail.docx", "A 6082-2025")</f>
-        <v/>
-      </c>
-      <c r="AE22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 6082-2025 prioriterade fågelarter.docx", "A 6082-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 23704-2024 tillsynsbegäran mail.docx", "A 23704-2024")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 30862-2026</t>
+          <t>A 49988-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2934,10 +2934,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46212</v>
+        <v>45215</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2950,7 +2950,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="J23" t="n">
         <v>1</v>
@@ -2983,49 +2983,49 @@
         <v>1</v>
       </c>
       <c r="T23" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U23" t="n">
         <v>0</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 30862-2026 artfynd.xlsx", "A 30862-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 49988-2023 artfynd.xlsx", "A 49988-2023")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 30862-2026 karta.png", "A 30862-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 49988-2023 karta.png", "A 49988-2023")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 30862-2026 georefererad karta.tif", "A 30862-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 49988-2023 georefererad karta.tif", "A 49988-2023")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 30862-2026 FSC-klagomål.docx", "A 30862-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 49988-2023 FSC-klagomål.docx", "A 49988-2023")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 30862-2026 FSC-klagomål mail.docx", "A 30862-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 49988-2023 FSC-klagomål mail.docx", "A 49988-2023")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 30862-2026 tillsynsbegäran.docx", "A 30862-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 49988-2023 tillsynsbegäran.docx", "A 49988-2023")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 30862-2026 tillsynsbegäran mail.docx", "A 30862-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 49988-2023 tillsynsbegäran mail.docx", "A 49988-2023")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 23704-2024</t>
+          <t>A 30862-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3039,10 +3039,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45454</v>
+        <v>46212</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3055,7 +3055,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>4.9</v>
+        <v>1.7</v>
       </c>
       <c r="J24" t="n">
         <v>1</v>
@@ -3067,7 +3067,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
@@ -3079,51 +3079,51 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
       </c>
       <c r="T24" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="U24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Hedjohannesört</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 23704-2024 artfynd.xlsx", "A 23704-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 30862-2026 artfynd.xlsx", "A 30862-2026")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 23704-2024 karta.png", "A 23704-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 30862-2026 karta.png", "A 30862-2026")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 23704-2024 georefererad karta.tif", "A 23704-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 30862-2026 georefererad karta.tif", "A 30862-2026")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 23704-2024 FSC-klagomål.docx", "A 23704-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 30862-2026 FSC-klagomål.docx", "A 30862-2026")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 23704-2024 FSC-klagomål mail.docx", "A 23704-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 30862-2026 FSC-klagomål mail.docx", "A 30862-2026")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 23704-2024 tillsynsbegäran.docx", "A 23704-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 30862-2026 tillsynsbegäran.docx", "A 30862-2026")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 23704-2024 tillsynsbegäran mail.docx", "A 23704-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 30862-2026 tillsynsbegäran mail.docx", "A 30862-2026")</f>
         <v/>
       </c>
     </row>
@@ -3147,7 +3147,7 @@
         <v>44691</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
         <v>44691</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         <v>44836</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3366,7 +3366,7 @@
         <v>44760</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         <v>44760</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
         <v>44760</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3568,7 +3568,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 62221-2023</t>
+          <t>A 17455-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3582,10 +3582,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45267</v>
+        <v>45757</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3598,7 +3598,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.3</v>
+        <v>2.1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3641,7 +3641,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 4204-2024</t>
+          <t>A 62221-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3655,10 +3655,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45324</v>
+        <v>45267</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3671,7 +3671,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>4.4</v>
+        <v>1.3</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3714,7 +3714,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 30170-2022</t>
+          <t>A 21240-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3728,10 +3728,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44757</v>
+        <v>45058</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3744,7 +3744,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>3.1</v>
+        <v>2.3</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3787,7 +3787,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 13880-2024</t>
+          <t>A 29223-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3801,10 +3801,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45391</v>
+        <v>45482</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3817,7 +3817,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2.4</v>
+        <v>5.6</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3860,7 +3860,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 1995-2024</t>
+          <t>A 10655-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3874,10 +3874,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45308</v>
+        <v>44624</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3890,7 +3890,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.5</v>
+        <v>13.3</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3933,7 +3933,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 45990-2022</t>
+          <t>A 10677-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3947,10 +3947,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44846</v>
+        <v>45721</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3963,7 +3963,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>3.3</v>
+        <v>7.4</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4006,7 +4006,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 74285-2021</t>
+          <t>A 10679-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4020,10 +4020,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44558</v>
+        <v>45721</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.1</v>
+        <v>4.4</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4079,7 +4079,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 17922-2025</t>
+          <t>A 11237-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4093,10 +4093,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45758</v>
+        <v>45726</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4109,7 +4109,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.8</v>
+        <v>4.2</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4152,7 +4152,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 43520-2022</t>
+          <t>A 39714-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4166,10 +4166,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44837</v>
+        <v>45552</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4182,7 +4182,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4225,7 +4225,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 34366-2022</t>
+          <t>A 74285-2021</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4239,10 +4239,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44792</v>
+        <v>44558</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4255,7 +4255,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4298,7 +4298,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 4673-2026</t>
+          <t>A 40951-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4312,10 +4312,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46048</v>
+        <v>45897</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4328,7 +4328,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>8.199999999999999</v>
+        <v>0.8</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4371,7 +4371,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 40951-2025</t>
+          <t>A 61417-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4385,10 +4385,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45897</v>
+        <v>44916</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4401,7 +4401,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.8</v>
+        <v>3.6</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4444,7 +4444,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 29223-2024</t>
+          <t>A 32272-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4458,10 +4458,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45482</v>
+        <v>45120</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4474,7 +4474,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>5.6</v>
+        <v>4.9</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4517,7 +4517,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 6946-2026</t>
+          <t>A 32847-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4527,14 +4527,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46057</v>
+        <v>45124</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4547,7 +4547,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2.2</v>
+        <v>4.7</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4607,7 +4607,7 @@
         <v>45919</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4663,7 +4663,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 8334-2023</t>
+          <t>A 19531-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4677,10 +4677,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44975</v>
+        <v>45050</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4753,7 +4753,7 @@
         <v>45931</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4809,7 +4809,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 61417-2022</t>
+          <t>A 5705-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4819,14 +4819,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44916</v>
+        <v>45694</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>3.6</v>
+        <v>1.2</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4882,7 +4882,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 37443-2025</t>
+          <t>A 7505-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4896,10 +4896,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45877</v>
+        <v>45347</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4911,13 +4911,8 @@
           <t>KUNGÄLV</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I49" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4960,7 +4955,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 13990-2026</t>
+          <t>A 34244-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4974,10 +4969,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46098</v>
+        <v>45844</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4990,7 +4985,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5033,7 +5028,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 32272-2023</t>
+          <t>A 25624-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5047,10 +5042,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45120</v>
+        <v>45803</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5063,7 +5058,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5106,7 +5101,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 32847-2023</t>
+          <t>A 8334-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5120,10 +5115,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45124</v>
+        <v>44975</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5136,7 +5131,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>4.7</v>
+        <v>1.8</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5196,7 +5191,7 @@
         <v>45957</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5252,7 +5247,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 4262-2024</t>
+          <t>A 41442-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5266,10 +5261,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45324</v>
+        <v>45869</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5282,7 +5277,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>14</v>
+        <v>1.8</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5325,7 +5320,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 49985-2023</t>
+          <t>A 17922-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5339,10 +5334,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45215</v>
+        <v>45758</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5355,7 +5350,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>8.199999999999999</v>
+        <v>0.8</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5398,7 +5393,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 661-2025</t>
+          <t>A 34366-2022</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5412,10 +5407,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45664</v>
+        <v>44792</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5428,7 +5423,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>3.1</v>
+        <v>0.5</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5471,7 +5466,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 50071-2023</t>
+          <t>A 4673-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5485,10 +5480,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45215</v>
+        <v>46048</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5501,7 +5496,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5544,7 +5539,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 24461-2023</t>
+          <t>A 6946-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5554,14 +5549,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45082</v>
+        <v>46057</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5574,7 +5569,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5617,7 +5612,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 143-2023</t>
+          <t>A 49981-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5631,10 +5626,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44928</v>
+        <v>45215</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5647,7 +5642,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5690,7 +5685,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 22731-2026</t>
+          <t>A 56782-2022</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5704,10 +5699,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46157</v>
+        <v>44894</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5720,7 +5715,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5763,7 +5758,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 32391-2025</t>
+          <t>A 1995-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5777,10 +5772,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45837</v>
+        <v>45308</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5793,7 +5788,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>2.1</v>
+        <v>0.5</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5836,7 +5831,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 63319-2021</t>
+          <t>A 37443-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5850,10 +5845,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44508</v>
+        <v>45877</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5865,8 +5860,13 @@
           <t>KUNGÄLV</t>
         </is>
       </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I62" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5909,7 +5909,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 23607-2026</t>
+          <t>A 13990-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5923,10 +5923,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46163</v>
+        <v>46098</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5939,7 +5939,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>5.3</v>
+        <v>2.6</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5982,7 +5982,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 34244-2025</t>
+          <t>A 30170-2022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5996,10 +5996,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45844</v>
+        <v>44757</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6012,7 +6012,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6055,7 +6055,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 25135-2025</t>
+          <t>A 10810-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6069,10 +6069,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45798</v>
+        <v>44989</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6085,7 +6085,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6128,7 +6128,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 25624-2025</t>
+          <t>A 4204-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6142,10 +6142,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45803</v>
+        <v>45324</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6158,7 +6158,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6201,7 +6201,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 7505-2024</t>
+          <t>A 62128-2021</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6215,10 +6215,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45347</v>
+        <v>44502</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6274,7 +6274,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 41442-2025</t>
+          <t>A 62979-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6284,14 +6284,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45869</v>
+        <v>45271</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6304,7 +6304,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6347,7 +6347,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 10655-2022</t>
+          <t>A 49985-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6361,10 +6361,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44624</v>
+        <v>45215</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6377,7 +6377,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>13.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6420,7 +6420,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 17455-2025</t>
+          <t>A 50071-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6434,10 +6434,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45757</v>
+        <v>45215</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6450,7 +6450,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>2.1</v>
+        <v>4</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6493,7 +6493,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 29952-2026</t>
+          <t>A 44176-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6507,10 +6507,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46205</v>
+        <v>45188</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6523,7 +6523,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>2</v>
+        <v>7.1</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6566,7 +6566,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 19531-2023</t>
+          <t>A 26812-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6580,10 +6580,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45050</v>
+        <v>45470</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6596,7 +6596,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6639,7 +6639,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 34386-2026</t>
+          <t>A 29801-2022</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6653,10 +6653,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46254</v>
+        <v>44755</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6669,7 +6669,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.7</v>
+        <v>4.8</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6712,7 +6712,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 30738-2026</t>
+          <t>A 18852-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6726,10 +6726,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46211</v>
+        <v>45426</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6742,7 +6742,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>3.5</v>
+        <v>2.7</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6785,7 +6785,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 30859-2026</t>
+          <t>A 43520-2022</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6799,10 +6799,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46212</v>
+        <v>44837</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6815,7 +6815,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6858,7 +6858,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 34387-2026</t>
+          <t>A 22731-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6872,10 +6872,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46254</v>
+        <v>46157</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6888,7 +6888,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.3</v>
+        <v>1.8</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6931,7 +6931,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 34396-2026</t>
+          <t>A 16538-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6945,10 +6945,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46254</v>
+        <v>45751</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7004,7 +7004,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 34392-2026</t>
+          <t>A 32391-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7018,10 +7018,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46254</v>
+        <v>45837</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7034,7 +7034,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.4</v>
+        <v>2.1</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7077,7 +7077,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 5705-2025</t>
+          <t>A 45990-2022</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7087,14 +7087,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45694</v>
+        <v>44846</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7107,7 +7107,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.2</v>
+        <v>3.3</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7150,7 +7150,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 62979-2023</t>
+          <t>A 23607-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7160,14 +7160,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45271</v>
+        <v>46163</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7180,7 +7180,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.8</v>
+        <v>5.3</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7223,7 +7223,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 16538-2025</t>
+          <t>A 25135-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7237,10 +7237,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45751</v>
+        <v>45798</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7253,7 +7253,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7296,7 +7296,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 29801-2022</t>
+          <t>A 143-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7310,10 +7310,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44755</v>
+        <v>44928</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7326,7 +7326,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>4.8</v>
+        <v>0.5</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7369,7 +7369,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 49981-2023</t>
+          <t>A 18851-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7383,10 +7383,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45215</v>
+        <v>45426</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7459,7 +7459,7 @@
         <v>44543</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7515,7 +7515,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 38262-2026</t>
+          <t>A 51724-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7529,10 +7529,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46281</v>
+        <v>45222</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7545,7 +7545,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7588,7 +7588,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 56782-2022</t>
+          <t>A 661-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7602,10 +7602,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44894</v>
+        <v>45664</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7618,7 +7618,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>0.5</v>
+        <v>3.1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7661,7 +7661,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 26812-2024</t>
+          <t>A 24461-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7675,10 +7675,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45470</v>
+        <v>45082</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7691,7 +7691,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7734,7 +7734,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 10810-2023</t>
+          <t>A 13880-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7748,10 +7748,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>44989</v>
+        <v>45391</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7764,7 +7764,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0.4</v>
+        <v>2.4</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7807,7 +7807,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 62128-2021</t>
+          <t>A 29952-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7821,10 +7821,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>44502</v>
+        <v>46205</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7837,7 +7837,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7880,7 +7880,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 21240-2023</t>
+          <t>A 34392-2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7894,10 +7894,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45058</v>
+        <v>46254</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7910,7 +7910,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>2.3</v>
+        <v>0.4</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7953,7 +7953,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 18851-2024</t>
+          <t>A 34387-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7967,10 +7967,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45426</v>
+        <v>46254</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7983,7 +7983,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>2.7</v>
+        <v>0.3</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8026,7 +8026,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 21389-2023</t>
+          <t>A 34386-2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45063</v>
+        <v>46254</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8056,7 +8056,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>3.4</v>
+        <v>0.7</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 44176-2023</t>
+          <t>A 34396-2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8113,10 +8113,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45188</v>
+        <v>46254</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8129,7 +8129,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>7.1</v>
+        <v>0.8</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8172,7 +8172,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 23457-2024</t>
+          <t>A 30738-2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8186,10 +8186,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45453</v>
+        <v>46211</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8202,7 +8202,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>5.1</v>
+        <v>3.5</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8245,7 +8245,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 39714-2024</t>
+          <t>A 30859-2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8259,10 +8259,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45552</v>
+        <v>46212</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8275,7 +8275,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8318,7 +8318,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 18852-2024</t>
+          <t>A 23457-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8332,10 +8332,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45426</v>
+        <v>45453</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8348,7 +8348,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>2.7</v>
+        <v>5.1</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8391,7 +8391,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 51724-2023</t>
+          <t>A 21389-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8405,10 +8405,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45222</v>
+        <v>45063</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8421,7 +8421,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8464,7 +8464,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 10679-2025</t>
+          <t>A 4262-2024</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8478,10 +8478,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45721</v>
+        <v>45324</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8494,7 +8494,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>4.4</v>
+        <v>14</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8537,7 +8537,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 11237-2025</t>
+          <t>A 63319-2021</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8551,10 +8551,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45726</v>
+        <v>44508</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8567,7 +8567,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>4.2</v>
+        <v>1.6</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8610,7 +8610,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 10677-2025</t>
+          <t>A 38262-2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8624,10 +8624,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45721</v>
+        <v>46281</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8640,7 +8640,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>7.4</v>
+        <v>2.8</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8700,7 +8700,7 @@
         <v>45371</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>

--- a/Översikt KUNGÄLV.xlsx
+++ b/Översikt KUNGÄLV.xlsx
@@ -601,7 +601,7 @@
         <v>45548</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>45868</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -851,7 +851,7 @@
         <v>45526</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -965,7 +965,7 @@
         <v>45919</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
         <v>45695</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         <v>45993</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         <v>45324</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>45985</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>46199</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>45355</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>46212</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         <v>45957</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 57116-2025</t>
+          <t>A 56394-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1963,14 +1963,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45979</v>
+        <v>45974</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1983,7 +1983,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>3.5</v>
+        <v>1.3</v>
       </c>
       <c r="J14" t="n">
         <v>1</v>
@@ -2016,153 +2016,153 @@
         <v>2</v>
       </c>
       <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Kambräken
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 56394-2025 artfynd.xlsx", "A 56394-2025")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 56394-2025 karta.png", "A 56394-2025")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 56394-2025 georefererad karta.tif", "A 56394-2025")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 56394-2025 FSC-klagomål.docx", "A 56394-2025")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 56394-2025 FSC-klagomål mail.docx", "A 56394-2025")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 56394-2025 tillsynsbegäran.docx", "A 56394-2025")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 56394-2025 tillsynsbegäran mail.docx", "A 56394-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 57116-2025</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>45979</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>KUNGÄLV</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2</v>
+      </c>
+      <c r="T15" t="n">
         <v>3</v>
       </c>
-      <c r="U14" t="n">
+      <c r="U15" t="n">
         <v>3</v>
       </c>
-      <c r="V14" s="2" t="inlineStr">
+      <c r="V15" s="2" t="inlineStr">
         <is>
           <t>Västlig hakmossa
 Spillkråka</t>
         </is>
       </c>
-      <c r="W14">
+      <c r="W15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 57116-2025 artfynd.xlsx", "A 57116-2025")</f>
         <v/>
       </c>
-      <c r="X14">
+      <c r="X15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 57116-2025 karta.png", "A 57116-2025")</f>
         <v/>
       </c>
-      <c r="Y14">
+      <c r="Y15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 57116-2025 georefererad karta.tif", "A 57116-2025")</f>
         <v/>
       </c>
-      <c r="AA14">
+      <c r="AA15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 57116-2025 FSC-klagomål.docx", "A 57116-2025")</f>
         <v/>
       </c>
-      <c r="AB14">
+      <c r="AB15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 57116-2025 FSC-klagomål mail.docx", "A 57116-2025")</f>
         <v/>
       </c>
-      <c r="AC14">
+      <c r="AC15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 57116-2025 tillsynsbegäran.docx", "A 57116-2025")</f>
         <v/>
       </c>
-      <c r="AD14">
+      <c r="AD15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 57116-2025 tillsynsbegäran mail.docx", "A 57116-2025")</f>
         <v/>
       </c>
-      <c r="AE14">
+      <c r="AE15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 57116-2025 prioriterade fågelarter.docx", "A 57116-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 56394-2025</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>45974</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>KUNGÄLV</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="J15" t="n">
-        <v>1</v>
-      </c>
-      <c r="K15" t="n">
-        <v>1</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>Kambräken
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 56394-2025 artfynd.xlsx", "A 56394-2025")</f>
-        <v/>
-      </c>
-      <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 56394-2025 karta.png", "A 56394-2025")</f>
-        <v/>
-      </c>
-      <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 56394-2025 georefererad karta.tif", "A 56394-2025")</f>
-        <v/>
-      </c>
-      <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 56394-2025 FSC-klagomål.docx", "A 56394-2025")</f>
-        <v/>
-      </c>
-      <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 56394-2025 FSC-klagomål mail.docx", "A 56394-2025")</f>
-        <v/>
-      </c>
-      <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 56394-2025 tillsynsbegäran.docx", "A 56394-2025")</f>
-        <v/>
-      </c>
-      <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 56394-2025 tillsynsbegäran mail.docx", "A 56394-2025")</f>
         <v/>
       </c>
     </row>
@@ -2186,7 +2186,7 @@
         <v>46212</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 5631-2024</t>
+          <t>A 53007-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2293,10 +2293,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45334</v>
+        <v>45957</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2309,13 +2309,13 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.3</v>
+        <v>2.9</v>
       </c>
       <c r="J17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -2342,259 +2342,259 @@
         <v>2</v>
       </c>
       <c r="T17" t="n">
+        <v>5</v>
+      </c>
+      <c r="U17" t="n">
+        <v>5</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>Västlig hakmossa
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 53007-2025 artfynd.xlsx", "A 53007-2025")</f>
+        <v/>
+      </c>
+      <c r="X17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 53007-2025 karta.png", "A 53007-2025")</f>
+        <v/>
+      </c>
+      <c r="Y17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 53007-2025 georefererad karta.tif", "A 53007-2025")</f>
+        <v/>
+      </c>
+      <c r="AA17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 53007-2025 FSC-klagomål.docx", "A 53007-2025")</f>
+        <v/>
+      </c>
+      <c r="AB17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 53007-2025 FSC-klagomål mail.docx", "A 53007-2025")</f>
+        <v/>
+      </c>
+      <c r="AC17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 53007-2025 tillsynsbegäran.docx", "A 53007-2025")</f>
+        <v/>
+      </c>
+      <c r="AD17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 53007-2025 tillsynsbegäran mail.docx", "A 53007-2025")</f>
+        <v/>
+      </c>
+      <c r="AE17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 53007-2025 prioriterade fågelarter.docx", "A 53007-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>A 5631-2024</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>45334</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>KUNGÄLV</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J18" t="n">
         <v>2</v>
       </c>
-      <c r="U17" t="n">
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
         <v>1</v>
       </c>
-      <c r="V17" s="2" t="inlineStr">
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>Vanlig groda
 Fläcknycklar</t>
         </is>
       </c>
-      <c r="W17">
+      <c r="W18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 5631-2024 artfynd.xlsx", "A 5631-2024")</f>
         <v/>
       </c>
-      <c r="X17">
+      <c r="X18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 5631-2024 karta.png", "A 5631-2024")</f>
         <v/>
       </c>
-      <c r="Y17">
+      <c r="Y18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 5631-2024 georefererad karta.tif", "A 5631-2024")</f>
         <v/>
       </c>
-      <c r="AA17">
+      <c r="AA18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 5631-2024 FSC-klagomål.docx", "A 5631-2024")</f>
         <v/>
       </c>
-      <c r="AB17">
+      <c r="AB18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 5631-2024 FSC-klagomål mail.docx", "A 5631-2024")</f>
         <v/>
       </c>
-      <c r="AC17">
+      <c r="AC18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 5631-2024 tillsynsbegäran.docx", "A 5631-2024")</f>
         <v/>
       </c>
-      <c r="AD17">
+      <c r="AD18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 5631-2024 tillsynsbegäran mail.docx", "A 5631-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
         <is>
           <t>A 5637-2024</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
         <v>45334</v>
       </c>
-      <c r="E18" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>KUNGÄLV</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
+      <c r="E19" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>KUNGÄLV</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
         <v>1.8</v>
       </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
         <v>2</v>
       </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
         <v>2</v>
       </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
         <v>2</v>
       </c>
-      <c r="T18" t="n">
+      <c r="T19" t="n">
         <v>2</v>
       </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>Klofibbla
 Åkerrödtoppa</t>
         </is>
       </c>
-      <c r="W18">
+      <c r="W19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 5637-2024 artfynd.xlsx", "A 5637-2024")</f>
         <v/>
       </c>
-      <c r="X18">
+      <c r="X19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 5637-2024 karta.png", "A 5637-2024")</f>
         <v/>
       </c>
-      <c r="Y18">
+      <c r="Y19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 5637-2024 georefererad karta.tif", "A 5637-2024")</f>
         <v/>
       </c>
-      <c r="AA18">
+      <c r="AA19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 5637-2024 FSC-klagomål.docx", "A 5637-2024")</f>
         <v/>
       </c>
-      <c r="AB18">
+      <c r="AB19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 5637-2024 FSC-klagomål mail.docx", "A 5637-2024")</f>
         <v/>
       </c>
-      <c r="AC18">
+      <c r="AC19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 5637-2024 tillsynsbegäran.docx", "A 5637-2024")</f>
         <v/>
       </c>
-      <c r="AD18">
+      <c r="AD19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 5637-2024 tillsynsbegäran mail.docx", "A 5637-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>A 53007-2025</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>45957</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>KUNGÄLV</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="J19" t="n">
-        <v>1</v>
-      </c>
-      <c r="K19" t="n">
-        <v>1</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2</v>
-      </c>
-      <c r="T19" t="n">
-        <v>5</v>
-      </c>
-      <c r="U19" t="n">
-        <v>5</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>Västlig hakmossa
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 53007-2025 artfynd.xlsx", "A 53007-2025")</f>
-        <v/>
-      </c>
-      <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 53007-2025 karta.png", "A 53007-2025")</f>
-        <v/>
-      </c>
-      <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 53007-2025 georefererad karta.tif", "A 53007-2025")</f>
-        <v/>
-      </c>
-      <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 53007-2025 FSC-klagomål.docx", "A 53007-2025")</f>
-        <v/>
-      </c>
-      <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 53007-2025 FSC-klagomål mail.docx", "A 53007-2025")</f>
-        <v/>
-      </c>
-      <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 53007-2025 tillsynsbegäran.docx", "A 53007-2025")</f>
-        <v/>
-      </c>
-      <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 53007-2025 tillsynsbegäran mail.docx", "A 53007-2025")</f>
-        <v/>
-      </c>
-      <c r="AE19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 53007-2025 prioriterade fågelarter.docx", "A 53007-2025")</f>
         <v/>
       </c>
     </row>
@@ -2618,7 +2618,7 @@
         <v>44838</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2706,7 +2706,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 6082-2025</t>
+          <t>A 49988-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2720,10 +2720,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45697</v>
+        <v>45215</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="J21" t="n">
         <v>1</v>
@@ -2772,50 +2772,46 @@
         <v>1</v>
       </c>
       <c r="U21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 6082-2025 artfynd.xlsx", "A 6082-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 49988-2023 artfynd.xlsx", "A 49988-2023")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 6082-2025 karta.png", "A 6082-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 49988-2023 karta.png", "A 49988-2023")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 6082-2025 georefererad karta.tif", "A 6082-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 49988-2023 georefererad karta.tif", "A 49988-2023")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 6082-2025 FSC-klagomål.docx", "A 6082-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 49988-2023 FSC-klagomål.docx", "A 49988-2023")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 6082-2025 FSC-klagomål mail.docx", "A 6082-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 49988-2023 FSC-klagomål mail.docx", "A 49988-2023")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 6082-2025 tillsynsbegäran.docx", "A 6082-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 49988-2023 tillsynsbegäran.docx", "A 49988-2023")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 6082-2025 tillsynsbegäran mail.docx", "A 6082-2025")</f>
-        <v/>
-      </c>
-      <c r="AE21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 6082-2025 prioriterade fågelarter.docx", "A 6082-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 49988-2023 tillsynsbegäran mail.docx", "A 49988-2023")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 23704-2024</t>
+          <t>A 6082-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2829,10 +2825,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45454</v>
+        <v>45697</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2845,7 +2841,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>4.9</v>
+        <v>2.8</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
@@ -2857,7 +2853,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
@@ -2869,58 +2865,62 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
       </c>
       <c r="T22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U22" t="n">
         <v>1</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Hedjohannesört</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 23704-2024 artfynd.xlsx", "A 23704-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 6082-2025 artfynd.xlsx", "A 6082-2025")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 23704-2024 karta.png", "A 23704-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 6082-2025 karta.png", "A 6082-2025")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 23704-2024 georefererad karta.tif", "A 23704-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 6082-2025 georefererad karta.tif", "A 6082-2025")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 23704-2024 FSC-klagomål.docx", "A 23704-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 6082-2025 FSC-klagomål.docx", "A 6082-2025")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 23704-2024 FSC-klagomål mail.docx", "A 23704-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 6082-2025 FSC-klagomål mail.docx", "A 6082-2025")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 23704-2024 tillsynsbegäran.docx", "A 23704-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 6082-2025 tillsynsbegäran.docx", "A 6082-2025")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 23704-2024 tillsynsbegäran mail.docx", "A 23704-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 6082-2025 tillsynsbegäran mail.docx", "A 6082-2025")</f>
+        <v/>
+      </c>
+      <c r="AE22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 6082-2025 prioriterade fågelarter.docx", "A 6082-2025")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 49988-2023</t>
+          <t>A 30862-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2934,10 +2934,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45215</v>
+        <v>46212</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2950,7 +2950,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="J23" t="n">
         <v>1</v>
@@ -2983,49 +2983,49 @@
         <v>1</v>
       </c>
       <c r="T23" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U23" t="n">
         <v>0</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 49988-2023 artfynd.xlsx", "A 49988-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 30862-2026 artfynd.xlsx", "A 30862-2026")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 49988-2023 karta.png", "A 49988-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 30862-2026 karta.png", "A 30862-2026")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 49988-2023 georefererad karta.tif", "A 49988-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 30862-2026 georefererad karta.tif", "A 30862-2026")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 49988-2023 FSC-klagomål.docx", "A 49988-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 30862-2026 FSC-klagomål.docx", "A 30862-2026")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 49988-2023 FSC-klagomål mail.docx", "A 49988-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 30862-2026 FSC-klagomål mail.docx", "A 30862-2026")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 49988-2023 tillsynsbegäran.docx", "A 49988-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 30862-2026 tillsynsbegäran.docx", "A 30862-2026")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 49988-2023 tillsynsbegäran mail.docx", "A 49988-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 30862-2026 tillsynsbegäran mail.docx", "A 30862-2026")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 30862-2026</t>
+          <t>A 23704-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3039,10 +3039,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46212</v>
+        <v>45454</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3055,7 +3055,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.7</v>
+        <v>4.9</v>
       </c>
       <c r="J24" t="n">
         <v>1</v>
@@ -3067,7 +3067,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
@@ -3079,51 +3079,51 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
       </c>
       <c r="T24" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Hedjohannesört</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 30862-2026 artfynd.xlsx", "A 30862-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 23704-2024 artfynd.xlsx", "A 23704-2024")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 30862-2026 karta.png", "A 30862-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 23704-2024 karta.png", "A 23704-2024")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 30862-2026 georefererad karta.tif", "A 30862-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 23704-2024 georefererad karta.tif", "A 23704-2024")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 30862-2026 FSC-klagomål.docx", "A 30862-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 23704-2024 FSC-klagomål.docx", "A 23704-2024")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 30862-2026 FSC-klagomål mail.docx", "A 30862-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 23704-2024 FSC-klagomål mail.docx", "A 23704-2024")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 30862-2026 tillsynsbegäran.docx", "A 30862-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 23704-2024 tillsynsbegäran.docx", "A 23704-2024")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 30862-2026 tillsynsbegäran mail.docx", "A 30862-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 23704-2024 tillsynsbegäran mail.docx", "A 23704-2024")</f>
         <v/>
       </c>
     </row>
@@ -3147,7 +3147,7 @@
         <v>44691</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
         <v>44691</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         <v>44836</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3366,7 +3366,7 @@
         <v>44760</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         <v>44760</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
         <v>44760</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3568,7 +3568,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 17455-2025</t>
+          <t>A 62221-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3582,10 +3582,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45757</v>
+        <v>45267</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3598,7 +3598,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2.1</v>
+        <v>1.3</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3641,7 +3641,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 62221-2023</t>
+          <t>A 4204-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3655,10 +3655,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45267</v>
+        <v>45324</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3671,7 +3671,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.3</v>
+        <v>4.4</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3714,7 +3714,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 21240-2023</t>
+          <t>A 30170-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3728,10 +3728,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45058</v>
+        <v>44757</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3744,7 +3744,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3787,7 +3787,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 29223-2024</t>
+          <t>A 13880-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3801,10 +3801,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45482</v>
+        <v>45391</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3817,7 +3817,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>5.6</v>
+        <v>2.4</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3860,7 +3860,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 10655-2022</t>
+          <t>A 1995-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3874,10 +3874,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44624</v>
+        <v>45308</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3890,7 +3890,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>13.3</v>
+        <v>0.5</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3933,7 +3933,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 10677-2025</t>
+          <t>A 45990-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3947,10 +3947,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45721</v>
+        <v>44846</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3963,7 +3963,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>7.4</v>
+        <v>3.3</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4023,7 +4023,7 @@
         <v>45721</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4096,7 +4096,7 @@
         <v>45726</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4152,7 +4152,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 39714-2024</t>
+          <t>A 10677-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4166,10 +4166,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45552</v>
+        <v>45721</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4182,7 +4182,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.2</v>
+        <v>7.4</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4242,7 +4242,7 @@
         <v>44558</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4298,7 +4298,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 40951-2025</t>
+          <t>A 17922-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4312,10 +4312,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45897</v>
+        <v>45758</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4371,7 +4371,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 61417-2022</t>
+          <t>A 43520-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4385,10 +4385,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44916</v>
+        <v>44837</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4401,7 +4401,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>3.6</v>
+        <v>1.5</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4444,7 +4444,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 32272-2023</t>
+          <t>A 40951-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4458,10 +4458,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45120</v>
+        <v>45897</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4474,7 +4474,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>4.9</v>
+        <v>0.8</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4517,7 +4517,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 32847-2023</t>
+          <t>A 61417-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4531,10 +4531,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45124</v>
+        <v>44916</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4547,7 +4547,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>4.7</v>
+        <v>3.6</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4590,7 +4590,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 45124-2025</t>
+          <t>A 32272-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4604,10 +4604,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45919</v>
+        <v>45120</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4620,7 +4620,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>3.7</v>
+        <v>4.9</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4663,7 +4663,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 19531-2023</t>
+          <t>A 32847-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4677,10 +4677,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45050</v>
+        <v>45124</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.9</v>
+        <v>4.7</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4736,7 +4736,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 47564-2025</t>
+          <t>A 29223-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4750,10 +4750,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45931</v>
+        <v>45482</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4766,7 +4766,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2</v>
+        <v>5.6</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4809,7 +4809,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 5705-2025</t>
+          <t>A 34366-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4819,14 +4819,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45694</v>
+        <v>44792</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4882,7 +4882,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 7505-2024</t>
+          <t>A 45124-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4896,10 +4896,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45347</v>
+        <v>45919</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4912,7 +4912,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.8</v>
+        <v>3.7</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4955,7 +4955,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 34244-2025</t>
+          <t>A 8334-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4969,10 +4969,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45844</v>
+        <v>44975</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4985,7 +4985,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2.9</v>
+        <v>1.8</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5028,7 +5028,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 25624-2025</t>
+          <t>A 47564-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5042,10 +5042,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45803</v>
+        <v>45931</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5058,7 +5058,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5101,7 +5101,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 8334-2023</t>
+          <t>A 4673-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5115,10 +5115,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44975</v>
+        <v>46048</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5131,7 +5131,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5174,7 +5174,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 52932-2025</t>
+          <t>A 34244-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5188,10 +5188,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45957</v>
+        <v>45844</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5204,7 +5204,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5247,7 +5247,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 41442-2025</t>
+          <t>A 25624-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5261,10 +5261,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45869</v>
+        <v>45803</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5277,7 +5277,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.8</v>
+        <v>5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5320,7 +5320,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 17922-2025</t>
+          <t>A 41442-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5334,10 +5334,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45758</v>
+        <v>45869</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5350,7 +5350,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.8</v>
+        <v>1.8</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5393,7 +5393,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 34366-2022</t>
+          <t>A 52932-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5407,10 +5407,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44792</v>
+        <v>45957</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5423,7 +5423,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.5</v>
+        <v>3.4</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5466,7 +5466,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 4673-2026</t>
+          <t>A 6946-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5476,14 +5476,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46048</v>
+        <v>46057</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5496,7 +5496,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>8.199999999999999</v>
+        <v>2.2</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5539,7 +5539,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 6946-2026</t>
+          <t>A 4262-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5549,14 +5549,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46057</v>
+        <v>45324</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5569,7 +5569,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>2.2</v>
+        <v>14</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5612,7 +5612,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 49981-2023</t>
+          <t>A 661-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5626,10 +5626,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45215</v>
+        <v>45664</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5642,7 +5642,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5685,7 +5685,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 56782-2022</t>
+          <t>A 37443-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5699,10 +5699,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44894</v>
+        <v>45877</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5714,8 +5714,13 @@
           <t>KUNGÄLV</t>
         </is>
       </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I60" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5758,7 +5763,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 1995-2024</t>
+          <t>A 13990-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5772,10 +5777,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45308</v>
+        <v>46098</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5788,7 +5793,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.5</v>
+        <v>2.6</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5831,7 +5836,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 37443-2025</t>
+          <t>A 24461-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5845,10 +5850,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45877</v>
+        <v>45082</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5860,13 +5865,8 @@
           <t>KUNGÄLV</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I62" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5909,7 +5909,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 13990-2026</t>
+          <t>A 143-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5923,10 +5923,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46098</v>
+        <v>44928</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5939,7 +5939,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>2.6</v>
+        <v>0.5</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5982,7 +5982,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 30170-2022</t>
+          <t>A 63319-2021</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5996,10 +5996,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44757</v>
+        <v>44508</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6012,7 +6012,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>3.1</v>
+        <v>1.6</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6055,7 +6055,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 10810-2023</t>
+          <t>A 49985-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6069,10 +6069,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44989</v>
+        <v>45215</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6085,7 +6085,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6128,7 +6128,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 4204-2024</t>
+          <t>A 50071-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6142,10 +6142,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45324</v>
+        <v>45215</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6158,7 +6158,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6201,7 +6201,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 62128-2021</t>
+          <t>A 7505-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6215,10 +6215,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44502</v>
+        <v>45347</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6274,7 +6274,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 62979-2023</t>
+          <t>A 10655-2022</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6284,14 +6284,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45271</v>
+        <v>44624</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6304,7 +6304,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.8</v>
+        <v>13.3</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6347,7 +6347,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 49985-2023</t>
+          <t>A 17455-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6361,10 +6361,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45215</v>
+        <v>45757</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6377,7 +6377,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>8.199999999999999</v>
+        <v>2.1</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6420,7 +6420,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 50071-2023</t>
+          <t>A 19531-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6434,10 +6434,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45215</v>
+        <v>45050</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6450,7 +6450,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>4</v>
+        <v>1.9</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6493,7 +6493,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 44176-2023</t>
+          <t>A 22731-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6507,10 +6507,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45188</v>
+        <v>46157</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6523,7 +6523,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>7.1</v>
+        <v>1.8</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6566,7 +6566,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 26812-2024</t>
+          <t>A 32391-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6580,10 +6580,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45470</v>
+        <v>45837</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6596,7 +6596,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6639,7 +6639,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 29801-2022</t>
+          <t>A 5705-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6649,14 +6649,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44755</v>
+        <v>45694</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6669,7 +6669,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>4.8</v>
+        <v>1.2</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6712,7 +6712,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 18852-2024</t>
+          <t>A 23607-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6726,10 +6726,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45426</v>
+        <v>46163</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6742,7 +6742,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>2.7</v>
+        <v>5.3</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6785,7 +6785,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 43520-2022</t>
+          <t>A 25135-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6799,10 +6799,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44837</v>
+        <v>45798</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6815,7 +6815,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6858,7 +6858,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 22731-2026</t>
+          <t>A 62979-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6868,14 +6868,14 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46157</v>
+        <v>45271</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6888,7 +6888,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6948,7 +6948,7 @@
         <v>45751</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7004,7 +7004,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 32391-2025</t>
+          <t>A 29801-2022</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7018,10 +7018,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45837</v>
+        <v>44755</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7034,7 +7034,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>2.1</v>
+        <v>4.8</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7077,7 +7077,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 45990-2022</t>
+          <t>A 49981-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7091,10 +7091,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44846</v>
+        <v>45215</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7107,7 +7107,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>3.3</v>
+        <v>2.5</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7150,7 +7150,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 23607-2026</t>
+          <t>A 71835-2021</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7164,10 +7164,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46163</v>
+        <v>44543</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7180,7 +7180,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>5.3</v>
+        <v>7.5</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7223,7 +7223,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 25135-2025</t>
+          <t>A 29952-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7237,10 +7237,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45798</v>
+        <v>46205</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7253,7 +7253,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7296,7 +7296,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 143-2023</t>
+          <t>A 34386-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7310,10 +7310,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44928</v>
+        <v>46254</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7326,7 +7326,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7369,7 +7369,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 18851-2024</t>
+          <t>A 30738-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7383,10 +7383,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45426</v>
+        <v>46211</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>2.7</v>
+        <v>3.5</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7442,7 +7442,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 71835-2021</t>
+          <t>A 30859-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7456,10 +7456,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44543</v>
+        <v>46212</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7472,7 +7472,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>7.5</v>
+        <v>0.5</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7515,7 +7515,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 51724-2023</t>
+          <t>A 34387-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7529,10 +7529,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45222</v>
+        <v>46254</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7545,7 +7545,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>3.1</v>
+        <v>0.3</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7588,7 +7588,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 661-2025</t>
+          <t>A 34396-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7602,10 +7602,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45664</v>
+        <v>46254</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7618,7 +7618,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>3.1</v>
+        <v>0.8</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7661,7 +7661,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 24461-2023</t>
+          <t>A 56782-2022</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7675,10 +7675,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45082</v>
+        <v>44894</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7691,7 +7691,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7734,7 +7734,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 13880-2024</t>
+          <t>A 34392-2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7748,10 +7748,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45391</v>
+        <v>46254</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7764,7 +7764,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>2.4</v>
+        <v>0.4</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7807,7 +7807,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 29952-2026</t>
+          <t>A 26812-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7821,10 +7821,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46205</v>
+        <v>45470</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7837,7 +7837,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7880,7 +7880,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 34392-2026</t>
+          <t>A 10810-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7894,10 +7894,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46254</v>
+        <v>44989</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7953,7 +7953,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 34387-2026</t>
+          <t>A 62128-2021</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7967,10 +7967,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46254</v>
+        <v>44502</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7983,7 +7983,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.3</v>
+        <v>1.8</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8026,7 +8026,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 34386-2026</t>
+          <t>A 38262-2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>46254</v>
+        <v>46281</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8056,7 +8056,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0.7</v>
+        <v>2.8</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 34396-2026</t>
+          <t>A 21240-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8113,10 +8113,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>46254</v>
+        <v>45058</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8129,7 +8129,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>0.8</v>
+        <v>2.3</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8172,7 +8172,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 30738-2026</t>
+          <t>A 18851-2024</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8186,10 +8186,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>46211</v>
+        <v>45426</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8202,7 +8202,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>3.5</v>
+        <v>2.7</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8245,7 +8245,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 30859-2026</t>
+          <t>A 21389-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8259,10 +8259,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>46212</v>
+        <v>45063</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8275,7 +8275,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.5</v>
+        <v>3.4</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8318,7 +8318,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 23457-2024</t>
+          <t>A 44176-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8332,10 +8332,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45453</v>
+        <v>45188</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8348,7 +8348,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>5.1</v>
+        <v>7.1</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8391,7 +8391,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 21389-2023</t>
+          <t>A 23457-2024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8405,10 +8405,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45063</v>
+        <v>45453</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8421,7 +8421,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>3.4</v>
+        <v>5.1</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8464,7 +8464,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 4262-2024</t>
+          <t>A 39714-2024</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8478,10 +8478,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45324</v>
+        <v>45552</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8494,7 +8494,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>14</v>
+        <v>1.2</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8537,7 +8537,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 63319-2021</t>
+          <t>A 18852-2024</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8551,10 +8551,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>44508</v>
+        <v>45426</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8567,7 +8567,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1.6</v>
+        <v>2.7</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8610,7 +8610,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 38262-2026</t>
+          <t>A 51724-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8624,10 +8624,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>46281</v>
+        <v>45222</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8640,7 +8640,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8700,7 +8700,7 @@
         <v>45371</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>

--- a/Översikt KUNGÄLV.xlsx
+++ b/Översikt KUNGÄLV.xlsx
@@ -601,7 +601,7 @@
         <v>45548</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>45868</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -851,7 +851,7 @@
         <v>45526</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -965,7 +965,7 @@
         <v>45919</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
         <v>45695</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 59985-2025</t>
+          <t>A 4263-2024</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1188,10 +1188,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45993</v>
+        <v>45324</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1204,16 +1204,16 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>5.3</v>
+        <v>2.6</v>
       </c>
       <c r="J7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -1228,7 +1228,7 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1237,12 +1237,124 @@
         <v>4</v>
       </c>
       <c r="T7" t="n">
+        <v>6</v>
+      </c>
+      <c r="U7" t="n">
+        <v>6</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Mindre hackspett
+Klippfrullania
+Gråsiska
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 4263-2024 artfynd.xlsx", "A 4263-2024")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 4263-2024 karta.png", "A 4263-2024")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 4263-2024 georefererad karta.tif", "A 4263-2024")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 4263-2024 FSC-klagomål.docx", "A 4263-2024")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 4263-2024 FSC-klagomål mail.docx", "A 4263-2024")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 4263-2024 tillsynsbegäran.docx", "A 4263-2024")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 4263-2024 tillsynsbegäran mail.docx", "A 4263-2024")</f>
+        <v/>
+      </c>
+      <c r="AE7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 4263-2024 prioriterade fågelarter.docx", "A 4263-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 59985-2025</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>45993</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>KUNGÄLV</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2</v>
+      </c>
+      <c r="K8" t="n">
+        <v>2</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>4</v>
+      </c>
+      <c r="T8" t="n">
         <v>19</v>
       </c>
-      <c r="U7" t="n">
+      <c r="U8" t="n">
         <v>19</v>
       </c>
-      <c r="V7" s="2" t="inlineStr">
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>Blåmossa
 Västlig hakmossa
@@ -1250,148 +1362,36 @@
 Äkta lopplummer</t>
         </is>
       </c>
-      <c r="W7">
+      <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 59985-2025 artfynd.xlsx", "A 59985-2025")</f>
         <v/>
       </c>
-      <c r="X7">
+      <c r="X8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 59985-2025 karta.png", "A 59985-2025")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 59985-2025 georefererad karta.tif", "A 59985-2025")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 59985-2025 FSC-klagomål.docx", "A 59985-2025")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 59985-2025 FSC-klagomål mail.docx", "A 59985-2025")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 59985-2025 tillsynsbegäran.docx", "A 59985-2025")</f>
         <v/>
       </c>
-      <c r="AD7">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 59985-2025 tillsynsbegäran mail.docx", "A 59985-2025")</f>
         <v/>
       </c>
-      <c r="AE7">
+      <c r="AE8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 59985-2025 prioriterade fågelarter.docx", "A 59985-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A 4263-2024</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>45324</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>KUNGÄLV</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="J8" t="n">
-        <v>3</v>
-      </c>
-      <c r="K8" t="n">
-        <v>1</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>4</v>
-      </c>
-      <c r="T8" t="n">
-        <v>6</v>
-      </c>
-      <c r="U8" t="n">
-        <v>6</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>Mindre hackspett
-Klippfrullania
-Gråsiska
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 4263-2024 artfynd.xlsx", "A 4263-2024")</f>
-        <v/>
-      </c>
-      <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 4263-2024 karta.png", "A 4263-2024")</f>
-        <v/>
-      </c>
-      <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 4263-2024 georefererad karta.tif", "A 4263-2024")</f>
-        <v/>
-      </c>
-      <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 4263-2024 FSC-klagomål.docx", "A 4263-2024")</f>
-        <v/>
-      </c>
-      <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 4263-2024 FSC-klagomål mail.docx", "A 4263-2024")</f>
-        <v/>
-      </c>
-      <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 4263-2024 tillsynsbegäran.docx", "A 4263-2024")</f>
-        <v/>
-      </c>
-      <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 4263-2024 tillsynsbegäran mail.docx", "A 4263-2024")</f>
-        <v/>
-      </c>
-      <c r="AE8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 4263-2024 prioriterade fågelarter.docx", "A 4263-2024")</f>
         <v/>
       </c>
     </row>
@@ -1415,7 +1415,7 @@
         <v>45985</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>46199</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>45355</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>46212</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         <v>45957</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 56394-2025</t>
+          <t>A 5631-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1963,14 +1963,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45974</v>
+        <v>45334</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1986,10 +1986,10 @@
         <v>1.3</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -2019,582 +2019,582 @@
         <v>2</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Vanlig groda
+Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 5631-2024 artfynd.xlsx", "A 5631-2024")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 5631-2024 karta.png", "A 5631-2024")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 5631-2024 georefererad karta.tif", "A 5631-2024")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 5631-2024 FSC-klagomål.docx", "A 5631-2024")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 5631-2024 FSC-klagomål mail.docx", "A 5631-2024")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 5631-2024 tillsynsbegäran.docx", "A 5631-2024")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 5631-2024 tillsynsbegäran mail.docx", "A 5631-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 5637-2024</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>45334</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>KUNGÄLV</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>2</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Klofibbla
+Åkerrödtoppa</t>
+        </is>
+      </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 5637-2024 artfynd.xlsx", "A 5637-2024")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 5637-2024 karta.png", "A 5637-2024")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 5637-2024 georefererad karta.tif", "A 5637-2024")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 5637-2024 FSC-klagomål.docx", "A 5637-2024")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 5637-2024 FSC-klagomål mail.docx", "A 5637-2024")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 5637-2024 tillsynsbegäran.docx", "A 5637-2024")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 5637-2024 tillsynsbegäran mail.docx", "A 5637-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 56394-2025</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>45974</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>KUNGÄLV</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>Kambräken
 Revlummer</t>
         </is>
       </c>
-      <c r="W14">
+      <c r="W16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 56394-2025 artfynd.xlsx", "A 56394-2025")</f>
         <v/>
       </c>
-      <c r="X14">
+      <c r="X16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 56394-2025 karta.png", "A 56394-2025")</f>
         <v/>
       </c>
-      <c r="Y14">
+      <c r="Y16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 56394-2025 georefererad karta.tif", "A 56394-2025")</f>
         <v/>
       </c>
-      <c r="AA14">
+      <c r="AA16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 56394-2025 FSC-klagomål.docx", "A 56394-2025")</f>
         <v/>
       </c>
-      <c r="AB14">
+      <c r="AB16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 56394-2025 FSC-klagomål mail.docx", "A 56394-2025")</f>
         <v/>
       </c>
-      <c r="AC14">
+      <c r="AC16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 56394-2025 tillsynsbegäran.docx", "A 56394-2025")</f>
         <v/>
       </c>
-      <c r="AD14">
+      <c r="AD16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 56394-2025 tillsynsbegäran mail.docx", "A 56394-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
         <is>
           <t>A 57116-2025</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
         <v>45979</v>
       </c>
-      <c r="E15" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>KUNGÄLV</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
+      <c r="E17" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>KUNGÄLV</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
         <v>3.5</v>
       </c>
-      <c r="J15" t="n">
+      <c r="J17" t="n">
         <v>1</v>
       </c>
-      <c r="K15" t="n">
+      <c r="K17" t="n">
         <v>1</v>
       </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
         <v>2</v>
       </c>
-      <c r="T15" t="n">
+      <c r="T17" t="n">
         <v>3</v>
       </c>
-      <c r="U15" t="n">
+      <c r="U17" t="n">
         <v>3</v>
       </c>
-      <c r="V15" s="2" t="inlineStr">
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>Västlig hakmossa
 Spillkråka</t>
         </is>
       </c>
-      <c r="W15">
+      <c r="W17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 57116-2025 artfynd.xlsx", "A 57116-2025")</f>
         <v/>
       </c>
-      <c r="X15">
+      <c r="X17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 57116-2025 karta.png", "A 57116-2025")</f>
         <v/>
       </c>
-      <c r="Y15">
+      <c r="Y17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 57116-2025 georefererad karta.tif", "A 57116-2025")</f>
         <v/>
       </c>
-      <c r="AA15">
+      <c r="AA17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 57116-2025 FSC-klagomål.docx", "A 57116-2025")</f>
         <v/>
       </c>
-      <c r="AB15">
+      <c r="AB17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 57116-2025 FSC-klagomål mail.docx", "A 57116-2025")</f>
         <v/>
       </c>
-      <c r="AC15">
+      <c r="AC17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 57116-2025 tillsynsbegäran.docx", "A 57116-2025")</f>
         <v/>
       </c>
-      <c r="AD15">
+      <c r="AD17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 57116-2025 tillsynsbegäran mail.docx", "A 57116-2025")</f>
         <v/>
       </c>
-      <c r="AE15">
+      <c r="AE17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 57116-2025 prioriterade fågelarter.docx", "A 57116-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
         <is>
           <t>A 30860-2026</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
         <v>46212</v>
       </c>
-      <c r="E16" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>KUNGÄLV</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
+      <c r="E18" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>KUNGÄLV</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
         <v>1.7</v>
       </c>
-      <c r="J16" t="n">
+      <c r="J18" t="n">
         <v>1</v>
       </c>
-      <c r="K16" t="n">
+      <c r="K18" t="n">
         <v>1</v>
       </c>
-      <c r="L16" t="n">
+      <c r="L18" t="n">
         <v>1</v>
       </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
         <v>1</v>
       </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
         <v>2</v>
       </c>
-      <c r="T16" t="n">
+      <c r="T18" t="n">
         <v>2</v>
       </c>
-      <c r="U16" t="n">
+      <c r="U18" t="n">
         <v>1</v>
       </c>
-      <c r="V16" s="2" t="inlineStr">
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>Grönsångare
 Västlig hakmossa</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 30860-2026 artfynd.xlsx", "A 30860-2026")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 30860-2026 karta.png", "A 30860-2026")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 30860-2026 georefererad karta.tif", "A 30860-2026")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 30860-2026 FSC-klagomål.docx", "A 30860-2026")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 30860-2026 FSC-klagomål mail.docx", "A 30860-2026")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 30860-2026 tillsynsbegäran.docx", "A 30860-2026")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 30860-2026 tillsynsbegäran mail.docx", "A 30860-2026")</f>
         <v/>
       </c>
-      <c r="AE16">
+      <c r="AE18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 30860-2026 prioriterade fågelarter.docx", "A 30860-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
         <is>
           <t>A 53007-2025</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
         <v>45957</v>
       </c>
-      <c r="E17" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>KUNGÄLV</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
+      <c r="E19" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>KUNGÄLV</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
         <v>2.9</v>
       </c>
-      <c r="J17" t="n">
+      <c r="J19" t="n">
         <v>1</v>
       </c>
-      <c r="K17" t="n">
+      <c r="K19" t="n">
         <v>1</v>
       </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
         <v>2</v>
       </c>
-      <c r="T17" t="n">
+      <c r="T19" t="n">
         <v>5</v>
       </c>
-      <c r="U17" t="n">
+      <c r="U19" t="n">
         <v>5</v>
       </c>
-      <c r="V17" s="2" t="inlineStr">
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>Västlig hakmossa
 Spillkråka</t>
         </is>
       </c>
-      <c r="W17">
+      <c r="W19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 53007-2025 artfynd.xlsx", "A 53007-2025")</f>
         <v/>
       </c>
-      <c r="X17">
+      <c r="X19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 53007-2025 karta.png", "A 53007-2025")</f>
         <v/>
       </c>
-      <c r="Y17">
+      <c r="Y19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 53007-2025 georefererad karta.tif", "A 53007-2025")</f>
         <v/>
       </c>
-      <c r="AA17">
+      <c r="AA19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 53007-2025 FSC-klagomål.docx", "A 53007-2025")</f>
         <v/>
       </c>
-      <c r="AB17">
+      <c r="AB19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 53007-2025 FSC-klagomål mail.docx", "A 53007-2025")</f>
         <v/>
       </c>
-      <c r="AC17">
+      <c r="AC19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 53007-2025 tillsynsbegäran.docx", "A 53007-2025")</f>
         <v/>
       </c>
-      <c r="AD17">
+      <c r="AD19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 53007-2025 tillsynsbegäran mail.docx", "A 53007-2025")</f>
         <v/>
       </c>
-      <c r="AE17">
+      <c r="AE19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 53007-2025 prioriterade fågelarter.docx", "A 53007-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 5631-2024</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>45334</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>KUNGÄLV</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="J18" t="n">
-        <v>2</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>Vanlig groda
-Fläcknycklar</t>
-        </is>
-      </c>
-      <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 5631-2024 artfynd.xlsx", "A 5631-2024")</f>
-        <v/>
-      </c>
-      <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 5631-2024 karta.png", "A 5631-2024")</f>
-        <v/>
-      </c>
-      <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 5631-2024 georefererad karta.tif", "A 5631-2024")</f>
-        <v/>
-      </c>
-      <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 5631-2024 FSC-klagomål.docx", "A 5631-2024")</f>
-        <v/>
-      </c>
-      <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 5631-2024 FSC-klagomål mail.docx", "A 5631-2024")</f>
-        <v/>
-      </c>
-      <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 5631-2024 tillsynsbegäran.docx", "A 5631-2024")</f>
-        <v/>
-      </c>
-      <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 5631-2024 tillsynsbegäran mail.docx", "A 5631-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>A 5637-2024</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>45334</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>KUNGÄLV</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>2</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>2</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>Klofibbla
-Åkerrödtoppa</t>
-        </is>
-      </c>
-      <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 5637-2024 artfynd.xlsx", "A 5637-2024")</f>
-        <v/>
-      </c>
-      <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 5637-2024 karta.png", "A 5637-2024")</f>
-        <v/>
-      </c>
-      <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 5637-2024 georefererad karta.tif", "A 5637-2024")</f>
-        <v/>
-      </c>
-      <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 5637-2024 FSC-klagomål.docx", "A 5637-2024")</f>
-        <v/>
-      </c>
-      <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 5637-2024 FSC-klagomål mail.docx", "A 5637-2024")</f>
-        <v/>
-      </c>
-      <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 5637-2024 tillsynsbegäran.docx", "A 5637-2024")</f>
-        <v/>
-      </c>
-      <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 5637-2024 tillsynsbegäran mail.docx", "A 5637-2024")</f>
         <v/>
       </c>
     </row>
@@ -2618,7 +2618,7 @@
         <v>44838</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2723,7 +2723,7 @@
         <v>45215</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2828,7 +2828,7 @@
         <v>45697</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2920,7 +2920,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 30862-2026</t>
+          <t>A 23704-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2934,10 +2934,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46212</v>
+        <v>45454</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2950,7 +2950,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.7</v>
+        <v>4.9</v>
       </c>
       <c r="J23" t="n">
         <v>1</v>
@@ -2962,7 +2962,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
@@ -2974,58 +2974,58 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
       </c>
       <c r="T23" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Hedjohannesört</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 30862-2026 artfynd.xlsx", "A 30862-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 23704-2024 artfynd.xlsx", "A 23704-2024")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 30862-2026 karta.png", "A 30862-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 23704-2024 karta.png", "A 23704-2024")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 30862-2026 georefererad karta.tif", "A 30862-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 23704-2024 georefererad karta.tif", "A 23704-2024")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 30862-2026 FSC-klagomål.docx", "A 30862-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 23704-2024 FSC-klagomål.docx", "A 23704-2024")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 30862-2026 FSC-klagomål mail.docx", "A 30862-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 23704-2024 FSC-klagomål mail.docx", "A 23704-2024")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 30862-2026 tillsynsbegäran.docx", "A 30862-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 23704-2024 tillsynsbegäran.docx", "A 23704-2024")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 30862-2026 tillsynsbegäran mail.docx", "A 30862-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 23704-2024 tillsynsbegäran mail.docx", "A 23704-2024")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 23704-2024</t>
+          <t>A 30862-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3039,10 +3039,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45454</v>
+        <v>46212</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3055,7 +3055,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>4.9</v>
+        <v>1.7</v>
       </c>
       <c r="J24" t="n">
         <v>1</v>
@@ -3067,7 +3067,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
@@ -3079,51 +3079,51 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
       </c>
       <c r="T24" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="U24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Hedjohannesört</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 23704-2024 artfynd.xlsx", "A 23704-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 30862-2026 artfynd.xlsx", "A 30862-2026")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 23704-2024 karta.png", "A 23704-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 30862-2026 karta.png", "A 30862-2026")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 23704-2024 georefererad karta.tif", "A 23704-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 30862-2026 georefererad karta.tif", "A 30862-2026")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 23704-2024 FSC-klagomål.docx", "A 23704-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 30862-2026 FSC-klagomål.docx", "A 30862-2026")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 23704-2024 FSC-klagomål mail.docx", "A 23704-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 30862-2026 FSC-klagomål mail.docx", "A 30862-2026")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 23704-2024 tillsynsbegäran.docx", "A 23704-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 30862-2026 tillsynsbegäran.docx", "A 30862-2026")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 23704-2024 tillsynsbegäran mail.docx", "A 23704-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 30862-2026 tillsynsbegäran mail.docx", "A 30862-2026")</f>
         <v/>
       </c>
     </row>
@@ -3147,7 +3147,7 @@
         <v>44691</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
         <v>44691</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         <v>44836</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3366,7 +3366,7 @@
         <v>44760</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         <v>44760</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
         <v>44760</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3568,7 +3568,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 62221-2023</t>
+          <t>A 17455-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3582,10 +3582,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45267</v>
+        <v>45757</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3598,7 +3598,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.3</v>
+        <v>2.1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3641,7 +3641,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 4204-2024</t>
+          <t>A 62221-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3655,10 +3655,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45324</v>
+        <v>45267</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3671,7 +3671,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>4.4</v>
+        <v>1.3</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3714,7 +3714,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 30170-2022</t>
+          <t>A 43520-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3728,10 +3728,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44757</v>
+        <v>44837</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3744,7 +3744,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>3.1</v>
+        <v>1.5</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3787,7 +3787,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 13880-2024</t>
+          <t>A 21389-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3801,10 +3801,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45391</v>
+        <v>45063</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3817,7 +3817,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2.4</v>
+        <v>3.4</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3860,7 +3860,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 1995-2024</t>
+          <t>A 4262-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3874,10 +3874,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45308</v>
+        <v>45324</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3890,7 +3890,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.5</v>
+        <v>14</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3933,7 +3933,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 45990-2022</t>
+          <t>A 21240-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3947,10 +3947,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44846</v>
+        <v>45058</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3963,7 +3963,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>3.3</v>
+        <v>2.3</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4006,7 +4006,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 10679-2025</t>
+          <t>A 16538-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4020,10 +4020,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45721</v>
+        <v>45751</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>4.4</v>
+        <v>0.8</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4079,7 +4079,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 11237-2025</t>
+          <t>A 45990-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4093,10 +4093,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45726</v>
+        <v>44846</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4109,7 +4109,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4152,7 +4152,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 10677-2025</t>
+          <t>A 143-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4166,10 +4166,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45721</v>
+        <v>44928</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4182,7 +4182,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>7.4</v>
+        <v>0.5</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4225,7 +4225,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 74285-2021</t>
+          <t>A 18851-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4239,10 +4239,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44558</v>
+        <v>45426</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4255,7 +4255,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.1</v>
+        <v>2.7</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4298,7 +4298,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 17922-2025</t>
+          <t>A 71835-2021</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4312,10 +4312,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45758</v>
+        <v>44543</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4328,7 +4328,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.8</v>
+        <v>7.5</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4371,7 +4371,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 43520-2022</t>
+          <t>A 63319-2021</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4385,10 +4385,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44837</v>
+        <v>44508</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4401,7 +4401,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4444,7 +4444,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 40951-2025</t>
+          <t>A 29223-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4458,10 +4458,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45897</v>
+        <v>45482</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4474,7 +4474,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.8</v>
+        <v>5.6</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4517,7 +4517,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 61417-2022</t>
+          <t>A 10655-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4531,10 +4531,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44916</v>
+        <v>44624</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4547,7 +4547,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>3.6</v>
+        <v>13.3</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4590,7 +4590,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 32272-2023</t>
+          <t>A 49981-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4604,10 +4604,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45120</v>
+        <v>45215</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4620,7 +4620,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>4.9</v>
+        <v>2.5</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4663,7 +4663,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 32847-2023</t>
+          <t>A 56782-2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4677,10 +4677,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45124</v>
+        <v>44894</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>4.7</v>
+        <v>0.5</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4736,7 +4736,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 29223-2024</t>
+          <t>A 1995-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4750,10 +4750,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45482</v>
+        <v>45308</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4766,7 +4766,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>5.6</v>
+        <v>0.5</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4809,7 +4809,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 34366-2022</t>
+          <t>A 30170-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4823,10 +4823,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44792</v>
+        <v>44757</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.5</v>
+        <v>3.1</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4882,7 +4882,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 45124-2025</t>
+          <t>A 10810-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4896,10 +4896,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45919</v>
+        <v>44989</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4912,7 +4912,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>3.7</v>
+        <v>0.4</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4955,7 +4955,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 8334-2023</t>
+          <t>A 51724-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4969,10 +4969,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44975</v>
+        <v>45222</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4985,7 +4985,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.8</v>
+        <v>3.1</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5028,7 +5028,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 47564-2025</t>
+          <t>A 10677-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5042,10 +5042,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45931</v>
+        <v>45721</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5058,7 +5058,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2</v>
+        <v>7.4</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5101,7 +5101,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 4673-2026</t>
+          <t>A 10679-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5115,10 +5115,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46048</v>
+        <v>45721</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5131,7 +5131,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>8.199999999999999</v>
+        <v>4.4</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5174,7 +5174,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 34244-2025</t>
+          <t>A 11237-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5188,10 +5188,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45844</v>
+        <v>45726</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5204,7 +5204,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2.9</v>
+        <v>4.2</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5247,7 +5247,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 25624-2025</t>
+          <t>A 4204-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5261,10 +5261,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45803</v>
+        <v>45324</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5277,7 +5277,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5320,7 +5320,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 41442-2025</t>
+          <t>A 39714-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5334,10 +5334,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45869</v>
+        <v>45552</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5350,7 +5350,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5393,7 +5393,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 52932-2025</t>
+          <t>A 74285-2021</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5407,10 +5407,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45957</v>
+        <v>44558</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5423,7 +5423,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>3.4</v>
+        <v>1.1</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5466,7 +5466,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 6946-2026</t>
+          <t>A 661-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5476,14 +5476,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46057</v>
+        <v>45664</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5496,7 +5496,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2.2</v>
+        <v>3.1</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5539,7 +5539,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 4262-2024</t>
+          <t>A 24461-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5553,10 +5553,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45324</v>
+        <v>45082</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5569,7 +5569,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>14</v>
+        <v>1.5</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5612,7 +5612,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 661-2025</t>
+          <t>A 13880-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5626,10 +5626,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45664</v>
+        <v>45391</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5642,7 +5642,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5685,7 +5685,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 37443-2025</t>
+          <t>A 62128-2021</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5699,10 +5699,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45877</v>
+        <v>44502</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5714,13 +5714,8 @@
           <t>KUNGÄLV</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I60" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5763,7 +5758,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 13990-2026</t>
+          <t>A 61417-2022</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5777,10 +5772,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46098</v>
+        <v>44916</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5793,7 +5788,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5836,7 +5831,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 24461-2023</t>
+          <t>A 32272-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5850,10 +5845,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45082</v>
+        <v>45120</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5866,7 +5861,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.5</v>
+        <v>4.9</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5909,7 +5904,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 143-2023</t>
+          <t>A 62979-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5919,14 +5914,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44928</v>
+        <v>45271</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5939,7 +5934,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5982,7 +5977,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 63319-2021</t>
+          <t>A 32847-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5996,10 +5991,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44508</v>
+        <v>45124</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6012,7 +6007,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.6</v>
+        <v>4.7</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6055,7 +6050,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 49985-2023</t>
+          <t>A 19531-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6069,10 +6064,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45215</v>
+        <v>45050</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6085,7 +6080,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>8.199999999999999</v>
+        <v>1.9</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6128,7 +6123,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 50071-2023</t>
+          <t>A 5705-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6138,14 +6133,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45215</v>
+        <v>45694</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6158,7 +6153,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>4</v>
+        <v>1.2</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6201,7 +6196,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 7505-2024</t>
+          <t>A 44176-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6215,10 +6210,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45347</v>
+        <v>45188</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6231,7 +6226,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.8</v>
+        <v>7.1</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6274,7 +6269,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 10655-2022</t>
+          <t>A 23457-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6288,10 +6283,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44624</v>
+        <v>45453</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6304,7 +6299,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>13.3</v>
+        <v>5.1</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6347,7 +6342,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 17455-2025</t>
+          <t>A 7505-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6361,10 +6356,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45757</v>
+        <v>45347</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6377,7 +6372,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6420,7 +6415,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 19531-2023</t>
+          <t>A 26812-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6434,10 +6429,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45050</v>
+        <v>45470</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6450,7 +6445,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6493,7 +6488,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 22731-2026</t>
+          <t>A 34244-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6507,10 +6502,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46157</v>
+        <v>45844</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6523,7 +6518,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.8</v>
+        <v>2.9</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6566,7 +6561,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 32391-2025</t>
+          <t>A 25624-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6580,10 +6575,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45837</v>
+        <v>45803</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6596,7 +6591,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>2.1</v>
+        <v>5</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6639,7 +6634,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 5705-2025</t>
+          <t>A 29801-2022</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6649,14 +6644,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45694</v>
+        <v>44755</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6669,7 +6664,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.2</v>
+        <v>4.8</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6712,7 +6707,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 23607-2026</t>
+          <t>A 18852-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6726,10 +6721,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46163</v>
+        <v>45426</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6742,7 +6737,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>5.3</v>
+        <v>2.7</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6785,7 +6780,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 25135-2025</t>
+          <t>A 41442-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6799,10 +6794,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45798</v>
+        <v>45869</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6815,7 +6810,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6858,7 +6853,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 62979-2023</t>
+          <t>A 8334-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6868,14 +6863,14 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45271</v>
+        <v>44975</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6888,7 +6883,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.8</v>
+        <v>1.8</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6931,7 +6926,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 16538-2025</t>
+          <t>A 17922-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6945,10 +6940,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45751</v>
+        <v>45758</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7004,7 +6999,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 29801-2022</t>
+          <t>A 40951-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7018,10 +7013,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44755</v>
+        <v>45897</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7034,7 +7029,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>4.8</v>
+        <v>0.8</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7077,7 +7072,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 49981-2023</t>
+          <t>A 52932-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7091,10 +7086,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45215</v>
+        <v>45957</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7107,7 +7102,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>2.5</v>
+        <v>3.4</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7150,7 +7145,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 71835-2021</t>
+          <t>A 45124-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7164,10 +7159,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44543</v>
+        <v>45919</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7180,7 +7175,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>7.5</v>
+        <v>3.7</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7223,7 +7218,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 29952-2026</t>
+          <t>A 47564-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7237,10 +7232,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46205</v>
+        <v>45931</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7296,7 +7291,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 34386-2026</t>
+          <t>A 34366-2022</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7310,10 +7305,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46254</v>
+        <v>44792</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7326,7 +7321,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7369,7 +7364,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 30738-2026</t>
+          <t>A 4673-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7383,10 +7378,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46211</v>
+        <v>46048</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7399,7 +7394,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>3.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7442,7 +7437,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 30859-2026</t>
+          <t>A 6946-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7452,14 +7447,14 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46212</v>
+        <v>46057</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7472,7 +7467,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>0.5</v>
+        <v>2.2</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7515,7 +7510,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 34387-2026</t>
+          <t>A 37443-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7529,10 +7524,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46254</v>
+        <v>45877</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7544,8 +7539,13 @@
           <t>KUNGÄLV</t>
         </is>
       </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I85" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7588,7 +7588,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 34396-2026</t>
+          <t>A 13990-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7602,10 +7602,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46254</v>
+        <v>46098</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7618,7 +7618,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>0.8</v>
+        <v>2.6</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7661,7 +7661,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 56782-2022</t>
+          <t>A 49985-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7675,10 +7675,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>44894</v>
+        <v>45215</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7691,7 +7691,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7734,7 +7734,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 34392-2026</t>
+          <t>A 50071-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7748,10 +7748,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>46254</v>
+        <v>45215</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7764,7 +7764,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0.4</v>
+        <v>4</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7807,7 +7807,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 26812-2024</t>
+          <t>A 22731-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7821,10 +7821,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45470</v>
+        <v>46157</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7837,7 +7837,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7880,7 +7880,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 10810-2023</t>
+          <t>A 32391-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7894,10 +7894,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>44989</v>
+        <v>45837</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7910,7 +7910,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0.4</v>
+        <v>2.1</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7953,7 +7953,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 62128-2021</t>
+          <t>A 23607-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7967,10 +7967,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>44502</v>
+        <v>46163</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7983,7 +7983,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1.8</v>
+        <v>5.3</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8026,7 +8026,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 38262-2026</t>
+          <t>A 25135-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>46281</v>
+        <v>45798</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8056,7 +8056,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>2.8</v>
+        <v>1.1</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 21240-2023</t>
+          <t>A 29952-2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8113,10 +8113,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45058</v>
+        <v>46205</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8129,7 +8129,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8172,7 +8172,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 18851-2024</t>
+          <t>A 34392-2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8186,10 +8186,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45426</v>
+        <v>46254</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8202,7 +8202,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>2.7</v>
+        <v>0.4</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8245,7 +8245,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 21389-2023</t>
+          <t>A 34387-2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8259,10 +8259,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45063</v>
+        <v>46254</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8275,7 +8275,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>3.4</v>
+        <v>0.3</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8318,7 +8318,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 44176-2023</t>
+          <t>A 34386-2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8332,10 +8332,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45188</v>
+        <v>46254</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8348,7 +8348,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>7.1</v>
+        <v>0.7</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8391,7 +8391,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 23457-2024</t>
+          <t>A 34396-2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8405,10 +8405,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45453</v>
+        <v>46254</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8421,7 +8421,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>5.1</v>
+        <v>0.8</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8464,7 +8464,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 39714-2024</t>
+          <t>A 30738-2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8478,10 +8478,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45552</v>
+        <v>46211</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8494,7 +8494,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1.2</v>
+        <v>3.5</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8537,7 +8537,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 18852-2024</t>
+          <t>A 30859-2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8551,10 +8551,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45426</v>
+        <v>46212</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8567,7 +8567,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>2.7</v>
+        <v>0.5</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8610,7 +8610,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 51724-2023</t>
+          <t>A 38262-2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8624,10 +8624,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45222</v>
+        <v>46281</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8640,7 +8640,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8700,7 +8700,7 @@
         <v>45371</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>

--- a/Översikt KUNGÄLV.xlsx
+++ b/Översikt KUNGÄLV.xlsx
@@ -601,7 +601,7 @@
         <v>45548</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>45868</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -851,7 +851,7 @@
         <v>45526</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -965,7 +965,7 @@
         <v>45919</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
         <v>45695</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 4263-2024</t>
+          <t>A 59985-2025</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1188,10 +1188,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45324</v>
+        <v>45993</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1204,16 +1204,16 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>2.6</v>
+        <v>5.3</v>
       </c>
       <c r="J7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -1228,7 +1228,7 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1237,12 +1237,124 @@
         <v>4</v>
       </c>
       <c r="T7" t="n">
+        <v>19</v>
+      </c>
+      <c r="U7" t="n">
+        <v>19</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Blåmossa
+Västlig hakmossa
+Spillkråka
+Äkta lopplummer</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 59985-2025 artfynd.xlsx", "A 59985-2025")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 59985-2025 karta.png", "A 59985-2025")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 59985-2025 georefererad karta.tif", "A 59985-2025")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 59985-2025 FSC-klagomål.docx", "A 59985-2025")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 59985-2025 FSC-klagomål mail.docx", "A 59985-2025")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 59985-2025 tillsynsbegäran.docx", "A 59985-2025")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 59985-2025 tillsynsbegäran mail.docx", "A 59985-2025")</f>
+        <v/>
+      </c>
+      <c r="AE7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 59985-2025 prioriterade fågelarter.docx", "A 59985-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 4263-2024</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>45324</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>KUNGÄLV</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J8" t="n">
+        <v>3</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>4</v>
+      </c>
+      <c r="T8" t="n">
         <v>6</v>
       </c>
-      <c r="U7" t="n">
+      <c r="U8" t="n">
         <v>6</v>
       </c>
-      <c r="V7" s="2" t="inlineStr">
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>Mindre hackspett
 Klippfrullania
@@ -1250,148 +1362,36 @@
 Spillkråka</t>
         </is>
       </c>
-      <c r="W7">
+      <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 4263-2024 artfynd.xlsx", "A 4263-2024")</f>
         <v/>
       </c>
-      <c r="X7">
+      <c r="X8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 4263-2024 karta.png", "A 4263-2024")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 4263-2024 georefererad karta.tif", "A 4263-2024")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 4263-2024 FSC-klagomål.docx", "A 4263-2024")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 4263-2024 FSC-klagomål mail.docx", "A 4263-2024")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 4263-2024 tillsynsbegäran.docx", "A 4263-2024")</f>
         <v/>
       </c>
-      <c r="AD7">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 4263-2024 tillsynsbegäran mail.docx", "A 4263-2024")</f>
         <v/>
       </c>
-      <c r="AE7">
+      <c r="AE8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 4263-2024 prioriterade fågelarter.docx", "A 4263-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A 59985-2025</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>45993</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>KUNGÄLV</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="J8" t="n">
-        <v>2</v>
-      </c>
-      <c r="K8" t="n">
-        <v>2</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>4</v>
-      </c>
-      <c r="T8" t="n">
-        <v>19</v>
-      </c>
-      <c r="U8" t="n">
-        <v>19</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>Blåmossa
-Västlig hakmossa
-Spillkråka
-Äkta lopplummer</t>
-        </is>
-      </c>
-      <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 59985-2025 artfynd.xlsx", "A 59985-2025")</f>
-        <v/>
-      </c>
-      <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 59985-2025 karta.png", "A 59985-2025")</f>
-        <v/>
-      </c>
-      <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 59985-2025 georefererad karta.tif", "A 59985-2025")</f>
-        <v/>
-      </c>
-      <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 59985-2025 FSC-klagomål.docx", "A 59985-2025")</f>
-        <v/>
-      </c>
-      <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 59985-2025 FSC-klagomål mail.docx", "A 59985-2025")</f>
-        <v/>
-      </c>
-      <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 59985-2025 tillsynsbegäran.docx", "A 59985-2025")</f>
-        <v/>
-      </c>
-      <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 59985-2025 tillsynsbegäran mail.docx", "A 59985-2025")</f>
-        <v/>
-      </c>
-      <c r="AE8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 59985-2025 prioriterade fågelarter.docx", "A 59985-2025")</f>
         <v/>
       </c>
     </row>
@@ -1415,7 +1415,7 @@
         <v>45985</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>46199</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>45355</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>46212</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         <v>45957</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 5631-2024</t>
+          <t>A 56394-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1963,14 +1963,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45334</v>
+        <v>45974</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1986,10 +1986,10 @@
         <v>1.3</v>
       </c>
       <c r="J14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -2019,582 +2019,582 @@
         <v>2</v>
       </c>
       <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Kambräken
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 56394-2025 artfynd.xlsx", "A 56394-2025")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 56394-2025 karta.png", "A 56394-2025")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 56394-2025 georefererad karta.tif", "A 56394-2025")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 56394-2025 FSC-klagomål.docx", "A 56394-2025")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 56394-2025 FSC-klagomål mail.docx", "A 56394-2025")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 56394-2025 tillsynsbegäran.docx", "A 56394-2025")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 56394-2025 tillsynsbegäran mail.docx", "A 56394-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 57116-2025</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>45979</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>KUNGÄLV</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J15" t="n">
         <v>1</v>
       </c>
-      <c r="V14" s="2" t="inlineStr">
+      <c r="K15" t="n">
+        <v>1</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>3</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Västlig hakmossa
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 57116-2025 artfynd.xlsx", "A 57116-2025")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 57116-2025 karta.png", "A 57116-2025")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 57116-2025 georefererad karta.tif", "A 57116-2025")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 57116-2025 FSC-klagomål.docx", "A 57116-2025")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 57116-2025 FSC-klagomål mail.docx", "A 57116-2025")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 57116-2025 tillsynsbegäran.docx", "A 57116-2025")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 57116-2025 tillsynsbegäran mail.docx", "A 57116-2025")</f>
+        <v/>
+      </c>
+      <c r="AE15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 57116-2025 prioriterade fågelarter.docx", "A 57116-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 30860-2026</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>46212</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>KUNGÄLV</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Grönsångare
+Västlig hakmossa</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 30860-2026 artfynd.xlsx", "A 30860-2026")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 30860-2026 karta.png", "A 30860-2026")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 30860-2026 georefererad karta.tif", "A 30860-2026")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 30860-2026 FSC-klagomål.docx", "A 30860-2026")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 30860-2026 FSC-klagomål mail.docx", "A 30860-2026")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 30860-2026 tillsynsbegäran.docx", "A 30860-2026")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 30860-2026 tillsynsbegäran mail.docx", "A 30860-2026")</f>
+        <v/>
+      </c>
+      <c r="AE16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 30860-2026 prioriterade fågelarter.docx", "A 30860-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 53007-2025</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>45957</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>KUNGÄLV</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2</v>
+      </c>
+      <c r="T17" t="n">
+        <v>5</v>
+      </c>
+      <c r="U17" t="n">
+        <v>5</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>Västlig hakmossa
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 53007-2025 artfynd.xlsx", "A 53007-2025")</f>
+        <v/>
+      </c>
+      <c r="X17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 53007-2025 karta.png", "A 53007-2025")</f>
+        <v/>
+      </c>
+      <c r="Y17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 53007-2025 georefererad karta.tif", "A 53007-2025")</f>
+        <v/>
+      </c>
+      <c r="AA17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 53007-2025 FSC-klagomål.docx", "A 53007-2025")</f>
+        <v/>
+      </c>
+      <c r="AB17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 53007-2025 FSC-klagomål mail.docx", "A 53007-2025")</f>
+        <v/>
+      </c>
+      <c r="AC17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 53007-2025 tillsynsbegäran.docx", "A 53007-2025")</f>
+        <v/>
+      </c>
+      <c r="AD17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 53007-2025 tillsynsbegäran mail.docx", "A 53007-2025")</f>
+        <v/>
+      </c>
+      <c r="AE17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 53007-2025 prioriterade fågelarter.docx", "A 53007-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>A 5631-2024</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>45334</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>KUNGÄLV</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>Vanlig groda
 Fläcknycklar</t>
         </is>
       </c>
-      <c r="W14">
+      <c r="W18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 5631-2024 artfynd.xlsx", "A 5631-2024")</f>
         <v/>
       </c>
-      <c r="X14">
+      <c r="X18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 5631-2024 karta.png", "A 5631-2024")</f>
         <v/>
       </c>
-      <c r="Y14">
+      <c r="Y18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 5631-2024 georefererad karta.tif", "A 5631-2024")</f>
         <v/>
       </c>
-      <c r="AA14">
+      <c r="AA18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 5631-2024 FSC-klagomål.docx", "A 5631-2024")</f>
         <v/>
       </c>
-      <c r="AB14">
+      <c r="AB18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 5631-2024 FSC-klagomål mail.docx", "A 5631-2024")</f>
         <v/>
       </c>
-      <c r="AC14">
+      <c r="AC18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 5631-2024 tillsynsbegäran.docx", "A 5631-2024")</f>
         <v/>
       </c>
-      <c r="AD14">
+      <c r="AD18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 5631-2024 tillsynsbegäran mail.docx", "A 5631-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
         <is>
           <t>A 5637-2024</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
         <v>45334</v>
       </c>
-      <c r="E15" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>KUNGÄLV</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
+      <c r="E19" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>KUNGÄLV</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
         <v>1.8</v>
       </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
         <v>2</v>
       </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
         <v>2</v>
       </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
         <v>2</v>
       </c>
-      <c r="T15" t="n">
+      <c r="T19" t="n">
         <v>2</v>
       </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>Klofibbla
 Åkerrödtoppa</t>
         </is>
       </c>
-      <c r="W15">
+      <c r="W19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 5637-2024 artfynd.xlsx", "A 5637-2024")</f>
         <v/>
       </c>
-      <c r="X15">
+      <c r="X19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 5637-2024 karta.png", "A 5637-2024")</f>
         <v/>
       </c>
-      <c r="Y15">
+      <c r="Y19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 5637-2024 georefererad karta.tif", "A 5637-2024")</f>
         <v/>
       </c>
-      <c r="AA15">
+      <c r="AA19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 5637-2024 FSC-klagomål.docx", "A 5637-2024")</f>
         <v/>
       </c>
-      <c r="AB15">
+      <c r="AB19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 5637-2024 FSC-klagomål mail.docx", "A 5637-2024")</f>
         <v/>
       </c>
-      <c r="AC15">
+      <c r="AC19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 5637-2024 tillsynsbegäran.docx", "A 5637-2024")</f>
         <v/>
       </c>
-      <c r="AD15">
+      <c r="AD19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 5637-2024 tillsynsbegäran mail.docx", "A 5637-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 56394-2025</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>45974</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>KUNGÄLV</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="J16" t="n">
-        <v>1</v>
-      </c>
-      <c r="K16" t="n">
-        <v>1</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>Kambräken
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 56394-2025 artfynd.xlsx", "A 56394-2025")</f>
-        <v/>
-      </c>
-      <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 56394-2025 karta.png", "A 56394-2025")</f>
-        <v/>
-      </c>
-      <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 56394-2025 georefererad karta.tif", "A 56394-2025")</f>
-        <v/>
-      </c>
-      <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 56394-2025 FSC-klagomål.docx", "A 56394-2025")</f>
-        <v/>
-      </c>
-      <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 56394-2025 FSC-klagomål mail.docx", "A 56394-2025")</f>
-        <v/>
-      </c>
-      <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 56394-2025 tillsynsbegäran.docx", "A 56394-2025")</f>
-        <v/>
-      </c>
-      <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 56394-2025 tillsynsbegäran mail.docx", "A 56394-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 57116-2025</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>45979</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>KUNGÄLV</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="J17" t="n">
-        <v>1</v>
-      </c>
-      <c r="K17" t="n">
-        <v>1</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2</v>
-      </c>
-      <c r="T17" t="n">
-        <v>3</v>
-      </c>
-      <c r="U17" t="n">
-        <v>3</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Västlig hakmossa
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 57116-2025 artfynd.xlsx", "A 57116-2025")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 57116-2025 karta.png", "A 57116-2025")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 57116-2025 georefererad karta.tif", "A 57116-2025")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 57116-2025 FSC-klagomål.docx", "A 57116-2025")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 57116-2025 FSC-klagomål mail.docx", "A 57116-2025")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 57116-2025 tillsynsbegäran.docx", "A 57116-2025")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 57116-2025 tillsynsbegäran mail.docx", "A 57116-2025")</f>
-        <v/>
-      </c>
-      <c r="AE17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 57116-2025 prioriterade fågelarter.docx", "A 57116-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 30860-2026</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>46212</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>KUNGÄLV</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="J18" t="n">
-        <v>1</v>
-      </c>
-      <c r="K18" t="n">
-        <v>1</v>
-      </c>
-      <c r="L18" t="n">
-        <v>1</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>1</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>Grönsångare
-Västlig hakmossa</t>
-        </is>
-      </c>
-      <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 30860-2026 artfynd.xlsx", "A 30860-2026")</f>
-        <v/>
-      </c>
-      <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 30860-2026 karta.png", "A 30860-2026")</f>
-        <v/>
-      </c>
-      <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 30860-2026 georefererad karta.tif", "A 30860-2026")</f>
-        <v/>
-      </c>
-      <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 30860-2026 FSC-klagomål.docx", "A 30860-2026")</f>
-        <v/>
-      </c>
-      <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 30860-2026 FSC-klagomål mail.docx", "A 30860-2026")</f>
-        <v/>
-      </c>
-      <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 30860-2026 tillsynsbegäran.docx", "A 30860-2026")</f>
-        <v/>
-      </c>
-      <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 30860-2026 tillsynsbegäran mail.docx", "A 30860-2026")</f>
-        <v/>
-      </c>
-      <c r="AE18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 30860-2026 prioriterade fågelarter.docx", "A 30860-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>A 53007-2025</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>45957</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>KUNGÄLV</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="J19" t="n">
-        <v>1</v>
-      </c>
-      <c r="K19" t="n">
-        <v>1</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2</v>
-      </c>
-      <c r="T19" t="n">
-        <v>5</v>
-      </c>
-      <c r="U19" t="n">
-        <v>5</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>Västlig hakmossa
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 53007-2025 artfynd.xlsx", "A 53007-2025")</f>
-        <v/>
-      </c>
-      <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 53007-2025 karta.png", "A 53007-2025")</f>
-        <v/>
-      </c>
-      <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 53007-2025 georefererad karta.tif", "A 53007-2025")</f>
-        <v/>
-      </c>
-      <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 53007-2025 FSC-klagomål.docx", "A 53007-2025")</f>
-        <v/>
-      </c>
-      <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 53007-2025 FSC-klagomål mail.docx", "A 53007-2025")</f>
-        <v/>
-      </c>
-      <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 53007-2025 tillsynsbegäran.docx", "A 53007-2025")</f>
-        <v/>
-      </c>
-      <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 53007-2025 tillsynsbegäran mail.docx", "A 53007-2025")</f>
-        <v/>
-      </c>
-      <c r="AE19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 53007-2025 prioriterade fågelarter.docx", "A 53007-2025")</f>
         <v/>
       </c>
     </row>
@@ -2618,7 +2618,7 @@
         <v>44838</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2723,7 +2723,7 @@
         <v>45215</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2828,7 +2828,7 @@
         <v>45697</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2920,7 +2920,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 23704-2024</t>
+          <t>A 30862-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2934,10 +2934,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45454</v>
+        <v>46212</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2950,7 +2950,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>4.9</v>
+        <v>1.7</v>
       </c>
       <c r="J23" t="n">
         <v>1</v>
@@ -2962,7 +2962,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
@@ -2974,58 +2974,58 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
       </c>
       <c r="T23" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="U23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Hedjohannesört</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 23704-2024 artfynd.xlsx", "A 23704-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 30862-2026 artfynd.xlsx", "A 30862-2026")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 23704-2024 karta.png", "A 23704-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 30862-2026 karta.png", "A 30862-2026")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 23704-2024 georefererad karta.tif", "A 23704-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 30862-2026 georefererad karta.tif", "A 30862-2026")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 23704-2024 FSC-klagomål.docx", "A 23704-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 30862-2026 FSC-klagomål.docx", "A 30862-2026")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 23704-2024 FSC-klagomål mail.docx", "A 23704-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 30862-2026 FSC-klagomål mail.docx", "A 30862-2026")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 23704-2024 tillsynsbegäran.docx", "A 23704-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 30862-2026 tillsynsbegäran.docx", "A 30862-2026")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 23704-2024 tillsynsbegäran mail.docx", "A 23704-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 30862-2026 tillsynsbegäran mail.docx", "A 30862-2026")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 30862-2026</t>
+          <t>A 23704-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3039,10 +3039,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46212</v>
+        <v>45454</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3055,7 +3055,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.7</v>
+        <v>4.9</v>
       </c>
       <c r="J24" t="n">
         <v>1</v>
@@ -3067,7 +3067,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
@@ -3079,51 +3079,51 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
       </c>
       <c r="T24" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Hedjohannesört</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 30862-2026 artfynd.xlsx", "A 30862-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 23704-2024 artfynd.xlsx", "A 23704-2024")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 30862-2026 karta.png", "A 30862-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 23704-2024 karta.png", "A 23704-2024")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 30862-2026 georefererad karta.tif", "A 30862-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 23704-2024 georefererad karta.tif", "A 23704-2024")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 30862-2026 FSC-klagomål.docx", "A 30862-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 23704-2024 FSC-klagomål.docx", "A 23704-2024")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 30862-2026 FSC-klagomål mail.docx", "A 30862-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 23704-2024 FSC-klagomål mail.docx", "A 23704-2024")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 30862-2026 tillsynsbegäran.docx", "A 30862-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 23704-2024 tillsynsbegäran.docx", "A 23704-2024")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 30862-2026 tillsynsbegäran mail.docx", "A 30862-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 23704-2024 tillsynsbegäran mail.docx", "A 23704-2024")</f>
         <v/>
       </c>
     </row>
@@ -3147,7 +3147,7 @@
         <v>44691</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
         <v>44691</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         <v>44836</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3366,7 +3366,7 @@
         <v>44760</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         <v>44760</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
         <v>44760</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3568,7 +3568,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 17455-2025</t>
+          <t>A 62221-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3582,10 +3582,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45757</v>
+        <v>45267</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3598,7 +3598,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2.1</v>
+        <v>1.3</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3641,7 +3641,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 62221-2023</t>
+          <t>A 4204-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3655,10 +3655,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45267</v>
+        <v>45324</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3671,7 +3671,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.3</v>
+        <v>4.4</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3714,7 +3714,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 43520-2022</t>
+          <t>A 30170-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3728,10 +3728,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44837</v>
+        <v>44757</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3744,7 +3744,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.5</v>
+        <v>3.1</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3787,7 +3787,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 21389-2023</t>
+          <t>A 13880-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3801,10 +3801,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45063</v>
+        <v>45391</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3817,7 +3817,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>3.4</v>
+        <v>2.4</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3860,7 +3860,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 4262-2024</t>
+          <t>A 1995-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3874,10 +3874,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45324</v>
+        <v>45308</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3890,7 +3890,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>14</v>
+        <v>0.5</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3933,7 +3933,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 21240-2023</t>
+          <t>A 45990-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3947,10 +3947,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45058</v>
+        <v>44846</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3963,7 +3963,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2.3</v>
+        <v>3.3</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4006,7 +4006,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 16538-2025</t>
+          <t>A 10679-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4020,10 +4020,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45751</v>
+        <v>45721</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.8</v>
+        <v>4.4</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4079,7 +4079,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 45990-2022</t>
+          <t>A 11237-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4093,10 +4093,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44846</v>
+        <v>45726</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4109,7 +4109,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4152,7 +4152,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 143-2023</t>
+          <t>A 17922-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4166,10 +4166,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44928</v>
+        <v>45758</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4182,7 +4182,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4225,7 +4225,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 18851-2024</t>
+          <t>A 10677-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4239,10 +4239,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45426</v>
+        <v>45721</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4255,7 +4255,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2.7</v>
+        <v>7.4</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4298,7 +4298,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 71835-2021</t>
+          <t>A 74285-2021</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4312,10 +4312,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44543</v>
+        <v>44558</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4328,7 +4328,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>7.5</v>
+        <v>1.1</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4371,7 +4371,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 63319-2021</t>
+          <t>A 34366-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4385,10 +4385,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44508</v>
+        <v>44792</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4401,7 +4401,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4444,7 +4444,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 29223-2024</t>
+          <t>A 4673-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4458,10 +4458,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45482</v>
+        <v>46048</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4474,7 +4474,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>5.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4517,7 +4517,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 10655-2022</t>
+          <t>A 40951-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4531,10 +4531,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44624</v>
+        <v>45897</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4547,7 +4547,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>13.3</v>
+        <v>0.8</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4590,7 +4590,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 49981-2023</t>
+          <t>A 43520-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4604,10 +4604,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45215</v>
+        <v>44837</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4620,7 +4620,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4663,7 +4663,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 56782-2022</t>
+          <t>A 6946-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4673,14 +4673,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44894</v>
+        <v>46057</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.5</v>
+        <v>2.2</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4736,7 +4736,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 1995-2024</t>
+          <t>A 29223-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4750,10 +4750,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45308</v>
+        <v>45482</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4766,7 +4766,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.5</v>
+        <v>5.6</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4809,7 +4809,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 30170-2022</t>
+          <t>A 45124-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4823,10 +4823,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44757</v>
+        <v>45919</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4882,7 +4882,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 10810-2023</t>
+          <t>A 47564-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4896,10 +4896,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44989</v>
+        <v>45931</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4912,7 +4912,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.4</v>
+        <v>2</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4955,7 +4955,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 51724-2023</t>
+          <t>A 37443-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4969,10 +4969,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45222</v>
+        <v>45877</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4984,8 +4984,13 @@
           <t>KUNGÄLV</t>
         </is>
       </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I50" t="n">
-        <v>3.1</v>
+        <v>0.7</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5028,7 +5033,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 10677-2025</t>
+          <t>A 8334-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5042,10 +5047,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45721</v>
+        <v>44975</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5058,7 +5063,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>7.4</v>
+        <v>1.8</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5101,7 +5106,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 10679-2025</t>
+          <t>A 61417-2022</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5115,10 +5120,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45721</v>
+        <v>44916</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5131,7 +5136,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>4.4</v>
+        <v>3.6</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5174,7 +5179,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 11237-2025</t>
+          <t>A 32272-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5188,10 +5193,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45726</v>
+        <v>45120</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5204,7 +5209,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5247,7 +5252,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 4204-2024</t>
+          <t>A 13990-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5261,10 +5266,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45324</v>
+        <v>46098</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5277,7 +5282,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>4.4</v>
+        <v>2.6</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5320,7 +5325,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 39714-2024</t>
+          <t>A 32847-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5334,10 +5339,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45552</v>
+        <v>45124</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5350,7 +5355,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.2</v>
+        <v>4.7</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5393,7 +5398,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 74285-2021</t>
+          <t>A 52932-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5407,10 +5412,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44558</v>
+        <v>45957</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5423,7 +5428,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.1</v>
+        <v>3.4</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5466,7 +5471,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 661-2025</t>
+          <t>A 4262-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5480,10 +5485,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45664</v>
+        <v>45324</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5496,7 +5501,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>3.1</v>
+        <v>14</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5539,7 +5544,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 24461-2023</t>
+          <t>A 49985-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5553,10 +5558,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45082</v>
+        <v>45215</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5569,7 +5574,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5612,7 +5617,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 13880-2024</t>
+          <t>A 661-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5626,10 +5631,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45391</v>
+        <v>45664</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5642,7 +5647,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5685,7 +5690,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 62128-2021</t>
+          <t>A 50071-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5699,10 +5704,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44502</v>
+        <v>45215</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5715,7 +5720,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.8</v>
+        <v>4</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5758,7 +5763,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 61417-2022</t>
+          <t>A 34244-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5772,10 +5777,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44916</v>
+        <v>45844</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5788,7 +5793,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>3.6</v>
+        <v>2.9</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5831,7 +5836,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 32272-2023</t>
+          <t>A 25624-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5845,10 +5850,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45120</v>
+        <v>45803</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5861,7 +5866,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5904,7 +5909,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 62979-2023</t>
+          <t>A 41442-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5914,14 +5919,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45271</v>
+        <v>45869</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5934,7 +5939,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.8</v>
+        <v>1.8</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5977,7 +5982,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 32847-2023</t>
+          <t>A 24461-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5991,10 +5996,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45124</v>
+        <v>45082</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6007,7 +6012,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>4.7</v>
+        <v>1.5</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6050,7 +6055,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 19531-2023</t>
+          <t>A 143-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6064,10 +6069,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45050</v>
+        <v>44928</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6080,7 +6085,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.9</v>
+        <v>0.5</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6123,7 +6128,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 5705-2025</t>
+          <t>A 63319-2021</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6133,14 +6138,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45694</v>
+        <v>44508</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6153,7 +6158,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6196,7 +6201,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 44176-2023</t>
+          <t>A 22731-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6210,10 +6215,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45188</v>
+        <v>46157</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6226,7 +6231,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>7.1</v>
+        <v>1.8</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6269,7 +6274,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 23457-2024</t>
+          <t>A 32391-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6283,10 +6288,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45453</v>
+        <v>45837</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6299,7 +6304,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>5.1</v>
+        <v>2.1</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6342,7 +6347,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 7505-2024</t>
+          <t>A 23607-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6356,10 +6361,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45347</v>
+        <v>46163</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6372,7 +6377,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.8</v>
+        <v>5.3</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6415,7 +6420,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 26812-2024</t>
+          <t>A 7505-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6429,10 +6434,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45470</v>
+        <v>45347</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6445,7 +6450,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6488,7 +6493,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 34244-2025</t>
+          <t>A 25135-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6502,10 +6507,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45844</v>
+        <v>45798</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6518,7 +6523,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>2.9</v>
+        <v>1.1</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6561,7 +6566,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 25624-2025</t>
+          <t>A 10655-2022</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6575,10 +6580,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45803</v>
+        <v>44624</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6591,7 +6596,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>5</v>
+        <v>13.3</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6634,7 +6639,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 29801-2022</t>
+          <t>A 17455-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6648,10 +6653,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44755</v>
+        <v>45757</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6664,7 +6669,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>4.8</v>
+        <v>2.1</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6707,7 +6712,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 18852-2024</t>
+          <t>A 19531-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6721,10 +6726,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45426</v>
+        <v>45050</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6737,7 +6742,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>2.7</v>
+        <v>1.9</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6780,7 +6785,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 41442-2025</t>
+          <t>A 5705-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6790,14 +6795,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45869</v>
+        <v>45694</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6810,7 +6815,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6853,7 +6858,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 8334-2023</t>
+          <t>A 29952-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6867,10 +6872,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44975</v>
+        <v>46205</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6883,7 +6888,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6926,7 +6931,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 17922-2025</t>
+          <t>A 62979-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6936,14 +6941,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45758</v>
+        <v>45271</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6999,7 +7004,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 40951-2025</t>
+          <t>A 30738-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7013,10 +7018,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45897</v>
+        <v>46211</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7029,7 +7034,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.8</v>
+        <v>3.5</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7072,7 +7077,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 52932-2025</t>
+          <t>A 30859-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7086,10 +7091,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45957</v>
+        <v>46212</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7102,7 +7107,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>3.4</v>
+        <v>0.5</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7145,7 +7150,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 45124-2025</t>
+          <t>A 16538-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7159,10 +7164,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45919</v>
+        <v>45751</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7175,7 +7180,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>3.7</v>
+        <v>0.8</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7218,7 +7223,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 47564-2025</t>
+          <t>A 29801-2022</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7232,10 +7237,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45931</v>
+        <v>44755</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7248,7 +7253,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>2</v>
+        <v>4.8</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7291,7 +7296,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 34366-2022</t>
+          <t>A 49981-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7305,10 +7310,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44792</v>
+        <v>45215</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7321,7 +7326,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7364,7 +7369,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 4673-2026</t>
+          <t>A 71835-2021</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7378,10 +7383,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46048</v>
+        <v>44543</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7394,7 +7399,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>8.199999999999999</v>
+        <v>7.5</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7437,7 +7442,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 6946-2026</t>
+          <t>A 38262-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7447,14 +7452,14 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46057</v>
+        <v>46281</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7467,7 +7472,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7510,7 +7515,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 37443-2025</t>
+          <t>A 56782-2022</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7524,10 +7529,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45877</v>
+        <v>44894</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7539,13 +7544,8 @@
           <t>KUNGÄLV</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I85" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7588,7 +7588,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 13990-2026</t>
+          <t>A 26812-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7602,10 +7602,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46098</v>
+        <v>45470</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7618,7 +7618,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>2.6</v>
+        <v>1.7</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7661,7 +7661,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 49985-2023</t>
+          <t>A 34386-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7675,10 +7675,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45215</v>
+        <v>46254</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7691,7 +7691,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>8.199999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7734,7 +7734,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 50071-2023</t>
+          <t>A 34396-2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7748,10 +7748,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45215</v>
+        <v>46254</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7764,7 +7764,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>4</v>
+        <v>0.8</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7807,7 +7807,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 22731-2026</t>
+          <t>A 10810-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7821,10 +7821,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46157</v>
+        <v>44989</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7837,7 +7837,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1.8</v>
+        <v>0.4</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7880,7 +7880,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 32391-2025</t>
+          <t>A 62128-2021</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7894,10 +7894,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45837</v>
+        <v>44502</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7910,7 +7910,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7953,7 +7953,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 23607-2026</t>
+          <t>A 34392-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7967,10 +7967,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46163</v>
+        <v>46254</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7983,7 +7983,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>5.3</v>
+        <v>0.4</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8026,7 +8026,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 25135-2025</t>
+          <t>A 34387-2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45798</v>
+        <v>46254</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8056,7 +8056,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1.1</v>
+        <v>0.3</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 29952-2026</t>
+          <t>A 21240-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8113,10 +8113,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>46205</v>
+        <v>45058</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8129,7 +8129,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8172,7 +8172,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 34392-2026</t>
+          <t>A 18851-2024</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8186,10 +8186,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>46254</v>
+        <v>45426</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8202,7 +8202,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>0.4</v>
+        <v>2.7</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8245,7 +8245,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 34387-2026</t>
+          <t>A 21389-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8259,10 +8259,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>46254</v>
+        <v>45063</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8275,7 +8275,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.3</v>
+        <v>3.4</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8318,7 +8318,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 34386-2026</t>
+          <t>A 44176-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8332,10 +8332,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>46254</v>
+        <v>45188</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8348,7 +8348,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>0.7</v>
+        <v>7.1</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8391,7 +8391,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 34396-2026</t>
+          <t>A 23457-2024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8405,10 +8405,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>46254</v>
+        <v>45453</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8421,7 +8421,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>0.8</v>
+        <v>5.1</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8464,7 +8464,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 30738-2026</t>
+          <t>A 39714-2024</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8478,10 +8478,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>46211</v>
+        <v>45552</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8494,7 +8494,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>3.5</v>
+        <v>1.2</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8537,7 +8537,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 30859-2026</t>
+          <t>A 18852-2024</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8551,10 +8551,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>46212</v>
+        <v>45426</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8567,7 +8567,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>0.5</v>
+        <v>2.7</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8610,7 +8610,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 38262-2026</t>
+          <t>A 51724-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8624,10 +8624,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>46281</v>
+        <v>45222</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8640,7 +8640,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8700,7 +8700,7 @@
         <v>45371</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>

--- a/Översikt KUNGÄLV.xlsx
+++ b/Översikt KUNGÄLV.xlsx
@@ -601,7 +601,7 @@
         <v>45548</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>45868</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -851,7 +851,7 @@
         <v>45526</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -965,7 +965,7 @@
         <v>45919</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
         <v>45695</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         <v>45993</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         <v>45324</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>45985</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>46199</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>45355</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>46212</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         <v>45957</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 56394-2025</t>
+          <t>A 57116-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1963,14 +1963,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45974</v>
+        <v>45979</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1983,7 +1983,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.3</v>
+        <v>3.5</v>
       </c>
       <c r="J14" t="n">
         <v>1</v>
@@ -2016,343 +2016,343 @@
         <v>2</v>
       </c>
       <c r="T14" t="n">
+        <v>3</v>
+      </c>
+      <c r="U14" t="n">
+        <v>3</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Västlig hakmossa
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 57116-2025 artfynd.xlsx", "A 57116-2025")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 57116-2025 karta.png", "A 57116-2025")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 57116-2025 georefererad karta.tif", "A 57116-2025")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 57116-2025 FSC-klagomål.docx", "A 57116-2025")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 57116-2025 FSC-klagomål mail.docx", "A 57116-2025")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 57116-2025 tillsynsbegäran.docx", "A 57116-2025")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 57116-2025 tillsynsbegäran mail.docx", "A 57116-2025")</f>
+        <v/>
+      </c>
+      <c r="AE14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 57116-2025 prioriterade fågelarter.docx", "A 57116-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 56394-2025</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>45974</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>KUNGÄLV</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
         <v>2</v>
       </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
         <is>
           <t>Kambräken
 Revlummer</t>
         </is>
       </c>
-      <c r="W14">
+      <c r="W15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 56394-2025 artfynd.xlsx", "A 56394-2025")</f>
         <v/>
       </c>
-      <c r="X14">
+      <c r="X15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 56394-2025 karta.png", "A 56394-2025")</f>
         <v/>
       </c>
-      <c r="Y14">
+      <c r="Y15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 56394-2025 georefererad karta.tif", "A 56394-2025")</f>
         <v/>
       </c>
-      <c r="AA14">
+      <c r="AA15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 56394-2025 FSC-klagomål.docx", "A 56394-2025")</f>
         <v/>
       </c>
-      <c r="AB14">
+      <c r="AB15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 56394-2025 FSC-klagomål mail.docx", "A 56394-2025")</f>
         <v/>
       </c>
-      <c r="AC14">
+      <c r="AC15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 56394-2025 tillsynsbegäran.docx", "A 56394-2025")</f>
         <v/>
       </c>
-      <c r="AD14">
+      <c r="AD15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 56394-2025 tillsynsbegäran mail.docx", "A 56394-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 57116-2025</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>45979</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46297</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>KUNGÄLV</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="J15" t="n">
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 30860-2026</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>46212</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>KUNGÄLV</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J16" t="n">
         <v>1</v>
       </c>
-      <c r="K15" t="n">
+      <c r="K16" t="n">
         <v>1</v>
       </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
+      <c r="L16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
         <v>2</v>
       </c>
-      <c r="T15" t="n">
-        <v>3</v>
-      </c>
-      <c r="U15" t="n">
-        <v>3</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Grönsångare
+Västlig hakmossa</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 30860-2026 artfynd.xlsx", "A 30860-2026")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 30860-2026 karta.png", "A 30860-2026")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 30860-2026 georefererad karta.tif", "A 30860-2026")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 30860-2026 FSC-klagomål.docx", "A 30860-2026")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 30860-2026 FSC-klagomål mail.docx", "A 30860-2026")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 30860-2026 tillsynsbegäran.docx", "A 30860-2026")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 30860-2026 tillsynsbegäran mail.docx", "A 30860-2026")</f>
+        <v/>
+      </c>
+      <c r="AE16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 30860-2026 prioriterade fågelarter.docx", "A 30860-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 53007-2025</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>45957</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>KUNGÄLV</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2</v>
+      </c>
+      <c r="T17" t="n">
+        <v>5</v>
+      </c>
+      <c r="U17" t="n">
+        <v>5</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>Västlig hakmossa
 Spillkråka</t>
         </is>
       </c>
-      <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 57116-2025 artfynd.xlsx", "A 57116-2025")</f>
-        <v/>
-      </c>
-      <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 57116-2025 karta.png", "A 57116-2025")</f>
-        <v/>
-      </c>
-      <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 57116-2025 georefererad karta.tif", "A 57116-2025")</f>
-        <v/>
-      </c>
-      <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 57116-2025 FSC-klagomål.docx", "A 57116-2025")</f>
-        <v/>
-      </c>
-      <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 57116-2025 FSC-klagomål mail.docx", "A 57116-2025")</f>
-        <v/>
-      </c>
-      <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 57116-2025 tillsynsbegäran.docx", "A 57116-2025")</f>
-        <v/>
-      </c>
-      <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 57116-2025 tillsynsbegäran mail.docx", "A 57116-2025")</f>
-        <v/>
-      </c>
-      <c r="AE15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 57116-2025 prioriterade fågelarter.docx", "A 57116-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 30860-2026</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>46212</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46297</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>KUNGÄLV</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="J16" t="n">
-        <v>1</v>
-      </c>
-      <c r="K16" t="n">
-        <v>1</v>
-      </c>
-      <c r="L16" t="n">
-        <v>1</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>Grönsångare
-Västlig hakmossa</t>
-        </is>
-      </c>
-      <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 30860-2026 artfynd.xlsx", "A 30860-2026")</f>
-        <v/>
-      </c>
-      <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 30860-2026 karta.png", "A 30860-2026")</f>
-        <v/>
-      </c>
-      <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 30860-2026 georefererad karta.tif", "A 30860-2026")</f>
-        <v/>
-      </c>
-      <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 30860-2026 FSC-klagomål.docx", "A 30860-2026")</f>
-        <v/>
-      </c>
-      <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 30860-2026 FSC-klagomål mail.docx", "A 30860-2026")</f>
-        <v/>
-      </c>
-      <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 30860-2026 tillsynsbegäran.docx", "A 30860-2026")</f>
-        <v/>
-      </c>
-      <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 30860-2026 tillsynsbegäran mail.docx", "A 30860-2026")</f>
-        <v/>
-      </c>
-      <c r="AE16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 30860-2026 prioriterade fågelarter.docx", "A 30860-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 53007-2025</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>45957</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46297</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>KUNGÄLV</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="J17" t="n">
-        <v>1</v>
-      </c>
-      <c r="K17" t="n">
-        <v>1</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2</v>
-      </c>
-      <c r="T17" t="n">
-        <v>5</v>
-      </c>
-      <c r="U17" t="n">
-        <v>5</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Västlig hakmossa
-Spillkråka</t>
-        </is>
-      </c>
       <c r="W17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 53007-2025 artfynd.xlsx", "A 53007-2025")</f>
         <v/>
@@ -2406,7 +2406,7 @@
         <v>45334</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2512,7 +2512,7 @@
         <v>45334</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
         <v>44838</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2706,7 +2706,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 49988-2023</t>
+          <t>A 6082-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2720,10 +2720,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45215</v>
+        <v>45697</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="J21" t="n">
         <v>1</v>
@@ -2772,46 +2772,50 @@
         <v>1</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 49988-2023 artfynd.xlsx", "A 49988-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 6082-2025 artfynd.xlsx", "A 6082-2025")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 49988-2023 karta.png", "A 49988-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 6082-2025 karta.png", "A 6082-2025")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 49988-2023 georefererad karta.tif", "A 49988-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 6082-2025 georefererad karta.tif", "A 6082-2025")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 49988-2023 FSC-klagomål.docx", "A 49988-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 6082-2025 FSC-klagomål.docx", "A 6082-2025")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 49988-2023 FSC-klagomål mail.docx", "A 49988-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 6082-2025 FSC-klagomål mail.docx", "A 6082-2025")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 49988-2023 tillsynsbegäran.docx", "A 49988-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 6082-2025 tillsynsbegäran.docx", "A 6082-2025")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 49988-2023 tillsynsbegäran mail.docx", "A 49988-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 6082-2025 tillsynsbegäran mail.docx", "A 6082-2025")</f>
+        <v/>
+      </c>
+      <c r="AE21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 6082-2025 prioriterade fågelarter.docx", "A 6082-2025")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 6082-2025</t>
+          <t>A 23704-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2825,10 +2829,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45697</v>
+        <v>45454</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2841,7 +2845,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>2.8</v>
+        <v>4.9</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
@@ -2853,7 +2857,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
@@ -2865,62 +2869,58 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
       </c>
       <c r="T22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U22" t="n">
         <v>1</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Hedjohannesört</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 6082-2025 artfynd.xlsx", "A 6082-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 23704-2024 artfynd.xlsx", "A 23704-2024")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 6082-2025 karta.png", "A 6082-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 23704-2024 karta.png", "A 23704-2024")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 6082-2025 georefererad karta.tif", "A 6082-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 23704-2024 georefererad karta.tif", "A 23704-2024")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 6082-2025 FSC-klagomål.docx", "A 6082-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 23704-2024 FSC-klagomål.docx", "A 23704-2024")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 6082-2025 FSC-klagomål mail.docx", "A 6082-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 23704-2024 FSC-klagomål mail.docx", "A 23704-2024")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 6082-2025 tillsynsbegäran.docx", "A 6082-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 23704-2024 tillsynsbegäran.docx", "A 23704-2024")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 6082-2025 tillsynsbegäran mail.docx", "A 6082-2025")</f>
-        <v/>
-      </c>
-      <c r="AE22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 6082-2025 prioriterade fågelarter.docx", "A 6082-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 23704-2024 tillsynsbegäran mail.docx", "A 23704-2024")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 30862-2026</t>
+          <t>A 49988-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2934,10 +2934,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46212</v>
+        <v>45215</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2950,7 +2950,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="J23" t="n">
         <v>1</v>
@@ -2983,49 +2983,49 @@
         <v>1</v>
       </c>
       <c r="T23" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U23" t="n">
         <v>0</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 30862-2026 artfynd.xlsx", "A 30862-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 49988-2023 artfynd.xlsx", "A 49988-2023")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 30862-2026 karta.png", "A 30862-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 49988-2023 karta.png", "A 49988-2023")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 30862-2026 georefererad karta.tif", "A 30862-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 49988-2023 georefererad karta.tif", "A 49988-2023")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 30862-2026 FSC-klagomål.docx", "A 30862-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 49988-2023 FSC-klagomål.docx", "A 49988-2023")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 30862-2026 FSC-klagomål mail.docx", "A 30862-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 49988-2023 FSC-klagomål mail.docx", "A 49988-2023")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 30862-2026 tillsynsbegäran.docx", "A 30862-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 49988-2023 tillsynsbegäran.docx", "A 49988-2023")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 30862-2026 tillsynsbegäran mail.docx", "A 30862-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 49988-2023 tillsynsbegäran mail.docx", "A 49988-2023")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 23704-2024</t>
+          <t>A 30862-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3039,10 +3039,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45454</v>
+        <v>46212</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3055,7 +3055,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>4.9</v>
+        <v>1.7</v>
       </c>
       <c r="J24" t="n">
         <v>1</v>
@@ -3067,7 +3067,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
@@ -3079,51 +3079,51 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
       </c>
       <c r="T24" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="U24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Hedjohannesört</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 23704-2024 artfynd.xlsx", "A 23704-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 30862-2026 artfynd.xlsx", "A 30862-2026")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 23704-2024 karta.png", "A 23704-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 30862-2026 karta.png", "A 30862-2026")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 23704-2024 georefererad karta.tif", "A 23704-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 30862-2026 georefererad karta.tif", "A 30862-2026")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 23704-2024 FSC-klagomål.docx", "A 23704-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 30862-2026 FSC-klagomål.docx", "A 30862-2026")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 23704-2024 FSC-klagomål mail.docx", "A 23704-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 30862-2026 FSC-klagomål mail.docx", "A 30862-2026")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 23704-2024 tillsynsbegäran.docx", "A 23704-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 30862-2026 tillsynsbegäran.docx", "A 30862-2026")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 23704-2024 tillsynsbegäran mail.docx", "A 23704-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 30862-2026 tillsynsbegäran mail.docx", "A 30862-2026")</f>
         <v/>
       </c>
     </row>
@@ -3147,7 +3147,7 @@
         <v>44691</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
         <v>44691</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         <v>44836</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3366,7 +3366,7 @@
         <v>44760</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         <v>44760</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
         <v>44760</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3568,7 +3568,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 62221-2023</t>
+          <t>A 17455-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3582,10 +3582,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45267</v>
+        <v>45757</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3598,7 +3598,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.3</v>
+        <v>2.1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3641,7 +3641,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 4204-2024</t>
+          <t>A 62221-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3655,10 +3655,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45324</v>
+        <v>45267</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3671,7 +3671,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>4.4</v>
+        <v>1.3</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3714,7 +3714,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 30170-2022</t>
+          <t>A 21240-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3728,10 +3728,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44757</v>
+        <v>45058</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3744,7 +3744,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>3.1</v>
+        <v>2.3</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3787,7 +3787,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 13880-2024</t>
+          <t>A 29223-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3801,10 +3801,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45391</v>
+        <v>45482</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3817,7 +3817,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2.4</v>
+        <v>5.6</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3860,7 +3860,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 1995-2024</t>
+          <t>A 10655-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3874,10 +3874,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45308</v>
+        <v>44624</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3890,7 +3890,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.5</v>
+        <v>13.3</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3933,7 +3933,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 45990-2022</t>
+          <t>A 39714-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3947,10 +3947,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44846</v>
+        <v>45552</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3963,7 +3963,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>3.3</v>
+        <v>1.2</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4006,7 +4006,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 10679-2025</t>
+          <t>A 10677-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4023,7 +4023,7 @@
         <v>45721</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>4.4</v>
+        <v>7.4</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4079,7 +4079,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 11237-2025</t>
+          <t>A 10679-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4093,10 +4093,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45726</v>
+        <v>45721</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4109,7 +4109,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4152,7 +4152,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 17922-2025</t>
+          <t>A 11237-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4166,10 +4166,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45758</v>
+        <v>45726</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4182,7 +4182,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.8</v>
+        <v>4.2</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4225,7 +4225,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 10677-2025</t>
+          <t>A 40951-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4239,10 +4239,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45721</v>
+        <v>45897</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4255,7 +4255,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>7.4</v>
+        <v>0.8</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4298,7 +4298,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 74285-2021</t>
+          <t>A 34366-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4312,10 +4312,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44558</v>
+        <v>44792</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4328,7 +4328,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4371,7 +4371,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 34366-2022</t>
+          <t>A 74285-2021</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4385,10 +4385,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44792</v>
+        <v>44558</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4401,7 +4401,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4461,7 +4461,7 @@
         <v>46048</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4517,7 +4517,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 40951-2025</t>
+          <t>A 45124-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4531,10 +4531,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45897</v>
+        <v>45919</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4547,7 +4547,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.8</v>
+        <v>3.7</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4590,7 +4590,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 43520-2022</t>
+          <t>A 19531-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4604,10 +4604,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44837</v>
+        <v>45050</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4620,7 +4620,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4663,7 +4663,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 6946-2026</t>
+          <t>A 61417-2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4673,14 +4673,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46057</v>
+        <v>44916</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2.2</v>
+        <v>3.6</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4736,7 +4736,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 29223-2024</t>
+          <t>A 5705-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4746,14 +4746,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45482</v>
+        <v>45694</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4766,7 +4766,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>5.6</v>
+        <v>1.2</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4809,7 +4809,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 45124-2025</t>
+          <t>A 6946-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4819,14 +4819,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45919</v>
+        <v>46057</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>3.7</v>
+        <v>2.2</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4899,7 +4899,7 @@
         <v>45931</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4955,7 +4955,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 37443-2025</t>
+          <t>A 7505-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4969,10 +4969,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45877</v>
+        <v>45347</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4984,13 +4984,8 @@
           <t>KUNGÄLV</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I50" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5050,7 +5045,7 @@
         <v>44975</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5106,7 +5101,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 61417-2022</t>
+          <t>A 32272-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5120,10 +5115,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44916</v>
+        <v>45120</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5136,7 +5131,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>3.6</v>
+        <v>4.9</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5179,7 +5174,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 32272-2023</t>
+          <t>A 52932-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5193,10 +5188,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45120</v>
+        <v>45957</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5209,7 +5204,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>4.9</v>
+        <v>3.4</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5252,7 +5247,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 13990-2026</t>
+          <t>A 32847-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5266,10 +5261,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46098</v>
+        <v>45124</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5282,7 +5277,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>2.6</v>
+        <v>4.7</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5325,7 +5320,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 32847-2023</t>
+          <t>A 37443-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5339,10 +5334,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45124</v>
+        <v>45877</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5354,8 +5349,13 @@
           <t>KUNGÄLV</t>
         </is>
       </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I55" t="n">
-        <v>4.7</v>
+        <v>0.7</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5398,7 +5398,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 52932-2025</t>
+          <t>A 13990-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5412,10 +5412,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45957</v>
+        <v>46098</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5428,7 +5428,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>3.4</v>
+        <v>2.6</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5471,7 +5471,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 4262-2024</t>
+          <t>A 49985-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5485,10 +5485,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45324</v>
+        <v>45215</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>14</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5544,7 +5544,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 49985-2023</t>
+          <t>A 49981-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5561,7 +5561,7 @@
         <v>45215</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5574,7 +5574,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>8.199999999999999</v>
+        <v>2.5</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5617,7 +5617,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 661-2025</t>
+          <t>A 56782-2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5631,10 +5631,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45664</v>
+        <v>44894</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5647,7 +5647,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>3.1</v>
+        <v>0.5</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5707,7 +5707,7 @@
         <v>45215</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5763,7 +5763,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 34244-2025</t>
+          <t>A 1995-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5777,10 +5777,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45844</v>
+        <v>45308</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5793,7 +5793,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>2.9</v>
+        <v>0.5</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5836,7 +5836,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 25624-2025</t>
+          <t>A 34244-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5850,10 +5850,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45803</v>
+        <v>45844</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5866,7 +5866,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>5</v>
+        <v>2.9</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5909,7 +5909,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 41442-2025</t>
+          <t>A 30170-2022</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5923,10 +5923,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45869</v>
+        <v>44757</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5939,7 +5939,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.8</v>
+        <v>3.1</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5982,7 +5982,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 24461-2023</t>
+          <t>A 10810-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5996,10 +5996,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45082</v>
+        <v>44989</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6012,7 +6012,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.5</v>
+        <v>0.4</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6055,7 +6055,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 143-2023</t>
+          <t>A 4204-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6069,10 +6069,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44928</v>
+        <v>45324</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6085,7 +6085,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.5</v>
+        <v>4.4</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6128,7 +6128,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 63319-2021</t>
+          <t>A 25624-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6142,10 +6142,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44508</v>
+        <v>45803</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6158,7 +6158,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.6</v>
+        <v>5</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6201,7 +6201,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 22731-2026</t>
+          <t>A 41442-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6215,10 +6215,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46157</v>
+        <v>45869</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6274,7 +6274,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 32391-2025</t>
+          <t>A 62128-2021</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6288,10 +6288,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45837</v>
+        <v>44502</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6304,7 +6304,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6347,7 +6347,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 23607-2026</t>
+          <t>A 62979-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6357,14 +6357,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46163</v>
+        <v>45271</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6377,7 +6377,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>5.3</v>
+        <v>0.8</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6420,7 +6420,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 7505-2024</t>
+          <t>A 22731-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6434,10 +6434,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45347</v>
+        <v>46157</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6493,7 +6493,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 25135-2025</t>
+          <t>A 32391-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6507,10 +6507,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45798</v>
+        <v>45837</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6523,7 +6523,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.1</v>
+        <v>2.1</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6566,7 +6566,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 10655-2022</t>
+          <t>A 44176-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6580,10 +6580,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44624</v>
+        <v>45188</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6596,7 +6596,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>13.3</v>
+        <v>7.1</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6639,7 +6639,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 17455-2025</t>
+          <t>A 23607-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6653,10 +6653,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45757</v>
+        <v>46163</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6669,7 +6669,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>2.1</v>
+        <v>5.3</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6712,7 +6712,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 19531-2023</t>
+          <t>A 25135-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6726,10 +6726,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45050</v>
+        <v>45798</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6742,7 +6742,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6785,7 +6785,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 5705-2025</t>
+          <t>A 26812-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6795,14 +6795,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45694</v>
+        <v>45470</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6815,7 +6815,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6858,7 +6858,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 29952-2026</t>
+          <t>A 29801-2022</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6872,10 +6872,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46205</v>
+        <v>44755</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6888,7 +6888,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>2</v>
+        <v>4.8</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6931,7 +6931,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 62979-2023</t>
+          <t>A 18852-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6941,14 +6941,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45271</v>
+        <v>45426</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6961,7 +6961,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.8</v>
+        <v>2.7</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7004,7 +7004,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 30738-2026</t>
+          <t>A 17922-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7018,10 +7018,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46211</v>
+        <v>45758</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7034,7 +7034,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>3.5</v>
+        <v>0.8</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7077,7 +7077,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 30859-2026</t>
+          <t>A 43520-2022</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7091,10 +7091,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46212</v>
+        <v>44837</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7107,7 +7107,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7167,7 +7167,7 @@
         <v>45751</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7223,7 +7223,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 29801-2022</t>
+          <t>A 45990-2022</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7237,10 +7237,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44755</v>
+        <v>44846</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7253,7 +7253,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>4.8</v>
+        <v>3.3</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7296,7 +7296,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 49981-2023</t>
+          <t>A 143-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7310,10 +7310,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45215</v>
+        <v>44928</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7326,7 +7326,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7369,7 +7369,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 71835-2021</t>
+          <t>A 29952-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7383,10 +7383,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>44543</v>
+        <v>46205</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>7.5</v>
+        <v>2</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7442,7 +7442,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 38262-2026</t>
+          <t>A 18851-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7456,10 +7456,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46281</v>
+        <v>45426</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7472,7 +7472,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7515,7 +7515,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 56782-2022</t>
+          <t>A 30738-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7529,10 +7529,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>44894</v>
+        <v>46211</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7545,7 +7545,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>0.5</v>
+        <v>3.5</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7588,7 +7588,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 26812-2024</t>
+          <t>A 30859-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7602,10 +7602,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45470</v>
+        <v>46212</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7618,7 +7618,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7661,7 +7661,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 34386-2026</t>
+          <t>A 71835-2021</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7675,10 +7675,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46254</v>
+        <v>44543</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7691,7 +7691,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.7</v>
+        <v>7.5</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7734,7 +7734,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 34396-2026</t>
+          <t>A 51724-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7748,10 +7748,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>46254</v>
+        <v>45222</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7764,7 +7764,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0.8</v>
+        <v>3.1</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7807,7 +7807,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 10810-2023</t>
+          <t>A 38262-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7821,10 +7821,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>44989</v>
+        <v>46281</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7837,7 +7837,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>0.4</v>
+        <v>2.8</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7880,7 +7880,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 62128-2021</t>
+          <t>A 661-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7894,10 +7894,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>44502</v>
+        <v>45664</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7910,7 +7910,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.8</v>
+        <v>3.1</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7953,7 +7953,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 34392-2026</t>
+          <t>A 24461-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7967,10 +7967,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46254</v>
+        <v>45082</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7983,7 +7983,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.4</v>
+        <v>1.5</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8026,7 +8026,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 34387-2026</t>
+          <t>A 13880-2024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>46254</v>
+        <v>45391</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8056,7 +8056,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0.3</v>
+        <v>2.4</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 21240-2023</t>
+          <t>A 23457-2024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8113,10 +8113,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45058</v>
+        <v>45453</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8129,7 +8129,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>2.3</v>
+        <v>5.1</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8172,7 +8172,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 18851-2024</t>
+          <t>A 34386-2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8186,10 +8186,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45426</v>
+        <v>46254</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8202,7 +8202,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>2.7</v>
+        <v>0.7</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8245,7 +8245,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 21389-2023</t>
+          <t>A 34396-2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8259,10 +8259,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45063</v>
+        <v>46254</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8275,7 +8275,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>3.4</v>
+        <v>0.8</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8318,7 +8318,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 44176-2023</t>
+          <t>A 34392-2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8332,10 +8332,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45188</v>
+        <v>46254</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8348,7 +8348,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>7.1</v>
+        <v>0.4</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8391,7 +8391,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 23457-2024</t>
+          <t>A 34387-2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8405,10 +8405,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45453</v>
+        <v>46254</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8421,7 +8421,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>5.1</v>
+        <v>0.3</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8464,7 +8464,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 39714-2024</t>
+          <t>A 21389-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8478,10 +8478,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45552</v>
+        <v>45063</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8494,7 +8494,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1.2</v>
+        <v>3.4</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8537,7 +8537,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 18852-2024</t>
+          <t>A 4262-2024</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8551,10 +8551,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45426</v>
+        <v>45324</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8567,7 +8567,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>2.7</v>
+        <v>14</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8610,7 +8610,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 51724-2023</t>
+          <t>A 63319-2021</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8624,10 +8624,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45222</v>
+        <v>44508</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8640,7 +8640,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>3.1</v>
+        <v>1.6</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8700,7 +8700,7 @@
         <v>45371</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>

--- a/Översikt KUNGÄLV.xlsx
+++ b/Översikt KUNGÄLV.xlsx
@@ -601,7 +601,7 @@
         <v>45548</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>45868</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -851,7 +851,7 @@
         <v>45526</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -965,7 +965,7 @@
         <v>45919</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
         <v>45695</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         <v>45993</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         <v>45324</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>45985</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>46199</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>45355</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>46212</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         <v>45957</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1970,7 +1970,7 @@
         <v>45979</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2080,7 +2080,7 @@
         <v>45974</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
         <v>46212</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
         <v>45957</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2406,7 +2406,7 @@
         <v>45334</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2512,7 +2512,7 @@
         <v>45334</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
         <v>44838</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2723,7 +2723,7 @@
         <v>45697</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
         <v>45454</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2937,7 +2937,7 @@
         <v>45215</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3042,7 +3042,7 @@
         <v>46212</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>44691</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
         <v>44691</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         <v>44836</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3366,7 +3366,7 @@
         <v>44760</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         <v>44760</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
         <v>44760</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3585,7 +3585,7 @@
         <v>45757</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3658,7 +3658,7 @@
         <v>45267</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3731,7 +3731,7 @@
         <v>45058</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3804,7 +3804,7 @@
         <v>45482</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3877,7 +3877,7 @@
         <v>44624</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3950,7 +3950,7 @@
         <v>45552</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4023,7 +4023,7 @@
         <v>45721</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4096,7 +4096,7 @@
         <v>45721</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
         <v>45726</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4242,7 +4242,7 @@
         <v>45897</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4315,7 +4315,7 @@
         <v>44792</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4388,7 +4388,7 @@
         <v>44558</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4461,7 +4461,7 @@
         <v>46048</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4534,7 +4534,7 @@
         <v>45919</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4607,7 +4607,7 @@
         <v>45050</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4680,7 +4680,7 @@
         <v>44916</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4753,7 +4753,7 @@
         <v>45694</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4826,7 +4826,7 @@
         <v>46057</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4899,7 +4899,7 @@
         <v>45931</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4972,7 +4972,7 @@
         <v>45347</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5045,7 +5045,7 @@
         <v>44975</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5118,7 +5118,7 @@
         <v>45120</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5191,7 +5191,7 @@
         <v>45957</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5264,7 +5264,7 @@
         <v>45124</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5337,7 +5337,7 @@
         <v>45877</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5415,7 +5415,7 @@
         <v>46098</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5488,7 +5488,7 @@
         <v>45215</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5561,7 +5561,7 @@
         <v>45215</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5634,7 +5634,7 @@
         <v>44894</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5707,7 +5707,7 @@
         <v>45215</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5780,7 +5780,7 @@
         <v>45308</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5853,7 +5853,7 @@
         <v>45844</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5926,7 +5926,7 @@
         <v>44757</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         <v>44989</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6072,7 +6072,7 @@
         <v>45324</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6145,7 +6145,7 @@
         <v>45803</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6218,7 +6218,7 @@
         <v>45869</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6291,7 +6291,7 @@
         <v>44502</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6364,7 +6364,7 @@
         <v>45271</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6437,7 +6437,7 @@
         <v>46157</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6510,7 +6510,7 @@
         <v>45837</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6583,7 +6583,7 @@
         <v>45188</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6656,7 +6656,7 @@
         <v>46163</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6729,7 +6729,7 @@
         <v>45798</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6802,7 +6802,7 @@
         <v>45470</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6875,7 +6875,7 @@
         <v>44755</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6948,7 +6948,7 @@
         <v>45426</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7021,7 +7021,7 @@
         <v>45758</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7094,7 +7094,7 @@
         <v>44837</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7167,7 +7167,7 @@
         <v>45751</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7240,7 +7240,7 @@
         <v>44846</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7313,7 +7313,7 @@
         <v>44928</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7386,7 +7386,7 @@
         <v>46205</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7459,7 +7459,7 @@
         <v>45426</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7532,7 +7532,7 @@
         <v>46211</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7605,7 +7605,7 @@
         <v>46212</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7678,7 +7678,7 @@
         <v>44543</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7751,7 +7751,7 @@
         <v>45222</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7824,7 +7824,7 @@
         <v>46281</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7897,7 +7897,7 @@
         <v>45664</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7970,7 +7970,7 @@
         <v>45082</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         <v>45391</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8116,7 +8116,7 @@
         <v>45453</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8189,7 +8189,7 @@
         <v>46254</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8262,7 +8262,7 @@
         <v>46254</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8335,7 +8335,7 @@
         <v>46254</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8408,7 +8408,7 @@
         <v>46254</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8481,7 +8481,7 @@
         <v>45063</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8554,7 +8554,7 @@
         <v>45324</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8627,7 +8627,7 @@
         <v>44508</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8700,7 +8700,7 @@
         <v>45371</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>

--- a/Översikt KUNGÄLV.xlsx
+++ b/Översikt KUNGÄLV.xlsx
@@ -601,7 +601,7 @@
         <v>45548</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>45868</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -851,7 +851,7 @@
         <v>45526</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -965,7 +965,7 @@
         <v>45919</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
         <v>45695</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         <v>45993</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         <v>45324</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>45985</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>46199</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>45355</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>46212</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         <v>45957</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1970,7 +1970,7 @@
         <v>45979</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2080,7 +2080,7 @@
         <v>45974</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
         <v>46212</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
         <v>45957</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2406,7 +2406,7 @@
         <v>45334</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2512,7 +2512,7 @@
         <v>45334</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
         <v>44838</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2723,7 +2723,7 @@
         <v>45697</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
         <v>45454</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2937,7 +2937,7 @@
         <v>45215</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3042,7 +3042,7 @@
         <v>46212</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>44691</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
         <v>44691</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         <v>44836</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3366,7 +3366,7 @@
         <v>44760</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         <v>44760</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
         <v>44760</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3585,7 +3585,7 @@
         <v>45757</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3658,7 +3658,7 @@
         <v>45267</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3731,7 +3731,7 @@
         <v>45058</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3804,7 +3804,7 @@
         <v>45482</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3877,7 +3877,7 @@
         <v>44624</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3950,7 +3950,7 @@
         <v>45552</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4023,7 +4023,7 @@
         <v>45721</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4096,7 +4096,7 @@
         <v>45721</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
         <v>45726</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4242,7 +4242,7 @@
         <v>45897</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4315,7 +4315,7 @@
         <v>44792</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4388,7 +4388,7 @@
         <v>44558</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4461,7 +4461,7 @@
         <v>46048</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4534,7 +4534,7 @@
         <v>45919</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4607,7 +4607,7 @@
         <v>45050</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4680,7 +4680,7 @@
         <v>44916</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4753,7 +4753,7 @@
         <v>45694</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4826,7 +4826,7 @@
         <v>46057</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4899,7 +4899,7 @@
         <v>45931</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4972,7 +4972,7 @@
         <v>45347</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5045,7 +5045,7 @@
         <v>44975</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5118,7 +5118,7 @@
         <v>45120</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5191,7 +5191,7 @@
         <v>45957</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5264,7 +5264,7 @@
         <v>45124</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5337,7 +5337,7 @@
         <v>45877</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5415,7 +5415,7 @@
         <v>46098</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5488,7 +5488,7 @@
         <v>45215</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5561,7 +5561,7 @@
         <v>45215</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5634,7 +5634,7 @@
         <v>44894</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5707,7 +5707,7 @@
         <v>45215</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5780,7 +5780,7 @@
         <v>45308</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5853,7 +5853,7 @@
         <v>45844</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5926,7 +5926,7 @@
         <v>44757</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         <v>44989</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6072,7 +6072,7 @@
         <v>45324</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6145,7 +6145,7 @@
         <v>45803</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6218,7 +6218,7 @@
         <v>45869</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6291,7 +6291,7 @@
         <v>44502</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6364,7 +6364,7 @@
         <v>45271</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6437,7 +6437,7 @@
         <v>46157</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6510,7 +6510,7 @@
         <v>45837</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6583,7 +6583,7 @@
         <v>45188</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6656,7 +6656,7 @@
         <v>46163</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6729,7 +6729,7 @@
         <v>45798</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6802,7 +6802,7 @@
         <v>45470</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6875,7 +6875,7 @@
         <v>44755</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6948,7 +6948,7 @@
         <v>45426</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7021,7 +7021,7 @@
         <v>45758</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7094,7 +7094,7 @@
         <v>44837</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7167,7 +7167,7 @@
         <v>45751</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7240,7 +7240,7 @@
         <v>44846</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7313,7 +7313,7 @@
         <v>44928</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7386,7 +7386,7 @@
         <v>46205</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7459,7 +7459,7 @@
         <v>45426</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7532,7 +7532,7 @@
         <v>46211</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7605,7 +7605,7 @@
         <v>46212</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7678,7 +7678,7 @@
         <v>44543</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7751,7 +7751,7 @@
         <v>45222</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7824,7 +7824,7 @@
         <v>46281</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7897,7 +7897,7 @@
         <v>45664</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7970,7 +7970,7 @@
         <v>45082</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         <v>45391</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8116,7 +8116,7 @@
         <v>45453</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8189,7 +8189,7 @@
         <v>46254</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8262,7 +8262,7 @@
         <v>46254</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8335,7 +8335,7 @@
         <v>46254</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8408,7 +8408,7 @@
         <v>46254</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8481,7 +8481,7 @@
         <v>45063</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8554,7 +8554,7 @@
         <v>45324</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8627,7 +8627,7 @@
         <v>44508</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8700,7 +8700,7 @@
         <v>45371</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>

--- a/Översikt KUNGÄLV.xlsx
+++ b/Översikt KUNGÄLV.xlsx
@@ -601,7 +601,7 @@
         <v>45548</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>45868</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -851,7 +851,7 @@
         <v>45526</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -965,7 +965,7 @@
         <v>45919</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
         <v>45695</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         <v>45993</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         <v>45324</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>45985</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>46199</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>45355</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>46212</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         <v>45957</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 57116-2025</t>
+          <t>A 56394-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1963,14 +1963,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45979</v>
+        <v>45974</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1983,7 +1983,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>3.5</v>
+        <v>1.3</v>
       </c>
       <c r="J14" t="n">
         <v>1</v>
@@ -2016,153 +2016,153 @@
         <v>2</v>
       </c>
       <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Kambräken
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 56394-2025 artfynd.xlsx", "A 56394-2025")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 56394-2025 karta.png", "A 56394-2025")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 56394-2025 georefererad karta.tif", "A 56394-2025")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 56394-2025 FSC-klagomål.docx", "A 56394-2025")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 56394-2025 FSC-klagomål mail.docx", "A 56394-2025")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 56394-2025 tillsynsbegäran.docx", "A 56394-2025")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 56394-2025 tillsynsbegäran mail.docx", "A 56394-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 57116-2025</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>45979</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>KUNGÄLV</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2</v>
+      </c>
+      <c r="T15" t="n">
         <v>3</v>
       </c>
-      <c r="U14" t="n">
+      <c r="U15" t="n">
         <v>3</v>
       </c>
-      <c r="V14" s="2" t="inlineStr">
+      <c r="V15" s="2" t="inlineStr">
         <is>
           <t>Västlig hakmossa
 Spillkråka</t>
         </is>
       </c>
-      <c r="W14">
+      <c r="W15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 57116-2025 artfynd.xlsx", "A 57116-2025")</f>
         <v/>
       </c>
-      <c r="X14">
+      <c r="X15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 57116-2025 karta.png", "A 57116-2025")</f>
         <v/>
       </c>
-      <c r="Y14">
+      <c r="Y15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 57116-2025 georefererad karta.tif", "A 57116-2025")</f>
         <v/>
       </c>
-      <c r="AA14">
+      <c r="AA15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 57116-2025 FSC-klagomål.docx", "A 57116-2025")</f>
         <v/>
       </c>
-      <c r="AB14">
+      <c r="AB15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 57116-2025 FSC-klagomål mail.docx", "A 57116-2025")</f>
         <v/>
       </c>
-      <c r="AC14">
+      <c r="AC15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 57116-2025 tillsynsbegäran.docx", "A 57116-2025")</f>
         <v/>
       </c>
-      <c r="AD14">
+      <c r="AD15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 57116-2025 tillsynsbegäran mail.docx", "A 57116-2025")</f>
         <v/>
       </c>
-      <c r="AE14">
+      <c r="AE15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 57116-2025 prioriterade fågelarter.docx", "A 57116-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 56394-2025</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>45974</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>KUNGÄLV</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="J15" t="n">
-        <v>1</v>
-      </c>
-      <c r="K15" t="n">
-        <v>1</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>Kambräken
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 56394-2025 artfynd.xlsx", "A 56394-2025")</f>
-        <v/>
-      </c>
-      <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 56394-2025 karta.png", "A 56394-2025")</f>
-        <v/>
-      </c>
-      <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 56394-2025 georefererad karta.tif", "A 56394-2025")</f>
-        <v/>
-      </c>
-      <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 56394-2025 FSC-klagomål.docx", "A 56394-2025")</f>
-        <v/>
-      </c>
-      <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 56394-2025 FSC-klagomål mail.docx", "A 56394-2025")</f>
-        <v/>
-      </c>
-      <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 56394-2025 tillsynsbegäran.docx", "A 56394-2025")</f>
-        <v/>
-      </c>
-      <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 56394-2025 tillsynsbegäran mail.docx", "A 56394-2025")</f>
         <v/>
       </c>
     </row>
@@ -2186,7 +2186,7 @@
         <v>46212</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
         <v>45957</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2406,7 +2406,7 @@
         <v>45334</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2512,7 +2512,7 @@
         <v>45334</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
         <v>44838</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2706,7 +2706,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 6082-2025</t>
+          <t>A 49988-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2720,10 +2720,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45697</v>
+        <v>45215</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="J21" t="n">
         <v>1</v>
@@ -2772,50 +2772,46 @@
         <v>1</v>
       </c>
       <c r="U21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 6082-2025 artfynd.xlsx", "A 6082-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 49988-2023 artfynd.xlsx", "A 49988-2023")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 6082-2025 karta.png", "A 6082-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 49988-2023 karta.png", "A 49988-2023")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 6082-2025 georefererad karta.tif", "A 6082-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 49988-2023 georefererad karta.tif", "A 49988-2023")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 6082-2025 FSC-klagomål.docx", "A 6082-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 49988-2023 FSC-klagomål.docx", "A 49988-2023")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 6082-2025 FSC-klagomål mail.docx", "A 6082-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 49988-2023 FSC-klagomål mail.docx", "A 49988-2023")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 6082-2025 tillsynsbegäran.docx", "A 6082-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 49988-2023 tillsynsbegäran.docx", "A 49988-2023")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 6082-2025 tillsynsbegäran mail.docx", "A 6082-2025")</f>
-        <v/>
-      </c>
-      <c r="AE21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 6082-2025 prioriterade fågelarter.docx", "A 6082-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 49988-2023 tillsynsbegäran mail.docx", "A 49988-2023")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 23704-2024</t>
+          <t>A 6082-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2829,10 +2825,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45454</v>
+        <v>45697</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2845,7 +2841,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>4.9</v>
+        <v>2.8</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
@@ -2857,7 +2853,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
@@ -2869,58 +2865,62 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
       </c>
       <c r="T22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U22" t="n">
         <v>1</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Hedjohannesört</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 23704-2024 artfynd.xlsx", "A 23704-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 6082-2025 artfynd.xlsx", "A 6082-2025")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 23704-2024 karta.png", "A 23704-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 6082-2025 karta.png", "A 6082-2025")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 23704-2024 georefererad karta.tif", "A 23704-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 6082-2025 georefererad karta.tif", "A 6082-2025")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 23704-2024 FSC-klagomål.docx", "A 23704-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 6082-2025 FSC-klagomål.docx", "A 6082-2025")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 23704-2024 FSC-klagomål mail.docx", "A 23704-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 6082-2025 FSC-klagomål mail.docx", "A 6082-2025")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 23704-2024 tillsynsbegäran.docx", "A 23704-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 6082-2025 tillsynsbegäran.docx", "A 6082-2025")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 23704-2024 tillsynsbegäran mail.docx", "A 23704-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 6082-2025 tillsynsbegäran mail.docx", "A 6082-2025")</f>
+        <v/>
+      </c>
+      <c r="AE22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 6082-2025 prioriterade fågelarter.docx", "A 6082-2025")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 49988-2023</t>
+          <t>A 30862-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2934,10 +2934,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45215</v>
+        <v>46212</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2950,7 +2950,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="J23" t="n">
         <v>1</v>
@@ -2983,49 +2983,49 @@
         <v>1</v>
       </c>
       <c r="T23" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U23" t="n">
         <v>0</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 49988-2023 artfynd.xlsx", "A 49988-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 30862-2026 artfynd.xlsx", "A 30862-2026")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 49988-2023 karta.png", "A 49988-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 30862-2026 karta.png", "A 30862-2026")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 49988-2023 georefererad karta.tif", "A 49988-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 30862-2026 georefererad karta.tif", "A 30862-2026")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 49988-2023 FSC-klagomål.docx", "A 49988-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 30862-2026 FSC-klagomål.docx", "A 30862-2026")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 49988-2023 FSC-klagomål mail.docx", "A 49988-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 30862-2026 FSC-klagomål mail.docx", "A 30862-2026")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 49988-2023 tillsynsbegäran.docx", "A 49988-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 30862-2026 tillsynsbegäran.docx", "A 30862-2026")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 49988-2023 tillsynsbegäran mail.docx", "A 49988-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 30862-2026 tillsynsbegäran mail.docx", "A 30862-2026")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 30862-2026</t>
+          <t>A 23704-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3039,10 +3039,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46212</v>
+        <v>45454</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3055,7 +3055,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.7</v>
+        <v>4.9</v>
       </c>
       <c r="J24" t="n">
         <v>1</v>
@@ -3067,7 +3067,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
@@ -3079,51 +3079,51 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
       </c>
       <c r="T24" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Hedjohannesört</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 30862-2026 artfynd.xlsx", "A 30862-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 23704-2024 artfynd.xlsx", "A 23704-2024")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 30862-2026 karta.png", "A 30862-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 23704-2024 karta.png", "A 23704-2024")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 30862-2026 georefererad karta.tif", "A 30862-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 23704-2024 georefererad karta.tif", "A 23704-2024")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 30862-2026 FSC-klagomål.docx", "A 30862-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 23704-2024 FSC-klagomål.docx", "A 23704-2024")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 30862-2026 FSC-klagomål mail.docx", "A 30862-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 23704-2024 FSC-klagomål mail.docx", "A 23704-2024")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 30862-2026 tillsynsbegäran.docx", "A 30862-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 23704-2024 tillsynsbegäran.docx", "A 23704-2024")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 30862-2026 tillsynsbegäran mail.docx", "A 30862-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 23704-2024 tillsynsbegäran mail.docx", "A 23704-2024")</f>
         <v/>
       </c>
     </row>
@@ -3147,7 +3147,7 @@
         <v>44691</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
         <v>44691</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         <v>44836</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3366,7 +3366,7 @@
         <v>44760</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         <v>44760</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
         <v>44760</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3568,7 +3568,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 17455-2025</t>
+          <t>A 62221-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3582,10 +3582,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45757</v>
+        <v>45267</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3598,7 +3598,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2.1</v>
+        <v>1.3</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3641,7 +3641,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 62221-2023</t>
+          <t>A 4204-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3655,10 +3655,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45267</v>
+        <v>45324</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3671,7 +3671,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.3</v>
+        <v>4.4</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3714,7 +3714,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 21240-2023</t>
+          <t>A 30170-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3728,10 +3728,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45058</v>
+        <v>44757</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3744,7 +3744,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3787,7 +3787,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 29223-2024</t>
+          <t>A 13880-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3801,10 +3801,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45482</v>
+        <v>45391</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3817,7 +3817,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>5.6</v>
+        <v>2.4</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3860,7 +3860,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 10655-2022</t>
+          <t>A 1995-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3874,10 +3874,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44624</v>
+        <v>45308</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3890,7 +3890,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>13.3</v>
+        <v>0.5</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3933,7 +3933,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 39714-2024</t>
+          <t>A 45990-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3947,10 +3947,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45552</v>
+        <v>44846</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3963,7 +3963,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.2</v>
+        <v>3.3</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4006,7 +4006,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 10677-2025</t>
+          <t>A 43520-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4020,10 +4020,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45721</v>
+        <v>44837</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>7.4</v>
+        <v>1.5</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4079,7 +4079,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 10679-2025</t>
+          <t>A 34366-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4093,10 +4093,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45721</v>
+        <v>44792</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4109,7 +4109,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>4.4</v>
+        <v>0.5</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4152,7 +4152,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 11237-2025</t>
+          <t>A 29223-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4166,10 +4166,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45726</v>
+        <v>45482</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4182,7 +4182,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>4.2</v>
+        <v>5.6</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4225,7 +4225,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 40951-2025</t>
+          <t>A 17922-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4239,10 +4239,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45897</v>
+        <v>45758</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4298,7 +4298,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 34366-2022</t>
+          <t>A 61417-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4312,10 +4312,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44792</v>
+        <v>44916</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4328,7 +4328,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.5</v>
+        <v>3.6</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4371,7 +4371,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 74285-2021</t>
+          <t>A 32272-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4385,10 +4385,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44558</v>
+        <v>45120</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4401,7 +4401,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.1</v>
+        <v>4.9</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4444,7 +4444,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 4673-2026</t>
+          <t>A 32847-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4458,10 +4458,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46048</v>
+        <v>45124</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4474,7 +4474,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>8.199999999999999</v>
+        <v>4.7</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4517,7 +4517,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 45124-2025</t>
+          <t>A 4673-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4531,10 +4531,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45919</v>
+        <v>46048</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4547,7 +4547,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>3.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4590,7 +4590,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 19531-2023</t>
+          <t>A 40951-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4604,10 +4604,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45050</v>
+        <v>45897</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4620,7 +4620,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.9</v>
+        <v>0.8</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4663,7 +4663,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 61417-2022</t>
+          <t>A 8334-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4677,10 +4677,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44916</v>
+        <v>44975</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>3.6</v>
+        <v>1.8</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4736,7 +4736,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 5705-2025</t>
+          <t>A 34244-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4746,14 +4746,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45694</v>
+        <v>45844</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4766,7 +4766,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.2</v>
+        <v>2.9</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4809,7 +4809,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 6946-2026</t>
+          <t>A 25624-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4819,14 +4819,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46057</v>
+        <v>45803</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2.2</v>
+        <v>5</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4882,7 +4882,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 47564-2025</t>
+          <t>A 41442-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4896,10 +4896,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45931</v>
+        <v>45869</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4912,7 +4912,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4955,7 +4955,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 7505-2024</t>
+          <t>A 45124-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4969,10 +4969,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45347</v>
+        <v>45919</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4985,7 +4985,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.8</v>
+        <v>3.7</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5028,7 +5028,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 8334-2023</t>
+          <t>A 6946-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5038,14 +5038,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44975</v>
+        <v>46057</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5058,7 +5058,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5101,7 +5101,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 32272-2023</t>
+          <t>A 47564-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5115,10 +5115,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45120</v>
+        <v>45931</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5131,7 +5131,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>4.9</v>
+        <v>2</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5174,7 +5174,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 52932-2025</t>
+          <t>A 4262-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5188,10 +5188,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45957</v>
+        <v>45324</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5204,7 +5204,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>3.4</v>
+        <v>14</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5247,7 +5247,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 32847-2023</t>
+          <t>A 661-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5261,10 +5261,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45124</v>
+        <v>45664</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5277,7 +5277,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>4.7</v>
+        <v>3.1</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5320,7 +5320,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 37443-2025</t>
+          <t>A 52932-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5334,10 +5334,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45877</v>
+        <v>45957</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5349,13 +5349,8 @@
           <t>KUNGÄLV</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I55" t="n">
-        <v>0.7</v>
+        <v>3.4</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5398,7 +5393,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 13990-2026</t>
+          <t>A 37443-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5412,10 +5407,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46098</v>
+        <v>45877</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5427,8 +5422,13 @@
           <t>KUNGÄLV</t>
         </is>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I56" t="n">
-        <v>2.6</v>
+        <v>0.7</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5471,7 +5471,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 49985-2023</t>
+          <t>A 13990-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5485,10 +5485,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45215</v>
+        <v>46098</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>8.199999999999999</v>
+        <v>2.6</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5544,7 +5544,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 49981-2023</t>
+          <t>A 24461-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5558,10 +5558,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45215</v>
+        <v>45082</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5574,7 +5574,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5617,7 +5617,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 56782-2022</t>
+          <t>A 143-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5631,10 +5631,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44894</v>
+        <v>44928</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5690,7 +5690,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 50071-2023</t>
+          <t>A 49985-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5707,7 +5707,7 @@
         <v>45215</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5720,7 +5720,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5763,7 +5763,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 1995-2024</t>
+          <t>A 63319-2021</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5777,10 +5777,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45308</v>
+        <v>44508</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5793,7 +5793,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5836,7 +5836,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 34244-2025</t>
+          <t>A 50071-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5850,10 +5850,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45844</v>
+        <v>45215</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5866,7 +5866,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2.9</v>
+        <v>4</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5909,7 +5909,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 30170-2022</t>
+          <t>A 7505-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5923,10 +5923,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44757</v>
+        <v>45347</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5939,7 +5939,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>3.1</v>
+        <v>1.8</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5982,7 +5982,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 10810-2023</t>
+          <t>A 22731-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5996,10 +5996,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44989</v>
+        <v>46157</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6012,7 +6012,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.4</v>
+        <v>1.8</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6055,7 +6055,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 4204-2024</t>
+          <t>A 32391-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6069,10 +6069,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45324</v>
+        <v>45837</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6085,7 +6085,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>4.4</v>
+        <v>2.1</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6128,7 +6128,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 25624-2025</t>
+          <t>A 10655-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6142,10 +6142,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45803</v>
+        <v>44624</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6158,7 +6158,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>5</v>
+        <v>13.3</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6201,7 +6201,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 41442-2025</t>
+          <t>A 17455-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6215,10 +6215,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45869</v>
+        <v>45757</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6231,7 +6231,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6274,7 +6274,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 62128-2021</t>
+          <t>A 23607-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6288,10 +6288,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44502</v>
+        <v>46163</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6304,7 +6304,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.8</v>
+        <v>5.3</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6347,7 +6347,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 62979-2023</t>
+          <t>A 25135-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6357,14 +6357,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45271</v>
+        <v>45798</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6377,7 +6377,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6420,7 +6420,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 22731-2026</t>
+          <t>A 19531-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6434,10 +6434,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46157</v>
+        <v>45050</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6450,7 +6450,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6493,7 +6493,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 32391-2025</t>
+          <t>A 5705-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6503,14 +6503,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45837</v>
+        <v>45694</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6523,7 +6523,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>2.1</v>
+        <v>1.2</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6566,7 +6566,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 44176-2023</t>
+          <t>A 62979-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6576,14 +6576,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45188</v>
+        <v>45271</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6596,7 +6596,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>7.1</v>
+        <v>0.8</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6639,7 +6639,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 23607-2026</t>
+          <t>A 16538-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6653,10 +6653,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46163</v>
+        <v>45751</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6669,7 +6669,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>5.3</v>
+        <v>0.8</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6712,7 +6712,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 25135-2025</t>
+          <t>A 29801-2022</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6726,10 +6726,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45798</v>
+        <v>44755</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6742,7 +6742,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.1</v>
+        <v>4.8</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6785,7 +6785,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 26812-2024</t>
+          <t>A 49981-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6799,10 +6799,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45470</v>
+        <v>45215</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6815,7 +6815,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.7</v>
+        <v>2.5</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6858,7 +6858,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 29801-2022</t>
+          <t>A 71835-2021</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6872,10 +6872,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44755</v>
+        <v>44543</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6888,7 +6888,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>4.8</v>
+        <v>7.5</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6931,7 +6931,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 18852-2024</t>
+          <t>A 29952-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6945,10 +6945,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45426</v>
+        <v>46205</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6961,7 +6961,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7004,7 +7004,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 17922-2025</t>
+          <t>A 30738-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7018,10 +7018,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45758</v>
+        <v>46211</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7034,7 +7034,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.8</v>
+        <v>3.5</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7077,7 +7077,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 43520-2022</t>
+          <t>A 30859-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7091,10 +7091,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44837</v>
+        <v>46212</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7107,7 +7107,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7150,7 +7150,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 16538-2025</t>
+          <t>A 56782-2022</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7164,10 +7164,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45751</v>
+        <v>44894</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7180,7 +7180,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7223,7 +7223,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 45990-2022</t>
+          <t>A 26812-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7237,10 +7237,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44846</v>
+        <v>45470</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7253,7 +7253,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>3.3</v>
+        <v>1.7</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7296,7 +7296,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 143-2023</t>
+          <t>A 38262-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7310,10 +7310,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44928</v>
+        <v>46281</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7326,7 +7326,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.5</v>
+        <v>2.8</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7369,7 +7369,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 29952-2026</t>
+          <t>A 10810-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7383,10 +7383,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46205</v>
+        <v>44989</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>2</v>
+        <v>0.4</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7442,7 +7442,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 18851-2024</t>
+          <t>A 62128-2021</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7456,10 +7456,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45426</v>
+        <v>44502</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7472,7 +7472,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>2.7</v>
+        <v>1.8</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7515,7 +7515,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 30738-2026</t>
+          <t>A 21240-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7529,10 +7529,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46211</v>
+        <v>45058</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7545,7 +7545,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>3.5</v>
+        <v>2.3</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7588,7 +7588,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 30859-2026</t>
+          <t>A 18851-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7602,10 +7602,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46212</v>
+        <v>45426</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7618,7 +7618,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>0.5</v>
+        <v>2.7</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7661,7 +7661,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 71835-2021</t>
+          <t>A 21389-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7675,10 +7675,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>44543</v>
+        <v>45063</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7691,7 +7691,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>7.5</v>
+        <v>3.4</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7734,7 +7734,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 51724-2023</t>
+          <t>A 44176-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7748,10 +7748,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45222</v>
+        <v>45188</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7764,7 +7764,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>3.1</v>
+        <v>7.1</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7807,7 +7807,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 38262-2026</t>
+          <t>A 23457-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7821,10 +7821,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46281</v>
+        <v>45453</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7837,7 +7837,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>2.8</v>
+        <v>5.1</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7880,7 +7880,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 661-2025</t>
+          <t>A 39714-2024</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7894,10 +7894,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45664</v>
+        <v>45552</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7910,7 +7910,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>3.1</v>
+        <v>1.2</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7953,7 +7953,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 24461-2023</t>
+          <t>A 18852-2024</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7967,10 +7967,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45082</v>
+        <v>45426</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7983,7 +7983,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1.5</v>
+        <v>2.7</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8026,7 +8026,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 13880-2024</t>
+          <t>A 51724-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45391</v>
+        <v>45222</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8056,7 +8056,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 23457-2024</t>
+          <t>A 34387-2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8113,10 +8113,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45453</v>
+        <v>46254</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8129,7 +8129,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>5.1</v>
+        <v>0.3</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8189,7 +8189,7 @@
         <v>46254</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8245,7 +8245,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 34396-2026</t>
+          <t>A 10679-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8259,10 +8259,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>46254</v>
+        <v>45721</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8275,7 +8275,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.8</v>
+        <v>4.4</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8318,7 +8318,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 34392-2026</t>
+          <t>A 11237-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8332,10 +8332,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>46254</v>
+        <v>45726</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8348,7 +8348,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>0.4</v>
+        <v>4.2</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8391,7 +8391,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 34387-2026</t>
+          <t>A 10677-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8405,10 +8405,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>46254</v>
+        <v>45721</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8421,7 +8421,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>0.3</v>
+        <v>7.4</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8464,7 +8464,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 21389-2023</t>
+          <t>A 34392-2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8478,10 +8478,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45063</v>
+        <v>46254</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8494,7 +8494,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>3.4</v>
+        <v>0.4</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8537,7 +8537,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 4262-2024</t>
+          <t>A 34396-2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8551,10 +8551,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45324</v>
+        <v>46254</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8567,7 +8567,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>14</v>
+        <v>0.8</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8610,7 +8610,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 63319-2021</t>
+          <t>A 74285-2021</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8624,10 +8624,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>44508</v>
+        <v>44558</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8640,7 +8640,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8700,7 +8700,7 @@
         <v>45371</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>

--- a/Översikt KUNGÄLV.xlsx
+++ b/Översikt KUNGÄLV.xlsx
@@ -601,7 +601,7 @@
         <v>45548</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>45868</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -851,7 +851,7 @@
         <v>45526</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -965,7 +965,7 @@
         <v>45919</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
         <v>45695</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         <v>45993</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         <v>45324</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>45985</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>46199</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>45355</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>46212</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         <v>45957</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1970,7 +1970,7 @@
         <v>45974</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2076,7 +2076,7 @@
         <v>45979</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
         <v>46212</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
         <v>45957</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2406,7 +2406,7 @@
         <v>45334</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2512,7 +2512,7 @@
         <v>45334</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
         <v>44838</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2706,7 +2706,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 49988-2023</t>
+          <t>A 6082-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2720,10 +2720,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45215</v>
+        <v>45697</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="J21" t="n">
         <v>1</v>
@@ -2772,46 +2772,50 @@
         <v>1</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 49988-2023 artfynd.xlsx", "A 49988-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 6082-2025 artfynd.xlsx", "A 6082-2025")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 49988-2023 karta.png", "A 49988-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 6082-2025 karta.png", "A 6082-2025")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 49988-2023 georefererad karta.tif", "A 49988-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 6082-2025 georefererad karta.tif", "A 6082-2025")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 49988-2023 FSC-klagomål.docx", "A 49988-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 6082-2025 FSC-klagomål.docx", "A 6082-2025")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 49988-2023 FSC-klagomål mail.docx", "A 49988-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 6082-2025 FSC-klagomål mail.docx", "A 6082-2025")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 49988-2023 tillsynsbegäran.docx", "A 49988-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 6082-2025 tillsynsbegäran.docx", "A 6082-2025")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 49988-2023 tillsynsbegäran mail.docx", "A 49988-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 6082-2025 tillsynsbegäran mail.docx", "A 6082-2025")</f>
+        <v/>
+      </c>
+      <c r="AE21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 6082-2025 prioriterade fågelarter.docx", "A 6082-2025")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 6082-2025</t>
+          <t>A 23704-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2825,10 +2829,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45697</v>
+        <v>45454</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2841,7 +2845,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>2.8</v>
+        <v>4.9</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
@@ -2853,7 +2857,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
@@ -2865,55 +2869,51 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
       </c>
       <c r="T22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U22" t="n">
         <v>1</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Hedjohannesört</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 6082-2025 artfynd.xlsx", "A 6082-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 23704-2024 artfynd.xlsx", "A 23704-2024")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 6082-2025 karta.png", "A 6082-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 23704-2024 karta.png", "A 23704-2024")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 6082-2025 georefererad karta.tif", "A 6082-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 23704-2024 georefererad karta.tif", "A 23704-2024")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 6082-2025 FSC-klagomål.docx", "A 6082-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 23704-2024 FSC-klagomål.docx", "A 23704-2024")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 6082-2025 FSC-klagomål mail.docx", "A 6082-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 23704-2024 FSC-klagomål mail.docx", "A 23704-2024")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 6082-2025 tillsynsbegäran.docx", "A 6082-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 23704-2024 tillsynsbegäran.docx", "A 23704-2024")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 6082-2025 tillsynsbegäran mail.docx", "A 6082-2025")</f>
-        <v/>
-      </c>
-      <c r="AE22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 6082-2025 prioriterade fågelarter.docx", "A 6082-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 23704-2024 tillsynsbegäran mail.docx", "A 23704-2024")</f>
         <v/>
       </c>
     </row>
@@ -2937,7 +2937,7 @@
         <v>46212</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3025,7 +3025,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 23704-2024</t>
+          <t>A 49988-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3039,10 +3039,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45454</v>
+        <v>45215</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3055,7 +3055,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>4.9</v>
+        <v>2.3</v>
       </c>
       <c r="J24" t="n">
         <v>1</v>
@@ -3067,7 +3067,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
@@ -3079,51 +3079,51 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
       </c>
       <c r="T24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Hedjohannesört</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 23704-2024 artfynd.xlsx", "A 23704-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 49988-2023 artfynd.xlsx", "A 49988-2023")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 23704-2024 karta.png", "A 23704-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 49988-2023 karta.png", "A 49988-2023")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 23704-2024 georefererad karta.tif", "A 23704-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 49988-2023 georefererad karta.tif", "A 49988-2023")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 23704-2024 FSC-klagomål.docx", "A 23704-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 49988-2023 FSC-klagomål.docx", "A 49988-2023")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 23704-2024 FSC-klagomål mail.docx", "A 23704-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 49988-2023 FSC-klagomål mail.docx", "A 49988-2023")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 23704-2024 tillsynsbegäran.docx", "A 23704-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 49988-2023 tillsynsbegäran.docx", "A 49988-2023")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 23704-2024 tillsynsbegäran mail.docx", "A 23704-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 49988-2023 tillsynsbegäran mail.docx", "A 49988-2023")</f>
         <v/>
       </c>
     </row>
@@ -3147,7 +3147,7 @@
         <v>44691</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
         <v>44691</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         <v>44836</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3366,7 +3366,7 @@
         <v>44760</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         <v>44760</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
         <v>44760</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3568,7 +3568,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 62221-2023</t>
+          <t>A 17455-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3582,10 +3582,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45267</v>
+        <v>45757</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3598,7 +3598,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.3</v>
+        <v>2.1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3641,7 +3641,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 4204-2024</t>
+          <t>A 62221-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3655,10 +3655,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45324</v>
+        <v>45267</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3671,7 +3671,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>4.4</v>
+        <v>1.3</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3714,7 +3714,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 30170-2022</t>
+          <t>A 21240-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3728,10 +3728,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44757</v>
+        <v>45058</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3744,7 +3744,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>3.1</v>
+        <v>2.3</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3787,7 +3787,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 13880-2024</t>
+          <t>A 29223-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3801,10 +3801,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45391</v>
+        <v>45482</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3817,7 +3817,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2.4</v>
+        <v>5.6</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3860,7 +3860,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 1995-2024</t>
+          <t>A 10655-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3874,10 +3874,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45308</v>
+        <v>44624</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3890,7 +3890,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.5</v>
+        <v>13.3</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3933,7 +3933,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 45990-2022</t>
+          <t>A 39714-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3947,10 +3947,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44846</v>
+        <v>45552</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3963,7 +3963,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>3.3</v>
+        <v>1.2</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4006,7 +4006,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 43520-2022</t>
+          <t>A 19531-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4020,10 +4020,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44837</v>
+        <v>45050</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4079,7 +4079,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 34366-2022</t>
+          <t>A 5705-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4089,14 +4089,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44792</v>
+        <v>45694</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4109,7 +4109,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4152,7 +4152,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 29223-2024</t>
+          <t>A 61417-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4166,10 +4166,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45482</v>
+        <v>44916</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4182,7 +4182,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>5.6</v>
+        <v>3.6</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4225,7 +4225,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 17922-2025</t>
+          <t>A 34366-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4239,10 +4239,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45758</v>
+        <v>44792</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4255,7 +4255,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4298,7 +4298,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 61417-2022</t>
+          <t>A 7505-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4312,10 +4312,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44916</v>
+        <v>45347</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4328,7 +4328,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>3.6</v>
+        <v>1.8</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4388,7 +4388,7 @@
         <v>45120</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4444,7 +4444,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 32847-2023</t>
+          <t>A 4673-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4458,10 +4458,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45124</v>
+        <v>46048</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4474,7 +4474,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>4.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4517,7 +4517,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 4673-2026</t>
+          <t>A 32847-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4531,10 +4531,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46048</v>
+        <v>45124</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4547,7 +4547,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>8.199999999999999</v>
+        <v>4.7</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4607,7 +4607,7 @@
         <v>45897</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4663,7 +4663,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 8334-2023</t>
+          <t>A 6946-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4673,14 +4673,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44975</v>
+        <v>46057</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4736,7 +4736,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 34244-2025</t>
+          <t>A 8334-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4750,10 +4750,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45844</v>
+        <v>44975</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4766,7 +4766,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2.9</v>
+        <v>1.8</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4809,7 +4809,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 25624-2025</t>
+          <t>A 45124-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4823,10 +4823,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45803</v>
+        <v>45919</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>5</v>
+        <v>3.7</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4882,7 +4882,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 41442-2025</t>
+          <t>A 47564-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4896,10 +4896,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45869</v>
+        <v>45931</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4912,7 +4912,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4955,7 +4955,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 45124-2025</t>
+          <t>A 37443-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4969,10 +4969,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45919</v>
+        <v>45877</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4984,8 +4984,13 @@
           <t>KUNGÄLV</t>
         </is>
       </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I50" t="n">
-        <v>3.7</v>
+        <v>0.7</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5028,7 +5033,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 6946-2026</t>
+          <t>A 13990-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5038,14 +5043,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46057</v>
+        <v>46098</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5058,7 +5063,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5101,7 +5106,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 47564-2025</t>
+          <t>A 34244-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5115,10 +5120,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45931</v>
+        <v>45844</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5131,7 +5136,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2</v>
+        <v>2.9</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5174,7 +5179,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 4262-2024</t>
+          <t>A 25624-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5188,10 +5193,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45324</v>
+        <v>45803</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5204,7 +5209,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5247,7 +5252,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 661-2025</t>
+          <t>A 52932-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5261,10 +5266,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45664</v>
+        <v>45957</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5277,7 +5282,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5320,7 +5325,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 52932-2025</t>
+          <t>A 41442-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5334,10 +5339,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45957</v>
+        <v>45869</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5350,7 +5355,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>3.4</v>
+        <v>1.8</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5393,7 +5398,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 37443-2025</t>
+          <t>A 17922-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5407,10 +5412,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45877</v>
+        <v>45758</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5422,13 +5427,8 @@
           <t>KUNGÄLV</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I56" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5471,7 +5471,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 13990-2026</t>
+          <t>A 49985-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5485,10 +5485,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46098</v>
+        <v>45215</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5544,7 +5544,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 24461-2023</t>
+          <t>A 50071-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5558,10 +5558,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45082</v>
+        <v>45215</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5574,7 +5574,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.5</v>
+        <v>4</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5617,7 +5617,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 143-2023</t>
+          <t>A 49981-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5631,10 +5631,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44928</v>
+        <v>45215</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5647,7 +5647,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5690,7 +5690,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 49985-2023</t>
+          <t>A 22731-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5704,10 +5704,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45215</v>
+        <v>46157</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5720,7 +5720,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>8.199999999999999</v>
+        <v>1.8</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5763,7 +5763,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 63319-2021</t>
+          <t>A 32391-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5777,10 +5777,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44508</v>
+        <v>45837</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5793,7 +5793,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5836,7 +5836,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 50071-2023</t>
+          <t>A 23607-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5850,10 +5850,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45215</v>
+        <v>46163</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5866,7 +5866,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>4</v>
+        <v>5.3</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5909,7 +5909,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 7505-2024</t>
+          <t>A 25135-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5923,10 +5923,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45347</v>
+        <v>45798</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5939,7 +5939,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5982,7 +5982,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 22731-2026</t>
+          <t>A 56782-2022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5996,10 +5996,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46157</v>
+        <v>44894</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6012,7 +6012,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6055,7 +6055,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 32391-2025</t>
+          <t>A 1995-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6069,10 +6069,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45837</v>
+        <v>45308</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6085,7 +6085,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>2.1</v>
+        <v>0.5</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6128,7 +6128,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 10655-2022</t>
+          <t>A 30170-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6142,10 +6142,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44624</v>
+        <v>44757</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6158,7 +6158,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>13.3</v>
+        <v>3.1</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6201,7 +6201,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 17455-2025</t>
+          <t>A 10810-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6215,10 +6215,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45757</v>
+        <v>44989</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6231,7 +6231,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>2.1</v>
+        <v>0.4</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6274,7 +6274,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 23607-2026</t>
+          <t>A 4204-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6288,10 +6288,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46163</v>
+        <v>45324</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6304,7 +6304,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>5.3</v>
+        <v>4.4</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6347,7 +6347,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 25135-2025</t>
+          <t>A 62128-2021</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6361,10 +6361,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45798</v>
+        <v>44502</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6377,7 +6377,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6420,7 +6420,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 19531-2023</t>
+          <t>A 62979-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6430,14 +6430,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45050</v>
+        <v>45271</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6450,7 +6450,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.9</v>
+        <v>0.8</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6493,7 +6493,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 5705-2025</t>
+          <t>A 29952-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6503,14 +6503,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45694</v>
+        <v>46205</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6523,7 +6523,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6566,7 +6566,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 62979-2023</t>
+          <t>A 44176-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6576,14 +6576,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45271</v>
+        <v>45188</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6596,7 +6596,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.8</v>
+        <v>7.1</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6639,7 +6639,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 16538-2025</t>
+          <t>A 30738-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6653,10 +6653,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45751</v>
+        <v>46211</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6669,7 +6669,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.8</v>
+        <v>3.5</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6712,7 +6712,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 29801-2022</t>
+          <t>A 30859-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6726,10 +6726,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44755</v>
+        <v>46212</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6742,7 +6742,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>4.8</v>
+        <v>0.5</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6785,7 +6785,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 49981-2023</t>
+          <t>A 26812-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6799,10 +6799,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45215</v>
+        <v>45470</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6815,7 +6815,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>2.5</v>
+        <v>1.7</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6858,7 +6858,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 71835-2021</t>
+          <t>A 29801-2022</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6872,10 +6872,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44543</v>
+        <v>44755</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6888,7 +6888,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>7.5</v>
+        <v>4.8</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6931,7 +6931,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 29952-2026</t>
+          <t>A 18852-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6945,10 +6945,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46205</v>
+        <v>45426</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6961,7 +6961,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7004,7 +7004,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 30738-2026</t>
+          <t>A 43520-2022</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7018,10 +7018,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46211</v>
+        <v>44837</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7034,7 +7034,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>3.5</v>
+        <v>1.5</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7077,7 +7077,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 30859-2026</t>
+          <t>A 16538-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7091,10 +7091,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46212</v>
+        <v>45751</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7107,7 +7107,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7150,7 +7150,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 56782-2022</t>
+          <t>A 45990-2022</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7164,10 +7164,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44894</v>
+        <v>44846</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7180,7 +7180,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.5</v>
+        <v>3.3</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7223,7 +7223,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 26812-2024</t>
+          <t>A 143-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7237,10 +7237,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45470</v>
+        <v>44928</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7253,7 +7253,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7296,7 +7296,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 38262-2026</t>
+          <t>A 18851-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7310,10 +7310,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46281</v>
+        <v>45426</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7326,7 +7326,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7369,7 +7369,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 10810-2023</t>
+          <t>A 38262-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7383,10 +7383,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>44989</v>
+        <v>46281</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>0.4</v>
+        <v>2.8</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7442,7 +7442,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 62128-2021</t>
+          <t>A 71835-2021</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7456,10 +7456,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44502</v>
+        <v>44543</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7472,7 +7472,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.8</v>
+        <v>7.5</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7515,7 +7515,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 21240-2023</t>
+          <t>A 51724-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7529,10 +7529,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45058</v>
+        <v>45222</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7545,7 +7545,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7588,7 +7588,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 18851-2024</t>
+          <t>A 661-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7602,10 +7602,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45426</v>
+        <v>45664</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7618,7 +7618,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7661,7 +7661,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 21389-2023</t>
+          <t>A 24461-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7675,10 +7675,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45063</v>
+        <v>45082</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7691,7 +7691,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>3.4</v>
+        <v>1.5</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7734,7 +7734,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 44176-2023</t>
+          <t>A 13880-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7748,10 +7748,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45188</v>
+        <v>45391</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7764,7 +7764,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>7.1</v>
+        <v>2.4</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7807,7 +7807,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 23457-2024</t>
+          <t>A 34386-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7821,10 +7821,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45453</v>
+        <v>46254</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7837,7 +7837,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>5.1</v>
+        <v>0.7</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7880,7 +7880,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 39714-2024</t>
+          <t>A 34396-2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7894,10 +7894,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45552</v>
+        <v>46254</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7910,7 +7910,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7953,7 +7953,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 18852-2024</t>
+          <t>A 34392-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7967,10 +7967,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45426</v>
+        <v>46254</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7983,7 +7983,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>2.7</v>
+        <v>0.4</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8026,7 +8026,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 51724-2023</t>
+          <t>A 34387-2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45222</v>
+        <v>46254</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8056,7 +8056,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>3.1</v>
+        <v>0.3</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 34387-2026</t>
+          <t>A 23457-2024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8113,10 +8113,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>46254</v>
+        <v>45453</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8129,7 +8129,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>0.3</v>
+        <v>5.1</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8172,7 +8172,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 34386-2026</t>
+          <t>A 21389-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8186,10 +8186,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>46254</v>
+        <v>45063</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8202,7 +8202,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>0.7</v>
+        <v>3.4</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8245,7 +8245,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 10679-2025</t>
+          <t>A 4262-2024</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8259,10 +8259,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45721</v>
+        <v>45324</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8275,7 +8275,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>4.4</v>
+        <v>14</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8318,7 +8318,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 11237-2025</t>
+          <t>A 63319-2021</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8332,10 +8332,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45726</v>
+        <v>44508</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8348,7 +8348,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>4.2</v>
+        <v>1.6</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8408,7 +8408,7 @@
         <v>45721</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8464,7 +8464,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 34392-2026</t>
+          <t>A 10679-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8478,10 +8478,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>46254</v>
+        <v>45721</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8494,7 +8494,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>0.4</v>
+        <v>4.4</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8537,7 +8537,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 34396-2026</t>
+          <t>A 11237-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8551,10 +8551,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>46254</v>
+        <v>45726</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8567,7 +8567,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>0.8</v>
+        <v>4.2</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8627,7 +8627,7 @@
         <v>44558</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8700,7 +8700,7 @@
         <v>45371</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>

--- a/Översikt KUNGÄLV.xlsx
+++ b/Översikt KUNGÄLV.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE101"/>
+  <dimension ref="A1:AE102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45548</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>45868</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -851,7 +851,7 @@
         <v>45526</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -965,7 +965,7 @@
         <v>45919</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
         <v>45695</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 59985-2025</t>
+          <t>A 4263-2024</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1188,10 +1188,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45993</v>
+        <v>45324</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1204,16 +1204,16 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>5.3</v>
+        <v>2.6</v>
       </c>
       <c r="J7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -1228,7 +1228,7 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1237,12 +1237,124 @@
         <v>4</v>
       </c>
       <c r="T7" t="n">
+        <v>6</v>
+      </c>
+      <c r="U7" t="n">
+        <v>6</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Mindre hackspett
+Klippfrullania
+Gråsiska
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 4263-2024 artfynd.xlsx", "A 4263-2024")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 4263-2024 karta.png", "A 4263-2024")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 4263-2024 georefererad karta.tif", "A 4263-2024")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 4263-2024 FSC-klagomål.docx", "A 4263-2024")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 4263-2024 FSC-klagomål mail.docx", "A 4263-2024")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 4263-2024 tillsynsbegäran.docx", "A 4263-2024")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 4263-2024 tillsynsbegäran mail.docx", "A 4263-2024")</f>
+        <v/>
+      </c>
+      <c r="AE7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 4263-2024 prioriterade fågelarter.docx", "A 4263-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 59985-2025</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>45993</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>KUNGÄLV</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2</v>
+      </c>
+      <c r="K8" t="n">
+        <v>2</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>4</v>
+      </c>
+      <c r="T8" t="n">
         <v>19</v>
       </c>
-      <c r="U7" t="n">
+      <c r="U8" t="n">
         <v>19</v>
       </c>
-      <c r="V7" s="2" t="inlineStr">
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>Blåmossa
 Västlig hakmossa
@@ -1250,148 +1362,36 @@
 Äkta lopplummer</t>
         </is>
       </c>
-      <c r="W7">
+      <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 59985-2025 artfynd.xlsx", "A 59985-2025")</f>
         <v/>
       </c>
-      <c r="X7">
+      <c r="X8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 59985-2025 karta.png", "A 59985-2025")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 59985-2025 georefererad karta.tif", "A 59985-2025")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 59985-2025 FSC-klagomål.docx", "A 59985-2025")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 59985-2025 FSC-klagomål mail.docx", "A 59985-2025")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 59985-2025 tillsynsbegäran.docx", "A 59985-2025")</f>
         <v/>
       </c>
-      <c r="AD7">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 59985-2025 tillsynsbegäran mail.docx", "A 59985-2025")</f>
         <v/>
       </c>
-      <c r="AE7">
+      <c r="AE8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 59985-2025 prioriterade fågelarter.docx", "A 59985-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A 4263-2024</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>45324</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46302</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>KUNGÄLV</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="J8" t="n">
-        <v>3</v>
-      </c>
-      <c r="K8" t="n">
-        <v>1</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>4</v>
-      </c>
-      <c r="T8" t="n">
-        <v>6</v>
-      </c>
-      <c r="U8" t="n">
-        <v>6</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>Mindre hackspett
-Klippfrullania
-Gråsiska
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 4263-2024 artfynd.xlsx", "A 4263-2024")</f>
-        <v/>
-      </c>
-      <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 4263-2024 karta.png", "A 4263-2024")</f>
-        <v/>
-      </c>
-      <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 4263-2024 georefererad karta.tif", "A 4263-2024")</f>
-        <v/>
-      </c>
-      <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 4263-2024 FSC-klagomål.docx", "A 4263-2024")</f>
-        <v/>
-      </c>
-      <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 4263-2024 FSC-klagomål mail.docx", "A 4263-2024")</f>
-        <v/>
-      </c>
-      <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 4263-2024 tillsynsbegäran.docx", "A 4263-2024")</f>
-        <v/>
-      </c>
-      <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 4263-2024 tillsynsbegäran mail.docx", "A 4263-2024")</f>
-        <v/>
-      </c>
-      <c r="AE8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 4263-2024 prioriterade fågelarter.docx", "A 4263-2024")</f>
         <v/>
       </c>
     </row>
@@ -1415,7 +1415,7 @@
         <v>45985</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>46199</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>45355</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>46212</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         <v>45957</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 56394-2025</t>
+          <t>A 5631-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1963,14 +1963,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45974</v>
+        <v>45334</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1986,10 +1986,10 @@
         <v>1.3</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -2019,582 +2019,582 @@
         <v>2</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Vanlig groda
+Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 5631-2024 artfynd.xlsx", "A 5631-2024")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 5631-2024 karta.png", "A 5631-2024")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 5631-2024 georefererad karta.tif", "A 5631-2024")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 5631-2024 FSC-klagomål.docx", "A 5631-2024")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 5631-2024 FSC-klagomål mail.docx", "A 5631-2024")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 5631-2024 tillsynsbegäran.docx", "A 5631-2024")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 5631-2024 tillsynsbegäran mail.docx", "A 5631-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 5637-2024</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>45334</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>KUNGÄLV</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>2</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Klofibbla
+Åkerrödtoppa</t>
+        </is>
+      </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 5637-2024 artfynd.xlsx", "A 5637-2024")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 5637-2024 karta.png", "A 5637-2024")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 5637-2024 georefererad karta.tif", "A 5637-2024")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 5637-2024 FSC-klagomål.docx", "A 5637-2024")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 5637-2024 FSC-klagomål mail.docx", "A 5637-2024")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 5637-2024 tillsynsbegäran.docx", "A 5637-2024")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 5637-2024 tillsynsbegäran mail.docx", "A 5637-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 56394-2025</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>45974</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>KUNGÄLV</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>Kambräken
 Revlummer</t>
         </is>
       </c>
-      <c r="W14">
+      <c r="W16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 56394-2025 artfynd.xlsx", "A 56394-2025")</f>
         <v/>
       </c>
-      <c r="X14">
+      <c r="X16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 56394-2025 karta.png", "A 56394-2025")</f>
         <v/>
       </c>
-      <c r="Y14">
+      <c r="Y16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 56394-2025 georefererad karta.tif", "A 56394-2025")</f>
         <v/>
       </c>
-      <c r="AA14">
+      <c r="AA16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 56394-2025 FSC-klagomål.docx", "A 56394-2025")</f>
         <v/>
       </c>
-      <c r="AB14">
+      <c r="AB16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 56394-2025 FSC-klagomål mail.docx", "A 56394-2025")</f>
         <v/>
       </c>
-      <c r="AC14">
+      <c r="AC16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 56394-2025 tillsynsbegäran.docx", "A 56394-2025")</f>
         <v/>
       </c>
-      <c r="AD14">
+      <c r="AD16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 56394-2025 tillsynsbegäran mail.docx", "A 56394-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
         <is>
           <t>A 57116-2025</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
         <v>45979</v>
       </c>
-      <c r="E15" s="1" t="n">
-        <v>46302</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>KUNGÄLV</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
+      <c r="E17" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>KUNGÄLV</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
         <v>3.5</v>
       </c>
-      <c r="J15" t="n">
+      <c r="J17" t="n">
         <v>1</v>
       </c>
-      <c r="K15" t="n">
+      <c r="K17" t="n">
         <v>1</v>
       </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
         <v>2</v>
       </c>
-      <c r="T15" t="n">
+      <c r="T17" t="n">
         <v>3</v>
       </c>
-      <c r="U15" t="n">
+      <c r="U17" t="n">
         <v>3</v>
       </c>
-      <c r="V15" s="2" t="inlineStr">
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>Västlig hakmossa
 Spillkråka</t>
         </is>
       </c>
-      <c r="W15">
+      <c r="W17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 57116-2025 artfynd.xlsx", "A 57116-2025")</f>
         <v/>
       </c>
-      <c r="X15">
+      <c r="X17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 57116-2025 karta.png", "A 57116-2025")</f>
         <v/>
       </c>
-      <c r="Y15">
+      <c r="Y17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 57116-2025 georefererad karta.tif", "A 57116-2025")</f>
         <v/>
       </c>
-      <c r="AA15">
+      <c r="AA17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 57116-2025 FSC-klagomål.docx", "A 57116-2025")</f>
         <v/>
       </c>
-      <c r="AB15">
+      <c r="AB17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 57116-2025 FSC-klagomål mail.docx", "A 57116-2025")</f>
         <v/>
       </c>
-      <c r="AC15">
+      <c r="AC17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 57116-2025 tillsynsbegäran.docx", "A 57116-2025")</f>
         <v/>
       </c>
-      <c r="AD15">
+      <c r="AD17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 57116-2025 tillsynsbegäran mail.docx", "A 57116-2025")</f>
         <v/>
       </c>
-      <c r="AE15">
+      <c r="AE17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 57116-2025 prioriterade fågelarter.docx", "A 57116-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
         <is>
           <t>A 30860-2026</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
         <v>46212</v>
       </c>
-      <c r="E16" s="1" t="n">
-        <v>46302</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>KUNGÄLV</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
+      <c r="E18" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>KUNGÄLV</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
         <v>1.7</v>
       </c>
-      <c r="J16" t="n">
+      <c r="J18" t="n">
         <v>1</v>
       </c>
-      <c r="K16" t="n">
+      <c r="K18" t="n">
         <v>1</v>
       </c>
-      <c r="L16" t="n">
+      <c r="L18" t="n">
         <v>1</v>
       </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
         <v>1</v>
       </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
         <v>2</v>
       </c>
-      <c r="T16" t="n">
+      <c r="T18" t="n">
         <v>2</v>
       </c>
-      <c r="U16" t="n">
+      <c r="U18" t="n">
         <v>1</v>
       </c>
-      <c r="V16" s="2" t="inlineStr">
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>Grönsångare
 Västlig hakmossa</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 30860-2026 artfynd.xlsx", "A 30860-2026")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 30860-2026 karta.png", "A 30860-2026")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 30860-2026 georefererad karta.tif", "A 30860-2026")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 30860-2026 FSC-klagomål.docx", "A 30860-2026")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 30860-2026 FSC-klagomål mail.docx", "A 30860-2026")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 30860-2026 tillsynsbegäran.docx", "A 30860-2026")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 30860-2026 tillsynsbegäran mail.docx", "A 30860-2026")</f>
         <v/>
       </c>
-      <c r="AE16">
+      <c r="AE18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 30860-2026 prioriterade fågelarter.docx", "A 30860-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
         <is>
           <t>A 53007-2025</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
         <v>45957</v>
       </c>
-      <c r="E17" s="1" t="n">
-        <v>46302</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>KUNGÄLV</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
+      <c r="E19" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>KUNGÄLV</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
         <v>2.9</v>
       </c>
-      <c r="J17" t="n">
+      <c r="J19" t="n">
         <v>1</v>
       </c>
-      <c r="K17" t="n">
+      <c r="K19" t="n">
         <v>1</v>
       </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
         <v>2</v>
       </c>
-      <c r="T17" t="n">
+      <c r="T19" t="n">
         <v>5</v>
       </c>
-      <c r="U17" t="n">
+      <c r="U19" t="n">
         <v>5</v>
       </c>
-      <c r="V17" s="2" t="inlineStr">
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>Västlig hakmossa
 Spillkråka</t>
         </is>
       </c>
-      <c r="W17">
+      <c r="W19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 53007-2025 artfynd.xlsx", "A 53007-2025")</f>
         <v/>
       </c>
-      <c r="X17">
+      <c r="X19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 53007-2025 karta.png", "A 53007-2025")</f>
         <v/>
       </c>
-      <c r="Y17">
+      <c r="Y19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 53007-2025 georefererad karta.tif", "A 53007-2025")</f>
         <v/>
       </c>
-      <c r="AA17">
+      <c r="AA19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 53007-2025 FSC-klagomål.docx", "A 53007-2025")</f>
         <v/>
       </c>
-      <c r="AB17">
+      <c r="AB19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 53007-2025 FSC-klagomål mail.docx", "A 53007-2025")</f>
         <v/>
       </c>
-      <c r="AC17">
+      <c r="AC19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 53007-2025 tillsynsbegäran.docx", "A 53007-2025")</f>
         <v/>
       </c>
-      <c r="AD17">
+      <c r="AD19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 53007-2025 tillsynsbegäran mail.docx", "A 53007-2025")</f>
         <v/>
       </c>
-      <c r="AE17">
+      <c r="AE19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 53007-2025 prioriterade fågelarter.docx", "A 53007-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 5631-2024</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>45334</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46302</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>KUNGÄLV</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="J18" t="n">
-        <v>2</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>Vanlig groda
-Fläcknycklar</t>
-        </is>
-      </c>
-      <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 5631-2024 artfynd.xlsx", "A 5631-2024")</f>
-        <v/>
-      </c>
-      <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 5631-2024 karta.png", "A 5631-2024")</f>
-        <v/>
-      </c>
-      <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 5631-2024 georefererad karta.tif", "A 5631-2024")</f>
-        <v/>
-      </c>
-      <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 5631-2024 FSC-klagomål.docx", "A 5631-2024")</f>
-        <v/>
-      </c>
-      <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 5631-2024 FSC-klagomål mail.docx", "A 5631-2024")</f>
-        <v/>
-      </c>
-      <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 5631-2024 tillsynsbegäran.docx", "A 5631-2024")</f>
-        <v/>
-      </c>
-      <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 5631-2024 tillsynsbegäran mail.docx", "A 5631-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>A 5637-2024</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>45334</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>46302</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>KUNGÄLV</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>2</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>2</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>Klofibbla
-Åkerrödtoppa</t>
-        </is>
-      </c>
-      <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 5637-2024 artfynd.xlsx", "A 5637-2024")</f>
-        <v/>
-      </c>
-      <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 5637-2024 karta.png", "A 5637-2024")</f>
-        <v/>
-      </c>
-      <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 5637-2024 georefererad karta.tif", "A 5637-2024")</f>
-        <v/>
-      </c>
-      <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 5637-2024 FSC-klagomål.docx", "A 5637-2024")</f>
-        <v/>
-      </c>
-      <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 5637-2024 FSC-klagomål mail.docx", "A 5637-2024")</f>
-        <v/>
-      </c>
-      <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 5637-2024 tillsynsbegäran.docx", "A 5637-2024")</f>
-        <v/>
-      </c>
-      <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 5637-2024 tillsynsbegäran mail.docx", "A 5637-2024")</f>
         <v/>
       </c>
     </row>
@@ -2618,7 +2618,7 @@
         <v>44838</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2706,7 +2706,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 6082-2025</t>
+          <t>A 49988-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2720,10 +2720,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45697</v>
+        <v>45215</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="J21" t="n">
         <v>1</v>
@@ -2772,43 +2772,39 @@
         <v>1</v>
       </c>
       <c r="U21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 6082-2025 artfynd.xlsx", "A 6082-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 49988-2023 artfynd.xlsx", "A 49988-2023")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 6082-2025 karta.png", "A 6082-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 49988-2023 karta.png", "A 49988-2023")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 6082-2025 georefererad karta.tif", "A 6082-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 49988-2023 georefererad karta.tif", "A 49988-2023")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 6082-2025 FSC-klagomål.docx", "A 6082-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 49988-2023 FSC-klagomål.docx", "A 49988-2023")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 6082-2025 FSC-klagomål mail.docx", "A 6082-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 49988-2023 FSC-klagomål mail.docx", "A 49988-2023")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 6082-2025 tillsynsbegäran.docx", "A 6082-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 49988-2023 tillsynsbegäran.docx", "A 49988-2023")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 6082-2025 tillsynsbegäran mail.docx", "A 6082-2025")</f>
-        <v/>
-      </c>
-      <c r="AE21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 6082-2025 prioriterade fågelarter.docx", "A 6082-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 49988-2023 tillsynsbegäran mail.docx", "A 49988-2023")</f>
         <v/>
       </c>
     </row>
@@ -2832,7 +2828,7 @@
         <v>45454</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2920,7 +2916,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 30862-2026</t>
+          <t>A 6082-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2934,10 +2930,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46212</v>
+        <v>45697</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2950,7 +2946,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.7</v>
+        <v>2.8</v>
       </c>
       <c r="J23" t="n">
         <v>1</v>
@@ -2983,49 +2979,53 @@
         <v>1</v>
       </c>
       <c r="T23" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 30862-2026 artfynd.xlsx", "A 30862-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 6082-2025 artfynd.xlsx", "A 6082-2025")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 30862-2026 karta.png", "A 30862-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 6082-2025 karta.png", "A 6082-2025")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 30862-2026 georefererad karta.tif", "A 30862-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 6082-2025 georefererad karta.tif", "A 6082-2025")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 30862-2026 FSC-klagomål.docx", "A 30862-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 6082-2025 FSC-klagomål.docx", "A 6082-2025")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 30862-2026 FSC-klagomål mail.docx", "A 30862-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 6082-2025 FSC-klagomål mail.docx", "A 6082-2025")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 30862-2026 tillsynsbegäran.docx", "A 30862-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 6082-2025 tillsynsbegäran.docx", "A 6082-2025")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 30862-2026 tillsynsbegäran mail.docx", "A 30862-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 6082-2025 tillsynsbegäran mail.docx", "A 6082-2025")</f>
+        <v/>
+      </c>
+      <c r="AE23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 6082-2025 prioriterade fågelarter.docx", "A 6082-2025")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 49988-2023</t>
+          <t>A 30862-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3039,10 +3039,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45215</v>
+        <v>46212</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3055,7 +3055,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="J24" t="n">
         <v>1</v>
@@ -3088,42 +3088,42 @@
         <v>1</v>
       </c>
       <c r="T24" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U24" t="n">
         <v>0</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 49988-2023 artfynd.xlsx", "A 49988-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 30862-2026 artfynd.xlsx", "A 30862-2026")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 49988-2023 karta.png", "A 49988-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 30862-2026 karta.png", "A 30862-2026")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 49988-2023 georefererad karta.tif", "A 49988-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 30862-2026 georefererad karta.tif", "A 30862-2026")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 49988-2023 FSC-klagomål.docx", "A 49988-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 30862-2026 FSC-klagomål.docx", "A 30862-2026")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 49988-2023 FSC-klagomål mail.docx", "A 49988-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 30862-2026 FSC-klagomål mail.docx", "A 30862-2026")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 49988-2023 tillsynsbegäran.docx", "A 49988-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 30862-2026 tillsynsbegäran.docx", "A 30862-2026")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 49988-2023 tillsynsbegäran mail.docx", "A 49988-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 30862-2026 tillsynsbegäran mail.docx", "A 30862-2026")</f>
         <v/>
       </c>
     </row>
@@ -3147,7 +3147,7 @@
         <v>44691</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
         <v>44691</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         <v>44836</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3366,7 +3366,7 @@
         <v>44760</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         <v>44760</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
         <v>44760</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3568,7 +3568,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 17455-2025</t>
+          <t>A 62221-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3582,10 +3582,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45757</v>
+        <v>45267</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3598,7 +3598,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2.1</v>
+        <v>1.3</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3641,7 +3641,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 62221-2023</t>
+          <t>A 4204-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3655,10 +3655,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45267</v>
+        <v>45324</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3671,7 +3671,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.3</v>
+        <v>4.4</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3714,7 +3714,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 21240-2023</t>
+          <t>A 30170-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3728,10 +3728,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45058</v>
+        <v>44757</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3744,7 +3744,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3787,7 +3787,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 29223-2024</t>
+          <t>A 51724-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3801,10 +3801,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45482</v>
+        <v>45222</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3817,7 +3817,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>5.6</v>
+        <v>3.1</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3860,7 +3860,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 10655-2022</t>
+          <t>A 17922-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3874,10 +3874,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44624</v>
+        <v>45758</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3890,7 +3890,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>13.3</v>
+        <v>0.8</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3933,7 +3933,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 39714-2024</t>
+          <t>A 13880-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3947,10 +3947,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45552</v>
+        <v>45391</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3963,7 +3963,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.2</v>
+        <v>2.4</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4006,7 +4006,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 19531-2023</t>
+          <t>A 24461-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4020,10 +4020,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45050</v>
+        <v>45082</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4079,7 +4079,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 5705-2025</t>
+          <t>A 10679-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4089,14 +4089,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45694</v>
+        <v>45721</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4109,7 +4109,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.2</v>
+        <v>4.4</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4152,7 +4152,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 61417-2022</t>
+          <t>A 11237-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4166,10 +4166,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44916</v>
+        <v>45726</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4182,7 +4182,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4225,7 +4225,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 34366-2022</t>
+          <t>A 1995-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4239,10 +4239,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44792</v>
+        <v>45308</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4298,7 +4298,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 7505-2024</t>
+          <t>A 143-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4312,10 +4312,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45347</v>
+        <v>44928</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4328,7 +4328,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4371,7 +4371,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 32272-2023</t>
+          <t>A 10677-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4385,10 +4385,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45120</v>
+        <v>45721</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4401,7 +4401,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>4.9</v>
+        <v>7.4</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4444,7 +4444,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 4673-2026</t>
+          <t>A 74285-2021</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4458,10 +4458,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46048</v>
+        <v>44558</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4474,7 +4474,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>8.199999999999999</v>
+        <v>1.1</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4517,7 +4517,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 32847-2023</t>
+          <t>A 45990-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4531,10 +4531,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45124</v>
+        <v>44846</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4547,7 +4547,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>4.7</v>
+        <v>3.3</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4607,7 +4607,7 @@
         <v>45897</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4663,7 +4663,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 6946-2026</t>
+          <t>A 63319-2021</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4673,14 +4673,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46057</v>
+        <v>44508</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2.2</v>
+        <v>1.6</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4736,7 +4736,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 8334-2023</t>
+          <t>A 61417-2022</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4750,10 +4750,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44975</v>
+        <v>44916</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4766,7 +4766,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.8</v>
+        <v>3.6</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4809,7 +4809,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 45124-2025</t>
+          <t>A 32272-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4823,10 +4823,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45919</v>
+        <v>45120</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>3.7</v>
+        <v>4.9</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4882,7 +4882,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 47564-2025</t>
+          <t>A 32847-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4896,10 +4896,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45931</v>
+        <v>45124</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4912,7 +4912,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2</v>
+        <v>4.7</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4955,7 +4955,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 37443-2025</t>
+          <t>A 45124-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4969,10 +4969,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45877</v>
+        <v>45919</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4984,13 +4984,8 @@
           <t>KUNGÄLV</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I50" t="n">
-        <v>0.7</v>
+        <v>3.7</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5033,7 +5028,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 13990-2026</t>
+          <t>A 7505-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5047,10 +5042,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46098</v>
+        <v>45347</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5063,7 +5058,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2.6</v>
+        <v>1.8</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5106,7 +5101,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 34244-2025</t>
+          <t>A 43520-2022</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5120,10 +5115,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45844</v>
+        <v>44837</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5136,7 +5131,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2.9</v>
+        <v>1.5</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5179,7 +5174,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 25624-2025</t>
+          <t>A 47564-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5193,10 +5188,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45803</v>
+        <v>45931</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5209,7 +5204,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5252,7 +5247,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 52932-2025</t>
+          <t>A 29223-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5266,10 +5261,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45957</v>
+        <v>45482</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5282,7 +5277,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>3.4</v>
+        <v>5.6</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5325,7 +5320,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 41442-2025</t>
+          <t>A 52932-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5339,10 +5334,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45869</v>
+        <v>45957</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5355,7 +5350,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.8</v>
+        <v>3.4</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5398,7 +5393,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 17922-2025</t>
+          <t>A 10655-2022</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5412,10 +5407,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45758</v>
+        <v>44624</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5428,7 +5423,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.8</v>
+        <v>13.3</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5471,7 +5466,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 49985-2023</t>
+          <t>A 17455-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5485,10 +5480,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45215</v>
+        <v>45757</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5501,7 +5496,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>8.199999999999999</v>
+        <v>2.1</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5544,7 +5539,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 50071-2023</t>
+          <t>A 34244-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5558,10 +5553,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45215</v>
+        <v>45844</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5574,7 +5569,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>4</v>
+        <v>2.9</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5617,7 +5612,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 49981-2023</t>
+          <t>A 25624-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5631,10 +5626,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45215</v>
+        <v>45803</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5647,7 +5642,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5690,7 +5685,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 22731-2026</t>
+          <t>A 41442-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5704,10 +5699,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46157</v>
+        <v>45869</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5763,7 +5758,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 32391-2025</t>
+          <t>A 8334-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5777,10 +5772,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45837</v>
+        <v>44975</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5793,7 +5788,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5836,7 +5831,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 23607-2026</t>
+          <t>A 19531-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5850,10 +5845,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46163</v>
+        <v>45050</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5866,7 +5861,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>5.3</v>
+        <v>1.9</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5909,7 +5904,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 25135-2025</t>
+          <t>A 5705-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5919,14 +5914,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45798</v>
+        <v>45694</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5939,7 +5934,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5982,7 +5977,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 56782-2022</t>
+          <t>A 62979-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5992,14 +5987,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44894</v>
+        <v>45271</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6012,7 +6007,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6055,7 +6050,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 1995-2024</t>
+          <t>A 22731-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6069,10 +6064,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45308</v>
+        <v>46157</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6085,7 +6080,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6128,7 +6123,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 30170-2022</t>
+          <t>A 32391-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6142,10 +6137,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44757</v>
+        <v>45837</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6158,7 +6153,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>3.1</v>
+        <v>2.1</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6201,7 +6196,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 10810-2023</t>
+          <t>A 4262-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6215,10 +6210,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44989</v>
+        <v>45324</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6231,7 +6226,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.4</v>
+        <v>14</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6274,7 +6269,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 4204-2024</t>
+          <t>A 16538-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6288,10 +6283,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45324</v>
+        <v>45751</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6304,7 +6299,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>4.4</v>
+        <v>0.8</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6347,7 +6342,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 62128-2021</t>
+          <t>A 23607-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6361,10 +6356,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44502</v>
+        <v>46163</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6377,7 +6372,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.8</v>
+        <v>5.3</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6420,7 +6415,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 62979-2023</t>
+          <t>A 25135-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6430,14 +6425,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45271</v>
+        <v>45798</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6450,7 +6445,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6493,7 +6488,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 29952-2026</t>
+          <t>A 29801-2022</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6507,10 +6502,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46205</v>
+        <v>44755</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6523,7 +6518,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>2</v>
+        <v>4.8</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6566,7 +6561,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 44176-2023</t>
+          <t>A 49981-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6580,10 +6575,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45188</v>
+        <v>45215</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6596,7 +6591,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>7.1</v>
+        <v>2.5</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6639,7 +6634,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 30738-2026</t>
+          <t>A 661-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6653,10 +6648,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46211</v>
+        <v>45664</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6669,7 +6664,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6712,7 +6707,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 30859-2026</t>
+          <t>A 71835-2021</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6726,10 +6721,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46212</v>
+        <v>44543</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6742,7 +6737,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.5</v>
+        <v>7.5</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6785,7 +6780,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 26812-2024</t>
+          <t>A 34366-2022</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6799,10 +6794,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45470</v>
+        <v>44792</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6815,7 +6810,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6858,7 +6853,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 29801-2022</t>
+          <t>A 4673-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6872,10 +6867,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44755</v>
+        <v>46048</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6888,7 +6883,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>4.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6931,7 +6926,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 18852-2024</t>
+          <t>A 6946-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6941,14 +6936,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45426</v>
+        <v>46057</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6961,7 +6956,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7004,7 +6999,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 43520-2022</t>
+          <t>A 37443-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7018,10 +7013,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44837</v>
+        <v>45877</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7033,8 +7028,13 @@
           <t>KUNGÄLV</t>
         </is>
       </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I78" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7077,7 +7077,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 16538-2025</t>
+          <t>A 56782-2022</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7091,10 +7091,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45751</v>
+        <v>44894</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7107,7 +7107,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7150,7 +7150,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 45990-2022</t>
+          <t>A 29952-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7164,10 +7164,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44846</v>
+        <v>46205</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7180,7 +7180,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>3.3</v>
+        <v>2</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7223,7 +7223,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 143-2023</t>
+          <t>A 13990-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7237,10 +7237,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44928</v>
+        <v>46098</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7253,7 +7253,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0.5</v>
+        <v>2.6</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7296,7 +7296,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 18851-2024</t>
+          <t>A 26812-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7310,10 +7310,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45426</v>
+        <v>45470</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7326,7 +7326,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>2.7</v>
+        <v>1.7</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7369,7 +7369,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 38262-2026</t>
+          <t>A 30738-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7383,10 +7383,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46281</v>
+        <v>46211</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7442,7 +7442,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 71835-2021</t>
+          <t>A 30859-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7456,10 +7456,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44543</v>
+        <v>46212</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7472,7 +7472,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>7.5</v>
+        <v>0.5</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7515,7 +7515,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 51724-2023</t>
+          <t>A 49985-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7529,10 +7529,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45222</v>
+        <v>45215</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7545,7 +7545,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>3.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7588,7 +7588,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 661-2025</t>
+          <t>A 10810-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7602,10 +7602,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45664</v>
+        <v>44989</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7618,7 +7618,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>3.1</v>
+        <v>0.4</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7661,7 +7661,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 24461-2023</t>
+          <t>A 62128-2021</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7675,10 +7675,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45082</v>
+        <v>44502</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7691,7 +7691,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7734,7 +7734,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 13880-2024</t>
+          <t>A 50071-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7748,10 +7748,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45391</v>
+        <v>45215</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7764,7 +7764,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>2.4</v>
+        <v>4</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7807,7 +7807,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 34386-2026</t>
+          <t>A 21240-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7821,10 +7821,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46254</v>
+        <v>45058</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7837,7 +7837,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>0.7</v>
+        <v>2.3</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7880,7 +7880,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 34396-2026</t>
+          <t>A 18851-2024</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7894,10 +7894,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46254</v>
+        <v>45426</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7910,7 +7910,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0.8</v>
+        <v>2.7</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7953,7 +7953,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 34392-2026</t>
+          <t>A 21389-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7967,10 +7967,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46254</v>
+        <v>45063</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7983,7 +7983,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.4</v>
+        <v>3.4</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8026,7 +8026,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 34387-2026</t>
+          <t>A 44176-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>46254</v>
+        <v>45188</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8056,7 +8056,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0.3</v>
+        <v>7.1</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8116,7 +8116,7 @@
         <v>45453</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8172,7 +8172,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 21389-2023</t>
+          <t>A 39714-2024</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8186,10 +8186,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45063</v>
+        <v>45552</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8202,7 +8202,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>3.4</v>
+        <v>1.2</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8245,7 +8245,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 4262-2024</t>
+          <t>A 18852-2024</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8259,10 +8259,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45324</v>
+        <v>45426</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8275,7 +8275,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>14</v>
+        <v>2.7</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8318,7 +8318,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 63319-2021</t>
+          <t>A 38262-2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8332,10 +8332,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>44508</v>
+        <v>46281</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8348,7 +8348,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1.6</v>
+        <v>2.8</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8391,7 +8391,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 10677-2025</t>
+          <t>A 34387-2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8405,10 +8405,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45721</v>
+        <v>46254</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8421,7 +8421,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>7.4</v>
+        <v>0.3</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8464,7 +8464,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 10679-2025</t>
+          <t>A 34386-2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8478,10 +8478,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45721</v>
+        <v>46254</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8494,7 +8494,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>4.4</v>
+        <v>0.7</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8537,7 +8537,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 11237-2025</t>
+          <t>A 34392-2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8551,10 +8551,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45726</v>
+        <v>46254</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8567,7 +8567,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>4.2</v>
+        <v>0.4</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8610,7 +8610,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 74285-2021</t>
+          <t>A 34396-2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8624,139 +8624,212 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>44558</v>
+        <v>46254</v>
       </c>
       <c r="E100" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>KUNGÄLV</t>
+        </is>
+      </c>
+      <c r="I100" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J100" t="n">
+        <v>0</v>
+      </c>
+      <c r="K100" t="n">
+        <v>0</v>
+      </c>
+      <c r="L100" t="n">
+        <v>0</v>
+      </c>
+      <c r="M100" t="n">
+        <v>0</v>
+      </c>
+      <c r="N100" t="n">
+        <v>0</v>
+      </c>
+      <c r="O100" t="n">
+        <v>0</v>
+      </c>
+      <c r="P100" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q100" t="n">
+        <v>0</v>
+      </c>
+      <c r="R100" t="n">
+        <v>0</v>
+      </c>
+      <c r="S100" t="n">
+        <v>0</v>
+      </c>
+      <c r="T100" t="n">
+        <v>0</v>
+      </c>
+      <c r="U100" t="n">
+        <v>0</v>
+      </c>
+      <c r="V100" s="2" t="inlineStr"/>
+    </row>
+    <row r="101" ht="15" customHeight="1">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>A 41656-2026</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D101" s="1" t="n">
         <v>46302</v>
       </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>KUNGÄLV</t>
-        </is>
-      </c>
-      <c r="I100" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="J100" t="n">
-        <v>0</v>
-      </c>
-      <c r="K100" t="n">
-        <v>0</v>
-      </c>
-      <c r="L100" t="n">
-        <v>0</v>
-      </c>
-      <c r="M100" t="n">
-        <v>0</v>
-      </c>
-      <c r="N100" t="n">
-        <v>0</v>
-      </c>
-      <c r="O100" t="n">
-        <v>0</v>
-      </c>
-      <c r="P100" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q100" t="n">
-        <v>0</v>
-      </c>
-      <c r="R100" t="n">
-        <v>0</v>
-      </c>
-      <c r="S100" t="n">
-        <v>0</v>
-      </c>
-      <c r="T100" t="n">
-        <v>0</v>
-      </c>
-      <c r="U100" t="n">
-        <v>0</v>
-      </c>
-      <c r="V100" s="2" t="inlineStr"/>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
+      <c r="E101" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>KUNGÄLV</t>
+        </is>
+      </c>
+      <c r="I101" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J101" t="n">
+        <v>0</v>
+      </c>
+      <c r="K101" t="n">
+        <v>0</v>
+      </c>
+      <c r="L101" t="n">
+        <v>0</v>
+      </c>
+      <c r="M101" t="n">
+        <v>0</v>
+      </c>
+      <c r="N101" t="n">
+        <v>0</v>
+      </c>
+      <c r="O101" t="n">
+        <v>0</v>
+      </c>
+      <c r="P101" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q101" t="n">
+        <v>0</v>
+      </c>
+      <c r="R101" t="n">
+        <v>0</v>
+      </c>
+      <c r="S101" t="n">
+        <v>0</v>
+      </c>
+      <c r="T101" t="n">
+        <v>0</v>
+      </c>
+      <c r="U101" t="n">
+        <v>0</v>
+      </c>
+      <c r="V101" s="2" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
         <is>
           <t>S 817-2024</t>
         </is>
       </c>
-      <c r="B101" t="inlineStr">
+      <c r="B102" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C101" t="inlineStr">
+      <c r="C102" t="inlineStr">
         <is>
           <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
-      <c r="D101" s="1" t="n">
+      <c r="D102" s="1" t="n">
         <v>45371</v>
       </c>
-      <c r="E101" s="1" t="n">
-        <v>46302</v>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>KUNGÄLV</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr">
+      <c r="E102" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>KUNGÄLV</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
         <is>
           <t>Övriga statliga verk och myndigheter</t>
         </is>
       </c>
-      <c r="I101" t="n">
+      <c r="I102" t="n">
         <v>2.4</v>
       </c>
-      <c r="J101" t="n">
-        <v>0</v>
-      </c>
-      <c r="K101" t="n">
-        <v>0</v>
-      </c>
-      <c r="L101" t="n">
-        <v>0</v>
-      </c>
-      <c r="M101" t="n">
-        <v>0</v>
-      </c>
-      <c r="N101" t="n">
-        <v>0</v>
-      </c>
-      <c r="O101" t="n">
-        <v>0</v>
-      </c>
-      <c r="P101" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q101" t="n">
-        <v>0</v>
-      </c>
-      <c r="R101" t="n">
-        <v>0</v>
-      </c>
-      <c r="S101" t="n">
-        <v>0</v>
-      </c>
-      <c r="T101" t="n">
-        <v>0</v>
-      </c>
-      <c r="U101" t="n">
-        <v>0</v>
-      </c>
-      <c r="V101" s="2" t="inlineStr"/>
+      <c r="J102" t="n">
+        <v>0</v>
+      </c>
+      <c r="K102" t="n">
+        <v>0</v>
+      </c>
+      <c r="L102" t="n">
+        <v>0</v>
+      </c>
+      <c r="M102" t="n">
+        <v>0</v>
+      </c>
+      <c r="N102" t="n">
+        <v>0</v>
+      </c>
+      <c r="O102" t="n">
+        <v>0</v>
+      </c>
+      <c r="P102" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q102" t="n">
+        <v>0</v>
+      </c>
+      <c r="R102" t="n">
+        <v>0</v>
+      </c>
+      <c r="S102" t="n">
+        <v>0</v>
+      </c>
+      <c r="T102" t="n">
+        <v>0</v>
+      </c>
+      <c r="U102" t="n">
+        <v>0</v>
+      </c>
+      <c r="V102" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt KUNGÄLV.xlsx
+++ b/Översikt KUNGÄLV.xlsx
@@ -601,7 +601,7 @@
         <v>45548</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>45868</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -851,7 +851,7 @@
         <v>45526</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -965,7 +965,7 @@
         <v>45919</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
         <v>45695</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 4263-2024</t>
+          <t>A 59985-2025</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1188,10 +1188,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45324</v>
+        <v>45993</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1204,16 +1204,16 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>2.6</v>
+        <v>5.3</v>
       </c>
       <c r="J7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -1228,7 +1228,7 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1237,12 +1237,124 @@
         <v>4</v>
       </c>
       <c r="T7" t="n">
+        <v>19</v>
+      </c>
+      <c r="U7" t="n">
+        <v>19</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Blåmossa
+Västlig hakmossa
+Spillkråka
+Äkta lopplummer</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 59985-2025 artfynd.xlsx", "A 59985-2025")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 59985-2025 karta.png", "A 59985-2025")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 59985-2025 georefererad karta.tif", "A 59985-2025")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 59985-2025 FSC-klagomål.docx", "A 59985-2025")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 59985-2025 FSC-klagomål mail.docx", "A 59985-2025")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 59985-2025 tillsynsbegäran.docx", "A 59985-2025")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 59985-2025 tillsynsbegäran mail.docx", "A 59985-2025")</f>
+        <v/>
+      </c>
+      <c r="AE7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 59985-2025 prioriterade fågelarter.docx", "A 59985-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 4263-2024</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>45324</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46304</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>KUNGÄLV</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J8" t="n">
+        <v>3</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>4</v>
+      </c>
+      <c r="T8" t="n">
         <v>6</v>
       </c>
-      <c r="U7" t="n">
+      <c r="U8" t="n">
         <v>6</v>
       </c>
-      <c r="V7" s="2" t="inlineStr">
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>Mindre hackspett
 Klippfrullania
@@ -1250,148 +1362,36 @@
 Spillkråka</t>
         </is>
       </c>
-      <c r="W7">
+      <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 4263-2024 artfynd.xlsx", "A 4263-2024")</f>
         <v/>
       </c>
-      <c r="X7">
+      <c r="X8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 4263-2024 karta.png", "A 4263-2024")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 4263-2024 georefererad karta.tif", "A 4263-2024")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 4263-2024 FSC-klagomål.docx", "A 4263-2024")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 4263-2024 FSC-klagomål mail.docx", "A 4263-2024")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 4263-2024 tillsynsbegäran.docx", "A 4263-2024")</f>
         <v/>
       </c>
-      <c r="AD7">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 4263-2024 tillsynsbegäran mail.docx", "A 4263-2024")</f>
         <v/>
       </c>
-      <c r="AE7">
+      <c r="AE8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 4263-2024 prioriterade fågelarter.docx", "A 4263-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A 59985-2025</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>45993</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46303</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>KUNGÄLV</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="J8" t="n">
-        <v>2</v>
-      </c>
-      <c r="K8" t="n">
-        <v>2</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>4</v>
-      </c>
-      <c r="T8" t="n">
-        <v>19</v>
-      </c>
-      <c r="U8" t="n">
-        <v>19</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>Blåmossa
-Västlig hakmossa
-Spillkråka
-Äkta lopplummer</t>
-        </is>
-      </c>
-      <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 59985-2025 artfynd.xlsx", "A 59985-2025")</f>
-        <v/>
-      </c>
-      <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 59985-2025 karta.png", "A 59985-2025")</f>
-        <v/>
-      </c>
-      <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 59985-2025 georefererad karta.tif", "A 59985-2025")</f>
-        <v/>
-      </c>
-      <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 59985-2025 FSC-klagomål.docx", "A 59985-2025")</f>
-        <v/>
-      </c>
-      <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 59985-2025 FSC-klagomål mail.docx", "A 59985-2025")</f>
-        <v/>
-      </c>
-      <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 59985-2025 tillsynsbegäran.docx", "A 59985-2025")</f>
-        <v/>
-      </c>
-      <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 59985-2025 tillsynsbegäran mail.docx", "A 59985-2025")</f>
-        <v/>
-      </c>
-      <c r="AE8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 59985-2025 prioriterade fågelarter.docx", "A 59985-2025")</f>
         <v/>
       </c>
     </row>
@@ -1415,7 +1415,7 @@
         <v>45985</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>46199</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>45355</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>46212</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         <v>45957</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 5631-2024</t>
+          <t>A 56394-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1963,14 +1963,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45334</v>
+        <v>45974</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1986,10 +1986,10 @@
         <v>1.3</v>
       </c>
       <c r="J14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -2019,552 +2019,552 @@
         <v>2</v>
       </c>
       <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Kambräken
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 56394-2025 artfynd.xlsx", "A 56394-2025")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 56394-2025 karta.png", "A 56394-2025")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 56394-2025 georefererad karta.tif", "A 56394-2025")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 56394-2025 FSC-klagomål.docx", "A 56394-2025")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 56394-2025 FSC-klagomål mail.docx", "A 56394-2025")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 56394-2025 tillsynsbegäran.docx", "A 56394-2025")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 56394-2025 tillsynsbegäran mail.docx", "A 56394-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 57116-2025</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>45979</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46304</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>KUNGÄLV</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J15" t="n">
         <v>1</v>
       </c>
-      <c r="V14" s="2" t="inlineStr">
+      <c r="K15" t="n">
+        <v>1</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>3</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Västlig hakmossa
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 57116-2025 artfynd.xlsx", "A 57116-2025")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 57116-2025 karta.png", "A 57116-2025")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 57116-2025 georefererad karta.tif", "A 57116-2025")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 57116-2025 FSC-klagomål.docx", "A 57116-2025")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 57116-2025 FSC-klagomål mail.docx", "A 57116-2025")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 57116-2025 tillsynsbegäran.docx", "A 57116-2025")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 57116-2025 tillsynsbegäran mail.docx", "A 57116-2025")</f>
+        <v/>
+      </c>
+      <c r="AE15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 57116-2025 prioriterade fågelarter.docx", "A 57116-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 30860-2026</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>46212</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46304</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>KUNGÄLV</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Grönsångare
+Västlig hakmossa</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 30860-2026 artfynd.xlsx", "A 30860-2026")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 30860-2026 karta.png", "A 30860-2026")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 30860-2026 georefererad karta.tif", "A 30860-2026")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 30860-2026 FSC-klagomål.docx", "A 30860-2026")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 30860-2026 FSC-klagomål mail.docx", "A 30860-2026")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 30860-2026 tillsynsbegäran.docx", "A 30860-2026")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 30860-2026 tillsynsbegäran mail.docx", "A 30860-2026")</f>
+        <v/>
+      </c>
+      <c r="AE16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 30860-2026 prioriterade fågelarter.docx", "A 30860-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 5631-2024</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>45334</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46304</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>KUNGÄLV</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>Vanlig groda
 Fläcknycklar</t>
         </is>
       </c>
-      <c r="W14">
+      <c r="W17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 5631-2024 artfynd.xlsx", "A 5631-2024")</f>
         <v/>
       </c>
-      <c r="X14">
+      <c r="X17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 5631-2024 karta.png", "A 5631-2024")</f>
         <v/>
       </c>
-      <c r="Y14">
+      <c r="Y17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 5631-2024 georefererad karta.tif", "A 5631-2024")</f>
         <v/>
       </c>
-      <c r="AA14">
+      <c r="AA17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 5631-2024 FSC-klagomål.docx", "A 5631-2024")</f>
         <v/>
       </c>
-      <c r="AB14">
+      <c r="AB17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 5631-2024 FSC-klagomål mail.docx", "A 5631-2024")</f>
         <v/>
       </c>
-      <c r="AC14">
+      <c r="AC17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 5631-2024 tillsynsbegäran.docx", "A 5631-2024")</f>
         <v/>
       </c>
-      <c r="AD14">
+      <c r="AD17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 5631-2024 tillsynsbegäran mail.docx", "A 5631-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
         <is>
           <t>A 5637-2024</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
         <v>45334</v>
       </c>
-      <c r="E15" s="1" t="n">
-        <v>46303</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>KUNGÄLV</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
+      <c r="E18" s="1" t="n">
+        <v>46304</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>KUNGÄLV</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
         <v>1.8</v>
       </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
         <v>2</v>
       </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
         <v>2</v>
       </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
         <v>2</v>
       </c>
-      <c r="T15" t="n">
+      <c r="T18" t="n">
         <v>2</v>
       </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>Klofibbla
 Åkerrödtoppa</t>
         </is>
       </c>
-      <c r="W15">
+      <c r="W18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 5637-2024 artfynd.xlsx", "A 5637-2024")</f>
         <v/>
       </c>
-      <c r="X15">
+      <c r="X18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 5637-2024 karta.png", "A 5637-2024")</f>
         <v/>
       </c>
-      <c r="Y15">
+      <c r="Y18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 5637-2024 georefererad karta.tif", "A 5637-2024")</f>
         <v/>
       </c>
-      <c r="AA15">
+      <c r="AA18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 5637-2024 FSC-klagomål.docx", "A 5637-2024")</f>
         <v/>
       </c>
-      <c r="AB15">
+      <c r="AB18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 5637-2024 FSC-klagomål mail.docx", "A 5637-2024")</f>
         <v/>
       </c>
-      <c r="AC15">
+      <c r="AC18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 5637-2024 tillsynsbegäran.docx", "A 5637-2024")</f>
         <v/>
       </c>
-      <c r="AD15">
+      <c r="AD18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 5637-2024 tillsynsbegäran mail.docx", "A 5637-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 56394-2025</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>45974</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46303</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>KUNGÄLV</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="J16" t="n">
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>A 53007-2025</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>45957</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>46304</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>KUNGÄLV</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J19" t="n">
         <v>1</v>
       </c>
-      <c r="K16" t="n">
+      <c r="K19" t="n">
         <v>1</v>
       </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
         <v>2</v>
       </c>
-      <c r="T16" t="n">
-        <v>2</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>Kambräken
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 56394-2025 artfynd.xlsx", "A 56394-2025")</f>
-        <v/>
-      </c>
-      <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 56394-2025 karta.png", "A 56394-2025")</f>
-        <v/>
-      </c>
-      <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 56394-2025 georefererad karta.tif", "A 56394-2025")</f>
-        <v/>
-      </c>
-      <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 56394-2025 FSC-klagomål.docx", "A 56394-2025")</f>
-        <v/>
-      </c>
-      <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 56394-2025 FSC-klagomål mail.docx", "A 56394-2025")</f>
-        <v/>
-      </c>
-      <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 56394-2025 tillsynsbegäran.docx", "A 56394-2025")</f>
-        <v/>
-      </c>
-      <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 56394-2025 tillsynsbegäran mail.docx", "A 56394-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 57116-2025</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>45979</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46303</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>KUNGÄLV</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="J17" t="n">
-        <v>1</v>
-      </c>
-      <c r="K17" t="n">
-        <v>1</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2</v>
-      </c>
-      <c r="T17" t="n">
-        <v>3</v>
-      </c>
-      <c r="U17" t="n">
-        <v>3</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
+      <c r="T19" t="n">
+        <v>5</v>
+      </c>
+      <c r="U19" t="n">
+        <v>5</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>Västlig hakmossa
 Spillkråka</t>
         </is>
       </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 57116-2025 artfynd.xlsx", "A 57116-2025")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 57116-2025 karta.png", "A 57116-2025")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 57116-2025 georefererad karta.tif", "A 57116-2025")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 57116-2025 FSC-klagomål.docx", "A 57116-2025")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 57116-2025 FSC-klagomål mail.docx", "A 57116-2025")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 57116-2025 tillsynsbegäran.docx", "A 57116-2025")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 57116-2025 tillsynsbegäran mail.docx", "A 57116-2025")</f>
-        <v/>
-      </c>
-      <c r="AE17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 57116-2025 prioriterade fågelarter.docx", "A 57116-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 30860-2026</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>46212</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46303</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>KUNGÄLV</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="J18" t="n">
-        <v>1</v>
-      </c>
-      <c r="K18" t="n">
-        <v>1</v>
-      </c>
-      <c r="L18" t="n">
-        <v>1</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>1</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>Grönsångare
-Västlig hakmossa</t>
-        </is>
-      </c>
-      <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 30860-2026 artfynd.xlsx", "A 30860-2026")</f>
-        <v/>
-      </c>
-      <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 30860-2026 karta.png", "A 30860-2026")</f>
-        <v/>
-      </c>
-      <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 30860-2026 georefererad karta.tif", "A 30860-2026")</f>
-        <v/>
-      </c>
-      <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 30860-2026 FSC-klagomål.docx", "A 30860-2026")</f>
-        <v/>
-      </c>
-      <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 30860-2026 FSC-klagomål mail.docx", "A 30860-2026")</f>
-        <v/>
-      </c>
-      <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 30860-2026 tillsynsbegäran.docx", "A 30860-2026")</f>
-        <v/>
-      </c>
-      <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 30860-2026 tillsynsbegäran mail.docx", "A 30860-2026")</f>
-        <v/>
-      </c>
-      <c r="AE18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 30860-2026 prioriterade fågelarter.docx", "A 30860-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>A 53007-2025</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>45957</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>46303</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>KUNGÄLV</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="J19" t="n">
-        <v>1</v>
-      </c>
-      <c r="K19" t="n">
-        <v>1</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2</v>
-      </c>
-      <c r="T19" t="n">
-        <v>5</v>
-      </c>
-      <c r="U19" t="n">
-        <v>5</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>Västlig hakmossa
-Spillkråka</t>
-        </is>
-      </c>
       <c r="W19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 53007-2025 artfynd.xlsx", "A 53007-2025")</f>
         <v/>
@@ -2618,7 +2618,7 @@
         <v>44838</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2706,7 +2706,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 49988-2023</t>
+          <t>A 23704-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2720,10 +2720,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45215</v>
+        <v>45454</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>2.3</v>
+        <v>4.9</v>
       </c>
       <c r="J21" t="n">
         <v>1</v>
@@ -2748,7 +2748,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -2760,58 +2760,58 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
       </c>
       <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
         <v>1</v>
       </c>
-      <c r="U21" t="n">
-        <v>0</v>
-      </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Hedjohannesört</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 49988-2023 artfynd.xlsx", "A 49988-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 23704-2024 artfynd.xlsx", "A 23704-2024")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 49988-2023 karta.png", "A 49988-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 23704-2024 karta.png", "A 23704-2024")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 49988-2023 georefererad karta.tif", "A 49988-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 23704-2024 georefererad karta.tif", "A 23704-2024")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 49988-2023 FSC-klagomål.docx", "A 49988-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 23704-2024 FSC-klagomål.docx", "A 23704-2024")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 49988-2023 FSC-klagomål mail.docx", "A 49988-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 23704-2024 FSC-klagomål mail.docx", "A 23704-2024")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 49988-2023 tillsynsbegäran.docx", "A 49988-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 23704-2024 tillsynsbegäran.docx", "A 23704-2024")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 49988-2023 tillsynsbegäran mail.docx", "A 49988-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 23704-2024 tillsynsbegäran mail.docx", "A 23704-2024")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 23704-2024</t>
+          <t>A 49988-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2825,10 +2825,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45454</v>
+        <v>45215</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2841,7 +2841,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>4.9</v>
+        <v>2.3</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
@@ -2853,7 +2853,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
@@ -2865,58 +2865,58 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
       </c>
       <c r="T22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Hedjohannesört</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 23704-2024 artfynd.xlsx", "A 23704-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 49988-2023 artfynd.xlsx", "A 49988-2023")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 23704-2024 karta.png", "A 23704-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 49988-2023 karta.png", "A 49988-2023")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 23704-2024 georefererad karta.tif", "A 23704-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 49988-2023 georefererad karta.tif", "A 49988-2023")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 23704-2024 FSC-klagomål.docx", "A 23704-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 49988-2023 FSC-klagomål.docx", "A 49988-2023")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 23704-2024 FSC-klagomål mail.docx", "A 23704-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 49988-2023 FSC-klagomål mail.docx", "A 49988-2023")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 23704-2024 tillsynsbegäran.docx", "A 23704-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 49988-2023 tillsynsbegäran.docx", "A 49988-2023")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 23704-2024 tillsynsbegäran mail.docx", "A 23704-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 49988-2023 tillsynsbegäran mail.docx", "A 49988-2023")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 6082-2025</t>
+          <t>A 30862-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2930,10 +2930,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45697</v>
+        <v>46212</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2946,7 +2946,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>2.8</v>
+        <v>1.7</v>
       </c>
       <c r="J23" t="n">
         <v>1</v>
@@ -2979,53 +2979,49 @@
         <v>1</v>
       </c>
       <c r="T23" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 6082-2025 artfynd.xlsx", "A 6082-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 30862-2026 artfynd.xlsx", "A 30862-2026")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 6082-2025 karta.png", "A 6082-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 30862-2026 karta.png", "A 30862-2026")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 6082-2025 georefererad karta.tif", "A 6082-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 30862-2026 georefererad karta.tif", "A 30862-2026")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 6082-2025 FSC-klagomål.docx", "A 6082-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 30862-2026 FSC-klagomål.docx", "A 30862-2026")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 6082-2025 FSC-klagomål mail.docx", "A 6082-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 30862-2026 FSC-klagomål mail.docx", "A 30862-2026")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 6082-2025 tillsynsbegäran.docx", "A 6082-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 30862-2026 tillsynsbegäran.docx", "A 30862-2026")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 6082-2025 tillsynsbegäran mail.docx", "A 6082-2025")</f>
-        <v/>
-      </c>
-      <c r="AE23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 6082-2025 prioriterade fågelarter.docx", "A 6082-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 30862-2026 tillsynsbegäran mail.docx", "A 30862-2026")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 30862-2026</t>
+          <t>A 6082-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3039,10 +3035,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46212</v>
+        <v>45697</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3055,7 +3051,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.7</v>
+        <v>2.8</v>
       </c>
       <c r="J24" t="n">
         <v>1</v>
@@ -3088,42 +3084,46 @@
         <v>1</v>
       </c>
       <c r="T24" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 30862-2026 artfynd.xlsx", "A 30862-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 6082-2025 artfynd.xlsx", "A 6082-2025")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 30862-2026 karta.png", "A 30862-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 6082-2025 karta.png", "A 6082-2025")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 30862-2026 georefererad karta.tif", "A 30862-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 6082-2025 georefererad karta.tif", "A 6082-2025")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 30862-2026 FSC-klagomål.docx", "A 30862-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 6082-2025 FSC-klagomål.docx", "A 6082-2025")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 30862-2026 FSC-klagomål mail.docx", "A 30862-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 6082-2025 FSC-klagomål mail.docx", "A 6082-2025")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 30862-2026 tillsynsbegäran.docx", "A 30862-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 6082-2025 tillsynsbegäran.docx", "A 6082-2025")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 30862-2026 tillsynsbegäran mail.docx", "A 30862-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 6082-2025 tillsynsbegäran mail.docx", "A 6082-2025")</f>
+        <v/>
+      </c>
+      <c r="AE24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 6082-2025 prioriterade fågelarter.docx", "A 6082-2025")</f>
         <v/>
       </c>
     </row>
@@ -3147,7 +3147,7 @@
         <v>44691</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
         <v>44691</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         <v>44836</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3366,7 +3366,7 @@
         <v>44760</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         <v>44760</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
         <v>44760</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3568,7 +3568,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 62221-2023</t>
+          <t>A 17455-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3582,10 +3582,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45267</v>
+        <v>45757</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3598,7 +3598,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.3</v>
+        <v>2.1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3641,7 +3641,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 4204-2024</t>
+          <t>A 62221-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3655,10 +3655,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45324</v>
+        <v>45267</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3671,7 +3671,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>4.4</v>
+        <v>1.3</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3714,7 +3714,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 30170-2022</t>
+          <t>A 21240-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3728,10 +3728,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44757</v>
+        <v>45058</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3744,7 +3744,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>3.1</v>
+        <v>2.3</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3787,7 +3787,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 51724-2023</t>
+          <t>A 29223-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3801,10 +3801,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45222</v>
+        <v>45482</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3817,7 +3817,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>3.1</v>
+        <v>5.6</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3860,7 +3860,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 17922-2025</t>
+          <t>A 10655-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3874,10 +3874,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45758</v>
+        <v>44624</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3890,7 +3890,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.8</v>
+        <v>13.3</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3933,7 +3933,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 13880-2024</t>
+          <t>A 39714-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3947,10 +3947,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45391</v>
+        <v>45552</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3963,7 +3963,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2.4</v>
+        <v>1.2</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4006,7 +4006,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 24461-2023</t>
+          <t>A 19531-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4020,10 +4020,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45082</v>
+        <v>45050</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4079,7 +4079,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 10679-2025</t>
+          <t>A 5705-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4089,14 +4089,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45721</v>
+        <v>45694</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4109,7 +4109,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>4.4</v>
+        <v>1.2</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4152,7 +4152,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 11237-2025</t>
+          <t>A 7505-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4166,10 +4166,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45726</v>
+        <v>45347</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4182,7 +4182,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>4.2</v>
+        <v>1.8</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4225,7 +4225,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 1995-2024</t>
+          <t>A 8334-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4239,10 +4239,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45308</v>
+        <v>44975</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4255,7 +4255,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4298,7 +4298,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 143-2023</t>
+          <t>A 34244-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4312,10 +4312,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44928</v>
+        <v>45844</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4328,7 +4328,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.5</v>
+        <v>2.9</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4371,7 +4371,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 10677-2025</t>
+          <t>A 25624-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4385,10 +4385,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45721</v>
+        <v>45803</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4401,7 +4401,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>7.4</v>
+        <v>5</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4444,7 +4444,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 74285-2021</t>
+          <t>A 37443-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4458,10 +4458,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44558</v>
+        <v>45877</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4473,8 +4473,13 @@
           <t>KUNGÄLV</t>
         </is>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I43" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4517,7 +4522,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 45990-2022</t>
+          <t>A 41442-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4531,10 +4536,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44846</v>
+        <v>45869</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4547,7 +4552,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>3.3</v>
+        <v>1.8</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4607,7 +4612,7 @@
         <v>45897</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4663,7 +4668,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 63319-2021</t>
+          <t>A 17922-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4677,10 +4682,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44508</v>
+        <v>45758</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4693,7 +4698,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4736,7 +4741,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 61417-2022</t>
+          <t>A 13990-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4750,10 +4755,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44916</v>
+        <v>46098</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4766,7 +4771,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>3.6</v>
+        <v>2.6</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4809,7 +4814,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 32272-2023</t>
+          <t>A 45124-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4823,10 +4828,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45120</v>
+        <v>45919</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4839,7 +4844,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>4.9</v>
+        <v>3.7</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4882,7 +4887,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 32847-2023</t>
+          <t>A 47564-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4896,10 +4901,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45124</v>
+        <v>45931</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4912,7 +4917,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>4.7</v>
+        <v>2</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4955,7 +4960,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 45124-2025</t>
+          <t>A 49981-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4969,10 +4974,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45919</v>
+        <v>45215</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4985,7 +4990,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>3.7</v>
+        <v>2.5</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5028,7 +5033,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 7505-2024</t>
+          <t>A 56782-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5042,10 +5047,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45347</v>
+        <v>44894</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5058,7 +5063,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5101,7 +5106,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 43520-2022</t>
+          <t>A 1995-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5115,10 +5120,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44837</v>
+        <v>45308</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5131,7 +5136,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5174,7 +5179,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 47564-2025</t>
+          <t>A 30170-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5188,10 +5193,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45931</v>
+        <v>44757</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5204,7 +5209,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2</v>
+        <v>3.1</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5247,7 +5252,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 29223-2024</t>
+          <t>A 52932-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5261,10 +5266,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45482</v>
+        <v>45957</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5277,7 +5282,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>5.6</v>
+        <v>3.4</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5320,7 +5325,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 52932-2025</t>
+          <t>A 10810-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5334,10 +5339,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45957</v>
+        <v>44989</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5350,7 +5355,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>3.4</v>
+        <v>0.4</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5393,7 +5398,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 10655-2022</t>
+          <t>A 4204-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5407,10 +5412,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44624</v>
+        <v>45324</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5423,7 +5428,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>13.3</v>
+        <v>4.4</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5466,7 +5471,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 17455-2025</t>
+          <t>A 62128-2021</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5480,10 +5485,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45757</v>
+        <v>44502</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5496,7 +5501,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5539,7 +5544,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 34244-2025</t>
+          <t>A 62979-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5549,14 +5554,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45844</v>
+        <v>45271</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5569,7 +5574,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>2.9</v>
+        <v>0.8</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5612,7 +5617,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 25624-2025</t>
+          <t>A 49985-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5626,10 +5631,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45803</v>
+        <v>45215</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5642,7 +5647,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5685,7 +5690,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 41442-2025</t>
+          <t>A 50071-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5699,10 +5704,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45869</v>
+        <v>45215</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5715,7 +5720,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.8</v>
+        <v>4</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5758,7 +5763,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 8334-2023</t>
+          <t>A 44176-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5772,10 +5777,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44975</v>
+        <v>45188</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5788,7 +5793,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.8</v>
+        <v>7.1</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5831,7 +5836,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 19531-2023</t>
+          <t>A 26812-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5845,10 +5850,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45050</v>
+        <v>45470</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5861,7 +5866,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5904,7 +5909,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 5705-2025</t>
+          <t>A 29801-2022</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5914,14 +5919,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45694</v>
+        <v>44755</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5934,7 +5939,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.2</v>
+        <v>4.8</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5977,7 +5982,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 62979-2023</t>
+          <t>A 18852-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5987,14 +5992,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45271</v>
+        <v>45426</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6007,7 +6012,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.8</v>
+        <v>2.7</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6050,7 +6055,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 22731-2026</t>
+          <t>A 34366-2022</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6064,10 +6069,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46157</v>
+        <v>44792</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6080,7 +6085,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6123,7 +6128,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 32391-2025</t>
+          <t>A 4673-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6137,10 +6142,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45837</v>
+        <v>46048</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6153,7 +6158,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>2.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6196,7 +6201,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 4262-2024</t>
+          <t>A 43520-2022</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6210,10 +6215,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45324</v>
+        <v>44837</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6226,7 +6231,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>14</v>
+        <v>1.5</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6269,7 +6274,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 16538-2025</t>
+          <t>A 6946-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6279,14 +6284,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45751</v>
+        <v>46057</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6299,7 +6304,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.8</v>
+        <v>2.2</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6342,7 +6347,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 23607-2026</t>
+          <t>A 16538-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6356,10 +6361,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46163</v>
+        <v>45751</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6372,7 +6377,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>5.3</v>
+        <v>0.8</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6415,7 +6420,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 25135-2025</t>
+          <t>A 45990-2022</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6429,10 +6434,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45798</v>
+        <v>44846</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6445,7 +6450,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.1</v>
+        <v>3.3</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6488,7 +6493,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 29801-2022</t>
+          <t>A 143-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6502,10 +6507,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44755</v>
+        <v>44928</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6518,7 +6523,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>4.8</v>
+        <v>0.5</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6561,7 +6566,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 49981-2023</t>
+          <t>A 18851-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6575,10 +6580,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45215</v>
+        <v>45426</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6591,7 +6596,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6634,7 +6639,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 661-2025</t>
+          <t>A 71835-2021</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6648,10 +6653,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45664</v>
+        <v>44543</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6664,7 +6669,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>3.1</v>
+        <v>7.5</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6707,7 +6712,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 71835-2021</t>
+          <t>A 22731-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6721,10 +6726,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44543</v>
+        <v>46157</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6737,7 +6742,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>7.5</v>
+        <v>1.8</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6780,7 +6785,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 34366-2022</t>
+          <t>A 32391-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6794,10 +6799,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44792</v>
+        <v>45837</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6810,7 +6815,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.5</v>
+        <v>2.1</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6853,7 +6858,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 4673-2026</t>
+          <t>A 23607-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6867,10 +6872,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46048</v>
+        <v>46163</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6883,7 +6888,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>8.199999999999999</v>
+        <v>5.3</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6926,7 +6931,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 6946-2026</t>
+          <t>A 25135-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6936,14 +6941,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46057</v>
+        <v>45798</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6956,7 +6961,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>2.2</v>
+        <v>1.1</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6999,7 +7004,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 37443-2025</t>
+          <t>A 51724-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7013,10 +7018,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45877</v>
+        <v>45222</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7028,13 +7033,8 @@
           <t>KUNGÄLV</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I78" t="n">
-        <v>0.7</v>
+        <v>3.1</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7077,7 +7077,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 56782-2022</t>
+          <t>A 661-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7091,10 +7091,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44894</v>
+        <v>45664</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7107,7 +7107,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.5</v>
+        <v>3.1</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7150,7 +7150,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 29952-2026</t>
+          <t>A 24461-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7164,10 +7164,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46205</v>
+        <v>45082</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7180,7 +7180,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7223,7 +7223,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 13990-2026</t>
+          <t>A 13880-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7237,10 +7237,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46098</v>
+        <v>45391</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7253,7 +7253,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7296,7 +7296,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 26812-2024</t>
+          <t>A 29952-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7310,10 +7310,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45470</v>
+        <v>46205</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7326,7 +7326,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7369,7 +7369,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 30738-2026</t>
+          <t>A 23457-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7383,10 +7383,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46211</v>
+        <v>45453</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>3.5</v>
+        <v>5.1</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7442,7 +7442,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 30859-2026</t>
+          <t>A 30738-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7456,10 +7456,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46212</v>
+        <v>46211</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7472,7 +7472,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>0.5</v>
+        <v>3.5</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7515,7 +7515,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 49985-2023</t>
+          <t>A 30859-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7529,10 +7529,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45215</v>
+        <v>46212</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7545,7 +7545,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>8.199999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7588,7 +7588,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 10810-2023</t>
+          <t>A 21389-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7602,10 +7602,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44989</v>
+        <v>45063</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7618,7 +7618,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>0.4</v>
+        <v>3.4</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7661,7 +7661,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 62128-2021</t>
+          <t>A 4262-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7675,10 +7675,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>44502</v>
+        <v>45324</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7691,7 +7691,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.8</v>
+        <v>14</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7734,7 +7734,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 50071-2023</t>
+          <t>A 63319-2021</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7748,10 +7748,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45215</v>
+        <v>44508</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7764,7 +7764,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>4</v>
+        <v>1.6</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7807,7 +7807,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 21240-2023</t>
+          <t>A 38262-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7821,10 +7821,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45058</v>
+        <v>46281</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7837,7 +7837,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7880,7 +7880,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 18851-2024</t>
+          <t>A 10677-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7894,10 +7894,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45426</v>
+        <v>45721</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7910,7 +7910,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>2.7</v>
+        <v>7.4</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7953,7 +7953,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 21389-2023</t>
+          <t>A 10679-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7967,10 +7967,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45063</v>
+        <v>45721</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7983,7 +7983,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>3.4</v>
+        <v>4.4</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8026,7 +8026,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 44176-2023</t>
+          <t>A 11237-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45188</v>
+        <v>45726</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8056,7 +8056,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>7.1</v>
+        <v>4.2</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 23457-2024</t>
+          <t>A 74285-2021</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8113,10 +8113,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45453</v>
+        <v>44558</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8129,7 +8129,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>5.1</v>
+        <v>1.1</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8172,7 +8172,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 39714-2024</t>
+          <t>A 61417-2022</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8186,10 +8186,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45552</v>
+        <v>44916</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8202,7 +8202,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1.2</v>
+        <v>3.6</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8245,7 +8245,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 18852-2024</t>
+          <t>A 32272-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8259,10 +8259,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45426</v>
+        <v>45120</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8275,7 +8275,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>2.7</v>
+        <v>4.9</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8318,7 +8318,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 38262-2026</t>
+          <t>A 32847-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8332,10 +8332,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>46281</v>
+        <v>45124</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8348,7 +8348,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>2.8</v>
+        <v>4.7</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8391,7 +8391,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 34387-2026</t>
+          <t>A 34386-2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8408,7 +8408,7 @@
         <v>46254</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8421,7 +8421,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8464,7 +8464,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 34386-2026</t>
+          <t>A 34396-2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8481,7 +8481,7 @@
         <v>46254</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8494,7 +8494,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8554,7 +8554,7 @@
         <v>46254</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8610,7 +8610,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 34396-2026</t>
+          <t>A 34387-2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8627,7 +8627,7 @@
         <v>46254</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8640,7 +8640,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8700,7 +8700,7 @@
         <v>46302</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8773,7 +8773,7 @@
         <v>45371</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>

--- a/Översikt KUNGÄLV.xlsx
+++ b/Översikt KUNGÄLV.xlsx
@@ -601,7 +601,7 @@
         <v>45548</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>45868</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -851,7 +851,7 @@
         <v>45526</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -965,7 +965,7 @@
         <v>45919</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
         <v>45695</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 59985-2025</t>
+          <t>A 4263-2024</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1188,10 +1188,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45993</v>
+        <v>45324</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1204,16 +1204,16 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>5.3</v>
+        <v>2.6</v>
       </c>
       <c r="J7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -1228,7 +1228,7 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1237,12 +1237,124 @@
         <v>4</v>
       </c>
       <c r="T7" t="n">
+        <v>6</v>
+      </c>
+      <c r="U7" t="n">
+        <v>6</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Mindre hackspett
+Klippfrullania
+Gråsiska
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 4263-2024 artfynd.xlsx", "A 4263-2024")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 4263-2024 karta.png", "A 4263-2024")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 4263-2024 georefererad karta.tif", "A 4263-2024")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 4263-2024 FSC-klagomål.docx", "A 4263-2024")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 4263-2024 FSC-klagomål mail.docx", "A 4263-2024")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 4263-2024 tillsynsbegäran.docx", "A 4263-2024")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 4263-2024 tillsynsbegäran mail.docx", "A 4263-2024")</f>
+        <v/>
+      </c>
+      <c r="AE7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 4263-2024 prioriterade fågelarter.docx", "A 4263-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 59985-2025</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>45993</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46305</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>KUNGÄLV</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2</v>
+      </c>
+      <c r="K8" t="n">
+        <v>2</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>4</v>
+      </c>
+      <c r="T8" t="n">
         <v>19</v>
       </c>
-      <c r="U7" t="n">
+      <c r="U8" t="n">
         <v>19</v>
       </c>
-      <c r="V7" s="2" t="inlineStr">
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>Blåmossa
 Västlig hakmossa
@@ -1250,148 +1362,36 @@
 Äkta lopplummer</t>
         </is>
       </c>
-      <c r="W7">
+      <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 59985-2025 artfynd.xlsx", "A 59985-2025")</f>
         <v/>
       </c>
-      <c r="X7">
+      <c r="X8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 59985-2025 karta.png", "A 59985-2025")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 59985-2025 georefererad karta.tif", "A 59985-2025")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 59985-2025 FSC-klagomål.docx", "A 59985-2025")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 59985-2025 FSC-klagomål mail.docx", "A 59985-2025")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 59985-2025 tillsynsbegäran.docx", "A 59985-2025")</f>
         <v/>
       </c>
-      <c r="AD7">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 59985-2025 tillsynsbegäran mail.docx", "A 59985-2025")</f>
         <v/>
       </c>
-      <c r="AE7">
+      <c r="AE8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 59985-2025 prioriterade fågelarter.docx", "A 59985-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A 4263-2024</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>45324</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46304</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>KUNGÄLV</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="J8" t="n">
-        <v>3</v>
-      </c>
-      <c r="K8" t="n">
-        <v>1</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>4</v>
-      </c>
-      <c r="T8" t="n">
-        <v>6</v>
-      </c>
-      <c r="U8" t="n">
-        <v>6</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>Mindre hackspett
-Klippfrullania
-Gråsiska
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 4263-2024 artfynd.xlsx", "A 4263-2024")</f>
-        <v/>
-      </c>
-      <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 4263-2024 karta.png", "A 4263-2024")</f>
-        <v/>
-      </c>
-      <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 4263-2024 georefererad karta.tif", "A 4263-2024")</f>
-        <v/>
-      </c>
-      <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 4263-2024 FSC-klagomål.docx", "A 4263-2024")</f>
-        <v/>
-      </c>
-      <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 4263-2024 FSC-klagomål mail.docx", "A 4263-2024")</f>
-        <v/>
-      </c>
-      <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 4263-2024 tillsynsbegäran.docx", "A 4263-2024")</f>
-        <v/>
-      </c>
-      <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 4263-2024 tillsynsbegäran mail.docx", "A 4263-2024")</f>
-        <v/>
-      </c>
-      <c r="AE8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 4263-2024 prioriterade fågelarter.docx", "A 4263-2024")</f>
         <v/>
       </c>
     </row>
@@ -1415,7 +1415,7 @@
         <v>45985</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>46199</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>45355</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>46212</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         <v>45957</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 56394-2025</t>
+          <t>A 5631-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1963,14 +1963,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45974</v>
+        <v>45334</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1986,10 +1986,10 @@
         <v>1.3</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -2019,472 +2019,472 @@
         <v>2</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Vanlig groda
+Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 5631-2024 artfynd.xlsx", "A 5631-2024")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 5631-2024 karta.png", "A 5631-2024")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 5631-2024 georefererad karta.tif", "A 5631-2024")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 5631-2024 FSC-klagomål.docx", "A 5631-2024")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 5631-2024 FSC-klagomål mail.docx", "A 5631-2024")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 5631-2024 tillsynsbegäran.docx", "A 5631-2024")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 5631-2024 tillsynsbegäran mail.docx", "A 5631-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 5637-2024</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>45334</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46305</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>KUNGÄLV</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>2</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Klofibbla
+Åkerrödtoppa</t>
+        </is>
+      </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 5637-2024 artfynd.xlsx", "A 5637-2024")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 5637-2024 karta.png", "A 5637-2024")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 5637-2024 georefererad karta.tif", "A 5637-2024")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 5637-2024 FSC-klagomål.docx", "A 5637-2024")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 5637-2024 FSC-klagomål mail.docx", "A 5637-2024")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 5637-2024 tillsynsbegäran.docx", "A 5637-2024")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 5637-2024 tillsynsbegäran mail.docx", "A 5637-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 56394-2025</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>45974</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46305</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>KUNGÄLV</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>Kambräken
 Revlummer</t>
         </is>
       </c>
-      <c r="W14">
+      <c r="W16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 56394-2025 artfynd.xlsx", "A 56394-2025")</f>
         <v/>
       </c>
-      <c r="X14">
+      <c r="X16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 56394-2025 karta.png", "A 56394-2025")</f>
         <v/>
       </c>
-      <c r="Y14">
+      <c r="Y16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 56394-2025 georefererad karta.tif", "A 56394-2025")</f>
         <v/>
       </c>
-      <c r="AA14">
+      <c r="AA16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 56394-2025 FSC-klagomål.docx", "A 56394-2025")</f>
         <v/>
       </c>
-      <c r="AB14">
+      <c r="AB16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 56394-2025 FSC-klagomål mail.docx", "A 56394-2025")</f>
         <v/>
       </c>
-      <c r="AC14">
+      <c r="AC16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 56394-2025 tillsynsbegäran.docx", "A 56394-2025")</f>
         <v/>
       </c>
-      <c r="AD14">
+      <c r="AD16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 56394-2025 tillsynsbegäran mail.docx", "A 56394-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
         <is>
           <t>A 57116-2025</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
         <v>45979</v>
       </c>
-      <c r="E15" s="1" t="n">
-        <v>46304</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>KUNGÄLV</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
+      <c r="E17" s="1" t="n">
+        <v>46305</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>KUNGÄLV</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
         <v>3.5</v>
       </c>
-      <c r="J15" t="n">
+      <c r="J17" t="n">
         <v>1</v>
       </c>
-      <c r="K15" t="n">
+      <c r="K17" t="n">
         <v>1</v>
       </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
         <v>2</v>
       </c>
-      <c r="T15" t="n">
+      <c r="T17" t="n">
         <v>3</v>
       </c>
-      <c r="U15" t="n">
+      <c r="U17" t="n">
         <v>3</v>
       </c>
-      <c r="V15" s="2" t="inlineStr">
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>Västlig hakmossa
 Spillkråka</t>
         </is>
       </c>
-      <c r="W15">
+      <c r="W17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 57116-2025 artfynd.xlsx", "A 57116-2025")</f>
         <v/>
       </c>
-      <c r="X15">
+      <c r="X17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 57116-2025 karta.png", "A 57116-2025")</f>
         <v/>
       </c>
-      <c r="Y15">
+      <c r="Y17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 57116-2025 georefererad karta.tif", "A 57116-2025")</f>
         <v/>
       </c>
-      <c r="AA15">
+      <c r="AA17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 57116-2025 FSC-klagomål.docx", "A 57116-2025")</f>
         <v/>
       </c>
-      <c r="AB15">
+      <c r="AB17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 57116-2025 FSC-klagomål mail.docx", "A 57116-2025")</f>
         <v/>
       </c>
-      <c r="AC15">
+      <c r="AC17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 57116-2025 tillsynsbegäran.docx", "A 57116-2025")</f>
         <v/>
       </c>
-      <c r="AD15">
+      <c r="AD17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 57116-2025 tillsynsbegäran mail.docx", "A 57116-2025")</f>
         <v/>
       </c>
-      <c r="AE15">
+      <c r="AE17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 57116-2025 prioriterade fågelarter.docx", "A 57116-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
         <is>
           <t>A 30860-2026</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
         <v>46212</v>
       </c>
-      <c r="E16" s="1" t="n">
-        <v>46304</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>KUNGÄLV</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
+      <c r="E18" s="1" t="n">
+        <v>46305</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>KUNGÄLV</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
         <v>1.7</v>
       </c>
-      <c r="J16" t="n">
+      <c r="J18" t="n">
         <v>1</v>
       </c>
-      <c r="K16" t="n">
+      <c r="K18" t="n">
         <v>1</v>
       </c>
-      <c r="L16" t="n">
+      <c r="L18" t="n">
         <v>1</v>
       </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
         <v>1</v>
       </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
         <v>2</v>
       </c>
-      <c r="T16" t="n">
+      <c r="T18" t="n">
         <v>2</v>
       </c>
-      <c r="U16" t="n">
+      <c r="U18" t="n">
         <v>1</v>
       </c>
-      <c r="V16" s="2" t="inlineStr">
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>Grönsångare
 Västlig hakmossa</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 30860-2026 artfynd.xlsx", "A 30860-2026")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 30860-2026 karta.png", "A 30860-2026")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 30860-2026 georefererad karta.tif", "A 30860-2026")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 30860-2026 FSC-klagomål.docx", "A 30860-2026")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 30860-2026 FSC-klagomål mail.docx", "A 30860-2026")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 30860-2026 tillsynsbegäran.docx", "A 30860-2026")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 30860-2026 tillsynsbegäran mail.docx", "A 30860-2026")</f>
         <v/>
       </c>
-      <c r="AE16">
+      <c r="AE18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 30860-2026 prioriterade fågelarter.docx", "A 30860-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 5631-2024</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>45334</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46304</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>KUNGÄLV</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="J17" t="n">
-        <v>2</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Vanlig groda
-Fläcknycklar</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 5631-2024 artfynd.xlsx", "A 5631-2024")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 5631-2024 karta.png", "A 5631-2024")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 5631-2024 georefererad karta.tif", "A 5631-2024")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 5631-2024 FSC-klagomål.docx", "A 5631-2024")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 5631-2024 FSC-klagomål mail.docx", "A 5631-2024")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 5631-2024 tillsynsbegäran.docx", "A 5631-2024")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 5631-2024 tillsynsbegäran mail.docx", "A 5631-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 5637-2024</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>45334</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46304</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>KUNGÄLV</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>2</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>2</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>Klofibbla
-Åkerrödtoppa</t>
-        </is>
-      </c>
-      <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 5637-2024 artfynd.xlsx", "A 5637-2024")</f>
-        <v/>
-      </c>
-      <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 5637-2024 karta.png", "A 5637-2024")</f>
-        <v/>
-      </c>
-      <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 5637-2024 georefererad karta.tif", "A 5637-2024")</f>
-        <v/>
-      </c>
-      <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 5637-2024 FSC-klagomål.docx", "A 5637-2024")</f>
-        <v/>
-      </c>
-      <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 5637-2024 FSC-klagomål mail.docx", "A 5637-2024")</f>
-        <v/>
-      </c>
-      <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 5637-2024 tillsynsbegäran.docx", "A 5637-2024")</f>
-        <v/>
-      </c>
-      <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 5637-2024 tillsynsbegäran mail.docx", "A 5637-2024")</f>
         <v/>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
         <v>45957</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
         <v>44838</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2706,7 +2706,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 23704-2024</t>
+          <t>A 49988-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2720,10 +2720,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45454</v>
+        <v>45215</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>4.9</v>
+        <v>2.3</v>
       </c>
       <c r="J21" t="n">
         <v>1</v>
@@ -2748,7 +2748,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -2760,58 +2760,58 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
       </c>
       <c r="T21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Hedjohannesört</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 23704-2024 artfynd.xlsx", "A 23704-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 49988-2023 artfynd.xlsx", "A 49988-2023")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 23704-2024 karta.png", "A 23704-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 49988-2023 karta.png", "A 49988-2023")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 23704-2024 georefererad karta.tif", "A 23704-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 49988-2023 georefererad karta.tif", "A 49988-2023")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 23704-2024 FSC-klagomål.docx", "A 23704-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 49988-2023 FSC-klagomål.docx", "A 49988-2023")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 23704-2024 FSC-klagomål mail.docx", "A 23704-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 49988-2023 FSC-klagomål mail.docx", "A 49988-2023")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 23704-2024 tillsynsbegäran.docx", "A 23704-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 49988-2023 tillsynsbegäran.docx", "A 49988-2023")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 23704-2024 tillsynsbegäran mail.docx", "A 23704-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 49988-2023 tillsynsbegäran mail.docx", "A 49988-2023")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 49988-2023</t>
+          <t>A 23704-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2825,10 +2825,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45215</v>
+        <v>45454</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2841,7 +2841,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>2.3</v>
+        <v>4.9</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
@@ -2853,7 +2853,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
@@ -2865,58 +2865,58 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
       </c>
       <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
         <v>1</v>
       </c>
-      <c r="U22" t="n">
-        <v>0</v>
-      </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Hedjohannesört</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 49988-2023 artfynd.xlsx", "A 49988-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 23704-2024 artfynd.xlsx", "A 23704-2024")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 49988-2023 karta.png", "A 49988-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 23704-2024 karta.png", "A 23704-2024")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 49988-2023 georefererad karta.tif", "A 49988-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 23704-2024 georefererad karta.tif", "A 23704-2024")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 49988-2023 FSC-klagomål.docx", "A 49988-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 23704-2024 FSC-klagomål.docx", "A 23704-2024")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 49988-2023 FSC-klagomål mail.docx", "A 49988-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 23704-2024 FSC-klagomål mail.docx", "A 23704-2024")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 49988-2023 tillsynsbegäran.docx", "A 49988-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 23704-2024 tillsynsbegäran.docx", "A 23704-2024")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 49988-2023 tillsynsbegäran mail.docx", "A 49988-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 23704-2024 tillsynsbegäran mail.docx", "A 23704-2024")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 30862-2026</t>
+          <t>A 6082-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2930,10 +2930,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46212</v>
+        <v>45697</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2946,7 +2946,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.7</v>
+        <v>2.8</v>
       </c>
       <c r="J23" t="n">
         <v>1</v>
@@ -2979,49 +2979,53 @@
         <v>1</v>
       </c>
       <c r="T23" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 30862-2026 artfynd.xlsx", "A 30862-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 6082-2025 artfynd.xlsx", "A 6082-2025")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 30862-2026 karta.png", "A 30862-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 6082-2025 karta.png", "A 6082-2025")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 30862-2026 georefererad karta.tif", "A 30862-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 6082-2025 georefererad karta.tif", "A 6082-2025")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 30862-2026 FSC-klagomål.docx", "A 30862-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 6082-2025 FSC-klagomål.docx", "A 6082-2025")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 30862-2026 FSC-klagomål mail.docx", "A 30862-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 6082-2025 FSC-klagomål mail.docx", "A 6082-2025")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 30862-2026 tillsynsbegäran.docx", "A 30862-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 6082-2025 tillsynsbegäran.docx", "A 6082-2025")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 30862-2026 tillsynsbegäran mail.docx", "A 30862-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 6082-2025 tillsynsbegäran mail.docx", "A 6082-2025")</f>
+        <v/>
+      </c>
+      <c r="AE23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 6082-2025 prioriterade fågelarter.docx", "A 6082-2025")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 6082-2025</t>
+          <t>A 30862-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3035,10 +3039,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45697</v>
+        <v>46212</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3051,7 +3055,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.8</v>
+        <v>1.7</v>
       </c>
       <c r="J24" t="n">
         <v>1</v>
@@ -3084,46 +3088,42 @@
         <v>1</v>
       </c>
       <c r="T24" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 6082-2025 artfynd.xlsx", "A 6082-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 30862-2026 artfynd.xlsx", "A 30862-2026")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 6082-2025 karta.png", "A 6082-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 30862-2026 karta.png", "A 30862-2026")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 6082-2025 georefererad karta.tif", "A 6082-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 30862-2026 georefererad karta.tif", "A 30862-2026")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 6082-2025 FSC-klagomål.docx", "A 6082-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 30862-2026 FSC-klagomål.docx", "A 30862-2026")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 6082-2025 FSC-klagomål mail.docx", "A 6082-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 30862-2026 FSC-klagomål mail.docx", "A 30862-2026")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 6082-2025 tillsynsbegäran.docx", "A 6082-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 30862-2026 tillsynsbegäran.docx", "A 30862-2026")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 6082-2025 tillsynsbegäran mail.docx", "A 6082-2025")</f>
-        <v/>
-      </c>
-      <c r="AE24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 6082-2025 prioriterade fågelarter.docx", "A 6082-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 30862-2026 tillsynsbegäran mail.docx", "A 30862-2026")</f>
         <v/>
       </c>
     </row>
@@ -3147,7 +3147,7 @@
         <v>44691</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
         <v>44691</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         <v>44836</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3349,7 +3349,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 30322-2022</t>
+          <t>A 30373-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3366,7 +3366,7 @@
         <v>44760</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3379,7 +3379,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.9</v>
+        <v>0.8</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3422,7 +3422,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 30373-2022</t>
+          <t>A 30377-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3439,7 +3439,7 @@
         <v>44760</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3452,7 +3452,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3495,7 +3495,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 30377-2022</t>
+          <t>A 30322-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3512,7 +3512,7 @@
         <v>44760</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3525,7 +3525,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3568,7 +3568,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 17455-2025</t>
+          <t>A 24461-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3582,10 +3582,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45757</v>
+        <v>45082</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3598,7 +3598,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3641,7 +3641,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 62221-2023</t>
+          <t>A 13880-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3655,10 +3655,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45267</v>
+        <v>45391</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3671,7 +3671,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.3</v>
+        <v>2.4</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3714,7 +3714,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 21240-2023</t>
+          <t>A 143-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3728,10 +3728,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45058</v>
+        <v>44928</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3744,7 +3744,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>2.3</v>
+        <v>0.5</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3787,7 +3787,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 29223-2024</t>
+          <t>A 62221-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3801,10 +3801,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45482</v>
+        <v>45267</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3817,7 +3817,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>5.6</v>
+        <v>1.3</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3860,7 +3860,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 10655-2022</t>
+          <t>A 4204-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3874,10 +3874,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44624</v>
+        <v>45324</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3890,7 +3890,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>13.3</v>
+        <v>4.4</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3933,7 +3933,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 39714-2024</t>
+          <t>A 1995-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3947,10 +3947,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45552</v>
+        <v>45308</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3963,7 +3963,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4006,7 +4006,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 19531-2023</t>
+          <t>A 30170-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4020,10 +4020,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45050</v>
+        <v>44757</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.9</v>
+        <v>3.1</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4079,7 +4079,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 5705-2025</t>
+          <t>A 10810-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4089,14 +4089,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45694</v>
+        <v>44989</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4109,7 +4109,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4152,7 +4152,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 7505-2024</t>
+          <t>A 45990-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4166,10 +4166,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45347</v>
+        <v>44846</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4182,7 +4182,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.8</v>
+        <v>3.3</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4225,7 +4225,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 8334-2023</t>
+          <t>A 63319-2021</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4239,10 +4239,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44975</v>
+        <v>44508</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4255,7 +4255,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4298,7 +4298,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 34244-2025</t>
+          <t>A 62128-2021</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4312,10 +4312,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45844</v>
+        <v>44502</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4328,7 +4328,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>2.9</v>
+        <v>1.8</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4371,7 +4371,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 25624-2025</t>
+          <t>A 21240-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4385,10 +4385,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45803</v>
+        <v>45058</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4401,7 +4401,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>5</v>
+        <v>2.3</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4444,7 +4444,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 37443-2025</t>
+          <t>A 17922-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4458,10 +4458,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45877</v>
+        <v>45758</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4473,13 +4473,8 @@
           <t>KUNGÄLV</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I43" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4522,7 +4517,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 41442-2025</t>
+          <t>A 18851-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4536,10 +4531,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45869</v>
+        <v>45426</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4552,7 +4547,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.8</v>
+        <v>2.7</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4595,7 +4590,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 40951-2025</t>
+          <t>A 21389-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4609,10 +4604,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45897</v>
+        <v>45063</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4625,7 +4620,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.8</v>
+        <v>3.4</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4668,7 +4663,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 17922-2025</t>
+          <t>A 44176-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4682,10 +4677,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45758</v>
+        <v>45188</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4698,7 +4693,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.8</v>
+        <v>7.1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4741,7 +4736,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 13990-2026</t>
+          <t>A 7505-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4755,10 +4750,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46098</v>
+        <v>45347</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4771,7 +4766,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2.6</v>
+        <v>1.8</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4814,7 +4809,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 45124-2025</t>
+          <t>A 40951-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4828,10 +4823,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45919</v>
+        <v>45897</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4844,7 +4839,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>3.7</v>
+        <v>0.8</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4887,7 +4882,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 47564-2025</t>
+          <t>A 23457-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4901,10 +4896,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45931</v>
+        <v>45453</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4917,7 +4912,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2</v>
+        <v>5.1</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4960,7 +4955,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 49981-2023</t>
+          <t>A 39714-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4974,10 +4969,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45215</v>
+        <v>45552</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4990,7 +4985,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2.5</v>
+        <v>1.2</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5033,7 +5028,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 56782-2022</t>
+          <t>A 18852-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5047,10 +5042,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44894</v>
+        <v>45426</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5063,7 +5058,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.5</v>
+        <v>2.7</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5106,7 +5101,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 1995-2024</t>
+          <t>A 43520-2022</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5120,10 +5115,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45308</v>
+        <v>44837</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5136,7 +5131,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5179,7 +5174,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 30170-2022</t>
+          <t>A 51724-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5193,10 +5188,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44757</v>
+        <v>45222</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5252,7 +5247,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 52932-2025</t>
+          <t>A 29223-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5266,10 +5261,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45957</v>
+        <v>45482</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5282,7 +5277,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>3.4</v>
+        <v>5.6</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5325,7 +5320,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 10810-2023</t>
+          <t>A 45124-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5339,10 +5334,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44989</v>
+        <v>45919</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5355,7 +5350,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.4</v>
+        <v>3.7</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5398,7 +5393,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 4204-2024</t>
+          <t>A 10679-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5412,10 +5407,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45324</v>
+        <v>45721</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5471,7 +5466,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 62128-2021</t>
+          <t>A 11237-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5485,10 +5480,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44502</v>
+        <v>45726</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5501,7 +5496,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.8</v>
+        <v>4.2</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5544,7 +5539,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 62979-2023</t>
+          <t>A 10677-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5554,14 +5549,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45271</v>
+        <v>45721</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5574,7 +5569,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.8</v>
+        <v>7.4</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5617,7 +5612,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 49985-2023</t>
+          <t>A 74285-2021</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5631,10 +5626,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45215</v>
+        <v>44558</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5647,7 +5642,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>8.199999999999999</v>
+        <v>1.1</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5690,7 +5685,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 50071-2023</t>
+          <t>A 10655-2022</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5704,10 +5699,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45215</v>
+        <v>44624</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5720,7 +5715,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>4</v>
+        <v>13.3</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5763,7 +5758,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 44176-2023</t>
+          <t>A 17455-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5777,10 +5772,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45188</v>
+        <v>45757</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5793,7 +5788,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>7.1</v>
+        <v>2.1</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5836,7 +5831,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 26812-2024</t>
+          <t>A 8334-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5850,10 +5845,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45470</v>
+        <v>44975</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5866,7 +5861,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5909,7 +5904,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 29801-2022</t>
+          <t>A 47564-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5923,10 +5918,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44755</v>
+        <v>45931</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5939,7 +5934,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>4.8</v>
+        <v>2</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5982,7 +5977,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 18852-2024</t>
+          <t>A 19531-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5996,10 +5991,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45426</v>
+        <v>45050</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6012,7 +6007,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2.7</v>
+        <v>1.9</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6055,7 +6050,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 34366-2022</t>
+          <t>A 61417-2022</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6069,10 +6064,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44792</v>
+        <v>44916</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6085,7 +6080,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.5</v>
+        <v>3.6</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6128,7 +6123,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 4673-2026</t>
+          <t>A 32272-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6142,10 +6137,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46048</v>
+        <v>45120</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6158,7 +6153,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>8.199999999999999</v>
+        <v>4.9</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6201,7 +6196,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 43520-2022</t>
+          <t>A 32847-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6215,10 +6210,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44837</v>
+        <v>45124</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6231,7 +6226,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.5</v>
+        <v>4.7</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6274,7 +6269,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 6946-2026</t>
+          <t>A 5705-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6288,10 +6283,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46057</v>
+        <v>45694</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6304,7 +6299,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2.2</v>
+        <v>1.2</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6347,7 +6342,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 16538-2025</t>
+          <t>A 62979-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6357,14 +6352,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45751</v>
+        <v>45271</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6420,7 +6415,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 45990-2022</t>
+          <t>A 52932-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6434,10 +6429,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44846</v>
+        <v>45957</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6450,7 +6445,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6493,7 +6488,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 143-2023</t>
+          <t>A 4262-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6507,10 +6502,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44928</v>
+        <v>45324</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6523,7 +6518,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.5</v>
+        <v>14</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6566,7 +6561,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 18851-2024</t>
+          <t>A 16538-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6580,10 +6575,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45426</v>
+        <v>45751</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6596,7 +6591,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>2.7</v>
+        <v>0.8</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6639,7 +6634,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 71835-2021</t>
+          <t>A 661-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6653,10 +6648,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44543</v>
+        <v>45664</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6669,7 +6664,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>7.5</v>
+        <v>3.1</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6712,7 +6707,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 22731-2026</t>
+          <t>A 34244-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6726,10 +6721,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46157</v>
+        <v>45844</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6742,7 +6737,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.8</v>
+        <v>2.9</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6785,7 +6780,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 32391-2025</t>
+          <t>A 29801-2022</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6799,10 +6794,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45837</v>
+        <v>44755</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6815,7 +6810,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>2.1</v>
+        <v>4.8</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6858,7 +6853,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 23607-2026</t>
+          <t>A 49981-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6872,10 +6867,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46163</v>
+        <v>45215</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6888,7 +6883,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>5.3</v>
+        <v>2.5</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6931,7 +6926,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 25135-2025</t>
+          <t>A 25624-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6945,10 +6940,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45798</v>
+        <v>45803</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6961,7 +6956,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.1</v>
+        <v>5</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7004,7 +6999,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 51724-2023</t>
+          <t>A 41442-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7018,10 +7013,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45222</v>
+        <v>45869</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7034,7 +7029,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>3.1</v>
+        <v>1.8</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7077,7 +7072,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 661-2025</t>
+          <t>A 71835-2021</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7091,10 +7086,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45664</v>
+        <v>44543</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7107,7 +7102,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>3.1</v>
+        <v>7.5</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7150,7 +7145,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 24461-2023</t>
+          <t>A 13990-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7164,10 +7159,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45082</v>
+        <v>46098</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7180,7 +7175,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.5</v>
+        <v>2.6</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7223,7 +7218,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 13880-2024</t>
+          <t>A 49985-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7237,10 +7232,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45391</v>
+        <v>45215</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7253,7 +7248,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>2.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7296,7 +7291,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 29952-2026</t>
+          <t>A 56782-2022</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7310,10 +7305,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46205</v>
+        <v>44894</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7326,7 +7321,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7369,7 +7364,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 23457-2024</t>
+          <t>A 50071-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7383,10 +7378,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45453</v>
+        <v>45215</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7399,7 +7394,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>5.1</v>
+        <v>4</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7442,7 +7437,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 30738-2026</t>
+          <t>A 26812-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7456,10 +7451,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46211</v>
+        <v>45470</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7472,7 +7467,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>3.5</v>
+        <v>1.7</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7515,7 +7510,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 30859-2026</t>
+          <t>A 34366-2022</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7529,10 +7524,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46212</v>
+        <v>44792</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7588,7 +7583,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 21389-2023</t>
+          <t>A 4673-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7602,10 +7597,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45063</v>
+        <v>46048</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7618,7 +7613,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>3.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7661,7 +7656,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 4262-2024</t>
+          <t>A 6946-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7671,14 +7666,14 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45324</v>
+        <v>46057</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7691,7 +7686,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>14</v>
+        <v>2.2</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7734,7 +7729,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 63319-2021</t>
+          <t>A 37443-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7748,10 +7743,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>44508</v>
+        <v>45877</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7763,8 +7758,13 @@
           <t>KUNGÄLV</t>
         </is>
       </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I88" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7807,7 +7807,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 38262-2026</t>
+          <t>A 22731-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7821,10 +7821,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46281</v>
+        <v>46157</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7837,7 +7837,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>2.8</v>
+        <v>1.8</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7880,7 +7880,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 10677-2025</t>
+          <t>A 32391-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7894,10 +7894,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45721</v>
+        <v>45837</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7910,7 +7910,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>7.4</v>
+        <v>2.1</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7953,7 +7953,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 10679-2025</t>
+          <t>A 23607-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7967,10 +7967,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45721</v>
+        <v>46163</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7983,7 +7983,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>4.4</v>
+        <v>5.3</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8026,7 +8026,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 11237-2025</t>
+          <t>A 25135-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45726</v>
+        <v>45798</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8056,7 +8056,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>4.2</v>
+        <v>1.1</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 74285-2021</t>
+          <t>A 29952-2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8113,10 +8113,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44558</v>
+        <v>46205</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8129,7 +8129,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8172,7 +8172,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 61417-2022</t>
+          <t>A 30738-2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8186,10 +8186,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>44916</v>
+        <v>46211</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8202,7 +8202,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8245,7 +8245,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 32272-2023</t>
+          <t>A 30859-2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8259,10 +8259,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45120</v>
+        <v>46212</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8275,7 +8275,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>4.9</v>
+        <v>0.5</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8318,7 +8318,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 32847-2023</t>
+          <t>A 38262-2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8332,10 +8332,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45124</v>
+        <v>46281</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8348,7 +8348,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>4.7</v>
+        <v>2.8</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8391,7 +8391,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 34386-2026</t>
+          <t>A 34387-2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8408,7 +8408,7 @@
         <v>46254</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8421,7 +8421,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8464,7 +8464,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 34396-2026</t>
+          <t>A 34386-2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8481,7 +8481,7 @@
         <v>46254</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8494,7 +8494,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8554,7 +8554,7 @@
         <v>46254</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8610,7 +8610,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 34387-2026</t>
+          <t>A 34396-2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8627,7 +8627,7 @@
         <v>46254</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8640,7 +8640,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8700,7 +8700,7 @@
         <v>46302</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8773,7 +8773,7 @@
         <v>45371</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>

--- a/Översikt KUNGÄLV.xlsx
+++ b/Översikt KUNGÄLV.xlsx
@@ -601,7 +601,7 @@
         <v>45548</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>45868</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -851,7 +851,7 @@
         <v>45526</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -965,7 +965,7 @@
         <v>45919</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
         <v>45695</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         <v>45324</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         <v>45993</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>45985</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>46199</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>45355</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>46212</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         <v>45957</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1970,7 +1970,7 @@
         <v>45334</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2076,7 +2076,7 @@
         <v>45334</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
         <v>45974</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2288,7 +2288,7 @@
         <v>45979</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2398,7 +2398,7 @@
         <v>46212</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2508,7 +2508,7 @@
         <v>45957</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
         <v>44838</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2723,7 +2723,7 @@
         <v>45215</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2828,7 +2828,7 @@
         <v>45454</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2933,7 +2933,7 @@
         <v>45697</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3042,7 +3042,7 @@
         <v>46212</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>44691</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
         <v>44691</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         <v>44836</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3366,7 +3366,7 @@
         <v>44760</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         <v>44760</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
         <v>44760</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3585,7 +3585,7 @@
         <v>45082</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3658,7 +3658,7 @@
         <v>45391</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3731,7 +3731,7 @@
         <v>44928</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3804,7 +3804,7 @@
         <v>45267</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3877,7 +3877,7 @@
         <v>45324</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3950,7 +3950,7 @@
         <v>45308</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4023,7 +4023,7 @@
         <v>44757</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4096,7 +4096,7 @@
         <v>44989</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
         <v>44846</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4242,7 +4242,7 @@
         <v>44508</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4315,7 +4315,7 @@
         <v>44502</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4388,7 +4388,7 @@
         <v>45058</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4461,7 +4461,7 @@
         <v>45758</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4534,7 +4534,7 @@
         <v>45426</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4607,7 +4607,7 @@
         <v>45063</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4680,7 +4680,7 @@
         <v>45188</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4753,7 +4753,7 @@
         <v>45347</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4826,7 +4826,7 @@
         <v>45897</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4899,7 +4899,7 @@
         <v>45453</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4972,7 +4972,7 @@
         <v>45552</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5045,7 +5045,7 @@
         <v>45426</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5118,7 +5118,7 @@
         <v>44837</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5191,7 +5191,7 @@
         <v>45222</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5264,7 +5264,7 @@
         <v>45482</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5337,7 +5337,7 @@
         <v>45919</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5410,7 +5410,7 @@
         <v>45721</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5483,7 +5483,7 @@
         <v>45726</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5556,7 +5556,7 @@
         <v>45721</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5629,7 +5629,7 @@
         <v>44558</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5702,7 +5702,7 @@
         <v>44624</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5775,7 +5775,7 @@
         <v>45757</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5848,7 +5848,7 @@
         <v>44975</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5921,7 +5921,7 @@
         <v>45931</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5994,7 +5994,7 @@
         <v>45050</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6067,7 +6067,7 @@
         <v>44916</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6140,7 +6140,7 @@
         <v>45120</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6213,7 +6213,7 @@
         <v>45124</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6286,7 +6286,7 @@
         <v>45694</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6359,7 +6359,7 @@
         <v>45271</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6432,7 +6432,7 @@
         <v>45957</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6505,7 +6505,7 @@
         <v>45324</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6578,7 +6578,7 @@
         <v>45751</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6651,7 +6651,7 @@
         <v>45664</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6724,7 +6724,7 @@
         <v>45844</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6797,7 +6797,7 @@
         <v>44755</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6870,7 +6870,7 @@
         <v>45215</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6943,7 +6943,7 @@
         <v>45803</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7016,7 +7016,7 @@
         <v>45869</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7089,7 +7089,7 @@
         <v>44543</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7162,7 +7162,7 @@
         <v>46098</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7235,7 +7235,7 @@
         <v>45215</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7308,7 +7308,7 @@
         <v>44894</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7381,7 +7381,7 @@
         <v>45215</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7454,7 +7454,7 @@
         <v>45470</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7527,7 +7527,7 @@
         <v>44792</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7600,7 +7600,7 @@
         <v>46048</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7673,7 +7673,7 @@
         <v>46057</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7746,7 +7746,7 @@
         <v>45877</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7824,7 +7824,7 @@
         <v>46157</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7897,7 +7897,7 @@
         <v>45837</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7970,7 +7970,7 @@
         <v>46163</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         <v>45798</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8116,7 +8116,7 @@
         <v>46205</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8189,7 +8189,7 @@
         <v>46211</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8262,7 +8262,7 @@
         <v>46212</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8335,7 +8335,7 @@
         <v>46281</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8408,7 +8408,7 @@
         <v>46254</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8481,7 +8481,7 @@
         <v>46254</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8554,7 +8554,7 @@
         <v>46254</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8627,7 +8627,7 @@
         <v>46254</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8700,7 +8700,7 @@
         <v>46302</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8773,7 +8773,7 @@
         <v>45371</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>

--- a/Översikt KUNGÄLV.xlsx
+++ b/Översikt KUNGÄLV.xlsx
@@ -601,7 +601,7 @@
         <v>45548</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>45868</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -851,7 +851,7 @@
         <v>45526</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -965,7 +965,7 @@
         <v>45919</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
         <v>45695</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         <v>45324</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         <v>45993</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>45985</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>46199</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>45355</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>46212</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         <v>45957</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1970,7 +1970,7 @@
         <v>45334</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2076,7 +2076,7 @@
         <v>45334</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
         <v>45974</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2288,7 +2288,7 @@
         <v>45979</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2398,7 +2398,7 @@
         <v>46212</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2508,7 +2508,7 @@
         <v>45957</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
         <v>44838</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2723,7 +2723,7 @@
         <v>45215</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2828,7 +2828,7 @@
         <v>45454</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2933,7 +2933,7 @@
         <v>45697</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3042,7 +3042,7 @@
         <v>46212</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>44691</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
         <v>44691</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         <v>44836</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3366,7 +3366,7 @@
         <v>44760</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         <v>44760</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
         <v>44760</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3585,7 +3585,7 @@
         <v>45082</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3658,7 +3658,7 @@
         <v>45391</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3731,7 +3731,7 @@
         <v>44928</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3804,7 +3804,7 @@
         <v>45267</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3877,7 +3877,7 @@
         <v>45324</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3950,7 +3950,7 @@
         <v>45308</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4023,7 +4023,7 @@
         <v>44757</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4096,7 +4096,7 @@
         <v>44989</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
         <v>44846</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4242,7 +4242,7 @@
         <v>44508</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4315,7 +4315,7 @@
         <v>44502</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4388,7 +4388,7 @@
         <v>45058</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4461,7 +4461,7 @@
         <v>45758</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4534,7 +4534,7 @@
         <v>45426</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4607,7 +4607,7 @@
         <v>45063</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4680,7 +4680,7 @@
         <v>45188</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4753,7 +4753,7 @@
         <v>45347</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4826,7 +4826,7 @@
         <v>45897</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4899,7 +4899,7 @@
         <v>45453</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4972,7 +4972,7 @@
         <v>45552</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5045,7 +5045,7 @@
         <v>45426</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5118,7 +5118,7 @@
         <v>44837</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5191,7 +5191,7 @@
         <v>45222</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5264,7 +5264,7 @@
         <v>45482</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5337,7 +5337,7 @@
         <v>45919</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5410,7 +5410,7 @@
         <v>45721</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5483,7 +5483,7 @@
         <v>45726</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5556,7 +5556,7 @@
         <v>45721</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5629,7 +5629,7 @@
         <v>44558</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5702,7 +5702,7 @@
         <v>44624</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5775,7 +5775,7 @@
         <v>45757</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5848,7 +5848,7 @@
         <v>44975</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5921,7 +5921,7 @@
         <v>45931</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5994,7 +5994,7 @@
         <v>45050</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6067,7 +6067,7 @@
         <v>44916</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6140,7 +6140,7 @@
         <v>45120</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6213,7 +6213,7 @@
         <v>45124</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6286,7 +6286,7 @@
         <v>45694</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6359,7 +6359,7 @@
         <v>45271</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6432,7 +6432,7 @@
         <v>45957</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6505,7 +6505,7 @@
         <v>45324</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6578,7 +6578,7 @@
         <v>45751</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6651,7 +6651,7 @@
         <v>45664</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6724,7 +6724,7 @@
         <v>45844</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6797,7 +6797,7 @@
         <v>44755</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6870,7 +6870,7 @@
         <v>45215</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6943,7 +6943,7 @@
         <v>45803</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7016,7 +7016,7 @@
         <v>45869</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7089,7 +7089,7 @@
         <v>44543</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7162,7 +7162,7 @@
         <v>46098</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7235,7 +7235,7 @@
         <v>45215</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7308,7 +7308,7 @@
         <v>44894</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7381,7 +7381,7 @@
         <v>45215</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7454,7 +7454,7 @@
         <v>45470</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7527,7 +7527,7 @@
         <v>44792</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7600,7 +7600,7 @@
         <v>46048</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7673,7 +7673,7 @@
         <v>46057</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7746,7 +7746,7 @@
         <v>45877</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7824,7 +7824,7 @@
         <v>46157</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7897,7 +7897,7 @@
         <v>45837</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7970,7 +7970,7 @@
         <v>46163</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         <v>45798</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8116,7 +8116,7 @@
         <v>46205</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8189,7 +8189,7 @@
         <v>46211</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8262,7 +8262,7 @@
         <v>46212</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8335,7 +8335,7 @@
         <v>46281</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8408,7 +8408,7 @@
         <v>46254</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8481,7 +8481,7 @@
         <v>46254</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8554,7 +8554,7 @@
         <v>46254</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8627,7 +8627,7 @@
         <v>46254</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8700,7 +8700,7 @@
         <v>46302</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8773,7 +8773,7 @@
         <v>45371</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>

--- a/Översikt KUNGÄLV.xlsx
+++ b/Översikt KUNGÄLV.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE102"/>
+  <dimension ref="A1:AE103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45548</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>45868</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -851,7 +851,7 @@
         <v>45526</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -948,7 +948,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 45243-2025</t>
+          <t>A 6041-2025</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -962,10 +962,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45919</v>
+        <v>45695</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -978,13 +978,13 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>8.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L5" t="n">
         <v>2</v>
@@ -1011,12 +1011,125 @@
         <v>5</v>
       </c>
       <c r="T5" t="n">
+        <v>10</v>
+      </c>
+      <c r="U5" t="n">
+        <v>10</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>Björktrast
+Talltita
+Blåmossa
+Kambräken
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 6041-2025 artfynd.xlsx", "A 6041-2025")</f>
+        <v/>
+      </c>
+      <c r="X5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 6041-2025 karta.png", "A 6041-2025")</f>
+        <v/>
+      </c>
+      <c r="Y5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 6041-2025 georefererad karta.tif", "A 6041-2025")</f>
+        <v/>
+      </c>
+      <c r="AA5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 6041-2025 FSC-klagomål.docx", "A 6041-2025")</f>
+        <v/>
+      </c>
+      <c r="AB5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 6041-2025 FSC-klagomål mail.docx", "A 6041-2025")</f>
+        <v/>
+      </c>
+      <c r="AC5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 6041-2025 tillsynsbegäran.docx", "A 6041-2025")</f>
+        <v/>
+      </c>
+      <c r="AD5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 6041-2025 tillsynsbegäran mail.docx", "A 6041-2025")</f>
+        <v/>
+      </c>
+      <c r="AE5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 6041-2025 prioriterade fågelarter.docx", "A 6041-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A 45243-2025</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>45919</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>46308</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>KUNGÄLV</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="J6" t="n">
+        <v>5</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>2</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>2</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="n">
         <v>9</v>
       </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>Gulsparv
 Nordfladdermus
@@ -1025,156 +1138,43 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W5">
+      <c r="W6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 45243-2025 artfynd.xlsx", "A 45243-2025")</f>
         <v/>
       </c>
-      <c r="X5">
+      <c r="X6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 45243-2025 karta.png", "A 45243-2025")</f>
         <v/>
       </c>
-      <c r="Y5">
+      <c r="Y6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 45243-2025 georefererad karta.tif", "A 45243-2025")</f>
         <v/>
       </c>
-      <c r="AA5">
+      <c r="AA6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 45243-2025 FSC-klagomål.docx", "A 45243-2025")</f>
         <v/>
       </c>
-      <c r="AB5">
+      <c r="AB6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 45243-2025 FSC-klagomål mail.docx", "A 45243-2025")</f>
         <v/>
       </c>
-      <c r="AC5">
+      <c r="AC6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 45243-2025 tillsynsbegäran.docx", "A 45243-2025")</f>
         <v/>
       </c>
-      <c r="AD5">
+      <c r="AD6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 45243-2025 tillsynsbegäran mail.docx", "A 45243-2025")</f>
         <v/>
       </c>
-      <c r="AE5">
+      <c r="AE6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 45243-2025 prioriterade fågelarter.docx", "A 45243-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>A 6041-2025</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>45695</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>46307</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>KUNGÄLV</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="J6" t="n">
-        <v>3</v>
-      </c>
-      <c r="K6" t="n">
-        <v>2</v>
-      </c>
-      <c r="L6" t="n">
-        <v>2</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>2</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
-        <v>5</v>
-      </c>
-      <c r="T6" t="n">
-        <v>10</v>
-      </c>
-      <c r="U6" t="n">
-        <v>10</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>Björktrast
-Talltita
-Blåmossa
-Kambräken
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 6041-2025 artfynd.xlsx", "A 6041-2025")</f>
-        <v/>
-      </c>
-      <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 6041-2025 karta.png", "A 6041-2025")</f>
-        <v/>
-      </c>
-      <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 6041-2025 georefererad karta.tif", "A 6041-2025")</f>
-        <v/>
-      </c>
-      <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 6041-2025 FSC-klagomål.docx", "A 6041-2025")</f>
-        <v/>
-      </c>
-      <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 6041-2025 FSC-klagomål mail.docx", "A 6041-2025")</f>
-        <v/>
-      </c>
-      <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 6041-2025 tillsynsbegäran.docx", "A 6041-2025")</f>
-        <v/>
-      </c>
-      <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 6041-2025 tillsynsbegäran mail.docx", "A 6041-2025")</f>
-        <v/>
-      </c>
-      <c r="AE6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 6041-2025 prioriterade fågelarter.docx", "A 6041-2025")</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 4263-2024</t>
+          <t>A 59985-2025</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1188,10 +1188,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45324</v>
+        <v>45993</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1204,16 +1204,16 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>2.6</v>
+        <v>5.3</v>
       </c>
       <c r="J7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -1228,7 +1228,7 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1237,12 +1237,124 @@
         <v>4</v>
       </c>
       <c r="T7" t="n">
+        <v>19</v>
+      </c>
+      <c r="U7" t="n">
+        <v>19</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Blåmossa
+Västlig hakmossa
+Spillkråka
+Äkta lopplummer</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 59985-2025 artfynd.xlsx", "A 59985-2025")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 59985-2025 karta.png", "A 59985-2025")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 59985-2025 georefererad karta.tif", "A 59985-2025")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 59985-2025 FSC-klagomål.docx", "A 59985-2025")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 59985-2025 FSC-klagomål mail.docx", "A 59985-2025")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 59985-2025 tillsynsbegäran.docx", "A 59985-2025")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 59985-2025 tillsynsbegäran mail.docx", "A 59985-2025")</f>
+        <v/>
+      </c>
+      <c r="AE7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 59985-2025 prioriterade fågelarter.docx", "A 59985-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 4263-2024</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>45324</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46308</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>KUNGÄLV</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J8" t="n">
+        <v>3</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>4</v>
+      </c>
+      <c r="T8" t="n">
         <v>6</v>
       </c>
-      <c r="U7" t="n">
+      <c r="U8" t="n">
         <v>6</v>
       </c>
-      <c r="V7" s="2" t="inlineStr">
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>Mindre hackspett
 Klippfrullania
@@ -1250,155 +1362,43 @@
 Spillkråka</t>
         </is>
       </c>
-      <c r="W7">
+      <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 4263-2024 artfynd.xlsx", "A 4263-2024")</f>
         <v/>
       </c>
-      <c r="X7">
+      <c r="X8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 4263-2024 karta.png", "A 4263-2024")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 4263-2024 georefererad karta.tif", "A 4263-2024")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 4263-2024 FSC-klagomål.docx", "A 4263-2024")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 4263-2024 FSC-klagomål mail.docx", "A 4263-2024")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 4263-2024 tillsynsbegäran.docx", "A 4263-2024")</f>
         <v/>
       </c>
-      <c r="AD7">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 4263-2024 tillsynsbegäran mail.docx", "A 4263-2024")</f>
         <v/>
       </c>
-      <c r="AE7">
+      <c r="AE8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 4263-2024 prioriterade fågelarter.docx", "A 4263-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A 59985-2025</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>45993</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46307</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>KUNGÄLV</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="J8" t="n">
-        <v>2</v>
-      </c>
-      <c r="K8" t="n">
-        <v>2</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>4</v>
-      </c>
-      <c r="T8" t="n">
-        <v>19</v>
-      </c>
-      <c r="U8" t="n">
-        <v>19</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>Blåmossa
-Västlig hakmossa
-Spillkråka
-Äkta lopplummer</t>
-        </is>
-      </c>
-      <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 59985-2025 artfynd.xlsx", "A 59985-2025")</f>
-        <v/>
-      </c>
-      <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 59985-2025 karta.png", "A 59985-2025")</f>
-        <v/>
-      </c>
-      <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 59985-2025 georefererad karta.tif", "A 59985-2025")</f>
-        <v/>
-      </c>
-      <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 59985-2025 FSC-klagomål.docx", "A 59985-2025")</f>
-        <v/>
-      </c>
-      <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 59985-2025 FSC-klagomål mail.docx", "A 59985-2025")</f>
-        <v/>
-      </c>
-      <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 59985-2025 tillsynsbegäran.docx", "A 59985-2025")</f>
-        <v/>
-      </c>
-      <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 59985-2025 tillsynsbegäran mail.docx", "A 59985-2025")</f>
-        <v/>
-      </c>
-      <c r="AE8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 59985-2025 prioriterade fågelarter.docx", "A 59985-2025")</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 58408-2025</t>
+          <t>A 29061-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1408,14 +1408,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45985</v>
+        <v>46199</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1428,16 +1428,16 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>8.1</v>
+        <v>7.5</v>
       </c>
       <c r="J9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -1452,7 +1452,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -1461,381 +1461,381 @@
         <v>3</v>
       </c>
       <c r="T9" t="n">
+        <v>4</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Blåsippa
+Spillkråka
+Skogsödla</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 29061-2026 artfynd.xlsx", "A 29061-2026")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 29061-2026 karta.png", "A 29061-2026")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 29061-2026 georefererad karta.tif", "A 29061-2026")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 29061-2026 FSC-klagomål.docx", "A 29061-2026")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 29061-2026 FSC-klagomål mail.docx", "A 29061-2026")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 29061-2026 tillsynsbegäran.docx", "A 29061-2026")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 29061-2026 tillsynsbegäran mail.docx", "A 29061-2026")</f>
+        <v/>
+      </c>
+      <c r="AE9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 29061-2026 prioriterade fågelarter.docx", "A 29061-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 8558-2024</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>45355</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46308</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>KUNGÄLV</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="J10" t="n">
         <v>3</v>
       </c>
-      <c r="U9" t="n">
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
         <v>3</v>
       </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>3</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Gulsparv
+Spillkråka
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 8558-2024 artfynd.xlsx", "A 8558-2024")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 8558-2024 karta.png", "A 8558-2024")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 8558-2024 georefererad karta.tif", "A 8558-2024")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 8558-2024 FSC-klagomål.docx", "A 8558-2024")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 8558-2024 FSC-klagomål mail.docx", "A 8558-2024")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 8558-2024 tillsynsbegäran.docx", "A 8558-2024")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 8558-2024 tillsynsbegäran mail.docx", "A 8558-2024")</f>
+        <v/>
+      </c>
+      <c r="AE10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 8558-2024 prioriterade fågelarter.docx", "A 8558-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 30872-2026</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>46212</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46308</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>KUNGÄLV</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>3</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Blåmossa
+Platt fjädermossa
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 30872-2026 artfynd.xlsx", "A 30872-2026")</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 30872-2026 karta.png", "A 30872-2026")</f>
+        <v/>
+      </c>
+      <c r="Y11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 30872-2026 georefererad karta.tif", "A 30872-2026")</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 30872-2026 FSC-klagomål.docx", "A 30872-2026")</f>
+        <v/>
+      </c>
+      <c r="AB11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 30872-2026 FSC-klagomål mail.docx", "A 30872-2026")</f>
+        <v/>
+      </c>
+      <c r="AC11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 30872-2026 tillsynsbegäran.docx", "A 30872-2026")</f>
+        <v/>
+      </c>
+      <c r="AD11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 30872-2026 tillsynsbegäran mail.docx", "A 30872-2026")</f>
+        <v/>
+      </c>
+      <c r="AE11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 30872-2026 prioriterade fågelarter.docx", "A 30872-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A 58408-2025</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>45985</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46308</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>KUNGÄLV</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3</v>
+      </c>
+      <c r="U12" t="n">
+        <v>3</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>Älg
 Spillkråka
 Revlummer</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 58408-2025 artfynd.xlsx", "A 58408-2025")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 58408-2025 karta.png", "A 58408-2025")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 58408-2025 georefererad karta.tif", "A 58408-2025")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 58408-2025 FSC-klagomål.docx", "A 58408-2025")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 58408-2025 FSC-klagomål mail.docx", "A 58408-2025")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 58408-2025 tillsynsbegäran.docx", "A 58408-2025")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 58408-2025 tillsynsbegäran mail.docx", "A 58408-2025")</f>
         <v/>
       </c>
-      <c r="AE9">
+      <c r="AE12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 58408-2025 prioriterade fågelarter.docx", "A 58408-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 29061-2026</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>46199</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46307</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>KUNGÄLV</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="J10" t="n">
-        <v>3</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3</v>
-      </c>
-      <c r="T10" t="n">
-        <v>4</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Blåsippa
-Spillkråka
-Skogsödla</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 29061-2026 artfynd.xlsx", "A 29061-2026")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 29061-2026 karta.png", "A 29061-2026")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 29061-2026 georefererad karta.tif", "A 29061-2026")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 29061-2026 FSC-klagomål.docx", "A 29061-2026")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 29061-2026 FSC-klagomål mail.docx", "A 29061-2026")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 29061-2026 tillsynsbegäran.docx", "A 29061-2026")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 29061-2026 tillsynsbegäran mail.docx", "A 29061-2026")</f>
-        <v/>
-      </c>
-      <c r="AE10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 29061-2026 prioriterade fågelarter.docx", "A 29061-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 8558-2024</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>45355</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46307</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>KUNGÄLV</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="J11" t="n">
-        <v>3</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3</v>
-      </c>
-      <c r="T11" t="n">
-        <v>3</v>
-      </c>
-      <c r="U11" t="n">
-        <v>3</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Gulsparv
-Spillkråka
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 8558-2024 artfynd.xlsx", "A 8558-2024")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 8558-2024 karta.png", "A 8558-2024")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 8558-2024 georefererad karta.tif", "A 8558-2024")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 8558-2024 FSC-klagomål.docx", "A 8558-2024")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 8558-2024 FSC-klagomål mail.docx", "A 8558-2024")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 8558-2024 tillsynsbegäran.docx", "A 8558-2024")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 8558-2024 tillsynsbegäran mail.docx", "A 8558-2024")</f>
-        <v/>
-      </c>
-      <c r="AE11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 8558-2024 prioriterade fågelarter.docx", "A 8558-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 30872-2026</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>46212</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46307</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>KUNGÄLV</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="J12" t="n">
-        <v>1</v>
-      </c>
-      <c r="K12" t="n">
-        <v>2</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>3</v>
-      </c>
-      <c r="T12" t="n">
-        <v>3</v>
-      </c>
-      <c r="U12" t="n">
-        <v>3</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>Blåmossa
-Platt fjädermossa
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 30872-2026 artfynd.xlsx", "A 30872-2026")</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 30872-2026 karta.png", "A 30872-2026")</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 30872-2026 georefererad karta.tif", "A 30872-2026")</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 30872-2026 FSC-klagomål.docx", "A 30872-2026")</f>
-        <v/>
-      </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 30872-2026 FSC-klagomål mail.docx", "A 30872-2026")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 30872-2026 tillsynsbegäran.docx", "A 30872-2026")</f>
-        <v/>
-      </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 30872-2026 tillsynsbegäran mail.docx", "A 30872-2026")</f>
-        <v/>
-      </c>
-      <c r="AE12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 30872-2026 prioriterade fågelarter.docx", "A 30872-2026")</f>
         <v/>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
         <v>45957</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1970,7 +1970,7 @@
         <v>45334</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2076,7 +2076,7 @@
         <v>45334</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
         <v>45974</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 57116-2025</t>
+          <t>A 30860-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2285,10 +2285,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45979</v>
+        <v>46212</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>3.5</v>
+        <v>1.7</v>
       </c>
       <c r="J17" t="n">
         <v>1</v>
@@ -2310,7 +2310,7 @@
         <v>1</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -2325,7 +2325,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -2334,157 +2334,157 @@
         <v>2</v>
       </c>
       <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>Grönsångare
+Västlig hakmossa</t>
+        </is>
+      </c>
+      <c r="W17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 30860-2026 artfynd.xlsx", "A 30860-2026")</f>
+        <v/>
+      </c>
+      <c r="X17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 30860-2026 karta.png", "A 30860-2026")</f>
+        <v/>
+      </c>
+      <c r="Y17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 30860-2026 georefererad karta.tif", "A 30860-2026")</f>
+        <v/>
+      </c>
+      <c r="AA17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 30860-2026 FSC-klagomål.docx", "A 30860-2026")</f>
+        <v/>
+      </c>
+      <c r="AB17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 30860-2026 FSC-klagomål mail.docx", "A 30860-2026")</f>
+        <v/>
+      </c>
+      <c r="AC17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 30860-2026 tillsynsbegäran.docx", "A 30860-2026")</f>
+        <v/>
+      </c>
+      <c r="AD17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 30860-2026 tillsynsbegäran mail.docx", "A 30860-2026")</f>
+        <v/>
+      </c>
+      <c r="AE17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 30860-2026 prioriterade fågelarter.docx", "A 30860-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>A 57116-2025</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>45979</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>46308</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>KUNGÄLV</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2</v>
+      </c>
+      <c r="T18" t="n">
         <v>3</v>
       </c>
-      <c r="U17" t="n">
+      <c r="U18" t="n">
         <v>3</v>
       </c>
-      <c r="V17" s="2" t="inlineStr">
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>Västlig hakmossa
 Spillkråka</t>
         </is>
       </c>
-      <c r="W17">
+      <c r="W18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 57116-2025 artfynd.xlsx", "A 57116-2025")</f>
         <v/>
       </c>
-      <c r="X17">
+      <c r="X18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 57116-2025 karta.png", "A 57116-2025")</f>
         <v/>
       </c>
-      <c r="Y17">
+      <c r="Y18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 57116-2025 georefererad karta.tif", "A 57116-2025")</f>
         <v/>
       </c>
-      <c r="AA17">
+      <c r="AA18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 57116-2025 FSC-klagomål.docx", "A 57116-2025")</f>
         <v/>
       </c>
-      <c r="AB17">
+      <c r="AB18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 57116-2025 FSC-klagomål mail.docx", "A 57116-2025")</f>
         <v/>
       </c>
-      <c r="AC17">
+      <c r="AC18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 57116-2025 tillsynsbegäran.docx", "A 57116-2025")</f>
         <v/>
       </c>
-      <c r="AD17">
+      <c r="AD18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 57116-2025 tillsynsbegäran mail.docx", "A 57116-2025")</f>
         <v/>
       </c>
-      <c r="AE17">
+      <c r="AE18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 57116-2025 prioriterade fågelarter.docx", "A 57116-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 30860-2026</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>46212</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46307</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>KUNGÄLV</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="J18" t="n">
-        <v>1</v>
-      </c>
-      <c r="K18" t="n">
-        <v>1</v>
-      </c>
-      <c r="L18" t="n">
-        <v>1</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>1</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>Grönsångare
-Västlig hakmossa</t>
-        </is>
-      </c>
-      <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 30860-2026 artfynd.xlsx", "A 30860-2026")</f>
-        <v/>
-      </c>
-      <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 30860-2026 karta.png", "A 30860-2026")</f>
-        <v/>
-      </c>
-      <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 30860-2026 georefererad karta.tif", "A 30860-2026")</f>
-        <v/>
-      </c>
-      <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 30860-2026 FSC-klagomål.docx", "A 30860-2026")</f>
-        <v/>
-      </c>
-      <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 30860-2026 FSC-klagomål mail.docx", "A 30860-2026")</f>
-        <v/>
-      </c>
-      <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 30860-2026 tillsynsbegäran.docx", "A 30860-2026")</f>
-        <v/>
-      </c>
-      <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 30860-2026 tillsynsbegäran mail.docx", "A 30860-2026")</f>
-        <v/>
-      </c>
-      <c r="AE18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 30860-2026 prioriterade fågelarter.docx", "A 30860-2026")</f>
         <v/>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
         <v>45957</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
         <v>44838</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2706,7 +2706,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 49988-2023</t>
+          <t>A 30862-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2720,10 +2720,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45215</v>
+        <v>46212</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="J21" t="n">
         <v>1</v>
@@ -2769,49 +2769,49 @@
         <v>1</v>
       </c>
       <c r="T21" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U21" t="n">
         <v>0</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 49988-2023 artfynd.xlsx", "A 49988-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 30862-2026 artfynd.xlsx", "A 30862-2026")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 49988-2023 karta.png", "A 49988-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 30862-2026 karta.png", "A 30862-2026")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 49988-2023 georefererad karta.tif", "A 49988-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 30862-2026 georefererad karta.tif", "A 30862-2026")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 49988-2023 FSC-klagomål.docx", "A 49988-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 30862-2026 FSC-klagomål.docx", "A 30862-2026")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 49988-2023 FSC-klagomål mail.docx", "A 49988-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 30862-2026 FSC-klagomål mail.docx", "A 30862-2026")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 49988-2023 tillsynsbegäran.docx", "A 49988-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 30862-2026 tillsynsbegäran.docx", "A 30862-2026")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 49988-2023 tillsynsbegäran mail.docx", "A 49988-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 30862-2026 tillsynsbegäran mail.docx", "A 30862-2026")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 23704-2024</t>
+          <t>A 6082-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2825,10 +2825,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45454</v>
+        <v>45697</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2841,7 +2841,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>4.9</v>
+        <v>2.8</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
@@ -2853,7 +2853,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
@@ -2865,58 +2865,62 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
       </c>
       <c r="T22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U22" t="n">
         <v>1</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Hedjohannesört</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 23704-2024 artfynd.xlsx", "A 23704-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 6082-2025 artfynd.xlsx", "A 6082-2025")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 23704-2024 karta.png", "A 23704-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 6082-2025 karta.png", "A 6082-2025")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 23704-2024 georefererad karta.tif", "A 23704-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 6082-2025 georefererad karta.tif", "A 6082-2025")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 23704-2024 FSC-klagomål.docx", "A 23704-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 6082-2025 FSC-klagomål.docx", "A 6082-2025")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 23704-2024 FSC-klagomål mail.docx", "A 23704-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 6082-2025 FSC-klagomål mail.docx", "A 6082-2025")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 23704-2024 tillsynsbegäran.docx", "A 23704-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 6082-2025 tillsynsbegäran.docx", "A 6082-2025")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 23704-2024 tillsynsbegäran mail.docx", "A 23704-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 6082-2025 tillsynsbegäran mail.docx", "A 6082-2025")</f>
+        <v/>
+      </c>
+      <c r="AE22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 6082-2025 prioriterade fågelarter.docx", "A 6082-2025")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 6082-2025</t>
+          <t>A 42407-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2930,10 +2934,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45697</v>
+        <v>46307</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2946,17 +2950,17 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>2.8</v>
+        <v>1.7</v>
       </c>
       <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
         <v>1</v>
       </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
       <c r="M23" t="n">
         <v>0</v>
       </c>
@@ -2970,7 +2974,7 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -2982,50 +2986,46 @@
         <v>1</v>
       </c>
       <c r="U23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dunmossa</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 6082-2025 artfynd.xlsx", "A 6082-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 42407-2026 artfynd.xlsx", "A 42407-2026")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 6082-2025 karta.png", "A 6082-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 42407-2026 karta.png", "A 42407-2026")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 6082-2025 georefererad karta.tif", "A 6082-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 42407-2026 georefererad karta.tif", "A 42407-2026")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 6082-2025 FSC-klagomål.docx", "A 6082-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 42407-2026 FSC-klagomål.docx", "A 42407-2026")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 6082-2025 FSC-klagomål mail.docx", "A 6082-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 42407-2026 FSC-klagomål mail.docx", "A 42407-2026")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 6082-2025 tillsynsbegäran.docx", "A 6082-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 42407-2026 tillsynsbegäran.docx", "A 42407-2026")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 6082-2025 tillsynsbegäran mail.docx", "A 6082-2025")</f>
-        <v/>
-      </c>
-      <c r="AE23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 6082-2025 prioriterade fågelarter.docx", "A 6082-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 42407-2026 tillsynsbegäran mail.docx", "A 42407-2026")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 30862-2026</t>
+          <t>A 23704-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3039,10 +3039,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46212</v>
+        <v>45454</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3055,7 +3055,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.7</v>
+        <v>4.9</v>
       </c>
       <c r="J24" t="n">
         <v>1</v>
@@ -3067,7 +3067,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
@@ -3079,58 +3079,58 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
       </c>
       <c r="T24" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Hedjohannesört</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 30862-2026 artfynd.xlsx", "A 30862-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 23704-2024 artfynd.xlsx", "A 23704-2024")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 30862-2026 karta.png", "A 30862-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 23704-2024 karta.png", "A 23704-2024")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 30862-2026 georefererad karta.tif", "A 30862-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 23704-2024 georefererad karta.tif", "A 23704-2024")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 30862-2026 FSC-klagomål.docx", "A 30862-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 23704-2024 FSC-klagomål.docx", "A 23704-2024")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 30862-2026 FSC-klagomål mail.docx", "A 30862-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 23704-2024 FSC-klagomål mail.docx", "A 23704-2024")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 30862-2026 tillsynsbegäran.docx", "A 30862-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 23704-2024 tillsynsbegäran.docx", "A 23704-2024")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 30862-2026 tillsynsbegäran mail.docx", "A 30862-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 23704-2024 tillsynsbegäran mail.docx", "A 23704-2024")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 19132-2022</t>
+          <t>A 49988-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3144,10 +3144,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44691</v>
+        <v>45215</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3160,10 +3160,10 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.3</v>
+        <v>2.3</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -3190,20 +3190,52 @@
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U25" t="n">
         <v>0</v>
       </c>
-      <c r="V25" s="2" t="inlineStr"/>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="W25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 49988-2023 artfynd.xlsx", "A 49988-2023")</f>
+        <v/>
+      </c>
+      <c r="X25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 49988-2023 karta.png", "A 49988-2023")</f>
+        <v/>
+      </c>
+      <c r="Y25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 49988-2023 georefererad karta.tif", "A 49988-2023")</f>
+        <v/>
+      </c>
+      <c r="AA25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 49988-2023 FSC-klagomål.docx", "A 49988-2023")</f>
+        <v/>
+      </c>
+      <c r="AB25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 49988-2023 FSC-klagomål mail.docx", "A 49988-2023")</f>
+        <v/>
+      </c>
+      <c r="AC25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 49988-2023 tillsynsbegäran.docx", "A 49988-2023")</f>
+        <v/>
+      </c>
+      <c r="AD25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 49988-2023 tillsynsbegäran mail.docx", "A 49988-2023")</f>
+        <v/>
+      </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 19133-2022</t>
+          <t>A 19132-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3220,7 +3252,7 @@
         <v>44691</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3276,7 +3308,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 43709-2022</t>
+          <t>A 19133-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3290,10 +3322,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44836</v>
+        <v>44691</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3306,7 +3338,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>3.5</v>
+        <v>1.3</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3349,7 +3381,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 30373-2022</t>
+          <t>A 43709-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3363,10 +3395,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44760</v>
+        <v>44836</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3379,7 +3411,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.8</v>
+        <v>3.5</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3422,7 +3454,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 30377-2022</t>
+          <t>A 30322-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3439,7 +3471,7 @@
         <v>44760</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3452,7 +3484,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3495,7 +3527,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 30322-2022</t>
+          <t>A 30373-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3512,7 +3544,7 @@
         <v>44760</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3525,7 +3557,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.9</v>
+        <v>0.8</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3568,7 +3600,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 24461-2023</t>
+          <t>A 30377-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3582,10 +3614,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45082</v>
+        <v>44760</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3598,7 +3630,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3641,7 +3673,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 13880-2024</t>
+          <t>A 17455-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3655,10 +3687,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45391</v>
+        <v>45757</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3671,7 +3703,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3714,7 +3746,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 143-2023</t>
+          <t>A 62221-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3728,10 +3760,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44928</v>
+        <v>45267</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3744,7 +3776,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3787,7 +3819,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 62221-2023</t>
+          <t>A 40951-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3801,10 +3833,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45267</v>
+        <v>45897</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3817,7 +3849,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3860,7 +3892,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 4204-2024</t>
+          <t>A 21389-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3874,10 +3906,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45324</v>
+        <v>45063</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3890,7 +3922,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>4.4</v>
+        <v>3.4</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3933,7 +3965,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 1995-2024</t>
+          <t>A 4262-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3947,10 +3979,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45308</v>
+        <v>45324</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3963,7 +3995,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.5</v>
+        <v>14</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4006,7 +4038,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 30170-2022</t>
+          <t>A 45124-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4020,10 +4052,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44757</v>
+        <v>45919</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4036,7 +4068,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4079,7 +4111,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 10810-2023</t>
+          <t>A 21240-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4093,10 +4125,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44989</v>
+        <v>45058</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4109,7 +4141,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.4</v>
+        <v>2.3</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4152,7 +4184,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 45990-2022</t>
+          <t>A 47564-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4166,10 +4198,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44846</v>
+        <v>45931</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4182,7 +4214,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>3.3</v>
+        <v>2</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4242,7 +4274,7 @@
         <v>44508</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4298,7 +4330,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 62128-2021</t>
+          <t>A 52932-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4312,10 +4344,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44502</v>
+        <v>45957</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4328,7 +4360,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.8</v>
+        <v>3.4</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4371,7 +4403,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 21240-2023</t>
+          <t>A 29952-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4385,10 +4417,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45058</v>
+        <v>46205</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4401,7 +4433,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4444,7 +4476,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 17922-2025</t>
+          <t>A 10677-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4458,10 +4490,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45758</v>
+        <v>45721</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4474,7 +4506,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.8</v>
+        <v>7.4</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4517,7 +4549,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 18851-2024</t>
+          <t>A 10679-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4531,10 +4563,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45426</v>
+        <v>45721</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4547,7 +4579,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2.7</v>
+        <v>4.4</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4590,7 +4622,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 21389-2023</t>
+          <t>A 11237-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4604,10 +4636,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45063</v>
+        <v>45726</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4620,7 +4652,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4663,7 +4695,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 44176-2023</t>
+          <t>A 30738-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4677,10 +4709,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45188</v>
+        <v>46211</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4693,7 +4725,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>7.1</v>
+        <v>3.5</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4736,7 +4768,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 7505-2024</t>
+          <t>A 30859-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4750,10 +4782,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45347</v>
+        <v>46212</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4766,7 +4798,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4809,7 +4841,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 40951-2025</t>
+          <t>A 74285-2021</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4823,10 +4855,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45897</v>
+        <v>44558</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4839,7 +4871,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4882,7 +4914,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 23457-2024</t>
+          <t>A 61417-2022</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4896,10 +4928,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45453</v>
+        <v>44916</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4912,7 +4944,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>5.1</v>
+        <v>3.6</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4955,7 +4987,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 39714-2024</t>
+          <t>A 32272-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4969,10 +5001,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45552</v>
+        <v>45120</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4985,7 +5017,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.2</v>
+        <v>4.9</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5028,7 +5060,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 18852-2024</t>
+          <t>A 32847-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5042,10 +5074,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45426</v>
+        <v>45124</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5058,7 +5090,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2.7</v>
+        <v>4.7</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5101,7 +5133,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 43520-2022</t>
+          <t>A 29223-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5115,10 +5147,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44837</v>
+        <v>45482</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5131,7 +5163,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.5</v>
+        <v>5.6</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5174,7 +5206,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 51724-2023</t>
+          <t>A 38262-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5188,10 +5220,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45222</v>
+        <v>46281</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5204,7 +5236,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5247,7 +5279,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 29223-2024</t>
+          <t>A 10655-2022</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5261,10 +5293,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45482</v>
+        <v>44624</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5277,7 +5309,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>5.6</v>
+        <v>13.3</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5320,7 +5352,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 45124-2025</t>
+          <t>A 34366-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5334,10 +5366,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45919</v>
+        <v>44792</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5350,7 +5382,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>3.7</v>
+        <v>0.5</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5393,7 +5425,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 10679-2025</t>
+          <t>A 4673-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5407,10 +5439,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45721</v>
+        <v>46048</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5423,7 +5455,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>4.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5466,7 +5498,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 11237-2025</t>
+          <t>A 34244-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5480,10 +5512,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45726</v>
+        <v>45844</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5496,7 +5528,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>4.2</v>
+        <v>2.9</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5539,7 +5571,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 10677-2025</t>
+          <t>A 25624-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5553,10 +5585,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45721</v>
+        <v>45803</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5569,7 +5601,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>7.4</v>
+        <v>5</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5612,7 +5644,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 74285-2021</t>
+          <t>A 6946-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5622,14 +5654,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44558</v>
+        <v>46057</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5642,7 +5674,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.1</v>
+        <v>2.2</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5685,7 +5717,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 10655-2022</t>
+          <t>A 41442-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5699,10 +5731,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44624</v>
+        <v>45869</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5715,7 +5747,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>13.3</v>
+        <v>1.8</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5758,7 +5790,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 17455-2025</t>
+          <t>A 39714-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5772,10 +5804,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45757</v>
+        <v>45552</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5788,7 +5820,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>2.1</v>
+        <v>1.2</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5831,7 +5863,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 8334-2023</t>
+          <t>A 17922-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5845,10 +5877,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44975</v>
+        <v>45758</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5861,7 +5893,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5904,7 +5936,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 47564-2025</t>
+          <t>A 37443-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5918,10 +5950,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45931</v>
+        <v>45877</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5933,8 +5965,13 @@
           <t>KUNGÄLV</t>
         </is>
       </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I63" t="n">
-        <v>2</v>
+        <v>0.7</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5977,7 +6014,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 19531-2023</t>
+          <t>A 34386-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5991,10 +6028,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45050</v>
+        <v>46254</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6007,7 +6044,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6050,7 +6087,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 61417-2022</t>
+          <t>A 34396-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6064,10 +6101,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44916</v>
+        <v>46254</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6080,7 +6117,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>3.6</v>
+        <v>0.8</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6123,7 +6160,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 32272-2023</t>
+          <t>A 13990-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6137,10 +6174,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45120</v>
+        <v>46098</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6153,7 +6190,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>4.9</v>
+        <v>2.6</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6196,7 +6233,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 32847-2023</t>
+          <t>A 34392-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6210,10 +6247,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45124</v>
+        <v>46254</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6226,7 +6263,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>4.7</v>
+        <v>0.4</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6269,7 +6306,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 5705-2025</t>
+          <t>A 34387-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6279,14 +6316,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45694</v>
+        <v>46254</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6299,7 +6336,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.2</v>
+        <v>0.3</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6342,7 +6379,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 62979-2023</t>
+          <t>A 41656-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6352,14 +6389,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45271</v>
+        <v>46302</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6415,7 +6452,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 52932-2025</t>
+          <t>A 19531-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6429,10 +6466,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45957</v>
+        <v>45050</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6445,7 +6482,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>3.4</v>
+        <v>1.9</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6488,7 +6525,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 4262-2024</t>
+          <t>A 49985-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6502,10 +6539,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45324</v>
+        <v>45215</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6518,7 +6555,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>14</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6561,7 +6598,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 16538-2025</t>
+          <t>A 5705-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6571,14 +6608,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45751</v>
+        <v>45694</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6591,7 +6628,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6634,7 +6671,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 661-2025</t>
+          <t>A 50071-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6648,10 +6685,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45664</v>
+        <v>45215</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6664,7 +6701,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6707,7 +6744,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 34244-2025</t>
+          <t>A 7505-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6721,10 +6758,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45844</v>
+        <v>45347</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6737,7 +6774,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>2.9</v>
+        <v>1.8</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6780,7 +6817,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 29801-2022</t>
+          <t>A 8334-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6794,10 +6831,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44755</v>
+        <v>44975</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6810,7 +6847,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>4.8</v>
+        <v>1.8</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6853,7 +6890,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 49981-2023</t>
+          <t>A 22731-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6867,10 +6904,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45215</v>
+        <v>46157</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6883,7 +6920,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6926,7 +6963,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 25624-2025</t>
+          <t>A 32391-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6940,10 +6977,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45803</v>
+        <v>45837</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6956,7 +6993,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>5</v>
+        <v>2.1</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6999,7 +7036,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 41442-2025</t>
+          <t>A 23607-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7013,10 +7050,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45869</v>
+        <v>46163</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7029,7 +7066,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.8</v>
+        <v>5.3</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7072,7 +7109,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 71835-2021</t>
+          <t>A 25135-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7086,10 +7123,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44543</v>
+        <v>45798</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7102,7 +7139,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>7.5</v>
+        <v>1.1</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7145,7 +7182,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 13990-2026</t>
+          <t>A 49981-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7159,10 +7196,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46098</v>
+        <v>45215</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7175,7 +7212,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7218,7 +7255,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 49985-2023</t>
+          <t>A 56782-2022</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7232,10 +7269,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45215</v>
+        <v>44894</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7248,7 +7285,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>8.199999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7291,7 +7328,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 56782-2022</t>
+          <t>A 1995-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7305,10 +7342,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44894</v>
+        <v>45308</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7364,7 +7401,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 50071-2023</t>
+          <t>A 30170-2022</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7378,10 +7415,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45215</v>
+        <v>44757</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7394,7 +7431,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>4</v>
+        <v>3.1</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7437,7 +7474,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 26812-2024</t>
+          <t>A 10810-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7451,10 +7488,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45470</v>
+        <v>44989</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7467,7 +7504,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.7</v>
+        <v>0.4</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7510,7 +7547,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 34366-2022</t>
+          <t>A 4204-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7524,10 +7561,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>44792</v>
+        <v>45324</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7540,7 +7577,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>0.5</v>
+        <v>4.4</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7583,7 +7620,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 4673-2026</t>
+          <t>A 62128-2021</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7597,10 +7634,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46048</v>
+        <v>44502</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7613,7 +7650,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>8.199999999999999</v>
+        <v>1.8</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7656,7 +7693,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 6946-2026</t>
+          <t>A 62979-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7670,10 +7707,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46057</v>
+        <v>45271</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7686,7 +7723,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>2.2</v>
+        <v>0.8</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7729,7 +7766,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 37443-2025</t>
+          <t>A 44176-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7743,10 +7780,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45877</v>
+        <v>45188</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7758,13 +7795,8 @@
           <t>KUNGÄLV</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I88" t="n">
-        <v>0.7</v>
+        <v>7.1</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7807,7 +7839,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 22731-2026</t>
+          <t>A 26812-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7821,10 +7853,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46157</v>
+        <v>45470</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7837,7 +7869,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7880,7 +7912,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 32391-2025</t>
+          <t>A 29801-2022</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7894,10 +7926,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45837</v>
+        <v>44755</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7910,7 +7942,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>2.1</v>
+        <v>4.8</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7953,7 +7985,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 23607-2026</t>
+          <t>A 18852-2024</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7967,10 +7999,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46163</v>
+        <v>45426</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7983,7 +8015,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>5.3</v>
+        <v>2.7</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8026,7 +8058,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 25135-2025</t>
+          <t>A 43520-2022</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8040,10 +8072,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45798</v>
+        <v>44837</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8056,7 +8088,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8099,7 +8131,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 29952-2026</t>
+          <t>A 16538-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8113,10 +8145,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>46205</v>
+        <v>45751</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8129,7 +8161,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8172,7 +8204,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 30738-2026</t>
+          <t>A 45990-2022</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8186,10 +8218,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>46211</v>
+        <v>44846</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8202,7 +8234,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8245,7 +8277,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 30859-2026</t>
+          <t>A 143-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8259,10 +8291,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>46212</v>
+        <v>44928</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8318,7 +8350,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 38262-2026</t>
+          <t>A 18851-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8332,10 +8364,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>46281</v>
+        <v>45426</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8348,7 +8380,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8391,7 +8423,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 34387-2026</t>
+          <t>A 71835-2021</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8405,10 +8437,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>46254</v>
+        <v>44543</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8421,7 +8453,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>0.3</v>
+        <v>7.5</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8464,7 +8496,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 34386-2026</t>
+          <t>A 51724-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8478,10 +8510,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>46254</v>
+        <v>45222</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8494,7 +8526,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>0.7</v>
+        <v>3.1</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8537,7 +8569,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 34392-2026</t>
+          <t>A 661-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8551,10 +8583,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>46254</v>
+        <v>45664</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8567,7 +8599,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>0.4</v>
+        <v>3.1</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8610,7 +8642,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 34396-2026</t>
+          <t>A 24461-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8624,10 +8656,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>46254</v>
+        <v>45082</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8640,7 +8672,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8683,7 +8715,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 41656-2026</t>
+          <t>A 13880-2024</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8697,10 +8729,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>46302</v>
+        <v>45391</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8713,7 +8745,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>0.8</v>
+        <v>2.4</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8753,83 +8785,156 @@
       </c>
       <c r="V101" s="2" t="inlineStr"/>
     </row>
-    <row r="102">
+    <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
+          <t>A 23457-2024</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D102" s="1" t="n">
+        <v>45453</v>
+      </c>
+      <c r="E102" s="1" t="n">
+        <v>46308</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>KUNGÄLV</t>
+        </is>
+      </c>
+      <c r="I102" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="J102" t="n">
+        <v>0</v>
+      </c>
+      <c r="K102" t="n">
+        <v>0</v>
+      </c>
+      <c r="L102" t="n">
+        <v>0</v>
+      </c>
+      <c r="M102" t="n">
+        <v>0</v>
+      </c>
+      <c r="N102" t="n">
+        <v>0</v>
+      </c>
+      <c r="O102" t="n">
+        <v>0</v>
+      </c>
+      <c r="P102" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q102" t="n">
+        <v>0</v>
+      </c>
+      <c r="R102" t="n">
+        <v>0</v>
+      </c>
+      <c r="S102" t="n">
+        <v>0</v>
+      </c>
+      <c r="T102" t="n">
+        <v>0</v>
+      </c>
+      <c r="U102" t="n">
+        <v>0</v>
+      </c>
+      <c r="V102" s="2" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
           <t>S 817-2024</t>
         </is>
       </c>
-      <c r="B102" t="inlineStr">
+      <c r="B103" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C102" t="inlineStr">
+      <c r="C103" t="inlineStr">
         <is>
           <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
-      <c r="D102" s="1" t="n">
+      <c r="D103" s="1" t="n">
         <v>45371</v>
       </c>
-      <c r="E102" s="1" t="n">
-        <v>46307</v>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>KUNGÄLV</t>
-        </is>
-      </c>
-      <c r="H102" t="inlineStr">
+      <c r="E103" s="1" t="n">
+        <v>46308</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>KUNGÄLV</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
         <is>
           <t>Övriga statliga verk och myndigheter</t>
         </is>
       </c>
-      <c r="I102" t="n">
+      <c r="I103" t="n">
         <v>2.4</v>
       </c>
-      <c r="J102" t="n">
-        <v>0</v>
-      </c>
-      <c r="K102" t="n">
-        <v>0</v>
-      </c>
-      <c r="L102" t="n">
-        <v>0</v>
-      </c>
-      <c r="M102" t="n">
-        <v>0</v>
-      </c>
-      <c r="N102" t="n">
-        <v>0</v>
-      </c>
-      <c r="O102" t="n">
-        <v>0</v>
-      </c>
-      <c r="P102" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q102" t="n">
-        <v>0</v>
-      </c>
-      <c r="R102" t="n">
-        <v>0</v>
-      </c>
-      <c r="S102" t="n">
-        <v>0</v>
-      </c>
-      <c r="T102" t="n">
-        <v>0</v>
-      </c>
-      <c r="U102" t="n">
-        <v>0</v>
-      </c>
-      <c r="V102" s="2" t="inlineStr"/>
+      <c r="J103" t="n">
+        <v>0</v>
+      </c>
+      <c r="K103" t="n">
+        <v>0</v>
+      </c>
+      <c r="L103" t="n">
+        <v>0</v>
+      </c>
+      <c r="M103" t="n">
+        <v>0</v>
+      </c>
+      <c r="N103" t="n">
+        <v>0</v>
+      </c>
+      <c r="O103" t="n">
+        <v>0</v>
+      </c>
+      <c r="P103" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q103" t="n">
+        <v>0</v>
+      </c>
+      <c r="R103" t="n">
+        <v>0</v>
+      </c>
+      <c r="S103" t="n">
+        <v>0</v>
+      </c>
+      <c r="T103" t="n">
+        <v>0</v>
+      </c>
+      <c r="U103" t="n">
+        <v>0</v>
+      </c>
+      <c r="V103" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt KUNGÄLV.xlsx
+++ b/Översikt KUNGÄLV.xlsx
@@ -601,7 +601,7 @@
         <v>45548</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>45868</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -851,7 +851,7 @@
         <v>45526</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -948,7 +948,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 6041-2025</t>
+          <t>A 45243-2025</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -962,10 +962,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45695</v>
+        <v>45919</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -978,13 +978,13 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>8.800000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="J5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
         <v>2</v>
@@ -1011,12 +1011,125 @@
         <v>5</v>
       </c>
       <c r="T5" t="n">
+        <v>9</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>Gulsparv
+Nordfladdermus
+Större vattensalamander
+Mindre vattensalamander
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 45243-2025 artfynd.xlsx", "A 45243-2025")</f>
+        <v/>
+      </c>
+      <c r="X5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 45243-2025 karta.png", "A 45243-2025")</f>
+        <v/>
+      </c>
+      <c r="Y5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 45243-2025 georefererad karta.tif", "A 45243-2025")</f>
+        <v/>
+      </c>
+      <c r="AA5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 45243-2025 FSC-klagomål.docx", "A 45243-2025")</f>
+        <v/>
+      </c>
+      <c r="AB5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 45243-2025 FSC-klagomål mail.docx", "A 45243-2025")</f>
+        <v/>
+      </c>
+      <c r="AC5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 45243-2025 tillsynsbegäran.docx", "A 45243-2025")</f>
+        <v/>
+      </c>
+      <c r="AD5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 45243-2025 tillsynsbegäran mail.docx", "A 45243-2025")</f>
+        <v/>
+      </c>
+      <c r="AE5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 45243-2025 prioriterade fågelarter.docx", "A 45243-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A 6041-2025</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>45695</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>46309</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>KUNGÄLV</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="J6" t="n">
+        <v>3</v>
+      </c>
+      <c r="K6" t="n">
+        <v>2</v>
+      </c>
+      <c r="L6" t="n">
+        <v>2</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>2</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="n">
         <v>10</v>
       </c>
-      <c r="U5" t="n">
+      <c r="U6" t="n">
         <v>10</v>
       </c>
-      <c r="V5" s="2" t="inlineStr">
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>Björktrast
 Talltita
@@ -1025,149 +1138,36 @@
 Spillkråka</t>
         </is>
       </c>
-      <c r="W5">
+      <c r="W6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 6041-2025 artfynd.xlsx", "A 6041-2025")</f>
         <v/>
       </c>
-      <c r="X5">
+      <c r="X6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 6041-2025 karta.png", "A 6041-2025")</f>
         <v/>
       </c>
-      <c r="Y5">
+      <c r="Y6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 6041-2025 georefererad karta.tif", "A 6041-2025")</f>
         <v/>
       </c>
-      <c r="AA5">
+      <c r="AA6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 6041-2025 FSC-klagomål.docx", "A 6041-2025")</f>
         <v/>
       </c>
-      <c r="AB5">
+      <c r="AB6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 6041-2025 FSC-klagomål mail.docx", "A 6041-2025")</f>
         <v/>
       </c>
-      <c r="AC5">
+      <c r="AC6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 6041-2025 tillsynsbegäran.docx", "A 6041-2025")</f>
         <v/>
       </c>
-      <c r="AD5">
+      <c r="AD6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 6041-2025 tillsynsbegäran mail.docx", "A 6041-2025")</f>
         <v/>
       </c>
-      <c r="AE5">
+      <c r="AE6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 6041-2025 prioriterade fågelarter.docx", "A 6041-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>A 45243-2025</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>45919</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>46308</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>KUNGÄLV</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="J6" t="n">
-        <v>5</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>2</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>2</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
-        <v>5</v>
-      </c>
-      <c r="T6" t="n">
-        <v>9</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>Gulsparv
-Nordfladdermus
-Större vattensalamander
-Mindre vattensalamander
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 45243-2025 artfynd.xlsx", "A 45243-2025")</f>
-        <v/>
-      </c>
-      <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 45243-2025 karta.png", "A 45243-2025")</f>
-        <v/>
-      </c>
-      <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 45243-2025 georefererad karta.tif", "A 45243-2025")</f>
-        <v/>
-      </c>
-      <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 45243-2025 FSC-klagomål.docx", "A 45243-2025")</f>
-        <v/>
-      </c>
-      <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 45243-2025 FSC-klagomål mail.docx", "A 45243-2025")</f>
-        <v/>
-      </c>
-      <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 45243-2025 tillsynsbegäran.docx", "A 45243-2025")</f>
-        <v/>
-      </c>
-      <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 45243-2025 tillsynsbegäran mail.docx", "A 45243-2025")</f>
-        <v/>
-      </c>
-      <c r="AE6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 45243-2025 prioriterade fågelarter.docx", "A 45243-2025")</f>
         <v/>
       </c>
     </row>
@@ -1191,7 +1191,7 @@
         <v>45993</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         <v>45324</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1398,7 +1398,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 29061-2026</t>
+          <t>A 58408-2025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1408,14 +1408,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46199</v>
+        <v>45985</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1428,16 +1428,16 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>7.5</v>
+        <v>8.1</v>
       </c>
       <c r="J9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -1452,7 +1452,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -1461,381 +1461,381 @@
         <v>3</v>
       </c>
       <c r="T9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>3</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Älg
+Spillkråka
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 58408-2025 artfynd.xlsx", "A 58408-2025")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 58408-2025 karta.png", "A 58408-2025")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 58408-2025 georefererad karta.tif", "A 58408-2025")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 58408-2025 FSC-klagomål.docx", "A 58408-2025")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 58408-2025 FSC-klagomål mail.docx", "A 58408-2025")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 58408-2025 tillsynsbegäran.docx", "A 58408-2025")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 58408-2025 tillsynsbegäran mail.docx", "A 58408-2025")</f>
+        <v/>
+      </c>
+      <c r="AE9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 58408-2025 prioriterade fågelarter.docx", "A 58408-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 29061-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>46199</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46309</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>KUNGÄLV</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3</v>
+      </c>
+      <c r="T10" t="n">
         <v>4</v>
       </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Blåsippa
 Spillkråka
 Skogsödla</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 29061-2026 artfynd.xlsx", "A 29061-2026")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 29061-2026 karta.png", "A 29061-2026")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 29061-2026 georefererad karta.tif", "A 29061-2026")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 29061-2026 FSC-klagomål.docx", "A 29061-2026")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 29061-2026 FSC-klagomål mail.docx", "A 29061-2026")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 29061-2026 tillsynsbegäran.docx", "A 29061-2026")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 29061-2026 tillsynsbegäran mail.docx", "A 29061-2026")</f>
         <v/>
       </c>
-      <c r="AE9">
+      <c r="AE10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 29061-2026 prioriterade fågelarter.docx", "A 29061-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
         <is>
           <t>A 8558-2024</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
         <v>45355</v>
       </c>
-      <c r="E10" s="1" t="n">
-        <v>46308</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>KUNGÄLV</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
+      <c r="E11" s="1" t="n">
+        <v>46309</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>KUNGÄLV</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
         <v>12.5</v>
       </c>
-      <c r="J10" t="n">
+      <c r="J11" t="n">
         <v>3</v>
       </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
         <v>1</v>
       </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
         <v>1</v>
       </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
         <v>3</v>
       </c>
-      <c r="T10" t="n">
+      <c r="T11" t="n">
         <v>3</v>
       </c>
-      <c r="U10" t="n">
+      <c r="U11" t="n">
         <v>3</v>
       </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Gulsparv
 Spillkråka
 Revlummer</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 8558-2024 artfynd.xlsx", "A 8558-2024")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 8558-2024 karta.png", "A 8558-2024")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 8558-2024 georefererad karta.tif", "A 8558-2024")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 8558-2024 FSC-klagomål.docx", "A 8558-2024")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 8558-2024 FSC-klagomål mail.docx", "A 8558-2024")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 8558-2024 tillsynsbegäran.docx", "A 8558-2024")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 8558-2024 tillsynsbegäran mail.docx", "A 8558-2024")</f>
         <v/>
       </c>
-      <c r="AE10">
+      <c r="AE11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 8558-2024 prioriterade fågelarter.docx", "A 8558-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
         <is>
           <t>A 30872-2026</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
         <v>46212</v>
       </c>
-      <c r="E11" s="1" t="n">
-        <v>46308</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>KUNGÄLV</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
+      <c r="E12" s="1" t="n">
+        <v>46309</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>KUNGÄLV</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
         <v>2.4</v>
       </c>
-      <c r="J11" t="n">
+      <c r="J12" t="n">
         <v>1</v>
       </c>
-      <c r="K11" t="n">
+      <c r="K12" t="n">
         <v>2</v>
       </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
         <v>3</v>
       </c>
-      <c r="T11" t="n">
+      <c r="T12" t="n">
         <v>3</v>
       </c>
-      <c r="U11" t="n">
+      <c r="U12" t="n">
         <v>3</v>
       </c>
-      <c r="V11" s="2" t="inlineStr">
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>Blåmossa
 Platt fjädermossa
 Spillkråka</t>
         </is>
       </c>
-      <c r="W11">
+      <c r="W12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 30872-2026 artfynd.xlsx", "A 30872-2026")</f>
         <v/>
       </c>
-      <c r="X11">
+      <c r="X12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 30872-2026 karta.png", "A 30872-2026")</f>
         <v/>
       </c>
-      <c r="Y11">
+      <c r="Y12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 30872-2026 georefererad karta.tif", "A 30872-2026")</f>
         <v/>
       </c>
-      <c r="AA11">
+      <c r="AA12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 30872-2026 FSC-klagomål.docx", "A 30872-2026")</f>
         <v/>
       </c>
-      <c r="AB11">
+      <c r="AB12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 30872-2026 FSC-klagomål mail.docx", "A 30872-2026")</f>
         <v/>
       </c>
-      <c r="AC11">
+      <c r="AC12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 30872-2026 tillsynsbegäran.docx", "A 30872-2026")</f>
         <v/>
       </c>
-      <c r="AD11">
+      <c r="AD12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 30872-2026 tillsynsbegäran mail.docx", "A 30872-2026")</f>
         <v/>
       </c>
-      <c r="AE11">
+      <c r="AE12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 30872-2026 prioriterade fågelarter.docx", "A 30872-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 58408-2025</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>45985</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46308</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>KUNGÄLV</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="J12" t="n">
-        <v>2</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>3</v>
-      </c>
-      <c r="T12" t="n">
-        <v>3</v>
-      </c>
-      <c r="U12" t="n">
-        <v>3</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>Älg
-Spillkråka
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 58408-2025 artfynd.xlsx", "A 58408-2025")</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 58408-2025 karta.png", "A 58408-2025")</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 58408-2025 georefererad karta.tif", "A 58408-2025")</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 58408-2025 FSC-klagomål.docx", "A 58408-2025")</f>
-        <v/>
-      </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 58408-2025 FSC-klagomål mail.docx", "A 58408-2025")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 58408-2025 tillsynsbegäran.docx", "A 58408-2025")</f>
-        <v/>
-      </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 58408-2025 tillsynsbegäran mail.docx", "A 58408-2025")</f>
-        <v/>
-      </c>
-      <c r="AE12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 58408-2025 prioriterade fågelarter.docx", "A 58408-2025")</f>
         <v/>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
         <v>45957</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 5631-2024</t>
+          <t>A 56394-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1963,14 +1963,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45334</v>
+        <v>45974</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1986,10 +1986,10 @@
         <v>1.3</v>
       </c>
       <c r="J14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -2019,552 +2019,552 @@
         <v>2</v>
       </c>
       <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Kambräken
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 56394-2025 artfynd.xlsx", "A 56394-2025")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 56394-2025 karta.png", "A 56394-2025")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 56394-2025 georefererad karta.tif", "A 56394-2025")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 56394-2025 FSC-klagomål.docx", "A 56394-2025")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 56394-2025 FSC-klagomål mail.docx", "A 56394-2025")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 56394-2025 tillsynsbegäran.docx", "A 56394-2025")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 56394-2025 tillsynsbegäran mail.docx", "A 56394-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 57116-2025</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>45979</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46309</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>KUNGÄLV</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J15" t="n">
         <v>1</v>
       </c>
-      <c r="V14" s="2" t="inlineStr">
+      <c r="K15" t="n">
+        <v>1</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>3</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Västlig hakmossa
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 57116-2025 artfynd.xlsx", "A 57116-2025")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 57116-2025 karta.png", "A 57116-2025")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 57116-2025 georefererad karta.tif", "A 57116-2025")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 57116-2025 FSC-klagomål.docx", "A 57116-2025")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 57116-2025 FSC-klagomål mail.docx", "A 57116-2025")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 57116-2025 tillsynsbegäran.docx", "A 57116-2025")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 57116-2025 tillsynsbegäran mail.docx", "A 57116-2025")</f>
+        <v/>
+      </c>
+      <c r="AE15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 57116-2025 prioriterade fågelarter.docx", "A 57116-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 30860-2026</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>46212</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46309</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>KUNGÄLV</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Grönsångare
+Västlig hakmossa</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 30860-2026 artfynd.xlsx", "A 30860-2026")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 30860-2026 karta.png", "A 30860-2026")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 30860-2026 georefererad karta.tif", "A 30860-2026")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 30860-2026 FSC-klagomål.docx", "A 30860-2026")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 30860-2026 FSC-klagomål mail.docx", "A 30860-2026")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 30860-2026 tillsynsbegäran.docx", "A 30860-2026")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 30860-2026 tillsynsbegäran mail.docx", "A 30860-2026")</f>
+        <v/>
+      </c>
+      <c r="AE16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 30860-2026 prioriterade fågelarter.docx", "A 30860-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 5631-2024</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>45334</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46309</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>KUNGÄLV</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>Vanlig groda
 Fläcknycklar</t>
         </is>
       </c>
-      <c r="W14">
+      <c r="W17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 5631-2024 artfynd.xlsx", "A 5631-2024")</f>
         <v/>
       </c>
-      <c r="X14">
+      <c r="X17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 5631-2024 karta.png", "A 5631-2024")</f>
         <v/>
       </c>
-      <c r="Y14">
+      <c r="Y17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 5631-2024 georefererad karta.tif", "A 5631-2024")</f>
         <v/>
       </c>
-      <c r="AA14">
+      <c r="AA17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 5631-2024 FSC-klagomål.docx", "A 5631-2024")</f>
         <v/>
       </c>
-      <c r="AB14">
+      <c r="AB17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 5631-2024 FSC-klagomål mail.docx", "A 5631-2024")</f>
         <v/>
       </c>
-      <c r="AC14">
+      <c r="AC17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 5631-2024 tillsynsbegäran.docx", "A 5631-2024")</f>
         <v/>
       </c>
-      <c r="AD14">
+      <c r="AD17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 5631-2024 tillsynsbegäran mail.docx", "A 5631-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
         <is>
           <t>A 5637-2024</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
         <v>45334</v>
       </c>
-      <c r="E15" s="1" t="n">
-        <v>46308</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>KUNGÄLV</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
+      <c r="E18" s="1" t="n">
+        <v>46309</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>KUNGÄLV</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
         <v>1.8</v>
       </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
         <v>2</v>
       </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
         <v>2</v>
       </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
         <v>2</v>
       </c>
-      <c r="T15" t="n">
+      <c r="T18" t="n">
         <v>2</v>
       </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>Klofibbla
 Åkerrödtoppa</t>
         </is>
       </c>
-      <c r="W15">
+      <c r="W18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 5637-2024 artfynd.xlsx", "A 5637-2024")</f>
         <v/>
       </c>
-      <c r="X15">
+      <c r="X18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 5637-2024 karta.png", "A 5637-2024")</f>
         <v/>
       </c>
-      <c r="Y15">
+      <c r="Y18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 5637-2024 georefererad karta.tif", "A 5637-2024")</f>
         <v/>
       </c>
-      <c r="AA15">
+      <c r="AA18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 5637-2024 FSC-klagomål.docx", "A 5637-2024")</f>
         <v/>
       </c>
-      <c r="AB15">
+      <c r="AB18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 5637-2024 FSC-klagomål mail.docx", "A 5637-2024")</f>
         <v/>
       </c>
-      <c r="AC15">
+      <c r="AC18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 5637-2024 tillsynsbegäran.docx", "A 5637-2024")</f>
         <v/>
       </c>
-      <c r="AD15">
+      <c r="AD18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 5637-2024 tillsynsbegäran mail.docx", "A 5637-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 56394-2025</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>45974</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46308</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>KUNGÄLV</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="J16" t="n">
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>A 53007-2025</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>45957</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>46309</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>KUNGÄLV</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J19" t="n">
         <v>1</v>
       </c>
-      <c r="K16" t="n">
+      <c r="K19" t="n">
         <v>1</v>
       </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
         <v>2</v>
       </c>
-      <c r="T16" t="n">
-        <v>2</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>Kambräken
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 56394-2025 artfynd.xlsx", "A 56394-2025")</f>
-        <v/>
-      </c>
-      <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 56394-2025 karta.png", "A 56394-2025")</f>
-        <v/>
-      </c>
-      <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 56394-2025 georefererad karta.tif", "A 56394-2025")</f>
-        <v/>
-      </c>
-      <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 56394-2025 FSC-klagomål.docx", "A 56394-2025")</f>
-        <v/>
-      </c>
-      <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 56394-2025 FSC-klagomål mail.docx", "A 56394-2025")</f>
-        <v/>
-      </c>
-      <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 56394-2025 tillsynsbegäran.docx", "A 56394-2025")</f>
-        <v/>
-      </c>
-      <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 56394-2025 tillsynsbegäran mail.docx", "A 56394-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 30860-2026</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>46212</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46308</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>KUNGÄLV</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="J17" t="n">
-        <v>1</v>
-      </c>
-      <c r="K17" t="n">
-        <v>1</v>
-      </c>
-      <c r="L17" t="n">
-        <v>1</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Grönsångare
-Västlig hakmossa</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 30860-2026 artfynd.xlsx", "A 30860-2026")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 30860-2026 karta.png", "A 30860-2026")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 30860-2026 georefererad karta.tif", "A 30860-2026")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 30860-2026 FSC-klagomål.docx", "A 30860-2026")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 30860-2026 FSC-klagomål mail.docx", "A 30860-2026")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 30860-2026 tillsynsbegäran.docx", "A 30860-2026")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 30860-2026 tillsynsbegäran mail.docx", "A 30860-2026")</f>
-        <v/>
-      </c>
-      <c r="AE17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 30860-2026 prioriterade fågelarter.docx", "A 30860-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 57116-2025</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>45979</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46308</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>KUNGÄLV</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="J18" t="n">
-        <v>1</v>
-      </c>
-      <c r="K18" t="n">
-        <v>1</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2</v>
-      </c>
-      <c r="T18" t="n">
-        <v>3</v>
-      </c>
-      <c r="U18" t="n">
-        <v>3</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
+      <c r="T19" t="n">
+        <v>5</v>
+      </c>
+      <c r="U19" t="n">
+        <v>5</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>Västlig hakmossa
 Spillkråka</t>
         </is>
       </c>
-      <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 57116-2025 artfynd.xlsx", "A 57116-2025")</f>
-        <v/>
-      </c>
-      <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 57116-2025 karta.png", "A 57116-2025")</f>
-        <v/>
-      </c>
-      <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 57116-2025 georefererad karta.tif", "A 57116-2025")</f>
-        <v/>
-      </c>
-      <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 57116-2025 FSC-klagomål.docx", "A 57116-2025")</f>
-        <v/>
-      </c>
-      <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 57116-2025 FSC-klagomål mail.docx", "A 57116-2025")</f>
-        <v/>
-      </c>
-      <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 57116-2025 tillsynsbegäran.docx", "A 57116-2025")</f>
-        <v/>
-      </c>
-      <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 57116-2025 tillsynsbegäran mail.docx", "A 57116-2025")</f>
-        <v/>
-      </c>
-      <c r="AE18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/fåglar/A 57116-2025 prioriterade fågelarter.docx", "A 57116-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>A 53007-2025</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>45957</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>46308</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>KUNGÄLV</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="J19" t="n">
-        <v>1</v>
-      </c>
-      <c r="K19" t="n">
-        <v>1</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2</v>
-      </c>
-      <c r="T19" t="n">
-        <v>5</v>
-      </c>
-      <c r="U19" t="n">
-        <v>5</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>Västlig hakmossa
-Spillkråka</t>
-        </is>
-      </c>
       <c r="W19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 53007-2025 artfynd.xlsx", "A 53007-2025")</f>
         <v/>
@@ -2618,7 +2618,7 @@
         <v>44838</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2706,7 +2706,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 30862-2026</t>
+          <t>A 49988-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2720,10 +2720,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46212</v>
+        <v>45215</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="J21" t="n">
         <v>1</v>
@@ -2769,42 +2769,42 @@
         <v>1</v>
       </c>
       <c r="T21" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U21" t="n">
         <v>0</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 30862-2026 artfynd.xlsx", "A 30862-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 49988-2023 artfynd.xlsx", "A 49988-2023")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 30862-2026 karta.png", "A 30862-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 49988-2023 karta.png", "A 49988-2023")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 30862-2026 georefererad karta.tif", "A 30862-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 49988-2023 georefererad karta.tif", "A 49988-2023")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 30862-2026 FSC-klagomål.docx", "A 30862-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 49988-2023 FSC-klagomål.docx", "A 49988-2023")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 30862-2026 FSC-klagomål mail.docx", "A 30862-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 49988-2023 FSC-klagomål mail.docx", "A 49988-2023")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 30862-2026 tillsynsbegäran.docx", "A 30862-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 49988-2023 tillsynsbegäran.docx", "A 49988-2023")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 30862-2026 tillsynsbegäran mail.docx", "A 30862-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 49988-2023 tillsynsbegäran mail.docx", "A 49988-2023")</f>
         <v/>
       </c>
     </row>
@@ -2828,7 +2828,7 @@
         <v>45697</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2920,7 +2920,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 42407-2026</t>
+          <t>A 30862-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2934,10 +2934,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46307</v>
+        <v>46212</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2953,13 +2953,13 @@
         <v>1.7</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
@@ -2974,7 +2974,7 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -2983,42 +2983,42 @@
         <v>1</v>
       </c>
       <c r="T23" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U23" t="n">
         <v>0</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Dunmossa</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 42407-2026 artfynd.xlsx", "A 42407-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 30862-2026 artfynd.xlsx", "A 30862-2026")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 42407-2026 karta.png", "A 42407-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 30862-2026 karta.png", "A 30862-2026")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 42407-2026 georefererad karta.tif", "A 42407-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 30862-2026 georefererad karta.tif", "A 30862-2026")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 42407-2026 FSC-klagomål.docx", "A 42407-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 30862-2026 FSC-klagomål.docx", "A 30862-2026")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 42407-2026 FSC-klagomål mail.docx", "A 42407-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 30862-2026 FSC-klagomål mail.docx", "A 30862-2026")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 42407-2026 tillsynsbegäran.docx", "A 42407-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 30862-2026 tillsynsbegäran.docx", "A 30862-2026")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 42407-2026 tillsynsbegäran mail.docx", "A 42407-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 30862-2026 tillsynsbegäran mail.docx", "A 30862-2026")</f>
         <v/>
       </c>
     </row>
@@ -3042,7 +3042,7 @@
         <v>45454</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3130,7 +3130,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 49988-2023</t>
+          <t>A 42407-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3144,10 +3144,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45215</v>
+        <v>46307</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3160,17 +3160,17 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
         <v>1</v>
       </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
       <c r="M25" t="n">
         <v>0</v>
       </c>
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -3200,35 +3200,35 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Dunmossa</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 49988-2023 artfynd.xlsx", "A 49988-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/artfynd/A 42407-2026 artfynd.xlsx", "A 42407-2026")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 49988-2023 karta.png", "A 49988-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor/A 42407-2026 karta.png", "A 42407-2026")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 49988-2023 georefererad karta.tif", "A 49988-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/kartor_geotiff/A 42407-2026 georefererad karta.tif", "A 42407-2026")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 49988-2023 FSC-klagomål.docx", "A 49988-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomål/A 42407-2026 FSC-klagomål.docx", "A 42407-2026")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 49988-2023 FSC-klagomål mail.docx", "A 49988-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/klagomålsmail/A 42407-2026 FSC-klagomål mail.docx", "A 42407-2026")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 49988-2023 tillsynsbegäran.docx", "A 49988-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsyn/A 42407-2026 tillsynsbegäran.docx", "A 42407-2026")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 49988-2023 tillsynsbegäran mail.docx", "A 49988-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1482/tillsynsmail/A 42407-2026 tillsynsbegäran mail.docx", "A 42407-2026")</f>
         <v/>
       </c>
     </row>
@@ -3252,7 +3252,7 @@
         <v>44691</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3325,7 +3325,7 @@
         <v>44691</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3398,7 +3398,7 @@
         <v>44836</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3471,7 +3471,7 @@
         <v>44760</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3544,7 +3544,7 @@
         <v>44760</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
         <v>44760</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3673,7 +3673,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 17455-2025</t>
+          <t>A 62221-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3687,10 +3687,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45757</v>
+        <v>45267</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>2.1</v>
+        <v>1.3</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3746,7 +3746,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 62221-2023</t>
+          <t>A 4204-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3760,10 +3760,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45267</v>
+        <v>45324</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3776,7 +3776,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.3</v>
+        <v>4.4</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3819,7 +3819,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 40951-2025</t>
+          <t>A 30170-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3833,10 +3833,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45897</v>
+        <v>44757</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3849,7 +3849,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.8</v>
+        <v>3.1</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3892,7 +3892,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 21389-2023</t>
+          <t>A 13880-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3906,10 +3906,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45063</v>
+        <v>45391</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3922,7 +3922,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>3.4</v>
+        <v>2.4</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3965,7 +3965,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 4262-2024</t>
+          <t>A 1995-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3979,10 +3979,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45324</v>
+        <v>45308</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3995,7 +3995,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>14</v>
+        <v>0.5</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4038,7 +4038,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 45124-2025</t>
+          <t>A 45990-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4052,10 +4052,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45919</v>
+        <v>44846</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4068,7 +4068,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4111,7 +4111,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 21240-2023</t>
+          <t>A 10679-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4125,10 +4125,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45058</v>
+        <v>45721</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4141,7 +4141,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2.3</v>
+        <v>4.4</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4184,7 +4184,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 47564-2025</t>
+          <t>A 11237-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4198,10 +4198,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45931</v>
+        <v>45726</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>2</v>
+        <v>4.2</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4257,7 +4257,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 63319-2021</t>
+          <t>A 10677-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4271,10 +4271,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44508</v>
+        <v>45721</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4287,7 +4287,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.6</v>
+        <v>7.4</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4330,7 +4330,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 52932-2025</t>
+          <t>A 74285-2021</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4344,10 +4344,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45957</v>
+        <v>44558</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4360,7 +4360,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>3.4</v>
+        <v>1.1</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4403,7 +4403,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 29952-2026</t>
+          <t>A 17922-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4417,10 +4417,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46205</v>
+        <v>45758</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4433,7 +4433,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4476,7 +4476,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 10677-2025</t>
+          <t>A 40951-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4490,10 +4490,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45721</v>
+        <v>45897</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4506,7 +4506,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>7.4</v>
+        <v>0.8</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4549,7 +4549,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 10679-2025</t>
+          <t>A 61417-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4563,10 +4563,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45721</v>
+        <v>44916</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4579,7 +4579,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>4.4</v>
+        <v>3.6</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4622,7 +4622,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 11237-2025</t>
+          <t>A 43520-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4636,10 +4636,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45726</v>
+        <v>44837</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4652,7 +4652,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>4.2</v>
+        <v>1.5</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4695,7 +4695,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 30738-2026</t>
+          <t>A 32272-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4709,10 +4709,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46211</v>
+        <v>45120</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4725,7 +4725,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>3.5</v>
+        <v>4.9</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4768,7 +4768,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 30859-2026</t>
+          <t>A 32847-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4782,10 +4782,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46212</v>
+        <v>45124</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4798,7 +4798,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.5</v>
+        <v>4.7</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4841,7 +4841,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 74285-2021</t>
+          <t>A 45124-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4855,10 +4855,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44558</v>
+        <v>45919</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4871,7 +4871,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.1</v>
+        <v>3.7</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4914,7 +4914,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 61417-2022</t>
+          <t>A 29223-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4928,10 +4928,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44916</v>
+        <v>45482</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4944,7 +4944,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>3.6</v>
+        <v>5.6</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4987,7 +4987,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 32272-2023</t>
+          <t>A 47564-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5001,10 +5001,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45120</v>
+        <v>45931</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5017,7 +5017,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>4.9</v>
+        <v>2</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5060,7 +5060,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 32847-2023</t>
+          <t>A 34366-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5074,10 +5074,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45124</v>
+        <v>44792</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5090,7 +5090,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>4.7</v>
+        <v>0.5</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5133,7 +5133,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 29223-2024</t>
+          <t>A 34244-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5147,10 +5147,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45482</v>
+        <v>45844</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5163,7 +5163,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>5.6</v>
+        <v>2.9</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5206,7 +5206,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 38262-2026</t>
+          <t>A 25624-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5220,10 +5220,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46281</v>
+        <v>45803</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5236,7 +5236,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2.8</v>
+        <v>5</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5279,7 +5279,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 10655-2022</t>
+          <t>A 4673-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5293,10 +5293,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44624</v>
+        <v>46048</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5309,7 +5309,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>13.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5352,7 +5352,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 34366-2022</t>
+          <t>A 8334-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5366,10 +5366,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44792</v>
+        <v>44975</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5382,7 +5382,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5425,7 +5425,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 4673-2026</t>
+          <t>A 41442-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5439,10 +5439,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46048</v>
+        <v>45869</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5455,7 +5455,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>8.199999999999999</v>
+        <v>1.8</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5498,7 +5498,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 34244-2025</t>
+          <t>A 52932-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5512,10 +5512,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45844</v>
+        <v>45957</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5528,7 +5528,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5571,7 +5571,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 25624-2025</t>
+          <t>A 6946-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5581,14 +5581,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45803</v>
+        <v>46057</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5601,7 +5601,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>5</v>
+        <v>2.2</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5644,7 +5644,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 6946-2026</t>
+          <t>A 4262-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5654,14 +5654,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46057</v>
+        <v>45324</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5674,7 +5674,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>2.2</v>
+        <v>14</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5717,7 +5717,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 41442-2025</t>
+          <t>A 661-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5731,10 +5731,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45869</v>
+        <v>45664</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.8</v>
+        <v>3.1</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5790,7 +5790,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 39714-2024</t>
+          <t>A 37443-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5804,10 +5804,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45552</v>
+        <v>45877</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5819,8 +5819,13 @@
           <t>KUNGÄLV</t>
         </is>
       </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I61" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5863,7 +5868,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 17922-2025</t>
+          <t>A 13990-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5877,10 +5882,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45758</v>
+        <v>46098</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5893,7 +5898,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.8</v>
+        <v>2.6</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5936,7 +5941,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 37443-2025</t>
+          <t>A 24461-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5950,10 +5955,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45877</v>
+        <v>45082</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5965,13 +5970,8 @@
           <t>KUNGÄLV</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I63" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6014,7 +6014,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 34386-2026</t>
+          <t>A 143-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6028,10 +6028,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46254</v>
+        <v>44928</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6044,7 +6044,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6087,7 +6087,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 34396-2026</t>
+          <t>A 49985-2023</t>
         </is>
       </c>
       <c r="B6